--- a/Main_project/master_qualified_leads.xlsx
+++ b/Main_project/master_qualified_leads.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$AN$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$AN$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN61"/>
+  <dimension ref="A1:AN121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -442,17 +442,17 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="54" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="41" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="60" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
@@ -10128,8 +10128,9280 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>13</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Third+Space+Canary+Wharf/data=!4m7!3m6!1s0x487602b0ae6b1903:0x463cbee3d194e6cd!8m2!3d51.5047861!4d-0.0167412!16s%2Fg%2F1tlbj0mb!19sChIJAxlrrrACdkgRzeaU0eO-PEY</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Third Space Canary Wharf</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>16-19 Canada Square, London E14 5ER, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10:30 pm"],"Monday":["5:30 am–10:30 pm"],"Saturday":["8 am–8 pm"],"Sunday":["8 am–8 pm"],"Thursday":["5:30 am–10:30 pm"],"Tuesday":["5:30 am–10:30 pm"],"Wednesday":["5:30 am–10:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thirdspace.london/clubs/canary-wharf/</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>+44 20 7970 0900</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>GX3M+W8 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>2997</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>{"1":135,"2":59,"3":50,"4":91,"5":2662}</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>51.504786</v>
+      </c>
+      <c r="R62" t="n">
+        <v>-0.016741</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5061129966940645069</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Upscale gym &amp; spa with a climbing wall</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>High-end fitness club featuring a pool, sauna &amp; spa, training equipment &amp; a climbing wall.</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnYa5QGVwvXo-x0D3NLQNMElJ1x-BStpRJK6lwSmCbeQfl8JtJJG5nqGkhGcV5IvYpFjfTudV6YG-grb9Z81SLvV6lUXG-3cX2aKh-8amqDuFm7-vHACY4lN6CpHpr1EOqv3bjd=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>0x487602b0ae6b1903:0x463cbee3d194e6cd</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>ChIJAxlrrrACdkgRzeaU0eO-PEY</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>{"id":"117098830810445809134","name":"Third Space Canary Wharf (Owner)","link":"https://www.google.com/maps/contrib/117098830810445809134"}</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>{"borough":"Canary Wharf Estate","street":"Third Space Canary Wharf, 16-19 Canada Square","city":"London","postal_code":"E14 5ER","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>[{"Name":"Csongor Osvay","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUqANQEBj83gJE53jT_ei6i_QUTXaMcrxZxzY1s9TlkZIAx68iU=s120-c-rp-mo-br100","Rating":2,"Description":"Could be a great gym, but it used to be a lot better. This year, every week something new is out of order. Leg press (multiple times), then cable row, then chest fly, now leg curl. Clips constantly go missing from cables. Recently lifting belts have disappeared. And it takes very long for anything to get fixed. Not what you’d expect from a £280 premium gym really. A lot of money is spent on a new spa, sauna, hyrox and ‘experiences’ but they can’t get the gym basics right. (Pictures all taken today by the way)","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNxe-lEX-3evNOeNvUEUwc_-P54zEXuhTxrbdr_Kl7ixUw4HuQ-ItB-NA_R6sYiIs4Z-zg1EWkgmXx5Uy5oQAkvNyeURu8ZfOau9vlVcDpzKAlUUdsvzvBSqL7UBGjD6uhLmU1diW1Kan_n=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOVzno16ksvebaZa9WccEsdhQHS5gDFjpARbPlFyU2lQD1UAlHapd1a05C5MGXloWIWnrvP4Kfc71VWgBd4Or01kP6guiC0-b_45PbZUqcVf4n-sM6enO5lmVsL2vHLFzcN5DaB72Jfx3v9=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPwbZ_80xoB4aobLYyIHKm-k0yOw6_1DCDmSa87oeuZPSLgIZQnwPdSQhU0usMLJk7dgtsruCex62LBUqqYuVNR1rsindOmi2w2Bzk3IdL7kjbj162zIlvx_3bog-U6bQcvgfkvZvw9uTFm=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMjEj8JwM4reQEeXTfSdGikMLWk3NK6j5_iLTDBahXZJGmFN3t68THx49bAs5YMe_Ck7l7PSvD_Ucj0xCrDY4pFVuPjvMgGd13q6LpLSpUUocQSjdrfk2fKS8s8q88okWz3trno0zKE88T6=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPQInDB9oHd6QevRz17iT65y6vLAcafdH7zwy1UgV4kneNVZtRJauZL_rvgkdgT8ut_cdMIyrRAlvNagZ3p8x5TX1KH6duhkDS8lbxODgFiZ0Ibnq4wE3YMSgKhHFe51r4zxV95oIUhhB0-=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tWeVdWRjFZVTlCWm1SSk5tdzVUbXRoV2w5Tk1WRRAB","source":"Google","rating_scale":5,"rating_float":2,"author_url":"https://www.google.com/maps/contrib/110501226306838259886/reviews?hl=en-GB","posted_at_unix_micros":1780330167244904,"updated_at_unix_micros":1780331095468222,"language":"en","translated_lang":"","text_original":"Could be a great gym, but it used to be a lot better. This year, every week something new is out of order. Leg press (multiple times), then cable row, then chest fly, now leg curl. Clips constantly go missing from cables. Recently lifting belts have disappeared. And it takes very long for anything to get fixed. Not what you’d expect from a £280 premium gym really. A lot of money is spent on a new spa, sauna, hyrox and ‘experiences’ but they can’t get the gym basics right. (Pictures all taken today by the way)","text_translated":"","reply_text_original":"Hi Csongor,\nThank you for your review and for taking the time to leave feedback. I'm sorry to hear about your experience here. Jack our Gym Floor Operations Manager is reaching out to you directly to talk through your concerns. \n\nKind regards,\nJen Lamb\nOperations Manager Third Space Canary Wharf","reply_language":"en","reply_posted_at_unix_micros":1780499575000000,"reply_updated_at_unix_micros":1780499575000000,"published_at":"2026-06-01T16:09:27.244904Z"},{"Name":"Riley","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWejyXcM4QWGR4v_YbuabtU8vjKfs8z7rfHL8Xrsh9Dp5ljTsh_hw=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This is the best gym I have been to in my entire life. I’ve been to 14 of 15 third space gyms (everything but Richmond). There are 90+ classes a day and something for everyone. Despite being such a massive gym it feels so personalized because all the trainers know your name before you even show up to class.\n\nHarriet husband is my idol - she is such a strong and powerful woman and really knows how to get you to push yourself. She’s so funny, everyone will be on the floor dying after class and she’s like you only did 60 seconds of work 60 seconds of rest! She’s dancing the entire class. Her run clubs are epic and I love hyrox. I want to try yard strong and her hyrox run. Did lift and WOD with her and lots of hyrox power / engine.\n\nSally is absolutely adorable and also a beast. She once came to my class as a participant and I didn’t realize and was wowed ! I think she’s done some abs classes I did too. She’s absolutely lovely\n\nRyan Dixon is the coolest guy, so suave and adorable and so much fun. I literally go to his classes to hang out with him because he’s such a busy guy he doesn’t have time to teach!\n\nI literally only had Danny once and yet he had made the cut for my favorites as it was such an iconic class. He is the brains behind everything.\n\nJurgen my PT is also so much fun and gets me to achieve things I never knew possible.\n\nShoutout to Caz too who I don’t know well but is stunningly beautiful and also a pleasure!\n\nI look forward to the pool opening\n\nI hadn’t run in 10 years and never lifted weights in my life but in 2-3 months of coming 5-7 days a week I lost 10% body fat mind you I don’t even eat well. I’m always so excited to come and stay for hours. Even the receptionists are lovely, I don’t remember her name but she’s got mid length dark blonde hair and is amazing too — EDIT; it is Amber, she’s great!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmObQWMmhpYwpuUJkcIVDRpE1Z4XF9V38KDCeAx0zMNMvDv3DKUixwsiO6JTdceBZTxEnKFvWL7wTMIWc3dHb5881o5rTrykdcuwdjGErtrqqnF-zzI_-2iIIbMPW1w27JmhDrLG93WZ8VXH=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOHs7aRyF_tquEjMmaSfZuPIjxLYtg8Su4cc6nbXHTY7GX6d57ygXUbnq2iLZI9CzYGj976a-vGH5KhCX_4fPmrIL41IvWUhQER2xRa12rbNJI4DGMrAJPtklqRAu0fSsKb5pbS9egsyIxq=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMHHP1Oek1bU99WpFBoDslwJUVhwGutAxALHULdKeO74xCrJzyOQEMc6TAzqMQAq_1uy5GVo6LBEBTq4CWScC_qlTseaYHKlICdSBVjz-IKEJ2EpsPKDTcTUjpROtI8CLjH7DQvgLKPHutD=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmP7LqN5etQbq5TfkQwMdXckzpeaj_mSMJkBWrbFABj9j3Zi2yQ-LcQNXyyCFMXxfzam8rleV-0Cmn6kAUnrtk1lLb5sUYD-GkFSYxlhn7RepGxRFlMSiuCeQYy7oN4ZQIbErinIol6SnGTV=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNIe6FKbYv1kDCoWYdNiLQVCq4--3hFADJfXNYI7QRKPxYeaOHPlb56-wE-oc79tjjA4ETBRk5G9RZFeDpENHrwWSj17QsbR6JfDy8cICyUu7GfC4m8KUFjf_xv2QhMrs4JFAAC7R8_szg=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMLNwllJ3BxWQ_yEEbd_QdIceAlHrQXKuFVucXV4f_efh-jrVFVYdqru-d_8GvvdwtkFgoyIjzw5689NMbae1IPwKJ3Sx0EHDnbQ4gn_fYw_XPK6mnASbJD_NA4XgaAISJauaAW3BoTco6z=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPfxmwVHK3rzocgJI4k5QYkB_IAkOBx-gexurcSqGqR-JVmSNsYp8k_BZV9kJEgc6nCB1m1bBGDFc86yh6Jk4ys7uZwsGidGkWU9_-PV8f3Qke0hJGgTe-2BwkPYZSHCPPHQSqUYN1Y3lhq=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO6eXtQBxoopyJhom2A8WNmRRQv8HmzfjxWduXcuGt1EzCkkBecTJX35-hynux5v1vuU7UX7yNvV18Hza3gLmyXcUvHBhd9gF_83qiNX4lBvPeYm3G2EztDa8eG5YFeQ6x442D-l1UC2OU=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMMNztdU1TxAMRICrn2DerF18TlXH4aD7E1IdqtVxZLkb15LO950u5KaoevrN7IupPZgzUaj5KEVv5cuV6HsQ3sZW_vHavQjdgAZ6SPBsET5rYsCTDyfeGqvfEUm0IbrRwwvk2AZ8qhqWo=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPb1JYiVuNzIAyjXAPitunMEE8nT3bM5w32aH05Aw386Ew80mnJeOpWn-XsUC-j-QcF_51VpTrFgfjDaIyHkM-DH-V9HgSQfW_fUG7F2PoTRwvxyA3TThCxxuIWdtBHmOcolLt_7epzXEmx=k-no"],"When":"Edited 2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xOcE1XTk5aa3BSYW1KQ2VtaEljMWQyTFRsblVVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109253920344878427775/reviews?hl=en-GB","posted_at_unix_micros":1782725592620843,"updated_at_unix_micros":1782904310843516,"language":"en","translated_lang":"","text_original":"This is the best gym I have been to in my entire life. I’ve been to 14 of 15 third space gyms (everything but Richmond). There are 90+ classes a day and something for everyone. Despite being such a massive gym it feels so personalized because all the trainers know your name before you even show up to class.\n\nHarriet husband is my idol - she is such a strong and powerful woman and really knows how to get you to push yourself. She’s so funny, everyone will be on the floor dying after class and she’s like you only did 60 seconds of work 60 seconds of rest! She’s dancing the entire class. Her run clubs are epic and I love hyrox. I want to try yard strong and her hyrox run. Did lift and WOD with her and lots of hyrox power / engine.\n\nSally is absolutely adorable and also a beast. She once came to my class as a participant and I didn’t realize and was wowed ! I think she’s done some abs classes I did too. She’s absolutely lovely\n\nRyan Dixon is the coolest guy, so suave and adorable and so much fun. I literally go to his classes to hang out with him because he’s such a busy guy he doesn’t have time to teach!\n\nI literally only had Danny once and yet he had made the cut for my favorites as it was such an iconic class. He is the brains behind everything.\n\nJurgen my PT is also so much fun and gets me to achieve things I never knew possible.\n\nShoutout to Caz too who I don’t know well but is stunningly beautiful and also a pleasure!\n\nI look forward to the pool opening\n\nI hadn’t run in 10 years and never lifted weights in my life but in 2-3 months of coming 5-7 days a week I lost 10% body fat mind you I don’t even eat well. I’m always so excited to come and stay for hours. Even the receptionists are lovely, I don’t remember her name but she’s got mid length dark blonde hair and is amazing too — EDIT; it is Amber, she’s great!","text_translated":"","reply_text_original":"Hi Riley,\n\nThank you for your 5* review and for your feedback. So pleased you are enjoying using the club and thank you for the shout outs to the team!  Please let myself or a member of the team know if we can ever help at all. See you in club soon.\n\nKind regards,\nKelsi Blashko\nConcierge Manager Third Space Canary Wharf","reply_language":"en","reply_posted_at_unix_micros":1782912474000000,"reply_updated_at_unix_micros":1782912474000000,"published_at":"2026-06-29T09:33:12.620843Z"},{"Name":"Dina Duong","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVzCOQCA1CQuHBWrlnMDT7PMBpWYpeumyjLKIFm19I5mhPDqc0=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been going to Third Space Canary Wharf for just over 1.5 years, and the highlight of my time there has definitely been getting Vincent as my PT. I started training with an injury, and the way he managed it was spot on, smart, calm, and very considered. When I later saw a physio, their advice ended up being basically the same as what Vincent had already been doing.\n\nDespite working around the injury, I’ve still made great progress with body recomposition and strength. Sessions are always challenging but well adapted, and he’s really good at adjusting things based on how I’m feeling on the day.\n\nI’ve also been going to the Pilates classes and genuinely love them. Few of my favourite instructors been Gavin, Peter, Micaela, Eve, Eliza.\n\nOverall, Third Space has great facilities and classes, but having a PT like Vincent really elevated the whole experience.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOePY45UrBBuSGcgmHCm_cLsJiIfSuMbTH0Tk7gHM4eONSXtKJNSIozgs0lmJxw56xOA6zrrn4H89j6x5_nZJO3F9EDnqWcyBdwRUVzXP4Px-hzPhb1jxV312f-audznukgZN4RrFQMEODl=k-no"],"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2paYU1qaHdTSE4yZERBeldHcFlZMUkyVms5TFVIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103013304521183126103/reviews?hl=en-GB","posted_at_unix_micros":1769076626757486,"updated_at_unix_micros":1769076626757486,"language":"en","translated_lang":"","text_original":"I’ve been going to Third Space Canary Wharf for just over 1.5 years, and the highlight of my time there has definitely been getting Vincent as my PT. I started training with an injury, and the way he managed it was spot on, smart, calm, and very considered. When I later saw a physio, their advice ended up being basically the same as what Vincent had already been doing.\n\nDespite working around the injury, I’ve still made great progress with body recomposition and strength. Sessions are always challenging but well adapted, and he’s really good at adjusting things based on how I’m feeling on the day.\n\nI’ve also been going to the Pilates classes and genuinely love them. Few of my favourite instructors been Gavin, Peter, Micaela, Eve, Eliza.\n\nOverall, Third Space has great facilities and classes, but having a PT like Vincent really elevated the whole experience.","text_translated":"","reply_text_original":"Hi Dina,\nThank you for your 5* review and for your feedback. So pleased to hear about your recovery experience and that you are getting the most out of your sessions from Vincent and from our instructors. Please let myself or a member of the team know if we can ever help at all. See you in club soon. \n\nKind regards,\nJen Lamb\nOperations Manager Third Space Canary Wharf","reply_language":"en","reply_posted_at_unix_micros":1769261581000000,"reply_updated_at_unix_micros":1769261581000000,"published_at":"2026-01-22T10:10:26.757486Z"},{"Name":"Paul MacDonald","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKwuKhH3XByLqJEV0N3DTSD6RtnLbrERK8mcA4ilABQAZnzIQ=s120-c-rp-mo-ba12-br100","Rating":3,"Description":"Very large, modern gym with plenty of equipment. Lots of people but doesn’t feel overly crowded.\n\nLet down by poor maintenance of equipment. Typically 3-5 pieces are out of order at anyone time. It can take many weeks to fix them as they seem pretty poor at predictive maintenance and holding the correct replacement parts for the multiple gyms they have across London.\n\nChanging areas can be crowded but generally clean. Again let down by poor maintenance. Locker door hinges are broken and the combination locks are unreliable as batteries are not checked and rely on guests to report them.\n\nOverall these are not deal breakers but the gym charges five star prices and delivers a three star service","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNGLxF7Dhm-ALSU-uZm7FEODkj5AbUpVJWCDac9wdt1-FWQUoOIVJiItpL5YbWmhoLYkoQTn7cHx80MLUaBnbp4Bi43xoFpt78PoxsZe5KzN3Beyk9UWeLcXhECx0R9hWl6MuQCcM6gRkc8=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMBjKVHAt9HYjKc_svFRTv3NC51SCOmdrD8qXDsFe9m05SfJG9pkNW0RfEqaoMk1uS_bV_nHFyXG46DSCD2hCakIyDFNuIuJzSs7PVP3AfVstpd39jzjcT64B3dwMn2zfiNFanh4SqWnvDv=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNOHgTBDVwTWSFeKqIDzMOAOqc0v6WOZdspYvASOOrimt5Y31OcDhaPtTOyJAZnAnZ7TwL61fBu0y5CsJVdx_DMGx8gkZLqkp0FLtZHtftfVjvZfMzvHqZjld5Elcjx231Dk68WNl_v6L84=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPaqAx18l6uKKiQfIuf-JzXTPQg3kZSU-e4IItkKcmqctwZbcb69od3BKgcxJJC_w0zbp1n6szHjeKlw0h2pxYGjhs-G9AJwRtVTPja9-lMyTqD8I-2gdexKqHpVlxPCjzAY3sqryEjuj0J=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPP8zjzsYKKjPTxvYNtYxFtET00op0E6ckbh1z9yoa9w9lW0yeyOFwTlgYjEomNbzzmEZq6AlZDPoJIfj6SdJdKW3CKaUVKDu1K2KqIpx9J0QXX1MFWIMJCF5vN0fPv2T5UZ8bON_702Ds=k-no"],"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2kweldUZ3RRWGQzTmtscWRFRkRVazFuVmtKeFkyYxAB","source":"Google","rating_scale":5,"rating_float":3,"author_url":"https://www.google.com/maps/contrib/109490335649306599789/reviews?hl=en-GB","posted_at_unix_micros":1785820495368035,"updated_at_unix_micros":1785821415767430,"language":"en","translated_lang":"","text_original":"Very large, modern gym with plenty of equipment. Lots of people but doesn’t feel overly crowded.\n\nLet down by poor maintenance of equipment. Typically 3-5 pieces are out of order at anyone time. It can take many weeks to fix them as they seem pretty poor at predictive maintenance and holding the correct replacement parts for the multiple gyms they have across London.\n\nChanging areas can be crowded but generally clean. Again let down by poor maintenance. Locker door hinges are broken and the combination locks are unreliable as batteries are not checked and rely on guests to report them.\n\nOverall these are not deal breakers but the gym charges five star prices and delivers a three star service","text_translated":"","reply_text_original":"Hi Paul,\n\nThank you for taking the time to share such detailed feedback. We're pleased to hear that you enjoy the size of the club, the range of equipment available, and that despite being a busy gym, it doesn't feel overcrowded.\n\nWe're sorry, however, that your experience has been impacted by equipment and maintenance issues. We understand your frustration when equipment is out of service for extended periods, and we appreciate that, as a premium facility, our members rightly expect a consistently high standard across all areas of the club.\n\nIn particular, we're sorry to hear about the issues you've encountered with both gym equipment and some of the locker facilities. Your feedback has been shared with the relevant teams, and I'm aware that Jack, our Gym Floor Operations Manager, has already reached out to you directly to discuss your concerns and provide further support.\n\nThank you again for your honest feedback. It helps us identify areas where we can improve, and we hope to have the opportunity to restore your confidence in the service we provide.\n\nBest wishes,\n\nTom Porter\n Concierge Manager\n Third Space London","reply_language":"en","reply_posted_at_unix_micros":1786018730000000,"reply_updated_at_unix_micros":1786018730000000,"published_at":"2026-08-04T05:14:55.368035Z"},{"Name":"Ahmad Durrani","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK9TwuPoTj4N7rE1jqHrRR7DF1ur2iUu8GNP2U8A4C5VkSz1g=s120-c-rp-mo-br100","Rating":5,"Description":"Brilliantly managed and impeccably maintained facilities. Visiting the club is one of the highlights of my day. The selection of classes offers great variety and the trainers are always helpful, engaging and coming up with new ways to make things more challenging and fun. I’ve particularly enjoyed group classes with Adam, Harriett, Harrison, Holly, Kat, and Kerys, as well as PT sessions with Sanjay.\n\nThe classes are matched by the excellent range of equipment and thoughtful design of spaces across different zones. The cleaning staff deserve a pat on the back as well for always making sure everything is neat, tidy and pleasant.\n\nThe changing areas are a sight to behold and have a great range of grooming products, absolutely free to use. The sauna and steam room attached to the lockers are serviceable, but a bit tight. But the club will soon be opening a world-class wellness spa, which should make up for this.\n\nBeing a member also comes with great benefits, such as discounts on restaurants and activewear brands, accessible through the Third Space app. Membership is definitely worth the price.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2paMlRIUnpORU40WmtobE1YRkVibDkzTFROdVduYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117958552736133615114/reviews?hl=en-GB","posted_at_unix_micros":1782919910001654,"updated_at_unix_micros":1782920781675623,"language":"en","translated_lang":"","text_original":"Brilliantly managed and impeccably maintained facilities. Visiting the club is one of the highlights of my day. The selection of classes offers great variety and the trainers are always helpful, engaging and coming up with new ways to make things more challenging and fun. I’ve particularly enjoyed group classes with Adam, Harriett, Harrison, Holly, Kat, and Kerys, as well as PT sessions with Sanjay.\n\nThe classes are matched by the excellent range of equipment and thoughtful design of spaces across different zones. The cleaning staff deserve a pat on the back as well for always making sure everything is neat, tidy and pleasant.\n\nThe changing areas are a sight to behold and have a great range of grooming products, absolutely free to use. The sauna and steam room attached to the lockers are serviceable, but a bit tight. But the club will soon be opening a world-class wellness spa, which should make up for this.\n\nBeing a member also comes with great benefits, such as discounts on restaurants and activewear brands, accessible through the Third Space app. Membership is definitely worth the price.","text_translated":"","reply_text_original":"Hi Ahmad,\n\nThank you for your 5* review and for your feedback. So pleased you are enjoying using the club, and the classes with our amazing instructors! Thank you for the special shout out to Sanjay! Please let myself or member of the team know if we can ever help at all. See you in club soon.\n\nKind regards,\nKelsi Blashko\nConcierge Manager Third Space Canary Wharf\n","reply_language":"en","reply_posted_at_unix_micros":1783078389000000,"reply_updated_at_unix_micros":1783078389000000,"published_at":"2026-07-01T15:31:50.001654Z"}]</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Third+Space+Soho/data=!4m7!3m6!1s0x487604d40da61abd:0x4f349752569e6abd!8m2!3d51.5112699!4d-0.1357459!16s%2Fg%2F1ptz_qdlg!19sChIJvRqmDdQEdkgRvWqeVlKXNE8</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Third Space Soho</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>67 Brewer St, London W1F 9US, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["8 am–8 pm"],"Sunday":["8 am–8 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thirdspace.london/clubs/soho/</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>+44 20 7439 6333</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>GV67+GP London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1500</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>{"1":47,"2":30,"3":15,"4":49,"5":1359}</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>51.51127</v>
+      </c>
+      <c r="R63" t="n">
+        <v>-0.135746</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>5707353007681596093</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmAjthXlyX95XMqh3d3CTdVb4oj9Csmfmok5Cf_V08y5xWqyvD2mc9I3UnSRVj8n7X_3BJvG6VWOBVWv8Mfhob9BF8HiPmqU01HS4AbAREIo-OL1RAdeMStLkmjdsE66hkUKso=w408-h276-k-no</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>0x487604d40da61abd:0x4f349752569e6abd</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>ChIJvRqmDdQEdkgRvWqeVlKXNE8</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>{"id":"114574720640403024592","name":"Third Space Soho (Owner)","link":"https://www.google.com/maps/contrib/114574720640403024592"}</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"67 Brewer St","city":"London","postal_code":"W1F 9US","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>[{"Name":"Sara Elman","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU8qEjWP1ABXfJFsOf4GwT6HCuhakF7JN0XY4WZ4J9cdEi2fI8=s120-c-rp-mo-br100","Rating":5,"Description":"I love this gym, from the moment you walk in you are made to feel super welcome. The concierge are fabulous and really helpful when you’re a newbie like me! The gym space is great, well laid out and the pool is fantastic. The girls changing room are kept spotlessly clean (as is the main gym space) the cleaners work so hard to keep it that way and are always around cleaning the equipment and gym floor. The classes are the best I’ve ever taken and all included in the membership and my especially lovely PT Eden Roberts is motivating  me (kindly and respectfully ) in to shape and is really  knowledgeable and I’m making great progress. It’s worth every penny and I’m so glad I took the leap from a basic gym to this private, friendly place where the staff (especially the Manager Luke ) are constantly striving to make my experience a positive one whenever I rock up, which is regularly. If you’re in any doubt about joining don’t be it’s the best investment you’ll make keeping fit! Ooh and a quick shout out to the smoothie team. They rock too. And the snacks are protein heaven! Thanks everyone - Sara :) x","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tWV1QzSndSM2xVY2xodGMwMURUVmN6V1V3NFowRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102497514452672425662/reviews?hl=en-GB","posted_at_unix_micros":1776286224135497,"updated_at_unix_micros":1776286224135497,"language":"en","translated_lang":"","text_original":"I love this gym, from the moment you walk in you are made to feel super welcome. The concierge are fabulous and really helpful when you’re a newbie like me! The gym space is great, well laid out and the pool is fantastic. The girls changing room are kept spotlessly clean (as is the main gym space) the cleaners work so hard to keep it that way and are always around cleaning the equipment and gym floor. The classes are the best I’ve ever taken and all included in the membership and my especially lovely PT Eden Roberts is motivating  me (kindly and respectfully ) in to shape and is really  knowledgeable and I’m making great progress. It’s worth every penny and I’m so glad I took the leap from a basic gym to this private, friendly place where the staff (especially the Manager Luke ) are constantly striving to make my experience a positive one whenever I rock up, which is regularly. If you’re in any doubt about joining don’t be it’s the best investment you’ll make keeping fit! Ooh and a quick shout out to the smoothie team. They rock too. And the snacks are protein heaven! Thanks everyone - Sara :) x","text_translated":"","published_at":"2026-04-15T20:50:24.135497Z"},{"Name":"Riley","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWejyXcM4QWGR4v_YbuabtU8vjKfs8z7rfHL8Xrsh9Dp5ljTsh_hw=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"The gym has some of the most talented lovable instructors of all third space locations. Holly Haywood is an icon - also love Maddie Daley Brown (for core/force), Sally Rees is the coolest most fun person I have ever met; Caz is absolutely gorgeous and a phenomenal runner and hyrox superstar - Echo is unbelievable at yoga and super advanced poses, and I really want to meet Kati Read because she’s friends with Holly and Harriet Husband and Will Pate from canary wharf! Charlotte Matthews also a great running coach - did her run club at Whiteley. Rebecca Raeburn does great afterburner and core. Olivia Arnold I also want to meet as her boyfriend Simon is the most hard working guy I know - he works out 4-5 hours a day! Lauren Elliot Griffiths also so much fun for speed fiends and formula 3. I would also like to add I am stunned to have found out Caz is a relatively new / junior instructor as her classes are top notch - on par or if not better than some of the group heads / elite instructors\n\nFrom Charlotte (this is my dog’s account, go figure)","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21KRmVEVkROakJaVG5ONFF6TjRSa1Y1Vnpkb05YYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109253920344878427775/reviews?hl=en-GB","posted_at_unix_micros":1785928226585136,"updated_at_unix_micros":1785928641281796,"language":"en","translated_lang":"","text_original":"The gym has some of the most talented lovable instructors of all third space locations. Holly Haywood is an icon - also love Maddie Daley Brown (for core/force), Sally Rees is the coolest most fun person I have ever met; Caz is absolutely gorgeous and a phenomenal runner and hyrox superstar - Echo is unbelievable at yoga and super advanced poses, and I really want to meet Kati Read because she’s friends with Holly and Harriet Husband and Will Pate from canary wharf! Charlotte Matthews also a great running coach - did her run club at Whiteley. Rebecca Raeburn does great afterburner and core. Olivia Arnold I also want to meet as her boyfriend Simon is the most hard working guy I know - he works out 4-5 hours a day! Lauren Elliot Griffiths also so much fun for speed fiends and formula 3. I would also like to add I am stunned to have found out Caz is a relatively new / junior instructor as her classes are top notch - on par or if not better than some of the group heads / elite instructors\n\nFrom Charlotte (this is my dog’s account, go figure)","text_translated":"","published_at":"2026-08-05T11:10:26.585136Z"},{"Name":"Sarah Tan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVFZ4wBVynGBDYFDT2h-duqBORpdruunDCU7NQq3BcNV8acCyKnDQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Love the facilities and community here - especially Bella and Fergal on concierge who are so welcoming and helpful. They put a smile on my face every day :)\n\nPTs are all wonderful (love Angel \u0026 Stan) and happy to help even out of session. Yoga classes are great. Started physio/sports rehab recently with Charlotte and love that she can incorporate exercises directly into my PT workout. Can’t wait for the refurb to be complete. Worth every penny.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xaSGJEQnJjakp4WVU5VE9FMXpjWFJYU0hSdWJVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103468562805923028017/reviews?hl=en-GB","posted_at_unix_micros":1778091277622629,"updated_at_unix_micros":1778091277622629,"language":"en","translated_lang":"","text_original":"Love the facilities and community here - especially Bella and Fergal on concierge who are so welcoming and helpful. They put a smile on my face every day :)\n\nPTs are all wonderful (love Angel \u0026 Stan) and happy to help even out of session. Yoga classes are great. Started physio/sports rehab recently with Charlotte and love that she can incorporate exercises directly into my PT workout. Can’t wait for the refurb to be complete. Worth every penny.","text_translated":"","reply_text_original":"Hi Sarah,\n\nThank you so much for your wonderful review!\n\nBella, Fergal, Angel, Stan and Charlotte will be so glad to hear how much they have impacted your experience here at Soho.\n\nWe hope to see you in club soon.\n\nBest,\nVinnie Durrant\nGeneral Manager","reply_language":"en","reply_posted_at_unix_micros":1779358714000000,"reply_updated_at_unix_micros":1779358714000000,"published_at":"2026-05-06T18:14:37.622629Z"},{"Name":"Klaudija Cermak","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV0weCrUHlC_vE0Vgm_vJPkOpqyyHzsUyV2ucffYuNQTmrniiU=s120-c-rp-mo-br100","Rating":5,"Description":"Third Space Soho is a wonderful gym. Friendly, spotless, smelling beautifully, lovely people, great equipment, fantastic classes and awesome swimming pool! 🏊‍♂️ Plus great personal trainers. Mine is Marcus. 😀 I never thought I could love a gym but I really love Third Space Soho. ❤️","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNa2AbtX9tuBJ3bsDVI2_sI6hY849Jl22YTu_2fxzl-LLvLwVZSGwrxG0nXTKM-eTVDkOeO99n9YhV47hkSFZ40Zw8EyiIAf4u1zjP1ZH7bGJhT2uCClugbFN5ISAfexikF5DdXIA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMFmmjcecaaDXYjlCx7vY5MtODpwwvTEvbL9LTWi4W2_2wCJKlV03qEwmsctNmKPQXtVXBdwtRbMKgun2D7Buuj6040U-TVIokGZEKze9AtJXT0TvFt9_CVvp2_fWnNDHReh86P=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOe5B1MBacKOKybKOMjefd8iOubgAffU5JQLVJrossxZibeTf43QZibdD_AqpJVWjJ8sC6fvypWNKC3VOSoll83LvoB_XgNrHlQdsAXsE8v0KukdClJA5aESphwD_-FySTbgMxN=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPopzI8YBNM6pFRV5KJjGdm87nN_HnQhlBYTpA7hqdE2kNnznQehVKW5OQkZ00OshTXynVmEcB_bq2KcBhw-tlAto7chLrnNGt2iT4rdisa49279HDNT36Mgdh3GFGxrDRttbMGjg=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOc8o1GMJeUpUs1WIRDjkt0cokNOwx-W4bXadgN7JCPOgrgZzUnrKE4i8SC-wrv1GnDyYCUoFdfF7qOBNP5d5b-o5b2RaoUoUJyHQen_lIwwlGXQrMUFIqowDrhDM94jEVTnhA2-Q=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmObHirgSNjw3noIhcLFJuXU0nrBU_Z2rIF6DKGgP_1H02n1XTQ2QeNBWq_h-_BiZ5diek00sJv1a6bOd63GN0BHqy4U4aHCy-e-NkGEaDEBM0d85K0WhyLQPAZXtCQza2CPzlhg=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNYc_URFiyv0ZxeGwLcK7PEd_cfx80cyT-ATtruLh1mxn18YGnX4bjHlBdwv1phEMMsa7_Ue86BChEzwYLWGSp463jbJdo6RPThNT5RdfT3OGU3DSwCUg8xZc6jkKIjvGZFxODC=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNiPNVkYJRMCyD5dixPaF2vZLNJbZaU0hlAXRQ9S3MGy9Whd4wcLbatCOfQlhb5KRDybVMg9lDU2QuNLpMopnBNaCXvmb8Stw307CsiX0TtMzf_L-r5YgOl0ptGY5HAdrgeKmThyA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMS5ejzwh96zeuuAbZxLSvuIckn7EgkRcxs77UIpMUPkOHh6Mg39hQA4U4CbIYdzaSey8zeSB7aJiE_5-Qu5UHLLgowHNHg9Ix-8vfj2t_9tCOBVL9tIOAx2_1nUW5VPHo3c7RN=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNRqN0WyWIERRPOWUx1bvbBjr2b5LhfnmOMSWvQNVoOIaHHs6LFbFMUJ_tjZtt_-Xl0W2sHEWOya6bv0HOrgo1JhqswU5aCOLEIA5Jc7hjB4p7wr9QurSR9O3pqG8uGv-5AJGgFMw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPAJpMcUt4b6UWBNkKCuOEJ3fkBy6KipOrkN4PQ5Waa-zaKB7pSRUlPmApTyf0CfBmqiHT7-WMg3P1rxYbvWRbQrk9-YIOMc3NDcp4opCH12_3Vvnp59DwrQE7Lq4uRtSEqYQOh=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmON2emCyskgll8zMmmh9nnZPssAiWLvcTvzsyyrtUn5d8EWIS44BOlavqc3F40QEf-sI7e-Z7svtfM0-kFZffARaWeaOWBb1FkHHZQx6y7u__JuVKGg-2bWxB13PuqXS3Qv1LhpqA=k-no"],"When":"Edited a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnTUNJMUt1bDZRRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111303376910741648401/reviews?hl=en-GB","posted_at_unix_micros":1743352978509875,"updated_at_unix_micros":1743800515546752,"language":"en","translated_lang":"","text_original":"Third Space Soho is a wonderful gym. Friendly, spotless, smelling beautifully, lovely people, great equipment, fantastic classes and awesome swimming pool! 🏊‍♂️ Plus great personal trainers. Mine is Marcus. 😀 I never thought I could love a gym but I really love Third Space Soho. ❤️","text_translated":"","reply_text_original":"Hey Klaudija, \n\nThank you so much for your fantastic feedback. I am so delighted that you really enjoy the club and your personal training sessions. We have a very professional team that help our members to achieve their fitness goals. I am sure you enjoy our new equipment as well. \n\nPlease let me know if there is anything that I can assist you with. \n\nKind regards, \nDaren Darby \nGeneral Manager, Third Space Soho","reply_language":"en","reply_posted_at_unix_micros":1743788680000000,"reply_updated_at_unix_micros":1743788680000000,"published_at":"2025-03-30T16:42:58.509875Z"},{"Name":"Natasha","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJrkKiBCBdzJ7Gc9G2GA8RCX6EAqM_CtmfSKl_elOqSYFrAIg=s120-c-rp-mo-br100","Rating":5,"Description":"I love Third Space Soho — it’s genuinely well worth the money. The gym is always clean, spacious and really well equipped, with everything you need for a great workout. The staff are also friendly and welcoming, which makes such a difference. THE best gym I’ve been to.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s1SFQzVXpibE01ZDFsSFEwMUliRFpIYW1GV1FXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101842372782383458240/reviews?hl=en-GB","posted_at_unix_micros":1781039981362623,"updated_at_unix_micros":1781039981362623,"language":"en","translated_lang":"","text_original":"I love Third Space Soho — it’s genuinely well worth the money. The gym is always clean, spacious and really well equipped, with everything you need for a great workout. The staff are also friendly and welcoming, which makes such a difference. THE best gym I’ve been to.","text_translated":"","reply_text_original":"Hi Natasha,\n\nThank you for taking the time to write this lovely review! \n\nWe are so grateful for your loyalty and hope to see you in club soon.\n\nAll the best,\nPip Amer\nOperations Manager","reply_language":"en","reply_posted_at_unix_micros":1782809991000000,"reply_updated_at_unix_micros":1782809991000000,"published_at":"2026-06-09T21:19:41.362623Z"}]</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>13</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Third+Space+Tower+Bridge/data=!4m7!3m6!1s0x4876036838efbd55:0x80936ddf7a5eb6fe!8m2!3d51.5053694!4d-0.0802477!16s%2Fg%2F11r9l8x18!19sChIJVb3vOGgDdkgR_rZeet9tk4A</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Third Space Tower Bridge</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2b More London Pl, London SE1 2AP, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["8 am–8 pm"],"Sunday":["8 am–8 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thirdspace.london/clubs/tower-bridge/</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>+44 20 7940 4937</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>GW49+4W London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1376</v>
+      </c>
+      <c r="O64" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>{"1":66,"2":36,"3":27,"4":92,"5":1155}</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>51.505369</v>
+      </c>
+      <c r="R64" t="n">
+        <v>-0.080248</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>9264869665029404414</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnyv7Q-EXyXsGrZGcs31ns2e3L2B-Qn8Xa1rzSt2qeIkioRWsc2FQLj6F5YCW6OQbAi9BdUsEzT5fqqUEH9_99HHMZ89Sdm9si4Pb6a2DmLy4cGpMZ-K2o9IpqcF9KL9AX4Stso=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>0x4876036838efbd55:0x80936ddf7a5eb6fe</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>ChIJVb3vOGgDdkgR_rZeet9tk4A</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>{"id":"114828927684740788803","name":"Third Space Tower Bridge (Owner)","link":"https://www.google.com/maps/contrib/114828927684740788803"}</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"2b More London Pl","city":"London","postal_code":"SE1 2AP","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>[{"Name":"Claire","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKfcGumOAEHT8_QILcvNCMWMbjWHIdn10dHyUdUw6PHmi7iDVg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My home club is Canary Wharf but I started coming to TB over a year ago for the yoga instructors. The staff are all so friendly and genuine and the facilities always sparkling clean. The pool, sauna and steam rooms are high end and worth spending time in. This year I have started Wattbike classes and really love the community, it has been great getting to grips with something I was nervous about with the support of the instructor Stacey. Sad that there is only one yoga studio now but the instructors are such high standard here, I can’t recommend enough Negeen, Carl and Oceania.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPlvz4nrnas82yohKrGQE2tVkc77b1B0NpQ6k2tD-LJkcEU2No-LSxKzXvI-2q1bn3eTdlMq7FA3qUbd69s16ElKniS69SPfbRyqaEipKHLVxLtDDv6akv-P01mDxZjUAj6GiWwf1fXjuEh=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNBaoqEeaN0bKDPDRoPkxydXpDQ5vyJ5PWpk6DGnHDf0iERBdM8-HzUaSOq7qe3Msgk-8MTy5hmU-YMXwLrf10gFJlxXuxv3X5PdFoUO112pAfw7qC1sUhw9ZJ2pHW4PVvvtuR0ANJFaCJU=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNqAlTFD0Q67vI4IYFMvCq7IrYcEpOaPSQ3d2ZZAoJ0h5gbDAjds3o7gXKIS2YU9n55zvQv8kjSPtutWwy3E5T7l1UCdThbrAGUuy1OSnKZfUCacA_Yrjeac9xyHZjkuYJT93Qj_WimQi81=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNuzbR6xW8ZNmv81htLokbeLhu6CYKwQkjAhGK28KtOQQJhT81pytV_7dF-YuzroCbU36NA4sz22WtL96xn4dAmTVdHMUzftdGtlXx-w6Y1CcLHL9tazdGqGkbPGDAiJ5trFmgXHa-UTbAD=k-no"],"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xGWWNXUnhZbWxXU1ZGV09HdFhYMXBpYm5SNk1tYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102244418856741644045/reviews?hl=en-GB","posted_at_unix_micros":1765517604147874,"updated_at_unix_micros":1765517604147874,"language":"en","translated_lang":"","text_original":"My home club is Canary Wharf but I started coming to TB over a year ago for the yoga instructors. The staff are all so friendly and genuine and the facilities always sparkling clean. The pool, sauna and steam rooms are high end and worth spending time in. This year I have started Wattbike classes and really love the community, it has been great getting to grips with something I was nervous about with the support of the instructor Stacey. Sad that there is only one yoga studio now but the instructors are such high standard here, I can’t recommend enough Negeen, Carl and Oceania.","text_translated":"","published_at":"2025-12-12T05:33:24.147874Z"},{"Name":"Misha T","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKhj9sHl2mv19BbfYtr-Xa-nXAHy0hxB1uS3Q7O6toeYc7J7w=s120-c-rp-mo-br100","Rating":5,"Description":"This was my ‘home’ club for a few months.\n\nCompact space but never really encountered issues with wait time that for the equipment I use. Love the reformer Pilates and cycle studios. Generally great experience at the gym.\n\nStaff are great - laundry is done ahead of schedule, the cleaning crew always seem to be in a good mood. Special shoutout to Tyree at the concierge team for going above and beyond to sort me out!!\n\nI’d recommend getting a tour if you’re curious.\n\nSad to be moving away","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25WVlQwNWhZa1JRUmxnMFJVMVhVWHBGYlZkRFMwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114640875433232579431/reviews?hl=en-GB","posted_at_unix_micros":1770976014536590,"updated_at_unix_micros":1770976014536590,"language":"en","translated_lang":"","text_original":"This was my ‘home’ club for a few months.\n\nCompact space but never really encountered issues with wait time that for the equipment I use. Love the reformer Pilates and cycle studios. Generally great experience at the gym.\n\nStaff are great - laundry is done ahead of schedule, the cleaning crew always seem to be in a good mood. Special shoutout to Tyree at the concierge team for going above and beyond to sort me out!!\n\nI’d recommend getting a tour if you’re curious.\n\nSad to be moving away","text_translated":"","published_at":"2026-02-13T09:46:54.53659Z"},{"Name":"AT","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV63ke89r77-SA31bfKqQEGCI1nSms0mS13CbP5vPQh50B1FfBz=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I honestly love this gym and some other branches of Third Space. Gives me an ability to have a bit of variety depending on what type of exercise I want to do, plus I enjoy their recovery facilities and spa. Showers and changing rooms are quite pleasant as well - I generally dislike public showers but these ones make me quite comfortable.  They have some awesome staff members making experience even better too :)","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21SdlFUVmpTbXR2ZUZwWFZVcHphMHhyZUd4UlpVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116498697019174312495/reviews?hl=en-GB","posted_at_unix_micros":1779976419763275,"updated_at_unix_micros":1779976419763275,"language":"en","translated_lang":"","text_original":"I honestly love this gym and some other branches of Third Space. Gives me an ability to have a bit of variety depending on what type of exercise I want to do, plus I enjoy their recovery facilities and spa. Showers and changing rooms are quite pleasant as well - I generally dislike public showers but these ones make me quite comfortable.  They have some awesome staff members making experience even better too :)","text_translated":"","published_at":"2026-05-28T13:53:39.763275Z"},{"Name":"Gilmartin Ellen","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJGPWIQEKzEWYAW4IJRmhLDzVT-KH4N2kApdgMD4Hu3muYuqw=s120-c-rp-mo-br100","Rating":5,"Description":"I joined Tower Bridge in May this year and I’ve been really enjoying my experience! There are lots of classes to suit all work schedules and the instructors are really good! I particularly enjoy the spin class and formula 3. All the staff at reception are really friendly and welcoming every time you come through the door. I would recommend third space Tower Bridge to anyone living or working in the area.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pZemJFNTZXSFp4V1RRM1l6aFJaM1ZrUVdNdFJuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108167224401425979581/reviews?hl=en-GB","posted_at_unix_micros":1781301792929817,"updated_at_unix_micros":1781301792929817,"language":"en","translated_lang":"","text_original":"I joined Tower Bridge in May this year and I’ve been really enjoying my experience! There are lots of classes to suit all work schedules and the instructors are really good! I particularly enjoy the spin class and formula 3. All the staff at reception are really friendly and welcoming every time you come through the door. I would recommend third space Tower Bridge to anyone living or working in the area.","text_translated":"","published_at":"2026-06-12T22:03:12.929817Z"},{"Name":"Indu Kw","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW-SIkQJeznSJYJWMQE5Y5aIZ8zaL68gu6k6MJWFNIh3nfIM02f=s120-c-rp-mo-ba12-br100","Rating":4,"Description":"Excellent service yesterday. Been coming to this club for a while, very good service at front desk people have always been nice but a big thanks to Mirela for going that extra mile she saw that I had a heavy bag and asked me if I wanted to leave it by reception. Been coming here for over a year and she’s the first person to offer and it made such a big difference. Club itself is nice, cardio area small and hard to get machines during busy times/classes. Think it’s just a restricted club not much space so definitely better off peak, still not the worst third space. Spa area is nice.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pGWU1UTXpOa1ZHWjBoVWFqWlBZM2swZUZOU2FIYxAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/115462179671329612837/reviews?hl=en-GB","posted_at_unix_micros":1778136817403457,"updated_at_unix_micros":1778136817403457,"language":"en","translated_lang":"","text_original":"Excellent service yesterday. Been coming to this club for a while, very good service at front desk people have always been nice but a big thanks to Mirela for going that extra mile she saw that I had a heavy bag and asked me if I wanted to leave it by reception. Been coming here for over a year and she’s the first person to offer and it made such a big difference. Club itself is nice, cardio area small and hard to get machines during busy times/classes. Think it’s just a restricted club not much space so definitely better off peak, still not the worst third space. Spa area is nice.","text_translated":"","published_at":"2026-05-07T06:53:37.403457Z"}]</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>13</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Fitness+First+Brixton/data=!4m7!3m6!1s0x48760467a78a4d09:0x92e678332dddbe7e!8m2!3d51.4644346!4d-0.1153028!16s%2Fg%2F11bbs_fxq2!19sChIJCU2Kp2cEdkgRfr7dLTN45pI</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Fitness First Brixton</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Blue Star House, 234-244 Stockwell Rd, London SW9 9SP, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–8:30 pm"],"Monday":["5:30 am–9:30 pm"],"Saturday":["8 am–6 pm"],"Sunday":["8 am–6 pm"],"Thursday":["5:30 am–9:30 pm"],"Tuesday":["5:30 am–9:30 pm"],"Wednesday":["5:30 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fitnessfirst.co.uk/find-a-gym/london-brixton</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>+44 20 3096 9319</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>FV7M+QV London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1165</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>{"1":42,"2":22,"3":26,"4":64,"5":1011}</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>51.464435</v>
+      </c>
+      <c r="R65" t="n">
+        <v>-0.115303</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>10585280135389101694</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl1T6_Qe-TFF8A7L0Rs0q-RofJSMUSH4NOl26j_vLRGYEKznxDyK9P2No899bYpsLJruE_Pdx7f9DHVwoaQy2AKEjhvQGLVQZJemOqM8_zMz9qrHTEP9D18Y5KSq11H1yJE5f1z=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>0x48760467a78a4d09:0x92e678332dddbe7e</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>ChIJCU2Kp2cEdkgRfr7dLTN45pI</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.fitnessfirst.co.uk/club-visit/?gym=BRIX\u0026utm_source=google\u0026utm_medium=organic\u0026utm_campaign=book-visit","source":"fitnessfirst.co.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>{"id":"102328469514463818919","name":"Fitness First Brixton (Owner)","link":"https://www.google.com/maps/contrib/102328469514463818919"}</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Blue Star House, 234-244 Stockwell Rd","city":"London","postal_code":"SW9 9SP","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>[{"Name":"Adam Moment","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWAzAg2gbX_CKXtgllNystlaYoNuXgGBfdKZqZSMNTdfzbGVvM=s120-c-rp-mo-br100","Rating":5,"Description":"Great classes I always attend and very professional staff. The management team always help me if I have any questions or need support and the gym is very clean and I like the range of equipment. The steam and sauna is incredible and I’d highly recommend Fitness First Brixton. Thank you all","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMdMHwPCcC1oUlML8rXOyaODTogRtFRwfp0MUtVt3GHmHI1-eBc43L0GbbkdsFKwyuUoRkuafxZxSAxdrkSdjZDrUwbYz13eyKKqF84AAFapGL4Nxd-UBpsaz4v8zcHqJqr0jsJpRM8Fs0=k-no"],"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21WTWF6bExablUxWm5sQlluQjVkRTk0Ykd0aE5IYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104703588900802027627/reviews?hl=en-GB","posted_at_unix_micros":1783527846395967,"updated_at_unix_micros":1783527846395967,"language":"en","translated_lang":"","text_original":"Great classes I always attend and very professional staff. The management team always help me if I have any questions or need support and the gym is very clean and I like the range of equipment. The steam and sauna is incredible and I’d highly recommend Fitness First Brixton. Thank you all","text_translated":"","reply_text_original":"Thank you so much for your wonderful review! We are thrilled to hear that you enjoy our classes and equipment, and that our staff and management have been helpful and professional. We strive to provide a clean and enjoyable gym experience for all our members. We appreciate your recommendation and can't wait to see you at Fitness First Brixton again soon!","reply_language":"en","reply_posted_at_unix_micros":1783611628000000,"reply_updated_at_unix_micros":1783611628000000,"published_at":"2026-07-08T16:24:06.395967Z"},{"Name":"HA","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVvNTulBbqVkd6DssJTdxyeO46z3Y9JVvg8fXJFeNVfQDzl4Zo=s120-c-rp-mo-br100","Rating":5,"Description":"Love this gym! The trainers here are honestly so lovely and supportive — always checking in and helping with form. Papa in particular deserves a mention, he's so patient and genuinely invested in helping members improve, always cheering you on and remembering little details about your goals. Gym's clean, equipment's solid, but honestly, feeling like part of a real community is what makes this place special. Highly recommend!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT205cmVrOWtUM3BCYUZCbmRXNTZOSGw1UlcxZmRGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115388882131898341938/reviews?hl=en-GB","posted_at_unix_micros":1783699178925232,"updated_at_unix_micros":1783699178925232,"language":"en","translated_lang":"","text_original":"Love this gym! The trainers here are honestly so lovely and supportive — always checking in and helping with form. Papa in particular deserves a mention, he's so patient and genuinely invested in helping members improve, always cheering you on and remembering little details about your goals. Gym's clean, equipment's solid, but honestly, feeling like part of a real community is what makes this place special. Highly recommend!","text_translated":"","reply_text_original":"We are thrilled to hear that you love our gym and feel like part of a supportive community! Our trainers, especially Papa, are dedicated to helping our members reach their goals and we are glad that their efforts have not gone unnoticed. Thank you for recommending us!","reply_language":"en","reply_posted_at_unix_micros":1783945508000000,"reply_updated_at_unix_micros":1783945508000000,"published_at":"2026-07-10T15:59:38.925232Z"},{"Name":"Sabit Matai","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXy4CS-0LajEMGTMPss0FKprHM5FgOHmNfWNvJDMZVDV98rU93FtA=s120-c-rp-mo-br100","Rating":5,"Description":"I joined at the beginning of this year and I've been really enjoying it. This is a well managed gym with a professional and friendly team. The staff are always smiling and welcoming which makes a big different.\nThe gym is kept tidy all the time, weights are always put back where they belong something you don't often see in other gyms, and which reflects excellent organisation. They also have very experienced personal trainers, so you are in safe hand if you work with them.\n\nA special big thank you to the team who ensure the gym stays spotless, they're always on the floor ensuring a clean and welcoming environment for everyone. 🙏🏽","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMUyBkKKJ-n-FLKEjEPSf2AsrdcWmXQ5FeyVLsuTwu99mNpQNf5EHWeXel6aDSCJa8l9HaOwOeXpBwU6BqoqZ61PBX51MCyoonvbZpf-j36JLTMyfDitvMVnWjQrFYq3uQB4gM8GgKAWjrO=k-no"],"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xWcllVcHRUVEJGVDFObFEyWkpWSHB2YTB4Uk9VRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111910885587823776721/reviews?hl=en-GB","posted_at_unix_micros":1769100912678682,"updated_at_unix_micros":1769100912678682,"language":"en","translated_lang":"","text_original":"I joined at the beginning of this year and I've been really enjoying it. This is a well managed gym with a professional and friendly team. The staff are always smiling and welcoming which makes a big different.\nThe gym is kept tidy all the time, weights are always put back where they belong something you don't often see in other gyms, and which reflects excellent organisation. They also have very experienced personal trainers, so you are in safe hand if you work with them.\n\nA special big thank you to the team who ensure the gym stays spotless, they're always on the floor ensuring a clean and welcoming environment for everyone. 🙏🏽","text_translated":"","reply_text_original":"Thank you for your kind words and support! Our team takes pride in providing a clean and welcoming environment for our members. We're so glad to hear that you've been enjoying your time at our club and appreciate your recognition of our organisation and experienced personal trainers. Keep up the great work and thanks for being a part of our community!","reply_language":"en","reply_posted_at_unix_micros":1769440073000000,"reply_updated_at_unix_micros":1769440073000000,"published_at":"2026-01-22T16:55:12.678682Z"},{"Name":"Benjamin Rolleston","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKChnyIeEYeL0lcHR_VQn16yOnQFEuhTgH_wXu_Ah2fUadA1A=s120-c-rp-mo-br100","Rating":5,"Description":"As soon as you walk into the gym you are greeted by the friendliest most welcoming staff ever! The gym is always kept clean and hygienic every time I come. Big shout out to the trainers for their contagiously positive energy and assistance in the gym.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPVkupwyDQ5kD4eYU5BwZ6BW33oge02NhAAJagRCw0aeT2EcrC2zNoMboWPaJVRlnZ0ZynOC27OXyDE6MlfDT_D_14VWPQ_wIJFOlYKq1TV7wmbhhfkfMCmSJm2m9nEvX3tDggBH0le7mYW=k-no"],"When":"Edited 2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tkTU4xUnlNRVJCUjBwV2VrcGtNRGxMV1VwS1IzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114184273923917156103/reviews?hl=en-GB","posted_at_unix_micros":1773061412927934,"updated_at_unix_micros":1782149442991763,"language":"en","translated_lang":"","text_original":"As soon as you walk into the gym you are greeted by the friendliest most welcoming staff ever! The gym is always kept clean and hygienic every time I come. Big shout out to the trainers for their contagiously positive energy and assistance in the gym.","text_translated":"","reply_text_original":"Thank you for your wonderful review! We strive to provide a clean and welcoming environment for all our members. Our trainers are dedicated to helping you reach your fitness goals with their positive energy. Keep up the great work.","reply_language":"en","reply_posted_at_unix_micros":1773073154000000,"reply_updated_at_unix_micros":1782212763000000,"published_at":"2026-03-09T13:03:32.927934Z"},{"Name":"Mel Etienne","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK5LWJZu3fDsvVETCPYnKsNXs8ZFCOo2TswoVs-gF8d_HP0B2oE=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve visited Fitness First Brixton twice using a visitor pass with a friend who is a member, and both experiences were really positive.\n\nOn my first visit, I attended a core class with Marlon the instructor, who was very friendly, welcoming, and informative. The class was well structured and enjoyable, and it created a great atmosphere for working out. After the class I also used the treadmill, and the gym floor felt well organised and easy to navigate.\n\nOn my second visit, I had the chance to use the steam room and sauna, which I really enjoyed. Both facilities were clean, relaxing, and a great way to unwind after a workout.\n\nOverall, the staff have been consistently welcoming and approachable, and the gym itself is very clean and well maintained. From my experience so far, it’s a great environment to exercise in and will deffo sign up!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pCSVVIRnRRbVl6VVdONmNXMTFVVWQyYW5SalNrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114737230339430924681/reviews?hl=en-GB","posted_at_unix_micros":1773155444565457,"updated_at_unix_micros":1773155444565457,"language":"en","translated_lang":"","text_original":"I’ve visited Fitness First Brixton twice using a visitor pass with a friend who is a member, and both experiences were really positive.\n\nOn my first visit, I attended a core class with Marlon the instructor, who was very friendly, welcoming, and informative. The class was well structured and enjoyable, and it created a great atmosphere for working out. After the class I also used the treadmill, and the gym floor felt well organised and easy to navigate.\n\nOn my second visit, I had the chance to use the steam room and sauna, which I really enjoyed. Both facilities were clean, relaxing, and a great way to unwind after a workout.\n\nOverall, the staff have been consistently welcoming and approachable, and the gym itself is very clean and well maintained. From my experience so far, it’s a great environment to exercise in and will deffo sign up!","text_translated":"","reply_text_original":"Thank you for your kind words! We’re thrilled to hear that you had a great experience at our club.  We hope to see you at the gym again soon!","reply_language":"en","reply_posted_at_unix_micros":1773307329000000,"reply_updated_at_unix_micros":1773307329000000,"published_at":"2026-03-10T15:10:44.565457Z"}]</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>13</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Third+Space+City/data=!4m7!3m6!1s0x487604d442622727:0x54383a402c73e234!8m2!3d51.5102576!4d-0.0805433!16s%2Fg%2F11bzswc1v7!19sChIJJydiQtQEdkgRNOJzLEA6OFQ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Third Space City</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>40 Mark Ln, London EC3R 7AT, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["8 am–8 pm"],"Sunday":["8 am–8 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thirdspace.london/clubs/city/</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>+44 20 7534 2888</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>GW69+4Q London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1123</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>{"1":31,"2":10,"3":16,"4":33,"5":1033}</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>51.510258</v>
+      </c>
+      <c r="R66" t="n">
+        <v>-0.080543</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>6068664545179853364</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Choice gym with a pool &amp; diverse classes</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Upscale fitness club offering a variety of classes, including dance &amp; combat, plus a pool &amp; a sauna.</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnRLbkAw3SlXMW1ZlR6XnrTkWo3Llcgb1DRk4MNkq1kbxJvSHGtJc_RKBEusaOuCr_QsNArLzwT_8yq_sdyAyY4ROWXgg3ne6qonbVqa40-qtqfrQXcZHKGVgzUbZUWT_K5ljjUDuUePMRq=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>0x487604d442622727:0x54383a402c73e234</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>ChIJJydiQtQEdkgRNOJzLEA6OFQ</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>{"id":"103886477158631875816","name":"Third Space City (Owner)","link":"https://www.google.com/maps/contrib/103886477158631875816"}</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"40 Mark Ln","city":"London","postal_code":"EC3R 7AT","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>[{"Name":"Nathan Davis","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVleqeYKf9wPdfPayVsxWYLgiZcsoU_6vNIb8_1-wGzOi81CGeEdg=s120-c-rp-mo-br100","Rating":5,"Description":"The gym itself is fantastic. Classes are great with top instructors. The facilities, including the sauna and cold plunge, are so well-maintained and you can feel like it's a high-quality premium gym.\n\nBut what really differentiates this place is the Natural Fitness Food cafe and its staff. The cafe has a lovely little area to work from in the mornings and Niko and Laura make it infinitely better with their friendliness and energy.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNdH5RlTGSwio72dKbuCt97Z8a8Kzo88Q9FldVgVzpEhQuZdrWCGW2knmk8th13OyKiNlatyyqp4s0aFBKIEXt5I0UnwzVeQRonrPNsNR-r_oGbBFnK736es00QFQEOOepMYagIKjVvv_k=k-no"],"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT210WmVtZzRSRll6UmxaaGRYVnRUVEp5VVRKaU5tYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107491408056594321909/reviews?hl=en-GB","posted_at_unix_micros":1785231596937792,"updated_at_unix_micros":1785231596937792,"language":"en","translated_lang":"","text_original":"The gym itself is fantastic. Classes are great with top instructors. The facilities, including the sauna and cold plunge, are so well-maintained and you can feel like it's a high-quality premium gym.\n\nBut what really differentiates this place is the Natural Fitness Food cafe and its staff. The cafe has a lovely little area to work from in the mornings and Niko and Laura make it infinitely better with their friendliness and energy.","text_translated":"","reply_text_original":"Hi Nathan,\n\nThank you for your 5 * review and wonderful feedback with a great shout out to the NFF team here, along with the club facilities.\n\nWe really appreciate the lovely comments and the continued support and are so pleased that your membership here at Third Space City is going so well.\n\nPlease don't hesitate to reach out to myself or a member of my team if you ever need any assistance.\n\nKind regards,\n\nJason Gibbons\nThird Space City\nOperations Manager","reply_language":"en","reply_posted_at_unix_micros":1786004020000000,"reply_updated_at_unix_micros":1786004020000000,"published_at":"2026-07-28T09:39:56.937792Z"},{"Name":"richard halle","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJeurB5Wz-1BXlZz2nktdmCwzpFL6p7wAOniCVx87dC82pl8Bs=s120-c-rp-mo-br100","Rating":5,"Description":"\"Sall is one of the best PTs I’ve worked with, and I’ve been training for years.\"\n\nI trained with Sall about 8-10 years ago, and when I overheard his voice at Third Space recently, I knew it was him. I’d been a member here since 2019 but never used PT  now I’m on my third block with him.\n\nSall gets what you need in your 50s: mobility, quality of life, performance. His corrective exercise knowledge is excellent, and he always asks three simple questions, “what are you doing, why, and what effect does it have on you? That makes every session make sense.\n\nHe’s also flexible with my travel schedule, a big reason I moved to blocks of sessions. Highly recommend.\n\n@Richard (Third Space member since April 2019)","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOiow-fA84B3sf9y6pB1ewPFA5tDNAKpnOmsWJtnJxPKEawGwJjgWb3rwNxsqze6cvu8x5SAsLd88bSItBOhqWDDtIAqswnwdeatWPT9FUpmZkgPQS03_JModZ3jckGKpJWPIV7-AlMgYGY=k-no"],"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tFeFRrMU9URlE1UldKMFZtNDVjRkZwY2tsUmQxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112521186158267640444/reviews?hl=en-GB","posted_at_unix_micros":1777374393841584,"updated_at_unix_micros":1777374393841584,"language":"en","translated_lang":"","text_original":"\"Sall is one of the best PTs I’ve worked with, and I’ve been training for years.\"\n\nI trained with Sall about 8-10 years ago, and when I overheard his voice at Third Space recently, I knew it was him. I’d been a member here since 2019 but never used PT  now I’m on my third block with him.\n\nSall gets what you need in your 50s: mobility, quality of life, performance. His corrective exercise knowledge is excellent, and he always asks three simple questions, “what are you doing, why, and what effect does it have on you? That makes every session make sense.\n\nHe’s also flexible with my travel schedule, a big reason I moved to blocks of sessions. Highly recommend.\n\n@Richard (Third Space member since April 2019)","text_translated":"","reply_text_original":"Hi Richard,\n\nThank you for your 5 * review and wonderful with your feedback on your sessions with Sal. \n\nWe really appreciate the score and continued support for us here at Third Space City.\n\nPlease don't hesitate to reach out to myself or a member of my team if you ever need any assistance.\n\nKind regards,\n\nJason Gibbons\nThird Space City\nOperations Manager","reply_language":"en","reply_posted_at_unix_micros":1778070395000000,"reply_updated_at_unix_micros":1778070395000000,"published_at":"2026-04-28T11:06:33.841584Z"},{"Name":"Willow Ritter","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKFEQfOmjqxIaLXB1uRBNE9FAJPdxVfmPNXRsBgY72BY-k7Qw=s120-c-rp-mo-br100","Rating":5,"Description":"I really like going to this gym. Kamilla at the front desk is always lovely, helpful, and friendly. Ezekiel is also always a joy to chat. Some of the other front desk workers…not so friendly or welcoming. So, Kamilla and Ezekiel are always a pleasure to see when I walk in.\nGym is pretty nice, clean, and the classes are wonderful. Unlimited classes and multiple facilities with the membership is awesome, especially given the price. Would recommend!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pNdFJqVm1WRWg0UzJkWmJGSnVkRWRZZVZGd2MyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115861420947830887687/reviews?hl=en-GB","posted_at_unix_micros":1772121267742836,"updated_at_unix_micros":1772121267742836,"language":"en","translated_lang":"","text_original":"I really like going to this gym. Kamilla at the front desk is always lovely, helpful, and friendly. Ezekiel is also always a joy to chat. Some of the other front desk workers…not so friendly or welcoming. So, Kamilla and Ezekiel are always a pleasure to see when I walk in.\nGym is pretty nice, clean, and the classes are wonderful. Unlimited classes and multiple facilities with the membership is awesome, especially given the price. Would recommend!","text_translated":"","reply_text_original":"Hi Willow,\n\nThank you for your 5 * review and wonderful feedback. It's really wonderful to read your detail review and the impact the team have on your experience. \n\nWe really appreciate the lovely comments and the continued support and are so pleased that your membership here at Third Space City is going so well.\n\nPlease don't hesitate to reach out to myself or a member of my team if you ever need any assistance.\n\nKind regards,\n\nJason Gibbons\nThird Space City\nOperations Manager","reply_language":"en","reply_posted_at_unix_micros":1772449083000000,"reply_updated_at_unix_micros":1772449083000000,"published_at":"2026-02-26T15:54:27.742836Z"},{"Name":"elle roya","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJy9cIIpyamwsuB1V7a9o1XaM4VrZCgUbu4FQNAgupsRM8Xnl0=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"If you’re somebody whose hobbies revolve around fitness \u0026 wellbeing, then this is the perfect gym for you.\nI used to go to PureGym prior to joining Third Space because I didn’t realise how much the gym environment could impact your willingness to go to the gym and focus on your health. Now I come here and sometimes spent 5 hours at a time on the classes, gym equipment, recovery, spa \u0026 cafe.\nI feel like coming here has completely switched up my fitness routine as I very often fit the gym into my schedule before I have plans, and the fact that you can comfortably get ready here and feel clean is a massive bonus.\nAll of the staff that I’ve met so far have been so lovely, from the concierge team, to the cafe team, to the PTs \u0026 class instructors, even the cleaners! And special shout out to the cleaners because I literally see them cleaning non-stop, and it definitely shows with how spotless the changing rooms are specifically.\nThe classes at Third Space are great value for money when you consider that usually in London you’re looking at £22-40 per hour for most disciplines, and as somebody that usually does 5 classes a week at other studios, I’ve managed to utilise the classes here really well. Third Space is actually the first place I tried Hot Yoga, Pilates, \u0026 Sound Baths and they are now my new addictions!\nI do aerial arts \u0026 pole outside of gym and the classes here have really complimented my training \u0026 conditioning well.\nThe workshops I’ve attended have been so useful too, such as the ‘hot flexibility flow’ and ‘hip rehab \u0026 prehab’ workshops which are great for flexibility.\nI’d like to specifically shout out 2 PTs that I had complimentary sessions with, as they were very knowledgeable and helpful even just in the short space of an hour. Sall \u0026 Honor are amazing at what they do and both have great experience.\nThe food \u0026 shakes in the cafe are sooo good too. Everything tastes fresh \u0026 high quality, and it’s really hard to resist grabbing something as you finish your workout. Get the Strawberry \u0026 pistachio shake but make it vegan!! 🤤\nMy only bit of feedback to improve is that the changing rooms have the air con blasting, which is not really ideal when you’re coming out of the pool area soaking wet and hot, so if that could be changed to room temperature it would be absolutely perfect! ☺️","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPOoABGzwCEpbvWgavJQtbuSS-8z1K0REDl9HJRfVtGJDWyZYvdYyZKPYA6MUUmbgHazBj7AVRjBeiqADHK3Cd4esHo3k5yJm1FnxuEGcun8UuAMy_DkPSE8VLtE-G67s6K-ggDbldSodrb=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMy2jafSAP06ZEQha2MnqlFnhhsA_CLlvFl0ZrqoT3-Ji1F28GFq0HMNasluSu9a6R2aIooIXjFEkXYGYTAIjhYC_a2vppS3bqUbAbO9PDAmVYcuwAodofvzfJfH0dq4TiBgHbLbHxuWRaN=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmP7Rfq1EDnAuuX07VQCQCAZ4eRIHhLAQL4hnnn4mbdoK4DEMBZPMzLGpCnuJTZFtg-_Ac411ULRnFhkoDJVJ5ohrIs3_5T6zbGpdT_tOv-Da1RQhDOIDGwCkaFnwo5URaFeX8zW0axh7l4U=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOIvYUR4sG1kXcmXtNORiHjI_BNPZaO-ALOV3fs2dLC_i6xCMIjl1mjHXmIJOEuqhv5FteS_ruYsLEk4E3sQ2cHoKjcBTKKAqtkPBxsTGzD8HH-6OigVZ0E5yCcDbuYiOyd7Yx5p-gR_-in=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNLnTlUotZDEvusxZ1LHsFULkA14Ot06LAfkS9M5P5Wa1lktDOQO-aDOXEYtNhe0guIvjveTABpo979SEAIt54CgHFHu1_M43NAWtUszbSdJDz3WGyTESoiWYFqOq1qEoWx8CiJx1VQr44=k-no"],"When":"Edited 8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pWbmFVTkZPR041Y1RKNk5tTXllVzVxT0ZoNmQxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106458148472051265158/reviews?hl=en-GB","posted_at_unix_micros":1767189995711392,"updated_at_unix_micros":1767381423628336,"language":"en","translated_lang":"","text_original":"If you’re somebody whose hobbies revolve around fitness \u0026 wellbeing, then this is the perfect gym for you.\nI used to go to PureGym prior to joining Third Space because I didn’t realise how much the gym environment could impact your willingness to go to the gym and focus on your health. Now I come here and sometimes spent 5 hours at a time on the classes, gym equipment, recovery, spa \u0026 cafe.\nI feel like coming here has completely switched up my fitness routine as I very often fit the gym into my schedule before I have plans, and the fact that you can comfortably get ready here and feel clean is a massive bonus.\nAll of the staff that I’ve met so far have been so lovely, from the concierge team, to the cafe team, to the PTs \u0026 class instructors, even the cleaners! And special shout out to the cleaners because I literally see them cleaning non-stop, and it definitely shows with how spotless the changing rooms are specifically.\nThe classes at Third Space are great value for money when you consider that usually in London you’re looking at £22-40 per hour for most disciplines, and as somebody that usually does 5 classes a week at other studios, I’ve managed to utilise the classes here really well. Third Space is actually the first place I tried Hot Yoga, Pilates, \u0026 Sound Baths and they are now my new addictions!\nI do aerial arts \u0026 pole outside of gym and the classes here have really complimented my training \u0026 conditioning well.\nThe workshops I’ve attended have been so useful too, such as the ‘hot flexibility flow’ and ‘hip rehab \u0026 prehab’ workshops which are great for flexibility.\nI’d like to specifically shout out 2 PTs that I had complimentary sessions with, as they were very knowledgeable and helpful even just in the short space of an hour. Sall \u0026 Honor are amazing at what they do and both have great experience.\nThe food \u0026 shakes in the cafe are sooo good too. Everything tastes fresh \u0026 high quality, and it’s really hard to resist grabbing something as you finish your workout. Get the Strawberry \u0026 pistachio shake but make it vegan!! 🤤\nMy only bit of feedback to improve is that the changing rooms have the air con blasting, which is not really ideal when you’re coming out of the pool area soaking wet and hot, so if that could be changed to room temperature it would be absolutely perfect! ☺️","text_translated":"","reply_text_original":"Hi Elle,\n\nThank you for your 5 * review and giving us such detail in your feedback, its wonderful to know you see and feel the benefit from different club spaces and we really hope that from facilities to PT's you are seeing the benefits not just in training but overall well being.\n\nWe really appreciate the score and continued support for us here at Third Space City.\n\nPlease don't hesitate to reach out to myself or a member of my team if you ever need any assistance.\n\nKind regards,\n\nJason Gibbons\nThird Space City\nOperations Manager","reply_language":"en","reply_posted_at_unix_micros":1768474161000000,"reply_updated_at_unix_micros":1768474161000000,"published_at":"2025-12-31T14:06:35.711392Z"},{"Name":"Catherine","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJLC_PDCqkQF9JGoSCo4KKBsRV5hyLkluSc9apOFPPIS57i3Q=s120-c-rp-mo-br100","Rating":5,"Description":"The club has a great array of equipment and it’s generally easy to access most of it when you need it. The classes are great and have a good variety. I’ve also been doing PT sessions with Lucy - she’s really helped build my confidence and I’m seeing a lot of progress with her quickly.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xsTmQwWTRUbXRQTUdGVVRYYzROME00WjJJeGRYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113003579215830032611/reviews?hl=en-GB","posted_at_unix_micros":1783967955553190,"updated_at_unix_micros":1783967955553190,"language":"en","translated_lang":"","text_original":"The club has a great array of equipment and it’s generally easy to access most of it when you need it. The classes are great and have a good variety. I’ve also been doing PT sessions with Lucy - she’s really helped build my confidence and I’m seeing a lot of progress with her quickly.","text_translated":"","reply_text_original":"Hi Catherine,\n\nThank you for your 5* review and wonderful feedback. it's great to read about your sessions with Lucy and hope this long continues together for you. \n\nWe really appreciate the lovely comments and the continued support and are so pleased that your membership here at Third Space City is going so well.\n\nPlease don't hesitate to reach out to myself or a member of my team if you ever need any assistance.\n\nKind regards,\n\nJason Gibbons\nThird Space City\nOperations Manager","reply_language":"en","reply_posted_at_unix_micros":1784286672000000,"reply_updated_at_unix_micros":1784286672000000,"published_at":"2026-07-13T18:39:15.55319Z"}]</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>13</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Fitness+First+The+Strand/data=!4m7!3m6!1s0x487604cc1c9974cb:0x5d7d804db13b534!8m2!3d51.5100295!4d-0.1238553!16s%2Fg%2F1hbpwr1pb!19sChIJy3SZHMwEdkgRNLUT2wTY1wU</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fitness First The Strand</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6 Bedford St, London WC2E 9HD, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9 pm"],"Monday":["6 am–9 pm"],"Saturday":["8 am–5 pm"],"Sunday":["8 am–5 pm"],"Thursday":["6 am–9 pm"],"Tuesday":["6 am–9 pm"],"Wednesday":["6 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fitnessfirst.co.uk/find-a-gym/london-the-strand-covent-garden</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>+44 20 3096 7551</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>GV6G+2F London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>791</v>
+      </c>
+      <c r="O67" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>{"1":31,"2":9,"3":21,"4":42,"5":688}</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>51.510029</v>
+      </c>
+      <c r="R67" t="n">
+        <v>-0.123855</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>421042605549401396</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn75-KNd72Xq6dY-QGvQUIRy-iKTrjCs2L9QUImVy5CtyT7TgD8yrswcvl8GzO90FQGPLC-Bpb0YxB8TizYWxMRuncKZcbFq90EhJmuUFI7z8FlbS2-DW4HAhLumzqIX5cWT71x=w576-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>0x487604cc1c9974cb:0x5d7d804db13b534</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>ChIJy3SZHMwEdkgRNLUT2wTY1wU</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.fitnessfirst.co.uk/club-visit/?gym=THEST\u0026utm_source=google\u0026utm_medium=organic\u0026utm_campaign=book-visit","source":"fitnessfirst.co.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>{"id":"110919378128633198690","name":"Fitness First The Strand (Owner)","link":"https://www.google.com/maps/contrib/110919378128633198690"}</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"6 Bedford St","city":"London","postal_code":"WC2E 9HD","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>[{"Name":"Justyna Bazinska","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVD6sxXzokUxzeOhmSWgxKtnQFe5Mq0-wpsvoq00IAYx8fNtZQ=s120-c-rp-mo-br100","Rating":5,"Description":"Hey\nI have visited this gym for a day pass and couldn’t be more happier with whole experience. August welcomed me and my friend with warm smile and showed us all around. Having a nice staff around makes a big difference. He was very polite, professional and funny in same time. That’s what makes your work out a good experience. Can’t wait to go back there .","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMJArjxmCT0svSuBYKnZi1v6bfFFleQNYbRwMoDEBWe-HREKPxIaGhza7XqodlXvLfju4q7mlif-hiBrylRuWlr6Fed_mYSeOUT-KFXa8V2V75-w_3OkWN6-JR7MS9hRRVjt_1zxLzLv9hS=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21ocmFucFhiVlZGUTNoVU5HRnJTbHAzY1ZFMlFVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100934342848269021726/reviews?hl=en-GB","posted_at_unix_micros":1780416604575559,"updated_at_unix_micros":1780416604575559,"language":"en","translated_lang":"","text_original":"Hey\nI have visited this gym for a day pass and couldn’t be more happier with whole experience. August welcomed me and my friend with warm smile and showed us all around. Having a nice staff around makes a big difference. He was very polite, professional and funny in same time. That’s what makes your work out a good experience. Can’t wait to go back there .","text_translated":"","reply_text_original":"Thank you for the glowing review! Our team works hard to create a welcoming and positive environment for all of our guests. We're so happy to hear that August made your visit memorable. We can't wait to have you back at the club soon!","reply_language":"en","reply_posted_at_unix_micros":1780672689000000,"reply_updated_at_unix_micros":1780672689000000,"published_at":"2026-06-02T16:10:04.575559Z"},{"Name":"Jaiden Smith","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIuglWQRV0r27D-53EIfXtjOm6kKqHAzthqandn6zz9NB9CoQ=s120-c-rp-mo-br100","Rating":5,"Description":"⭐⭐⭐⭐⭐\n\nI can’t recommend Fitness First London highly enough. The facilities are always clean, well-maintained, and welcoming, with a great atmosphere that makes training enjoyable.\n\nA special mention goes to August, the manager, whose exceptional customer service truly sets this club apart. August consistently goes above and beyond to ensure members feel valued, supported, and looked after. Their professionalism, attention to detail, and genuine commitment to creating a positive member experience are outstanding.\n\nIt’s rare to come across someone so dedicated to both their team and the people they serve. Thank you, August, and the entire Fitness First team, for making every visit such a positive experience. Highly recommended!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwdVdVNDNhbVpDVUVsdlNUWlZhRzlJWVVsV2JFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105463585408555885037/reviews?hl=en-GB","posted_at_unix_micros":1780483138199449,"updated_at_unix_micros":1780483138199449,"language":"en","translated_lang":"","text_original":"⭐⭐⭐⭐⭐\n\nI can’t recommend Fitness First London highly enough. The facilities are always clean, well-maintained, and welcoming, with a great atmosphere that makes training enjoyable.\n\nA special mention goes to August, the manager, whose exceptional customer service truly sets this club apart. August consistently goes above and beyond to ensure members feel valued, supported, and looked after. Their professionalism, attention to detail, and genuine commitment to creating a positive member experience are outstanding.\n\nIt’s rare to come across someone so dedicated to both their team and the people they serve. Thank you, August, and the entire Fitness First team, for making every visit such a positive experience. Highly recommended!","text_translated":"","reply_text_original":"Thank you for your glowing review! We are thrilled that you enjoy our clubs facilities and the exceptional customer service provided by our manager, August. We pride ourselves on creating a positive and welcoming atmosphere for all our members. Thank you for recognising our team's dedication, professionalism, and commitment. We look forward to welcoming you back soon!","reply_language":"en","reply_posted_at_unix_micros":1780672426000000,"reply_updated_at_unix_micros":1780672426000000,"published_at":"2026-06-03T10:38:58.199449Z"},{"Name":"The Busy Traveller","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVKydIESlRKyszyJtTOxkVobF1LGxmaVPYqu6lPxENV0UIyFLI=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My thanks to always smiley June, always positive August, massively motivating Neil, and attentive Weronika - plus all the staff - I love this gym. It's the best I've ever been a member of.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPngRKROoG8pUJpji-G7Sl2LcMdgTx2ZdPZ4CHjaPm2Q_7eoAQlPMa120CN5EAjfQDq11t19mepivI73JEBVdywQilgBbQGcLv3MSX4fp0c59TgrzS75Mrm7uYO9Iq9t-zDbK_r-g0YBjCq=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21wQlRsWlNSMGt5ZWtKUFdVNVdhWEJKT1VaWmVYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102000253466262667344/reviews?hl=en-GB","posted_at_unix_micros":1780587227629251,"updated_at_unix_micros":1780587227629251,"language":"en","translated_lang":"","text_original":"My thanks to always smiley June, always positive August, massively motivating Neil, and attentive Weronika - plus all the staff - I love this gym. It's the best I've ever been a member of.","text_translated":"","reply_text_original":"We are thrilled to hear that you love our club and our team! We strive to create a positive and motivating environment for all our members. Thank you for your support and dedication to our gym.","reply_language":"en","reply_posted_at_unix_micros":1780673148000000,"reply_updated_at_unix_micros":1780673148000000,"published_at":"2026-06-04T15:33:47.629251Z"},{"Name":"Léo Krickelberg","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocI7pE3rrp0fYY-muVBKfL1UK_vSnu2XBy2O1S2kyTySmYXJY6Q=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been training with Alex for a while now, and he’s an amazing coach. He puts full effort into every session and tailors the training to your goals, making each workout challenging but doable. He’s genuinely invested in your progress, motivating you, correcting your form, and helping you see real results. On top of that, he’s friendly, approachable, and always ready to help. If you want to improve in boxing with a coach who truly cares, he’s the one.","Images":null,"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xoV0xVVkhWRUp6Y25jM01qVm1VMHB1WW10UlNYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116644999073453527734/reviews?hl=en-GB","posted_at_unix_micros":1764686607606058,"updated_at_unix_micros":1764686607606058,"language":"en","translated_lang":"","text_original":"I’ve been training with Alex for a while now, and he’s an amazing coach. He puts full effort into every session and tailors the training to your goals, making each workout challenging but doable. He’s genuinely invested in your progress, motivating you, correcting your form, and helping you see real results. On top of that, he’s friendly, approachable, and always ready to help. If you want to improve in boxing with a coach who truly cares, he’s the one.","text_translated":"","published_at":"2025-12-02T14:43:27.606058Z"},{"Name":"Kenny Nguyen","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVIznFZFcPsRFX7xVIVWbWYAv7rU38xVz54t54bpB3dOlwGQVzeVQ=s120-c-rp-mo-br100","Rating":5,"Description":"Amazing place! Great equipment and clean. August at the front desk is very helpful and polite. We will definitely come back!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOhzWy6A3vLMA6kt4EOAUVxMRIZmHpekUxtj3SYjCroMoiNQaBc1uQMgazA1gifExbyGtO09b6oRdl7Xb3SzqFGtV7DgdMUsWYBdwp6IPDtKVjntLV5ryu3StaShp3ueaFijTK0Mmsv4kBm=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2t4blVXbE9jVU50UmtKdFp6SkRZWHB0Y0RKWGRVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114483483568600701391/reviews?hl=en-GB","posted_at_unix_micros":1775750327574828,"updated_at_unix_micros":1775750327574828,"language":"en","translated_lang":"","text_original":"Amazing place! Great equipment and clean. August at the front desk is very helpful and polite. We will definitely come back!","text_translated":"","reply_text_original":"Thank you for the amazing feedback! We take great pride in providing top-notch equipment and a clean environment. Our team, especially August, always strives to provide helpful and polite service. We can't wait to have you back!","reply_language":"en","reply_posted_at_unix_micros":1775834112000000,"reply_updated_at_unix_micros":1775834112000000,"published_at":"2026-04-09T15:58:47.574828Z"}]</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>13</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/F45+Oxford+Circus/data=!4m7!3m6!1s0x48761b58df07a96b:0x22a943fbf1a134b9!8m2!3d51.5174084!4d-0.1404045!16s%2Fg%2F11g0_rhv_d!19sChIJa6kH31gbdkgRuTSh8ftDqSI</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>F45 Oxford Circus</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>F45, F45 Oxford Circus, Oxford Circus, 2a Little Portland St, London W1W 7JA, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–8 pm"],"Monday":["6 am–8 pm"],"Saturday":["7 am–2 pm"],"Sunday":["7 am–2 pm"],"Thursday":["6 am–8 pm"],"Tuesday":["6 am–8 pm"],"Wednesday":["6 am–8 pm"]}</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>https://f45training.co.uk/oxfordcircus/home</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>+44 7394 851872</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>GV85+XR London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>665</v>
+      </c>
+      <c r="O68" t="n">
+        <v>5</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":2,"3":0,"4":10,"5":652}</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>51.517408</v>
+      </c>
+      <c r="R68" t="n">
+        <v>-0.140404</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>2497602217723376825</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmeHPc-N5aJ27XTakso9KCuBJsgtzFkVU9umZaxIUKP0uByWvS-cGTwR8UVPkKnANUuCBh92BpjbnFB8DFH5uJz7Ght3u6_iocAASCBTYx7tPRmhDNA2Apk1BbiUeWZyiXDrYPFsD_CvMMS=w408-h612-k-no</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>0x48761b58df07a96b:0x22a943fbf1a134b9</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>ChIJa6kH31gbdkgRuTSh8ftDqSI</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>{"id":"114086443407309253144","name":"F45 Oxford Circus (Owner)","link":"https://www.google.com/maps/contrib/114086443407309253144"}</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"F45, Oxford Circus, 2a Little Portland St","city":"London","postal_code":"W1W 7JA","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>[{"Name":"nasser hamad","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKZUT-SVPgpBhKF8T7nthZQ5c9mxTz1e4iLAtgsD53AVHkBIQ=s120-c-rp-mo-br100","Rating":5,"Description":"⭐⭐⭐⭐⭐\n\nAfter completing 27 classes at F45 Oxford Circus, I can honestly say this is one of the best decisions I have ever made. I only wish I had discovered it sooner — I would have started years ago.\n\nThe impact on my daily life has been truly life-changing. Years of extended desk work had left me with persistent pain and stiffness, but since joining, my day-to-day tasks feel noticeably easier and that discomfort has significantly reduced. On top of that, my stamina and strength have improved in ways I didn't expect so quickly.\n\nWhat I love most is the variety — I've attended strength, Pilates, and cardio classes all under one roof. There really is something for every goal and every mood, and the programming keeps things fresh every single session.\n\nThe staff and coaches are genuinely the nicest, most inspiring people. A special shoutout to Ally and Sam — they are consistently present, attentive, and always ready to push you in the best way possible. That kind of coaching makes a real difference to your progress and keeps you coming back.\n\nThe studio itself is brilliantly equipped with brand new gym equipment, and the added extras like the InBody scan and recovery equipment show they genuinely care about members' progress beyond just the workout.\n\nIf you're on the fence, stop hesitating. This place will change your life.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2twM2JVZFBTamxmTm1waVdtb3lXVzh3Ym0xSU4wRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109087458864329946378/reviews?hl=en-GB","posted_at_unix_micros":1773341715948893,"updated_at_unix_micros":1773342405395078,"language":"en","translated_lang":"","text_original":"⭐⭐⭐⭐⭐\n\nAfter completing 27 classes at F45 Oxford Circus, I can honestly say this is one of the best decisions I have ever made. I only wish I had discovered it sooner — I would have started years ago.\n\nThe impact on my daily life has been truly life-changing. Years of extended desk work had left me with persistent pain and stiffness, but since joining, my day-to-day tasks feel noticeably easier and that discomfort has significantly reduced. On top of that, my stamina and strength have improved in ways I didn't expect so quickly.\n\nWhat I love most is the variety — I've attended strength, Pilates, and cardio classes all under one roof. There really is something for every goal and every mood, and the programming keeps things fresh every single session.\n\nThe staff and coaches are genuinely the nicest, most inspiring people. A special shoutout to Ally and Sam — they are consistently present, attentive, and always ready to push you in the best way possible. That kind of coaching makes a real difference to your progress and keeps you coming back.\n\nThe studio itself is brilliantly equipped with brand new gym equipment, and the added extras like the InBody scan and recovery equipment show they genuinely care about members' progress beyond just the workout.\n\nIf you're on the fence, stop hesitating. This place will change your life.","text_translated":"","published_at":"2026-03-12T18:55:15.948893Z"},{"Name":"Kaylin Williams","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUCUqbdvcnP2T0g3ZQ_s-NEptNOB2jUEBWshbljG2TZadZxYDzz=s120-c-rp-mo-br100","Rating":5,"Description":"F45 is the hardest and most rewarding workout class I have ever been to. The wide range of exercises - from cardio to resistance and everything in between, create an engaging and challenging experience that leaves me exhausted (in the best way possible) every time! The instructors are incredibly encouraging and want to see you succeed! Could not recommend more!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25JNFQzY3dhR1k0YjNCMFYyUkNhSEl3VGw4NGRrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101048926519596932054/reviews?hl=en-GB","posted_at_unix_micros":1783507132881941,"updated_at_unix_micros":1783507132881941,"language":"en","translated_lang":"","text_original":"F45 is the hardest and most rewarding workout class I have ever been to. The wide range of exercises - from cardio to resistance and everything in between, create an engaging and challenging experience that leaves me exhausted (in the best way possible) every time! The instructors are incredibly encouraging and want to see you succeed! Could not recommend more!","text_translated":"","published_at":"2026-07-08T10:38:52.881941Z"},{"Name":"zevanya yashira","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVbfuLf-x_yGO5iG7IM2xqFzAt_iU2PB7qh0DFp1IlV51tKw12y=s120-c-rp-mo-br100","Rating":5,"Description":"love the workout!! very motivating trainers, and they pay attention to your form more than anything. the 2 week introduction offer is definitely worth it \u0026 i see results quickly, would recommend for beginners","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25GVlVYRTVXVEYzY21sWVJVRkxVRUZLZWxkcWIzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114202356283598918426/reviews?hl=en-GB","posted_at_unix_micros":1780569797757473,"updated_at_unix_micros":1780569797757473,"language":"en","translated_lang":"","text_original":"love the workout!! very motivating trainers, and they pay attention to your form more than anything. the 2 week introduction offer is definitely worth it \u0026 i see results quickly, would recommend for beginners","text_translated":"","reply_text_original":"Thanks for the amazing review! We're so glad you're loving the workouts and already seeing results. Our coaches are passionate about helping members move safely and effectively, so it's great to hear their focus on form made a positive impact. We're also happy you found value in the 2-week introductory offer. Thank you for the recommendation, and we look forward to supporting you on your fitness journey! 💪🎉\n","reply_language":"en","reply_posted_at_unix_micros":1781514129000000,"reply_updated_at_unix_micros":1781514129000000,"published_at":"2026-06-04T10:43:17.757473Z"},{"Name":"Andrew Lampe","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWIk5UR4MnrFcj-4QeSMHn8ew5soCbUBNqE8MYowlKEizZTlrg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"One of the best workouts I’ve ever had! Highly recommend trying it out!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOBVNK3NmlhElL2HxlYk03auaoAEEr4OIuGC5byFh8kXgpjEDK7oPtYZ5Zr6UmEye2HgqvmXGmJW2pTgr3gmDwc6mF7c0Kxeo3H0ixe6FF-D6e4_KGYtuJo75L28XIeMAh9Q8FVhxnYH3tW=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNUXPlPXKMykvesJ8od1cHc6ecWE57VExqqOT0MEaGlK4BNNq2OAtjlKgtdcK8Kw563ypKNKrbAxXxKkljonoZrxVEgm1SFWTWqDzPVbfoZ3g1gTV0Cw15xI9sR4wJThYMhn9cA4hFbxmgh=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNgYeuWG7OZZtpIYaanKvb-NepuddQImhJszHMka3gfnRIsevD3YXngaZj9_uWVliFmtRC_VV60VpMxlhlyUr6j3YrXIsYDNuq2F9gexjRrJKv1lUuuWcrEphpyW-ez8H6cRJxp-8Q9FpzP=k-no"],"When":"10 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2taWlQwdFNSMlpTZUdkTVEwaHVjemg2TTJsbGVVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107872866683270955531/reviews?hl=en-GB","posted_at_unix_micros":1761424574874312,"updated_at_unix_micros":1761424574874312,"language":"en","translated_lang":"","text_original":"One of the best workouts I’ve ever had! Highly recommend trying it out!","text_translated":"","reply_text_original":"Hey Andrew, \n\nReally appreciate you taking the time to check us out and even take pictures! Hopefully see you in the studio soon! ","reply_language":"en","reply_posted_at_unix_micros":1765387238000000,"reply_updated_at_unix_micros":1765387238000000,"published_at":"2025-10-25T20:36:14.874312Z"},{"Name":"Graziana Finocchiaro","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWsc0ennwIDll08D8PTR5HgFaH__g_O6lwkZAC-kU4YEv2Phqm8SQ=s120-c-rp-mo-br100","Rating":5,"Description":"Friendly, enthusiastic, energetic PTs welcoming you like you have always been a member! Love the gym and the people, classes are amazing! I'm enjoying the trial of 10 classes in 15 days, loved every bit so far :) Highly recommended!","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xsQlptMUtZMng2WVVoM2VXcFRkVGcwZGs0dE5FRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108869913771296722478/reviews?hl=en-GB","posted_at_unix_micros":1769037465988771,"updated_at_unix_micros":1769037465988771,"language":"en","translated_lang":"","text_original":"Friendly, enthusiastic, energetic PTs welcoming you like you have always been a member! Love the gym and the people, classes are amazing! I'm enjoying the trial of 10 classes in 15 days, loved every bit so far :) Highly recommended!","text_translated":"","reply_text_original":"Hi Graziana, thanks for your review! We’re so glad you are enjoying your trial and felt the energy of the studio 🙌\nYou smashed the sessions, and we’d absolutely love to keep training with you at F45 Oxford Circus!","reply_language":"en","reply_posted_at_unix_micros":1769078334000000,"reply_updated_at_unix_micros":1769078334000000,"published_at":"2026-01-21T23:17:45.988771Z"}]</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>13</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/The+Circle+Gym+and+Spa/data=!4m7!3m6!1s0x4876034663ee4565:0xe9af9e976fa48d7a!8m2!3d51.5015107!4d-0.0745931!16s%2Fg%2F1tgw9crn!19sChIJZUXuY0YDdkgReo2kb5eer-k</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>The Circle Gym and Spa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Queen Elizabeth St, London SE1 2JE, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:30 am–10 pm"],"Monday":["6:30 am–10 pm"],"Saturday":["8 am–8 pm"],"Sunday":["8 am–8 pm"],"Thursday":["6:30 am–10 pm"],"Tuesday":["6:30 am–10 pm"],"Wednesday":["6:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>http://www.thecirclegymandspa.co.uk/</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>+44 20 7378 7112</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>GW2G+J5 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>619</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>{"1":43,"2":10,"3":8,"4":25,"5":533}</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>51.501511</v>
+      </c>
+      <c r="R69" t="n">
+        <v>-0.07459300000000001</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>16838851905011879290</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmU_cdC7oS-8QUjITwMt5zQSHZo86hR25cOA6UXTxvEps48mUMaATH8kVS2_0y_QWr97sg61O2SwQlvcZ22MsTuUOgKpTNmOWvYcY4zXWPFiswCm92fNTjwh3z4e3oQjqaMNRvj=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>0x4876034663ee4565:0xe9af9e976fa48d7a</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>ChIJZUXuY0YDdkgReo2kb5eer-k</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>{"id":"112013932763218526132","name":"The Circle Gym and Spa (Owner)","link":"https://www.google.com/maps/contrib/112013932763218526132"}</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Queen Elizabeth St","city":"London","postal_code":"SE1 2JE","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>[{"Name":"Eleana Kyriacou","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIIqY-b22lQTCpxzdVTmCfb34ink8QqWuHl62ClehBJMBIY=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"If you want a gym where you actually look forward to going, one with positive vibes, amazing people, and an atmosphere that genuinely makes you want to exercise, plus the bonus of a pool, spa, and brilliant classes, then this is your spot! Don’t even think twice about it.\n\nI’ve been a member for over three years now. As someone who has tried many gyms in the past but always ended up quitting because I felt unmotivated, this place truly feels like home. The trainers and staff are fantastic and support you every step of the way. I cannot recommend this place more!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tjMlpGOTFURWRRVVZkd05GaE9URlV5VUZaVmFtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118229794238825548431/reviews?hl=en-GB","posted_at_unix_micros":1783364122329843,"updated_at_unix_micros":1783364122329843,"language":"en","translated_lang":"","text_original":"If you want a gym where you actually look forward to going, one with positive vibes, amazing people, and an atmosphere that genuinely makes you want to exercise, plus the bonus of a pool, spa, and brilliant classes, then this is your spot! Don’t even think twice about it.\n\nI’ve been a member for over three years now. As someone who has tried many gyms in the past but always ended up quitting because I felt unmotivated, this place truly feels like home. The trainers and staff are fantastic and support you every step of the way. I cannot recommend this place more!","text_translated":"","reply_text_original":"Thank you for your recommendation Eleana! We cannot thank you enough:) Your words truly made our day! ","reply_language":"en","reply_posted_at_unix_micros":1786123027000000,"reply_updated_at_unix_micros":1786123027000000,"published_at":"2026-07-06T18:55:22.329843Z"},{"Name":"Daisy","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUdutx62133TW9yzVkfLUhgCpFFy8L12QQkRy31cCnQnGbY_ynO=s120-c-rp-mo-br100","Rating":5,"Description":"Honestly such a great gym, the facilities are top notch. Loads of equipment so you’re never waiting, brilliant classes, and the sauna is fab. Everything is always spotless and well looked after too. Really friendly atmosphere on top of it all. 10/10 would recommend!​​​​​​​​​​​​​​​​","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT20weFFqTnNUMlp3YVVoRGVXVnhSbXB6UmxoVVVHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113287755066367183411/reviews?hl=en-GB","posted_at_unix_micros":1777106840603418,"updated_at_unix_micros":1777106840603418,"language":"en","translated_lang":"","text_original":"Honestly such a great gym, the facilities are top notch. Loads of equipment so you’re never waiting, brilliant classes, and the sauna is fab. Everything is always spotless and well looked after too. Really friendly atmosphere on top of it all. 10/10 would recommend!​​​​​​​​​​​​​​​​","text_translated":"","reply_text_original":"Another amazing 5-star review! Thank you so much Daisy! ","reply_language":"en","reply_posted_at_unix_micros":1779900477000000,"reply_updated_at_unix_micros":1779900477000000,"published_at":"2026-04-25T08:47:20.603418Z"},{"Name":"Scott Taylor","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLjk3gN6-pidYx2rkFSGONYXgvBWTLQkFgiMg5Vo7UsPVbYEQ=s120-c-rp-mo-br100","Rating":5,"Description":"I came here after a stressful morning and purchased a day pass. I knew of The Circle having seen it in the grand, shiny, purple bricked circle as a child when passing, I never did know what it was and that there was a spa! I was greeted at reception by a very personable young man called Oliver, he was very accommodating as I had a very stressful morning and he dealt with me very well. Very accommodating! Very thorough showing of the facilities. I loved when I came that the steam room had some eucalyptus in there, at least when I went!\n\nFacilities are great, they have an uber cool infra-red room. The pool wasn’t too cold either which was great. There classes are also insane! Very much worth the day pass for my time in the area. Will be back\n\nSpecial mention to Oliver who really went out of his way for a good customer experience","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25WTWJHSmZhbk5pZUV4a1VtbHBUVWhpV1UxNWEzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107199081209088152207/reviews?hl=en-GB","posted_at_unix_micros":1772451976396265,"updated_at_unix_micros":1772451976396265,"language":"en","translated_lang":"","text_original":"I came here after a stressful morning and purchased a day pass. I knew of The Circle having seen it in the grand, shiny, purple bricked circle as a child when passing, I never did know what it was and that there was a spa! I was greeted at reception by a very personable young man called Oliver, he was very accommodating as I had a very stressful morning and he dealt with me very well. Very accommodating! Very thorough showing of the facilities. I loved when I came that the steam room had some eucalyptus in there, at least when I went!\n\nFacilities are great, they have an uber cool infra-red room. The pool wasn’t too cold either which was great. There classes are also insane! Very much worth the day pass for my time in the area. Will be back\n\nSpecial mention to Oliver who really went out of his way for a good customer experience","text_translated":"","reply_text_original":"Thank you so much for your 5-star review! We truly appreciate your support and are delighted to hear you had a positive experience with us:) We look forward to welcoming you again and again!","reply_language":"en","reply_posted_at_unix_micros":1774529386000000,"reply_updated_at_unix_micros":1774529386000000,"published_at":"2026-03-02T11:46:16.396265Z"},{"Name":"Aries","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJcibuCfP4EHFjKjO0TSJv72BLDEBf63sAUS8Mx9k_m-_2ZKA=s120-c-rp-mo-br100","Rating":2,"Description":"While I love the instructors and updated gym equipment, it’s an extremely expensive membership for ZERO amenities. Ladies, they don’t even have tampons, face wash, quality toiletries, or anything we might need in case of an emergency. The changing rooms are always damp and musty to top it all off.\n\nIt’s hard to justify the cost of this membership when I could go to gyms such as Fitness First for a tad cheaper with the luxury amenities that match the premium price.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tKc2JYUnlTaTFvVlhGbE5VOXBVRFJ0VkhoQk5YYxAB","source":"Google","rating_scale":5,"rating_float":2,"author_url":"https://www.google.com/maps/contrib/114421676219187099620/reviews?hl=en-GB","posted_at_unix_micros":1780566734842125,"updated_at_unix_micros":1780566734842125,"language":"en","translated_lang":"","text_original":"While I love the instructors and updated gym equipment, it’s an extremely expensive membership for ZERO amenities. Ladies, they don’t even have tampons, face wash, quality toiletries, or anything we might need in case of an emergency. The changing rooms are always damp and musty to top it all off.\n\nIt’s hard to justify the cost of this membership when I could go to gyms such as Fitness First for a tad cheaper with the luxury amenities that match the premium price.","text_translated":"","reply_text_original":"Thank you for taking your time to share your feedback, sadly we must say we were unable to identify you as a current or previous member of The Circle Gym and Spa. We strongly believe it is important that reviews are actually made by genuine members. We are very surprised to hear we have 'zero amenities'! All our members can enjoy fully equipped gym, free group classes, heated swimming pool, jacuzzi and a beautiful spa area with traditional sauna, infrared sauna and steam room, all this for an affordable price. Memberships at our club are a great value for money:) Have a lovely day!","reply_language":"en","reply_posted_at_unix_micros":1786124195000000,"reply_updated_at_unix_micros":1786124195000000,"published_at":"2026-06-04T09:52:14.842125Z"},{"Name":"Sheetal Gandhi","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJpJ8VfuffY9dZMquo7eTp6wL6qwWwCrgTgbsS_9-wKa0BJow=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"A hidden gem in central London! I have my swimming lessons here and the pool, jacuzzi, and sauna and steam rooms are always super clean and well maintened. The staff are always lovely to speak to and are extremely accommodating. Highly recommend!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT201cVdURXpORll6WmxJMFR6UmZja3BwUVhCdGVVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100404633024452285227/reviews?hl=en-GB","posted_at_unix_micros":1779543563277374,"updated_at_unix_micros":1779543735127332,"language":"en","translated_lang":"","text_original":"A hidden gem in central London! I have my swimming lessons here and the pool, jacuzzi, and sauna and steam rooms are always super clean and well maintened. The staff are always lovely to speak to and are extremely accommodating. Highly recommend!","text_translated":"","reply_text_original":"Thank you Sheetal:) please keep enjoying the facilities and getting better and better at swimming! We're always happy to help if you need anything!","reply_language":"en","reply_posted_at_unix_micros":1779901421000000,"reply_updated_at_unix_micros":1779901421000000,"published_at":"2026-05-23T13:39:23.277374Z"}]</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Third+Space+Moorgate/data=!4m7!3m6!1s0x48761da7362970ef:0xdc146eb324238f10!8m2!3d51.518958!4d-0.0872695!16s%2Fg%2F11pvwwh7pb!19sChIJ73ApNqcddkgREI8jJLNuFNw</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Third Space Moorgate</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>16 South Pl, London EC2M 2AQ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["8 am–8 pm"],"Sunday":["8 am–8 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thirdspace.london/clubs/moorgate/</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>+44 20 7970 0930</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>GW97+H3 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>483</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>{"1":31,"2":21,"3":9,"4":16,"5":406}</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>51.518958</v>
+      </c>
+      <c r="R70" t="n">
+        <v>-0.087269</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>15858421903562870544</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk7Fgjq_4yPiNId7Lm23-lJZjdYq9sQM2gs0dEMS1_U6JJ95YfeKnfw8iMBj7TfYsy-ru7PMvkMyCL1jxikFeRQPN69YZdHfBS9lcvCFMHNrOIc4hwwMI8IYGvtirPOBplenb_V=w408-h510-k-no</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>0x48761da7362970ef:0xdc146eb324238f10</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>ChIJ73ApNqcddkgREI8jJLNuFNw</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>{"id":"104394580228400076833","name":"Third Space Moorgate (Owner)","link":"https://www.google.com/maps/contrib/104394580228400076833"}</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"16 South Pl","city":"London","postal_code":"EC2M 2AQ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible seating","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>[{"Name":"Ish","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXroVRKZ6LXsIn4sQhTk7MJDELVzMaaAqTmzFWiS19RCEcVUg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My first visit to Third Space Moorgate was fantastic from start to finish. Amanda from the concierge team welcomed me and was incredibly thorough and kind, taking the time to walk me through all the facilities and patiently answer every question I had. It made such a difference to feel so well looked after right from the beginning.\n\nI also took a Pilates class with Kerry, and she was absolutely amazing. She’s attentive, knowledgeable, and communicates so clearly. You can really tell she cares about what she does, and it shows in the way she guides the class. I’m already looking forward to booking another session with her.\n\nOverall, the facilities are excellent, always clean and well maintained. The cleaning staff clearly work hard and are consistently friendly and on top of everything. I’ve had a great experience at this branch and couldn’t be happier with how it’s been so far","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMaWgbqtwhCQzaStSVUFHpzto3H-F4nSBQU2fcREwSJGnG9e-7wn2-oqy2FFP7RoC4ksRoBBpqr5ZvuK4NYQ9DV3lwOXnjK_3F-v6PiP2ALgb1d8VqXLIXS8bsFrQGGc9Oa68eRqH06zi_E=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmN8QKnFmuUdtXRSmTEDS36FygE9rwW6MctKhy4vChv1xU9KYYhzWqArBvY9YDyT157i7VJWgQTNJjp0uDWzmlOVDpCMzS3HhGi1MiRC04FbcwG1RZTJZOEiDImoMwnbIcFQRPUiBH4phriI=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT20wNFZuWlRaM053WnpZd2RtRjFZMk16V0U1SllVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106709940042071529101/reviews?hl=en-GB","posted_at_unix_micros":1772136549414815,"updated_at_unix_micros":1772136549414815,"language":"en","translated_lang":"","text_original":"My first visit to Third Space Moorgate was fantastic from start to finish. Amanda from the concierge team welcomed me and was incredibly thorough and kind, taking the time to walk me through all the facilities and patiently answer every question I had. It made such a difference to feel so well looked after right from the beginning.\n\nI also took a Pilates class with Kerry, and she was absolutely amazing. She’s attentive, knowledgeable, and communicates so clearly. You can really tell she cares about what she does, and it shows in the way she guides the class. I’m already looking forward to booking another session with her.\n\nOverall, the facilities are excellent, always clean and well maintained. The cleaning staff clearly work hard and are consistently friendly and on top of everything. I’ve had a great experience at this branch and couldn’t be happier with how it’s been so far","text_translated":"","published_at":"2026-02-26T20:09:09.414815Z"},{"Name":"Soulla","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIFOhBPeiDvRVxnJ5y7gKekOPFXMI3b3tgpQepvG-jmbuSIfg=s120-c-rp-mo-br100","Rating":5,"Description":"Moorgate Third Space gym is a niche member of the group hence its appeal as it is not as overcrowded as some of the other member clubs I visited catering  primarily but not exclusively, because of its location, for a corporate clientele (so being less busy during corporate working hours but busier in the morning lunch hour and evening)\n\nThe concierge with its staff are all friendly and informative.\n\nThe facilities are all top notch (high calibre gym equipment  split on two levels)\nI particularly enjoy the cross trainer and step machine area, which are tucked in a quieter corner of the gym on the second level so you can work out in peace without the constant pound of blaring music and clunking weights and machinery which is a feature in some gyms.\n\nThe club is spotless) with an amazing changing room, which is constantly being cleaned as is the rest of the club, featuring high powered showers, an excellent sauna and top notch toiletries.\n\nThe club offers an array of classes lead by quality instructors.\n\nI am in constant spa gym heaven when I visit and always leave refreshed looking forward to my next visit.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tacFdGbFNVa3RxT1hCbVQwVjZTMU56VG1sQmNXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116756045684388746580/reviews?hl=en-GB","posted_at_unix_micros":1783143883558455,"updated_at_unix_micros":1783143883558455,"language":"en","translated_lang":"","text_original":"Moorgate Third Space gym is a niche member of the group hence its appeal as it is not as overcrowded as some of the other member clubs I visited catering  primarily but not exclusively, because of its location, for a corporate clientele (so being less busy during corporate working hours but busier in the morning lunch hour and evening)\n\nThe concierge with its staff are all friendly and informative.\n\nThe facilities are all top notch (high calibre gym equipment  split on two levels)\nI particularly enjoy the cross trainer and step machine area, which are tucked in a quieter corner of the gym on the second level so you can work out in peace without the constant pound of blaring music and clunking weights and machinery which is a feature in some gyms.\n\nThe club is spotless) with an amazing changing room, which is constantly being cleaned as is the rest of the club, featuring high powered showers, an excellent sauna and top notch toiletries.\n\nThe club offers an array of classes lead by quality instructors.\n\nI am in constant spa gym heaven when I visit and always leave refreshed looking forward to my next visit.","text_translated":"","published_at":"2026-07-04T05:44:43.558455Z"},{"Name":"Samuel Jackson","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ720tRbJEvKyo_px5pSnAL9aauHM6Ysu1p_fzWxWSAZ5pw6-w=s120-c-rp-mo-br100","Rating":5,"Description":"Third Space Moorgate is one of the best gyms I've been to. Amanda on the concierge team deserves a special mention. She remembers your name, always has a smile ready, and that kind of warmth sets the tone for your whole session.\n\nThe facilities are incredible, immaculate equipment, lovely studios and a great sauna. The kickboxing setup is great, a proper dedicated space that allows me to focus on my training. It's the kind of thing you don't expect to find and then can't imagine training without.\n\nEasily one of the best gyms in the city.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2w5SFJGWkJNbFk0YnpSbGRGcE1iMnRWVXkxS1prRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103778439293238572747/reviews?hl=en-GB","posted_at_unix_micros":1781524621354264,"updated_at_unix_micros":1781524621354264,"language":"en","translated_lang":"","text_original":"Third Space Moorgate is one of the best gyms I've been to. Amanda on the concierge team deserves a special mention. She remembers your name, always has a smile ready, and that kind of warmth sets the tone for your whole session.\n\nThe facilities are incredible, immaculate equipment, lovely studios and a great sauna. The kickboxing setup is great, a proper dedicated space that allows me to focus on my training. It's the kind of thing you don't expect to find and then can't imagine training without.\n\nEasily one of the best gyms in the city.","text_translated":"","published_at":"2026-06-15T11:57:01.354264Z"},{"Name":"Holly May","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU6ZDHQy3nHWmJcykrjo7qefiCsFrNzBVC4GusTueCqsuLGlO1p=s120-c-rp-mo-br100","Rating":5,"Description":"I have been attending Third Space Moorgate for a while now and have had the most wonderful time there. The Staff and Team are amazing and some of the most lovely people. The equipment, amenities, classes and layout is superb! 10/10 Club!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOP-qN4o74zmICciQzHtZWUPC-0jehKtbIntABmBjlZJCvru7ryP1b_6PyQPVRT04Z2p6xQBEI_xm4ewZzbcny_iIUYUzrS3Vfctrd3JhkKIy2hNlgAO6T4OWaexYvK8W_nUkOF5ic9kW4=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPUnITeKFEG8EqvaiTteRYU1F9-96jpR0AC6vVBdyWhN7R_OgTgabB-1MkB_4rNf_CgY5RwbGCeNFZ4wAxz12HgsTRTab6a6amcfJpVbTvCZAuCEndsEj4kD-hDqznkjep6I5YG5zT0khE=k-no"],"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21kcWQzWmpSa2hET0dwNVZYbFlRV0ZhVVRaMWJrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112651417412350353020/reviews?hl=en-GB","posted_at_unix_micros":1783002434753243,"updated_at_unix_micros":1783002434753243,"language":"en","translated_lang":"","text_original":"I have been attending Third Space Moorgate for a while now and have had the most wonderful time there. The Staff and Team are amazing and some of the most lovely people. The equipment, amenities, classes and layout is superb! 10/10 Club!","text_translated":"","published_at":"2026-07-02T14:27:14.753243Z"},{"Name":"London FoodieExpat","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWCR2QrPsClFJWEbulfjj3FqqInm8b7puGlHNY1cnd4-R-A5MM=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Third Space Soho is my favourite Third Space ever! I think the combat here is the best and not too crowded! Jack, my kickboxing teacher, is such a good vibe. He is so knowledgeable and very detailed!\n\nI also like the crowd at Moorgate. People respect personal space, quite sensible, but also very friendly. It is not cheap but if you do combat it is worth it!! Highly recommend Jack Butler’s Kickboxing class.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmN-_2CSENjj414NBfyFLsZ-9Sdi18gaze18YR3GnUbQ3G9AnDlxSj0GMRXwdChWg9vfR2Y7p_-u6_7wRMH873o5KtpH2ahk7wWLedT6Us_7B5Gp5SwkyeBHA5YA4gf83FMWrVpaITsrUFQ=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2w5aVNWOWlVSFo1TjJSTVZtUXhlbVpwWjBWUmJHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117103858160012090784/reviews?hl=en-GB","posted_at_unix_micros":1772476248769226,"updated_at_unix_micros":1772476248769226,"language":"en","translated_lang":"","text_original":"Third Space Soho is my favourite Third Space ever! I think the combat here is the best and not too crowded! Jack, my kickboxing teacher, is such a good vibe. He is so knowledgeable and very detailed!\n\nI also like the crowd at Moorgate. People respect personal space, quite sensible, but also very friendly. It is not cheap but if you do combat it is worth it!! Highly recommend Jack Butler’s Kickboxing class.","text_translated":"","published_at":"2026-03-02T18:30:48.769226Z"}]</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>13</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/HIIT+West+Hampstead/data=!4m7!3m6!1s0x4876107829b47e15:0x38a0190b23dd0edd!8m2!3d51.5465027!4d-0.1906203!16s%2Fg%2F11b682nv1y!19sChIJFX60KXgQdkgR3Q7dIwsZoDg</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>HIIT West Hampstead</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>198a Broadhurst Gardens, London NW6 3AY, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:30 am–8:30 pm"],"Monday":["6:30 am–8:30 pm"],"Saturday":["8 am–12 pm"],"Sunday":["8 am–12 pm","5–7 pm"],"Thursday":["6:30 am–8:30 pm"],"Tuesday":["6:30 am–8:30 pm"],"Wednesday":["6:30 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hiitgyms.com/</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>+44 7440 187893</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>GRW5+JQ London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>457</v>
+      </c>
+      <c r="O71" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>{"1":6,"2":2,"3":5,"4":17,"5":427}</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>51.546503</v>
+      </c>
+      <c r="R71" t="n">
+        <v>-0.19062</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>4080288798034693853</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Brick-walled gym for interval training</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Unassuming gym with brick walls &amp; open beams, specializing in high-intensity interval training.</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkQbJ2RX3ysSbJkmwk4wyIvydKOW5V29-drjNDDh-4zMEz-9q4DohmCvBl_rb_P45_gz97sqOf36fILpPg0LqWC6EvriFZz04PzVO6_yhS8-_DncVoiTQpaBy9X7OhhtrNlktkV=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>0x4876107829b47e15:0x38a0190b23dd0edd</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>ChIJFX60KXgQdkgR3Q7dIwsZoDg</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.hiitgyms.com/kickstart","source":"hiitgyms.com"}]</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>{"id":"101550426758339504508","name":"HIIT West Hampstead (Owner)","link":"https://www.google.com/maps/contrib/101550426758339504508"}</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"198a Broadhurst Gardens","city":"London","postal_code":"NW6 3AY","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>[{"Name":"Rahul Mohindra","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLiZ2yOlWvvVF53LOZpmK7fI95URq9ihuJ9Vc6638z9y2rKVg=s120-c-rp-mo-br100","Rating":5,"Description":"Great, well equipped gymnasium with top class coaching. I was made to feel very welcome by the team.\n\nThe workouts are intense, but enjoyable. In just 45mins you feel like you’ve covered all bases. Great for people leading busy lifestyles, but looking to stay fit!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tGWUxXaDBRemRZTWxoaGNXWm9hM0pYZEhSWVdYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110132473287008386021/reviews?hl=en-GB","posted_at_unix_micros":1778680051554134,"updated_at_unix_micros":1778680051554134,"language":"en","translated_lang":"","text_original":"Great, well equipped gymnasium with top class coaching. I was made to feel very welcome by the team.\n\nThe workouts are intense, but enjoyable. In just 45mins you feel like you’ve covered all bases. Great for people leading busy lifestyles, but looking to stay fit!","text_translated":"","reply_text_original":"Thank you so much for the amazing review! We’re thrilled you felt welcomed by the team and enjoyed the coaching. Our goal is to provide intense, effective 45-minute workouts that help busy people stay fit, strong, and healthy. We truly appreciate your support and look forward to seeing you again at the gym!","reply_language":"en","reply_posted_at_unix_micros":1778754064000000,"reply_updated_at_unix_micros":1778754064000000,"published_at":"2026-05-13T13:47:31.554134Z"},{"Name":"Daisy Knight","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWUntWbVKr6qs6T51IEGeDSQHp-dj09MgSWG-G14mBVWi9WXnMC=s120-c-rp-mo-br100","Rating":5,"Description":"I was looking for a high intensity, high cardio and a ‘sweat until you break’ class - HIIT’s Energy class did that, and the coach Molly was brilliant. Come to this club if you want an easy, no frills, no nonsense experience where you dive straight into the workout. It’s missing one star only because classes are 45 mins and I wanted to keep going!","Images":null,"When":"Edited 4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tsT1VFcFRSM1l6VkU1TFFuRldVa00xTjI1TVRuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107329223411176295596/reviews?hl=en-GB","posted_at_unix_micros":1777119648498431,"updated_at_unix_micros":1777466321864018,"language":"en","translated_lang":"","text_original":"I was looking for a high intensity, high cardio and a ‘sweat until you break’ class - HIIT’s Energy class did that, and the coach Molly was brilliant. Come to this club if you want an easy, no frills, no nonsense experience where you dive straight into the workout. It’s missing one star only because classes are 45 mins and I wanted to keep going!","text_translated":"","reply_text_original":"Thank you for the amazing feedback! We’re so glad you loved the high-intensity Energy class and that Coach Molly delivered a powerful, no-nonsense workout experience. We hear you on the 45-minute sessions, sometimes you just don’t want to stop! We hope to see you back for more sweat-worthy HIIT classes very soon.","reply_language":"en","reply_posted_at_unix_micros":1777282435000000,"reply_updated_at_unix_micros":1777282435000000,"published_at":"2026-04-25T12:20:48.498431Z"},{"Name":"Nessd","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW1Fo6UyIy1-V4FILWsLd_U8B8PT62rpm44ITy2IsKCnXDx0nwYqQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I love this studio ! It has all the equipment you need, and the sessions are really intense, you definitely work up a sweat. Workout are interesting and challenging, the coaches are very motivating, and the overall atmosphere is great. The space is clean, you can book on Classpass, just in front on West Hampstead station, so I would definitely recommend it!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tWVVRtaGZibU5TV0U1bmNrVTVTVGN3VEhCRk9FRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107750979251337328107/reviews?hl=en-GB","posted_at_unix_micros":1773316723698818,"updated_at_unix_micros":1773319978096968,"language":"en","translated_lang":"","text_original":"I love this studio ! It has all the equipment you need, and the sessions are really intense, you definitely work up a sweat. Workout are interesting and challenging, the coaches are very motivating, and the overall atmosphere is great. The space is clean, you can book on Classpass, just in front on West Hampstead station, so I would definitely recommend it!","text_translated":"","reply_text_original":"Thank you so much for your kind words! We’re thrilled you enjoy our West Hampstead studio, challenging workouts, and motivating coaches. Keeping our space clean and accessible for ClassPass users is always a priority. We can’t wait to see you back for another sweat session!","reply_language":"en","reply_posted_at_unix_micros":1773833346000000,"reply_updated_at_unix_micros":1773833346000000,"published_at":"2026-03-12T11:58:43.698818Z"},{"Name":"Talisa Wilmot","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK5uVcKoQ4Nh5XzM5R3GbI9Iftp3twd0tDMFLID8SZP1Zs8og=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been coming to this gym for years and a big reason I’ve stayed so consistent is the trainers. They make a real effort to get to know the members, which makes a huge difference.\nThey’ve been incredibly supportive and have helped me transform my strength over time!\n\nThe atmosphere is always welcoming and motivating, which makes it easy to keep showing up, I can't imagine being a member anywhere else.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pGYWNHYzFSelpDTjFjeFVFUlJOR1JVWW5BelEyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108396238110226166431/reviews?hl=en-GB","posted_at_unix_micros":1773165252450098,"updated_at_unix_micros":1773165252450098,"language":"en","translated_lang":"","text_original":"I’ve been coming to this gym for years and a big reason I’ve stayed so consistent is the trainers. They make a real effort to get to know the members, which makes a huge difference.\nThey’ve been incredibly supportive and have helped me transform my strength over time!\n\nThe atmosphere is always welcoming and motivating, which makes it easy to keep showing up, I can't imagine being a member anywhere else.","text_translated":"","reply_text_original":"Thank you so much for your kind words! We’re thrilled to hear that our trainers and welcoming atmosphere have helped you stay consistent and build your strength over the years. Creating a supportive, motivating gym community is exactly what we aim for, and it means a lot to know you feel at home here. We’re grateful to have you as part of our fitness family and look forward to continuing to support your strength and fitness journey!","reply_language":"en","reply_posted_at_unix_micros":1773228129000000,"reply_updated_at_unix_micros":1773228129000000,"published_at":"2026-03-10T17:54:12.450098Z"},{"Name":"Benjamin Cientanni","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ47dlW1jaTIXHWtmfpdxOp2VH8jAiW6kj-q2Vp8I2-ioKDXA=s120-c-rp-mo-br100","Rating":5,"Description":"If you’re someone like me who wants to get fit but can’t find motivation to spend time at the gym, then this place is for you. I started HIIT West Hampstead in January and have absolutely loved the experience. I’ve been doing 3 classes a week and am already seeing insane results with the way I look and feel. 35/45 minutes of hard work and you’re done. The workouts are challenging but also entertaining, with great variety. My favourite classes so far are HIIT power on a Friday with Raz, HIIT energy on a Saturday morning with Michael and HIIT circuits on a Sunday with Eva. Feeling stronger and healthier every day!","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pFMFVHdHVWVkpKY1hwR1FsbElPSFl4TTBaMWJVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112925252624457662763/reviews?hl=en-GB","posted_at_unix_micros":1770558017097458,"updated_at_unix_micros":1770558017097458,"language":"en","translated_lang":"","text_original":"If you’re someone like me who wants to get fit but can’t find motivation to spend time at the gym, then this place is for you. I started HIIT West Hampstead in January and have absolutely loved the experience. I’ve been doing 3 classes a week and am already seeing insane results with the way I look and feel. 35/45 minutes of hard work and you’re done. The workouts are challenging but also entertaining, with great variety. My favourite classes so far are HIIT power on a Friday with Raz, HIIT energy on a Saturday morning with Michael and HIIT circuits on a Sunday with Eva. Feeling stronger and healthier every day!","text_translated":"","reply_text_original":"Thank you so much for this amazing review! We’re thrilled you’re loving your experience at HIIT West Hampstead and already seeing incredible results after just a few weeks of training. Our 35–45 minute HIIT workouts are designed to be challenging, fun, and effective — so it’s fantastic to hear you’re feeling stronger and healthier every day. We’ll be sure to pass your kind words on to Raz, Michael, and Eva. See you in your next class!","reply_language":"en","reply_posted_at_unix_micros":1770982399000000,"reply_updated_at_unix_micros":1770982399000000,"published_at":"2026-02-08T13:40:17.097458Z"}]</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>13</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Anytime+Fitness/data=!4m7!3m6!1s0x48761d99ccaaf6f7:0x4eada6b64071ea4b!8m2!3d51.5404333!4d-0.0549544!16s%2Fg%2F11n8lf9_h8!19sChIJ9_aqzJkddkgRS-pxQLamrU4</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Anytime Fitness</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>8 Pemberton Pl, London E8 3RG, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>{"Friday":["Open 24 hours"],"Monday":["Open 24 hours"],"Saturday":["Open 24 hours"],"Sunday":["Open 24 hours"],"Thursday":["Open 24 hours"],"Tuesday":["Open 24 hours"],"Wednesday":["Open 24 hours"]}</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.anytimefitness.co.uk/gyms/uk-0433/london-fields-hackney-greater-london-e9-7qw/</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>+44 20 3903 9522</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>GWRW+52 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>424</v>
+      </c>
+      <c r="O72" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>{"1":4,"2":0,"3":6,"4":19,"5":395}</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>51.540433</v>
+      </c>
+      <c r="R72" t="n">
+        <v>-0.054954</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>5669370807624788555</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlGqjcBVkaxJNpF1IRCsDkB1lki8IQYqxQ5lZSUQ-it8rZRWWwNJhMcpgV07RiwuX2EEPIv17ILARUesG8ghc-5KnY991nL3aqNL0OYYNDe0EAXHSZ6ohir2iDAYSpdOEZlMa5S=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>0x48761d99ccaaf6f7:0x4eada6b64071ea4b</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>ChIJ9_aqzJkddkgRS-pxQLamrU4</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>[{"link":"https://secure13.clubwise.com/londonfields/enquiry.asp","source":"clubwise.com"}]</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>{"id":"108237689844035620012","name":"Anytime Fitness (Owner)","link":"https://www.google.com/maps/contrib/108237689844035620012"}</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"8 Pemberton Pl","city":"London","postal_code":"E8 3RG","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>[{"Name":"Lisa McCutcheon","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVVUFJgHrBFhY3J2vpF2cYOtIgRZ_iJ_Jjhi7k5TS2hl9m9NDdl=s120-c-rp-mo-br100","Rating":5,"Description":"Wonderful gym! This is my first time going to the gym and I was nervous at first but the atmosphere here is really great and staff are so welcoming and friendly, it's never too busy and always clean.\nThe personal changing rooms and showers are a huge plus!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25ReWFWbHhTMWg2YTFZNGVtZFJUbXcwTmsxYWFYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103700045987891385123/reviews?hl=en-GB","posted_at_unix_micros":1771874817969379,"updated_at_unix_micros":1771874817969379,"language":"en","translated_lang":"","text_original":"Wonderful gym! This is my first time going to the gym and I was nervous at first but the atmosphere here is really great and staff are so welcoming and friendly, it's never too busy and always clean.\nThe personal changing rooms and showers are a huge plus!","text_translated":"","reply_text_original":"Thank you for such a great and detailed review Lisa! I am so happy to hear that you were able to become less nervous because of our team and our lovely community! This is literally the most important thing to us! Please never hesitate to ask for help if we can ever be of assistance with your training! See you soon!","reply_language":"en","reply_posted_at_unix_micros":1771882571000000,"reply_updated_at_unix_micros":1771882571000000,"published_at":"2026-02-23T19:26:57.969379Z"},{"Name":"Gladys Tan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV6f5ymDT0b1hHYBmCL5NXa7X2KoVNw0_ZO-99qYzxtaur-ZEyf=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"After training at a dismal branch, I decided to heed my friend’s advice to try out this particular gym, and there were already raving reviews of this place. This gym was huge, clean and had all the machines I needed. There were proper sections for everything you need to do there — for exercise, washing up, and even just for waiting around. I appreciated the £1 coffee I could get afterwards as well. Kudos to the team for the amazing upkeep!","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21wNVRYZFJlbWxKZG1WRU1YWTJNemRoVFRGQ0xWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101562158173788913223/reviews?hl=en-GB","posted_at_unix_micros":1769104085394973,"updated_at_unix_micros":1769104085394973,"language":"en","translated_lang":"","text_original":"After training at a dismal branch, I decided to heed my friend’s advice to try out this particular gym, and there were already raving reviews of this place. This gym was huge, clean and had all the machines I needed. There were proper sections for everything you need to do there — for exercise, washing up, and even just for waiting around. I appreciated the £1 coffee I could get afterwards as well. Kudos to the team for the amazing upkeep!","text_translated":"","reply_text_original":"Thank you for taking the time to give such lovely feedback Gladys! it is unfortunate that you have had a less than positive experience at a different branch, but I am thrilled to hear that our gym has provided a great training experience for you. We cannot wait to welcome you again.","reply_language":"en","reply_posted_at_unix_micros":1769166820000000,"reply_updated_at_unix_micros":1769166820000000,"published_at":"2026-01-22T17:48:05.394973Z"},{"Name":"Jacob Adeyemi","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJtLLQv7TxYNDMqAgzYgi9Al2vv_ig7iRMkhGrI5fZWzuH6Aw=s120-c-rp-mo-br100","Rating":5,"Description":"This is an amazing gym, I’ve been going for a couple years great staff","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xNMk56SktNRE4yVW5NeVJUaG5aMVIzY0RsTWVHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114861217411652627641/reviews?hl=en-GB","posted_at_unix_micros":1784573396878111,"updated_at_unix_micros":1784573396878111,"language":"en","translated_lang":"","text_original":"This is an amazing gym, I’ve been going for a couple years great staff","text_translated":"","reply_text_original":"Thank you for taking the time to give us such great feedback! I'm so glad that the team has consistently looked after you for the years you've been with us! We promise to continue to do so","reply_language":"en","reply_posted_at_unix_micros":1784574633000000,"reply_updated_at_unix_micros":1784574633000000,"published_at":"2026-07-20T18:49:56.878111Z"},{"Name":"Jos Swanwick","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVQV_z7h6DuE30m1k-vLfENC2Wey77hYD_TeED4C_KTtbN0RRw=s120-c-rp-mo-br100","Rating":5,"Description":"Great gym, good equipment, has everything I need, not too busy","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2trMmMxQXdabEJLZFU1dlJqWldjVVpvYzBnd2QyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111858228398894107358/reviews?hl=en-GB","posted_at_unix_micros":1784653188156072,"updated_at_unix_micros":1784653188156072,"language":"en","translated_lang":"","text_original":"Great gym, good equipment, has everything I need, not too busy","text_translated":"","reply_text_original":"Thank you for such a great review Jos! So glad to hear that the gym is fully equipped for your training! See you in club soon!","reply_language":"en","reply_posted_at_unix_micros":1784654226000000,"reply_updated_at_unix_micros":1784654226000000,"published_at":"2026-07-21T16:59:48.156072Z"},{"Name":"Dana Button","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVsLM1jC9-AJ7vrG1xlC7wBM9cCCNsGW0ptQNNTybmPo2OJVwA=s120-c-rp-mo-br100","Rating":5,"Description":"Great gym. Got all the equipment you need. Great AC for hot days. 5/5","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2kxZlptUk1UelZQZWtkeFpuTTRiblo0UzNSTlYwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106352291550273700115/reviews?hl=en-GB","posted_at_unix_micros":1782556907276402,"updated_at_unix_micros":1782556907276402,"language":"en","translated_lang":"","text_original":"Great gym. Got all the equipment you need. Great AC for hot days. 5/5","text_translated":"","reply_text_original":"Thanks for the great review Dana! So glad to hear that we have everything you need and that we're able to keep you cool in the heatwave! See you in the gym soon!","reply_language":"en","reply_posted_at_unix_micros":1782567892000000,"reply_updated_at_unix_micros":1782567892000000,"published_at":"2026-06-27T10:41:47.276402Z"}]</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>13</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Psycle+Oxford+Circus/data=!4m7!3m6!1s0x48761ad5755586a9:0xb48c9259ff1ccd1e!8m2!3d51.5176409!4d-0.1423229!16s%2Fg%2F1ptxkdxyc!19sChIJqYZVddUadkgRHs0c_1mSjLQ</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Psycle Oxford Circus</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Indoor cycling</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>76 Mortimer St, London W1W 7SA, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:30 am–2 pm","3:45–8 pm"],"Monday":["6:10 am–2 pm","3:45–9 pm"],"Saturday":["7:30 am–4:30 pm"],"Sunday":["8:30 am–4:30 pm"],"Thursday":["6:10 am–2 pm","3:45–9 pm"],"Tuesday":["6:10 am–2 pm","3:45–9 pm"],"Wednesday":["6:10 am–2 pm","3:45–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>https://psyclelondon.com/pages/oxford-circus</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>+44 20 3150 2644</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>GV95+33 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>400</v>
+      </c>
+      <c r="O73" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>{"1":45,"2":20,"3":25,"4":42,"5":268}</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>51.517641</v>
+      </c>
+      <c r="R73" t="n">
+        <v>-0.142323</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>13009934338796342558</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnt8iIMLXIQfvagda2lNlevkIOFCJCnMdgwzZRRBMuZQfNrVXtmqrNPTiJY3Bm-X1LVDaW_sJx0TJcfWnk-aCxFzrr5TOeRoNvNvtheMxGL4CZ4Xu76AT7nPbmp-qWHrA1YFgAUWpL9h3T2=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>0x48761ad5755586a9:0xb48c9259ff1ccd1e</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>ChIJqYZVddUadkgRHs0c_1mSjLQ</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>{"id":"115785670874423540563","name":"Psycle Oxford Circus (Owner)","link":"https://www.google.com/maps/contrib/115785670874423540563"}</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"76 Mortimer St","city":"London","postal_code":"W1W 7SA","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>[{"Name":"Nabila T","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKkXOB6eaCfjh87Opw01TewA0MfQlM9yifLV4_KiuUYDJboTA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Has the best fitness classes in London with an amazing welcoming and community energy from the moment you enter, the locations are perfectly situated and so beautiful designed, the level of cleanliness is exceptional the facilities provided are fantastic every aspect is catered for from towels to premium toiletries to lockers even deodorant which something I always forget and am so grateful they provide, even gym wear and grippy socks you could pretty much turn up with nothing and they have everything you need to do a fitness class. Wow the instructors they are truly exceptional the attention to detail is phenomenal from the moment you enter the studio they greet each person are so welcoming and make a point of getting to know you, the class are fantastic they are tough, innovative, motivating, fun and really work I’ve only been a member for 4 months and can already see a difference in my body and wellbeing. I actually wish there were more hours in the day and days in the week just so I could do more classes the classes they offer from Barre to reform to infrared sculpt to strength to ride to yoga to lagree what a glorious selection. You can be a complete newbie to fitness or a fitness pro and they have classes for you. I am so grateful I was told about this place and want to say a big thank you to the front of house who are always so friendly welcoming and make it super easy to check in and a super big thank you a massive hug to the instructors Kate \u0026 Vinny for making every infrared sculpt so amazing as hard as it is working out in that heat you always keep me motivated and keep a huge smile on my face while my muscles are burning and I’m dripping with sweat, \u0026 Thank you Kate for making my first Lagree class less intimidating thanks to you I’ve been doing a Lagree class every week since to Beth who I did my very first class with and made me fall in love with Psycle London to Suze \u0026 Nancy for your fabulous reformer classes I feel more confident on those beds every time to Rod who has really helped me improve in Barre who has the best old school music and is hilarious which really helps when your shaking \u0026 burning thanks to Rod \u0026 Beth I’ve been able to try out Barre glide \u0026 sculpt with Josh who is fabulous, big thank you to Oliver Lee who has truly changed what I thought I new about lifting weights I never thought I would ever lift anything heavier then 3kg dumbbells and to think I’m lifting 10kg dumbbells in your class is mind blowing your technique is amazing and your positivity and grounding make such a difference and to Mark who I did my first ride class with I’d been doing spin classes at my previous gym and honestly never new a ride class could be so fun, entertaining and filled with such positive motivating energy and a big thank you to Luiz for your amazing Yoga classes. Big thank you to all at Psycle London you make fitness fun have designed classes that really work and locations that are a joy to come to and make you feel like your part of community with a real focus on loving who you are as you are Thank you","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25VMFRtOVlaMmN5T0RGc05VVnJhRFI1UW05M09IYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112010861871011074323/reviews?hl=en-GB","posted_at_unix_micros":1786178587015527,"updated_at_unix_micros":1786178587015527,"language":"en","translated_lang":"","text_original":"Has the best fitness classes in London with an amazing welcoming and community energy from the moment you enter, the locations are perfectly situated and so beautiful designed, the level of cleanliness is exceptional the facilities provided are fantastic every aspect is catered for from towels to premium toiletries to lockers even deodorant which something I always forget and am so grateful they provide, even gym wear and grippy socks you could pretty much turn up with nothing and they have everything you need to do a fitness class. Wow the instructors they are truly exceptional the attention to detail is phenomenal from the moment you enter the studio they greet each person are so welcoming and make a point of getting to know you, the class are fantastic they are tough, innovative, motivating, fun and really work I’ve only been a member for 4 months and can already see a difference in my body and wellbeing. I actually wish there were more hours in the day and days in the week just so I could do more classes the classes they offer from Barre to reform to infrared sculpt to strength to ride to yoga to lagree what a glorious selection. You can be a complete newbie to fitness or a fitness pro and they have classes for you. I am so grateful I was told about this place and want to say a big thank you to the front of house who are always so friendly welcoming and make it super easy to check in and a super big thank you a massive hug to the instructors Kate \u0026 Vinny for making every infrared sculpt so amazing as hard as it is working out in that heat you always keep me motivated and keep a huge smile on my face while my muscles are burning and I’m dripping with sweat, \u0026 Thank you Kate for making my first Lagree class less intimidating thanks to you I’ve been doing a Lagree class every week since to Beth who I did my very first class with and made me fall in love with Psycle London to Suze \u0026 Nancy for your fabulous reformer classes I feel more confident on those beds every time to Rod who has really helped me improve in Barre who has the best old school music and is hilarious which really helps when your shaking \u0026 burning thanks to Rod \u0026 Beth I’ve been able to try out Barre glide \u0026 sculpt with Josh who is fabulous, big thank you to Oliver Lee who has truly changed what I thought I new about lifting weights I never thought I would ever lift anything heavier then 3kg dumbbells and to think I’m lifting 10kg dumbbells in your class is mind blowing your technique is amazing and your positivity and grounding make such a difference and to Mark who I did my first ride class with I’d been doing spin classes at my previous gym and honestly never new a ride class could be so fun, entertaining and filled with such positive motivating energy and a big thank you to Luiz for your amazing Yoga classes. Big thank you to all at Psycle London you make fitness fun have designed classes that really work and locations that are a joy to come to and make you feel like your part of community with a real focus on loving who you are as you are Thank you","text_translated":"","reply_text_original":"Hi Nabila, \n\nThank you so much for taking the time to leave your review.\nThe feeling is very much mutual as we love having you as a member at Psycle and are so pleased that you are enjoying your experience in our studios so much! \n\nLooking forward to seeing you again soon.\nKindest regards, \nLyndsey \nGeneral Manager","reply_language":"en","reply_posted_at_unix_micros":1786534992000000,"reply_updated_at_unix_micros":1786534992000000,"published_at":"2026-08-08T08:43:07.015527Z"},{"Name":"Harrison","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX9ZqhihTMNOr2xojiReTRa7KlFMOOvuMJuaSQT4bZx4wZH-VaWBQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Just wanted to say a little thank you to Liv for her help today, who kindly offered to extend the expiry dates of my credits as a one-off / \"exceptional circumstances\" with a baby on the way. I am thankful for the gesture and it's one less thing to worry about. The customer service has always been great to be fair. Speaking more generally about the classes, I've been a member of Psycle over 18 months, mainly sticking to Ride classes. I found the classes to always really positive atmosphere, and from day one it was welcome change from previously having a militant style one-to-one PTs at the gyms. The intense cardo has helped with me lose weight, and and I enjoy switching myself off after work and being immersed in the class with no phone as a distraction. My go-to instructor is Queenie's Monday class - for me, it's a great way to start the week. I've also done a lot Rides with Ed and Eva's Throw Back Thursday classes were also great for the music.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT210amFFNXJVVlk0V0RoUk9HZ3pXbkZHUlZkUlRrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107366227503956756431/reviews?hl=en-GB","posted_at_unix_micros":1784551477109623,"updated_at_unix_micros":1784551477109623,"language":"en","translated_lang":"","text_original":"Just wanted to say a little thank you to Liv for her help today, who kindly offered to extend the expiry dates of my credits as a one-off / \"exceptional circumstances\" with a baby on the way. I am thankful for the gesture and it's one less thing to worry about. The customer service has always been great to be fair. Speaking more generally about the classes, I've been a member of Psycle over 18 months, mainly sticking to Ride classes. I found the classes to always really positive atmosphere, and from day one it was welcome change from previously having a militant style one-to-one PTs at the gyms. The intense cardo has helped with me lose weight, and and I enjoy switching myself off after work and being immersed in the class with no phone as a distraction. My go-to instructor is Queenie's Monday class - for me, it's a great way to start the week. I've also done a lot Rides with Ed and Eva's Throw Back Thursday classes were also great for the music.","text_translated":"","reply_text_original":"Hi Harrison, \n\nThank you so much for taking the time to leave your review. I'm so pleased to read that we were able to help out but also that you have had such great experiences at our studio. \n\nWe are looking forward to seeing you in the studio again soon and best of luck with the baby on the way!\n\nKindest regards, \nLyndsey \nGeneral Manager","reply_language":"en","reply_posted_at_unix_micros":1785157491000000,"reply_updated_at_unix_micros":1785157491000000,"published_at":"2026-07-20T12:44:37.109623Z"},{"Name":"Zoe Pol","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXKebD59X-JjjJXvIx1rwyMe08dPsQszqNpXZNFdizQv_qCgZ8=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I’ve been around many studios in London but Psycle somehow has the best instructors. They are all switched on, fun, professional and will drive you.\nRod 👑, Ben, Leagha and Jeison are amazing!!!\n\nTheir spaces are generally tidy, customer service via email in my experience is pretty bad, they also never pick up the phone but if you speak to the staff in person they are friendly and happy to help resolve any issues/ queries.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2sxNGVVMU9WamsxU0c5VFN6TlBOSE5rUWtRemVGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113716681504626327258/reviews?hl=en-GB","posted_at_unix_micros":1781040600184238,"updated_at_unix_micros":1781040643005066,"language":"en","translated_lang":"","text_original":"I’ve been around many studios in London but Psycle somehow has the best instructors. They are all switched on, fun, professional and will drive you.\nRod 👑, Ben, Leagha and Jeison are amazing!!!\n\nTheir spaces are generally tidy, customer service via email in my experience is pretty bad, they also never pick up the phone but if you speak to the staff in person they are friendly and happy to help resolve any issues/ queries.","text_translated":"","reply_text_original":"Hi Zoe, \n\nThank you so much for leaving your 5 star review! We really appreciate it your comments about our instructors and front of house team and will do our best to improve our email and telephone communication.\n\nThank you for the feedback.\nKind regards, \nLyndsey \nGeneral Manager","reply_language":"en","reply_posted_at_unix_micros":1783769031000000,"reply_updated_at_unix_micros":1783769031000000,"published_at":"2026-06-09T21:30:00.184238Z"},{"Name":"gel luciana","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWC7qVvIql3ai3408yP-aUF_L3NIgGJb_UzfFUWfMHztwKEyokY=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Joined this amazing community for a weekend and I loved being here so much xx wherever you turn your head you’ll see smiling faces, energetic people and super fun coaches. Go by the smoothie bar as well after your classes 😮‍💨 that Greenhouse smoothie is just the best recommendation!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT214M1JtVlBZbEUwY0ZWa2VHdDBiak5DZURSeVJVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100468597537138722465/reviews?hl=en-GB","posted_at_unix_micros":1783850248188945,"updated_at_unix_micros":1783850248188945,"language":"en","translated_lang":"","text_original":"Joined this amazing community for a weekend and I loved being here so much xx wherever you turn your head you’ll see smiling faces, energetic people and super fun coaches. Go by the smoothie bar as well after your classes 😮‍💨 that Greenhouse smoothie is just the best recommendation!","text_translated":"","reply_text_original":"Hi Gel, \n\nThank you so much for taking the time to leave your review! We loved meeting you for Psycle Worldwide weekend and hope that you have the opportunity to come and visit us again soon!! \n\nBest wishes, \nLyndsey \nGeneral Manager","reply_language":"en","reply_posted_at_unix_micros":1785157569000000,"reply_updated_at_unix_micros":1785157569000000,"published_at":"2026-07-12T09:57:28.188945Z"},{"Name":"Federica De Cillis","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXbhp6vWKcc2-YdqP8n0tKgJPKSD2hpmTvgUqQ1BrWsWPV9y2TG=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I’ve been a customer at Psycle since the early days, and what has kept me coming back is their incredible ability to evolve.\n\nFrom barre to reformer, and now newer concepts like infrared and mega reformer, they constantly introduce fresh ways to move while keeping the quality consistently high.\n\nThe teachers are truly exceptional and create an atmosphere that is both motivating and welcoming. Over the years, this studio has become much more than a place to work out for me. It’s where I’ve built a community and made real friendships.\n\nFrom the reception team to the level of cleanliness and care across the studio, everything is always thoughtful and professional. Psycle has genuinely become one of the happiest parts of my routine.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pKUlFrNXVVVjlEZVRNelNpMDNSVmN6VkdSd2FXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109046053703967317225/reviews?hl=en-GB","posted_at_unix_micros":1773259750846181,"updated_at_unix_micros":1773259750846181,"language":"en","translated_lang":"","text_original":"I’ve been a customer at Psycle since the early days, and what has kept me coming back is their incredible ability to evolve.\n\nFrom barre to reformer, and now newer concepts like infrared and mega reformer, they constantly introduce fresh ways to move while keeping the quality consistently high.\n\nThe teachers are truly exceptional and create an atmosphere that is both motivating and welcoming. Over the years, this studio has become much more than a place to work out for me. It’s where I’ve built a community and made real friendships.\n\nFrom the reception team to the level of cleanliness and care across the studio, everything is always thoughtful and professional. Psycle has genuinely become one of the happiest parts of my routine.","text_translated":"","reply_text_original":"Federica! Thank you so much for taking the time to leave us this review, it truly means a lot to us and we love having you as part of our community!\n\nLooking forward to seeing you in the studio again soon!\nLyndsey \nGeneral Manager","reply_language":"en","reply_posted_at_unix_micros":1773421169000000,"reply_updated_at_unix_micros":1773421169000000,"published_at":"2026-03-11T20:09:10.846181Z"}]</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/REGEN+LONDON/data=!4m7!3m6!1s0x487607d433852ddd:0x7ae8063d950694b7!8m2!3d51.4296967!4d-0.130138!16s%2Fg%2F11s6g9hvcn!19sChIJ3S2FM9QHdkgRt5QGlT0G6Ho</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>REGEN LONDON</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>121 Streatham High Rd, London SW16 1HJ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–11 pm"],"Monday":["6 am–11 pm"],"Saturday":["7 am–7 pm"],"Sunday":["7 am–7 pm"],"Thursday":["6 am–11 pm"],"Tuesday":["6 am–11 pm"],"Wednesday":["6 am–11 pm"]}</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>http://regen-london.com/</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>+44 20 8001 9037</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>CVH9+VW London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>396</v>
+      </c>
+      <c r="O74" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>{"1":5,"2":4,"3":5,"4":28,"5":354}</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>51.429697</v>
+      </c>
+      <c r="R74" t="n">
+        <v>-0.130138</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>8856335528787088567</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmHFkk3gxUQ9-D5BmHQuXyU6Knt-4UMACWROO_ew_hiCFsL_vl9DOe-q9MtenvIKTBheof5ADkcD3JmH9OxxkrPzgY-cF_DsNbtt14o95owd4xgPyfP4svipibR_6OY9VsQgIvcRQ=w408-h612-k-no</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>0x487607d433852ddd:0x7ae8063d950694b7</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>ChIJ3S2FM9QHdkgRt5QGlT0G6Ho</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>{"id":"103419778875311752933","name":"REGEN LONDON (Owner)","link":"https://www.google.com/maps/contrib/103419778875311752933"}</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"121 Streatham High Rd","city":"London","postal_code":"SW16 1HJ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible seating","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>[{"Name":"Marju Finnigan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU4OEUpjAQWXKnqu4BQKLnuMG1Kp12H5lnKaJ37yXxvWNkt1TU=s120-c-rp-mo-br100","Rating":5,"Description":"I've been a member of Regen for a couple of years, and I love it. The heavy, well-filled boxing punching bags were the main reason I joined, and they're still one of my favorite features. The gym also offers a great variety of classes, has friendly and helpful staff, and fosters a welcoming multicultural community. Highly recommended!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPTQcxth0Ny91YX0aJi7rvfUM0joknFzupZRcx1Lm0k1dqc-Vof8jNn2IZHrM_UP9VmC8iS32gvs61zdBfLj3GFjvmgcq1xCbIV-47IKyddbKjwz7zkz1_YvauAmAcNRl3M-fM86F5huSM3=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMXpaphc3-IjdDBgqC6ZnBxBWrciuLG2fhh7vwkRQLLzMh_tJWCJ9pj8ZS8HtpHkRWid-Nl471BOF0NYKGeWLLlotEFKPIYt8Oa72XVnxmgpS-24InpkEL1GZOjRtXUwWbKZ-p1tjxIfdA=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tsU2VHY3lSMkZ6Y0dJeVZWRjJWMkpVWWtadk5FRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115271621189226335502/reviews?hl=en-GB","posted_at_unix_micros":1780565065343665,"updated_at_unix_micros":1780565065343665,"language":"en","translated_lang":"","text_original":"I've been a member of Regen for a couple of years, and I love it. The heavy, well-filled boxing punching bags were the main reason I joined, and they're still one of my favorite features. The gym also offers a great variety of classes, has friendly and helpful staff, and fosters a welcoming multicultural community. Highly recommended!","text_translated":"","published_at":"2026-06-04T09:24:25.343665Z"},{"Name":"Emily Morgan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocL1_MbwYzzDyafuhuGTtMUZlSlbV2VnpXwSCnl7UPvohdpIoA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I recently rejoined after previously attending years ago back before the gym rebranded. The revamp is incredible; gym is way bigger with all the equipment you could want as a weight lifter and even in peak times it’s never too busy to get on the machine you want to use. I like that the cardio area (treadmills and elliptical machines) are in a separate area for privacy. Gym staff are super friendly, workout towels and massage guns are offered, and the overall atmosphere is relaxed. I’ve only been to one yoga class but I thoroughly enjoyed it. Only improvement I would suggest is better toilet facilities but it’s not a huge issue. Very reasonably priced for the amount of equipment, amenities (deodorant, women’s health products, dry shampoo etc) and overall quality of the gym.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21kT2MycExNMGRZYlc1UWQwTnBlVnBXTFU0MlJXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116369092442752582290/reviews?hl=en-GB","posted_at_unix_micros":1768394241920427,"updated_at_unix_micros":1768394241920427,"language":"en","translated_lang":"","text_original":"I recently rejoined after previously attending years ago back before the gym rebranded. The revamp is incredible; gym is way bigger with all the equipment you could want as a weight lifter and even in peak times it’s never too busy to get on the machine you want to use. I like that the cardio area (treadmills and elliptical machines) are in a separate area for privacy. Gym staff are super friendly, workout towels and massage guns are offered, and the overall atmosphere is relaxed. I’ve only been to one yoga class but I thoroughly enjoyed it. Only improvement I would suggest is better toilet facilities but it’s not a huge issue. Very reasonably priced for the amount of equipment, amenities (deodorant, women’s health products, dry shampoo etc) and overall quality of the gym.","text_translated":"","published_at":"2026-01-14T12:37:21.920427Z"},{"Name":"rekince","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUM7EtaNHXbaAbbIGJ82KF9SJyKRlz21Tu8pf9Kb7aKKMH_LMM=s120-c-rp-mo-br100","Rating":4,"Description":"Although the gym is not so spacious alongside the door/app no longer tracks gym capacity, it becomes an oven whenever its busy.\n\nThe AC is on the poorer side compared to other gyms around the area. Other than that it is a great place to train.\n\nCleanliness is no issue alongside the machines and the equipment selection is outstanding.\n\nplease resolve issues with the ac especially during summer and the door!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pSRGMyRjNRbUp1YTFjNGJYcEVlbDlWTjNkVWQxRRAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/110769143245742460812/reviews?hl=en-GB","posted_at_unix_micros":1782159428189534,"updated_at_unix_micros":1782159428189534,"language":"en","translated_lang":"","text_original":"Although the gym is not so spacious alongside the door/app no longer tracks gym capacity, it becomes an oven whenever its busy.\n\nThe AC is on the poorer side compared to other gyms around the area. Other than that it is a great place to train.\n\nCleanliness is no issue alongside the machines and the equipment selection is outstanding.\n\nplease resolve issues with the ac especially during summer and the door!","text_translated":"","published_at":"2026-06-22T20:17:08.189534Z"},{"Name":"Bradley Peake","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJG52CKfymPfgjOLIh9rZj-KH1kPGuOEvSOmi1bp4off68IEQ=s120-c-rp-mo-br100","Rating":5,"Description":"A superb gym for many different reasons. Great vibes, great people, friendly and enthusiastic staff. A huge plus are the punching bags available, and everyone is very respectful \u0026 focused, having some fun along the way. Highly recommend this gym!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s5UlN6Tm5lRlY1YURsWk5EWmtTVVpVTlZkRFpuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113487425465619220561/reviews?hl=en-GB","posted_at_unix_micros":1784637923293980,"updated_at_unix_micros":1784637923293980,"language":"en","translated_lang":"","text_original":"A superb gym for many different reasons. Great vibes, great people, friendly and enthusiastic staff. A huge plus are the punching bags available, and everyone is very respectful \u0026 focused, having some fun along the way. Highly recommend this gym!","text_translated":"","published_at":"2026-07-21T12:45:23.29398Z"},{"Name":"Charlie Edmondson","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLn-NZ5bjoir3u-IDuS3G5x3cuABrndBE57RFIU2EQWBkG-9w=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve just started the morning Pilates class at the gym and I’m honestly loving it! It’s such a good workout—definitely gives you that burn, but in a way that doesn’t feel too overwhelming. The instructor is great, super clear and easy to follow, which makes such a difference. I also really love that the classes are small, it makes it feel more personal and relaxed. Such a nice way to start the day—would 100% recommend!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25SdGJtNWhZMU15VXpGTWNrOVpjV3RYWDB4blJYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112447327089913839164/reviews?hl=en-GB","posted_at_unix_micros":1775549936370346,"updated_at_unix_micros":1775549936370346,"language":"en","translated_lang":"","text_original":"I’ve just started the morning Pilates class at the gym and I’m honestly loving it! It’s such a good workout—definitely gives you that burn, but in a way that doesn’t feel too overwhelming. The instructor is great, super clear and easy to follow, which makes such a difference. I also really love that the classes are small, it makes it feel more personal and relaxed. Such a nice way to start the day—would 100% recommend!","text_translated":"","published_at":"2026-04-07T08:18:56.370346Z"}]</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>13</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/ARETE+GYMS/data=!4m7!3m6!1s0x4876033598eba985:0xfce5b91ccf166d8f!8m2!3d51.5120448!4d-0.0689815!16s%2Fg%2F11bx78mlvw!19sChIJhanrmDUDdkgRj20Wzxy55fw</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ARETE GYMS</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sugar House, 75 Hooper St, London E1 8BP, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9 pm"],"Monday":["6 am–10 pm"],"Saturday":["8 am–8 pm"],"Sunday":["8 am–8 pm"],"Thursday":["6 am–10 pm"],"Tuesday":["6 am–10 pm"],"Wednesday":["6 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>https://aretegyms.com/</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>+44 20 7481 8513</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>GW6J+RC London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>381</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>{"1":23,"2":6,"3":11,"4":44,"5":297}</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>51.512045</v>
+      </c>
+      <c r="R75" t="n">
+        <v>-0.068982</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>18223175000609156495</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gym with fitness equipment &amp; classes</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Members-only gym offering cardio &amp; strength equipment, plus personal training &amp; diverse classes.</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnX5zmSC6QRAkhS-tvFbcYuRosaGkMjoOEalk54PbZJ8CtXXXCRXcomYD7LNHtk459-Lm4Q0hm-SkMN_Y0xkl3jf65hsdtkMYr2EJ4A9sfeavhq0K4h5vOvPL2vBvJe9tHkgWsu8NdxBgo=w408-h271-k-no</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>0x4876033598eba985:0xfce5b91ccf166d8f</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>ChIJhanrmDUDdkgRj20Wzxy55fw</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>{"id":"117203712057038126736","name":"ARETE GYMS (Owner)","link":"https://www.google.com/maps/contrib/117203712057038126736"}</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Sugar House, 75 Hooper St","city":"London","postal_code":"E1 8BP","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>[{"Name":"Theo Poupel","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocL1kvDbRxqTPc52hwwdHWb_ZHivo_jkL9wzaH3dGR_4IyWMHOQ=s120-c-rp-mo-br100","Rating":5,"Description":"Very clean gym and has all the equipment necessary. The sauna and cold plunge are a nice touch to relax and recover the muscles. The staff are really nice, and contrary to what people say, I really appreciated the new gym setup which lets us have more space for ourselves when training. The only things that need improving: The shower pressure, as sometimes only drops come out, and occasionally there is a foul smell in one particular area of the gym. But overall, very nice gym 👍","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tOR01FaDFSakpyYVVod1RtUkZZMHhpZG1KdlpVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113494071104435996194/reviews?hl=en-GB","posted_at_unix_micros":1779799910578416,"updated_at_unix_micros":1779799910578416,"language":"en","translated_lang":"","text_original":"Very clean gym and has all the equipment necessary. The sauna and cold plunge are a nice touch to relax and recover the muscles. The staff are really nice, and contrary to what people say, I really appreciated the new gym setup which lets us have more space for ourselves when training. The only things that need improving: The shower pressure, as sometimes only drops come out, and occasionally there is a foul smell in one particular area of the gym. But overall, very nice gym 👍","text_translated":"","reply_text_original":"Thank you Theo. 😀","reply_language":"en","reply_posted_at_unix_micros":1780394714000000,"reply_updated_at_unix_micros":1780394714000000,"published_at":"2026-05-26T12:51:50.578416Z"},{"Name":"Gemma Grant","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVH5Zxo-yRwWJDm6X8Qu5alOH3OW_FGjuqJWY3HnsNa6GIAF6M=s120-c-rp-mo-br100","Rating":5,"Description":"This is a genuinely fantastic independent gym in east London.\n\nThe staff are friendly and incredibly knowledgeable, and the recovery suite is top-tier, a huge bonus that sets this place apart. I really enjoy the Tuesday evening run club and with different paced groups, it’s welcoming for both new runners and experienced ones, creating a great sense of community.\n\nThe weights and cardio selection is ideal, and I’m excited to see they’re planning to install sled tracks soon! I also really value the independent nature of the gym. It’s refreshing to see real investment and passion going into a space rather than yet another franchise. The care, attention to detail, and overall experience here far exceeds anything I’ve had at the many franchise gyms I’ve been a member of over the years.\n\nA brilliant east London gem — highly recommend!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmP-A8WKB4Ogo8mAjiaHmdSSjgYmJF5yuocjkHFECj0SZzvRt7LgQOlq048S0dbqDTgvkXaZdIfo1KbcfOeKLrLChtu_JPtx6pBfEfMkAvrAQ5av6WaPgz5TZbl_UH4bKsejlMGT1VIk5D6i=k-no"],"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pOQmJsQmxabWxqZURremVHWmZRbnBUVDNwa2RrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112818738716849049871/reviews?hl=en-GB","posted_at_unix_micros":1763109938795353,"updated_at_unix_micros":1763109938795353,"language":"en","translated_lang":"","text_original":"This is a genuinely fantastic independent gym in east London.\n\nThe staff are friendly and incredibly knowledgeable, and the recovery suite is top-tier, a huge bonus that sets this place apart. I really enjoy the Tuesday evening run club and with different paced groups, it’s welcoming for both new runners and experienced ones, creating a great sense of community.\n\nThe weights and cardio selection is ideal, and I’m excited to see they’re planning to install sled tracks soon! I also really value the independent nature of the gym. It’s refreshing to see real investment and passion going into a space rather than yet another franchise. The care, attention to detail, and overall experience here far exceeds anything I’ve had at the many franchise gyms I’ve been a member of over the years.\n\nA brilliant east London gem — highly recommend!","text_translated":"","reply_text_original":"Thank you Gemma 😃","reply_language":"en","reply_posted_at_unix_micros":1764088949000000,"reply_updated_at_unix_micros":1764088949000000,"published_at":"2025-11-14T08:45:38.795353Z"},{"Name":"Sofia Bashir","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW2nDI8xLE9A97R7f6xl0-w82JdjcJg6Ddg53BTZq5a-dQoR_Wk=s120-c-rp-mo-br100","Rating":5,"Description":"I have been going to Arete for around 8 months now and it is a fantastic independent gym. The staff are lovely and the facilities are clean and well maintained. The sauna and cold plunge is a great addition. I have done a couple of classes and would definitely recommend if you want to push yourself, the staff are so supportive and encouraging.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT20wMmMzQjNjMmxPYlMxVFVtdGlVR2xRYTJadVJWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102386193243125525090/reviews?hl=en-GB","posted_at_unix_micros":1780393677886210,"updated_at_unix_micros":1780393677886210,"language":"en","translated_lang":"","text_original":"I have been going to Arete for around 8 months now and it is a fantastic independent gym. The staff are lovely and the facilities are clean and well maintained. The sauna and cold plunge is a great addition. I have done a couple of classes and would definitely recommend if you want to push yourself, the staff are so supportive and encouraging.","text_translated":"","reply_text_original":"Thank you Sofia, :-)","reply_language":"en","reply_posted_at_unix_micros":1780394645000000,"reply_updated_at_unix_micros":1780394645000000,"published_at":"2026-06-02T09:47:57.88621Z"},{"Name":"Anvay B","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK2cIxSJZeMrhMrjsVsCIkp9e4-8kpXpuGUleEG1vC-eufggQ=s120-c-rp-mo-br100","Rating":5,"Description":"Ben, Bruno and the rest of the Arete Team are nothing but welcoming and approachable. Facilities are high-quality and regularly maintained and I personally am looking forward to using the new equipment coming in very soon. It's clear the owner has put a lot of thought into the gym, though I particularly appreciate his focus on building a sense of community. Definitely worth the membership cost, and my favourite gym so far.","Images":null,"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21KVWVqWlpiWE41Y0ZKRU4wWnFUM05GYkhsTExVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100564700890658228053/reviews?hl=en-GB","posted_at_unix_micros":1763313338888751,"updated_at_unix_micros":1763314093580041,"language":"en","translated_lang":"","text_original":"Ben, Bruno and the rest of the Arete Team are nothing but welcoming and approachable. Facilities are high-quality and regularly maintained and I personally am looking forward to using the new equipment coming in very soon. It's clear the owner has put a lot of thought into the gym, though I particularly appreciate his focus on building a sense of community. Definitely worth the membership cost, and my favourite gym so far.","text_translated":"","reply_text_original":"Thank you Anvay 😀","reply_language":"en","reply_posted_at_unix_micros":1764088882000000,"reply_updated_at_unix_micros":1764088882000000,"published_at":"2025-11-16T17:15:38.888751Z"},{"Name":"mago pawino","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKo2vxXyw5utzgI3fEnBGJ9Mq2eiXA4ARNSEkiNChZzCz_2Hg=s120-c-rp-mo-ba12-br100","Rating":4,"Description":"I’ve been a member of Arete Gym since they opened, I’ve got a founding membership and I was very happy to support an independent gym. I’ve noticed quite soon that the management was committed to establishing their image in the area, through social media, and a rebranding of this previously Urban Fitness gym.\n\nDuring the time of being a member, there has been ups and downs in my experience at the gym, but overall this has been a positive journey. I have seen the management investing into the gym, some new equipment, some refurbished equipment (changing the padding of most benches), and the general effort to keep the gym kempt and clean.\n\nThe staff is reasonably friendly, and the facilities are overall good. I sometimes try to play with the layout in my mind to think how I would improve the gym. Although I do have some ideas, I also feel that this basement floor carries limitations that the gym management cannot overcome, such as pillars/columns that evidently cannot be moved, preventing better space management.\n\nThe areas where I think the gym should definitely improve focus on:\n•\tAllowing for night staff to work, extending the gym opening and closing times which currently are quite tight. A few metres away from here there is Anytime Fitness, which currently costs less, is quite similar in terms of gym offering, and is 24/7. I do feel that it could become more competitive in this sense.\n•\tAt the bottom right corner of the gym, near the 45 degree leg press and cable machines. There is a very small free body area, which I do think that as it is now it is quite useless. Why not replace it with a more valuable and popular squat machine? We finally have a hip thrust machine, a squat or deadlift machine, would be a very welcome addition.\n•\tThe yoga/classes area is quite nice, and it’s cool that when classes are not running people are allowed to use it. I do believe that there should be some more mirrors there, as it would allow people to control their form during exercises.\n\nI am not so sure about the recent layout changes. I don’t mind the new racks being moved and I do think it is interesting that we now have a functional exercise area, although it doesn’t really seem very popular at the moment.\n\nI definitely feel it, over the past four months, the gym has become incredibly busier. On one hand, I am happy for the management, as this is an independent project. However, as a customer, I do feel that this is starting to impact my experience at the gym, making me consider alternatives from time to time. I do appreciate we are in London, and it’s very hard to find a somewhat quiet gym at peak hours.\n\nOther pros of this gym include the culture of the people attending it. Despite a few unfortunate exceptions from time to time, there is a general culture of keeping equipment tidy, putting dumbbells and equipment away, ensuring that the next person will find everything in its right place. I do think this is a great way of keeping the gym safe and functional, and probably an outcome of keeping a price point that is not too high, but not too low either, avoiding the unfortunate lack of care that I’ve seen in cheaper gyms like PureGym in the past.\n\nI hope some of these improvements can be taken into consideration, it would be great.\n\nPerhaps there are some extra spaces that could be used, such as the area immediately past the entrance stairs?","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT210SE0wUjZhR2hqVERSSVdUWnlWR05mVlVkWVJtYxAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/112173893151256717204/reviews?hl=en-GB","posted_at_unix_micros":1777116432182241,"updated_at_unix_micros":1777116432182241,"language":"en","translated_lang":"","text_original":"I’ve been a member of Arete Gym since they opened, I’ve got a founding membership and I was very happy to support an independent gym. I’ve noticed quite soon that the management was committed to establishing their image in the area, through social media, and a rebranding of this previously Urban Fitness gym.\n\nDuring the time of being a member, there has been ups and downs in my experience at the gym, but overall this has been a positive journey. I have seen the management investing into the gym, some new equipment, some refurbished equipment (changing the padding of most benches), and the general effort to keep the gym kempt and clean.\n\nThe staff is reasonably friendly, and the facilities are overall good. I sometimes try to play with the layout in my mind to think how I would improve the gym. Although I do have some ideas, I also feel that this basement floor carries limitations that the gym management cannot overcome, such as pillars/columns that evidently cannot be moved, preventing better space management.\n\nThe areas where I think the gym should definitely improve focus on:\n•\tAllowing for night staff to work, extending the gym opening and closing times which currently are quite tight. A few metres away from here there is Anytime Fitness, which currently costs less, is quite similar in terms of gym offering, and is 24/7. I do feel that it could become more competitive in this sense.\n•\tAt the bottom right corner of the gym, near the 45 degree leg press and cable machines. There is a very small free body area, which I do think that as it is now it is quite useless. Why not replace it with a more valuable and popular squat machine? We finally have a hip thrust machine, a squat or deadlift machine, would be a very welcome addition.\n•\tThe yoga/classes area is quite nice, and it’s cool that when classes are not running people are allowed to use it. I do believe that there should be some more mirrors there, as it would allow people to control their form during exercises.\n\nI am not so sure about the recent layout changes. I don’t mind the new racks being moved and I do think it is interesting that we now have a functional exercise area, although it doesn’t really seem very popular at the moment.\n\nI definitely feel it, over the past four months, the gym has become incredibly busier. On one hand, I am happy for the management, as this is an independent project. However, as a customer, I do feel that this is starting to impact my experience at the gym, making me consider alternatives from time to time. I do appreciate we are in London, and it’s very hard to find a somewhat quiet gym at peak hours.\n\nOther pros of this gym include the culture of the people attending it. Despite a few unfortunate exceptions from time to time, there is a general culture of keeping equipment tidy, putting dumbbells and equipment away, ensuring that the next person will find everything in its right place. I do think this is a great way of keeping the gym safe and functional, and probably an outcome of keeping a price point that is not too high, but not too low either, avoiding the unfortunate lack of care that I’ve seen in cheaper gyms like PureGym in the past.\n\nI hope some of these improvements can be taken into consideration, it would be great.\n\nPerhaps there are some extra spaces that could be used, such as the area immediately past the entrance stairs?","text_translated":"","published_at":"2026-04-25T11:27:12.182241Z"}]</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>13</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/1Rebel+High+Street+Kensington/data=!4m7!3m6!1s0x48760ff1f20c6a0d:0xfd13da3d1f840f4e!8m2!3d51.499528!4d-0.1985245!16s%2Fg%2F11b7y78wrx!19sChIJDWoM8vEPdkgRTg-EHz3aE_0</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1Rebel High Street Kensington</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>45 Phillimore Walk, London W8 7RZ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–8:45 pm"],"Monday":["6 am–9:45 pm"],"Saturday":["7 am–6:45 pm"],"Sunday":["8 am–6:45 pm"],"Thursday":["6 am–8:45 pm"],"Tuesday":["6 am–9:45 pm"],"Wednesday":["6 am–9:45 pm"]}</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1rebel.com/en-gb</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>+44 20 3958 9500</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>FRX2+RH London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>379</v>
+      </c>
+      <c r="O76" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>{"1":61,"2":9,"3":13,"4":25,"5":271}</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>51.499528</v>
+      </c>
+      <c r="R76" t="n">
+        <v>-0.198524</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>18236159272209878862</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWke_-M_ZD9F2CdB4kCZ-dmdyC9lytcMLE16LbBIhRdFwWz8q7Af3j-4Rjii7tIWh7HgvSs4XrEUWQNf7YXA2gPV5A3KkyQWUJtNmF_UJi94Yq0Ya9CTD_jMsSw7TMBdK7LsGcPZ=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>0x48760ff1f20c6a0d:0xfd13da3d1f840f4e</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>ChIJDWoM8vEPdkgRTg-EHz3aE_0</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>{"id":"106943563970290059074","name":"1Rebel High Street Kensington (Owner)","link":"https://www.google.com/maps/contrib/106943563970290059074"}</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"45 Phillimore Walk","city":"London","postal_code":"W8 7RZ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>[{"Name":"Bibi Tukentegi","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU_PMFseJXD0WlGSAn0XqEPSa0Z_cYmKSMOWv4ZdUqsGJkc19xNTA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I absolutely adore this 1rebel branch!! I’ve been to more than half the studios in London but this is my fav for sure!! All the instructors are lovely, (Bronte is amazing!) the workouts are the perfect level of challenging and well paced (but not to the point where I feel like imma pass out), I always feel the burn!! And then feel great after!! The interior is gorgeous \u0026 dog friendly too! Plus the shakes are always the cherry on the top of every workout! Jordan \u0026 Sarine make such great shakes every time!! Big shoutout to them","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmN-DanI5ofvXqmzOgFLqTdUCgs--1wWK8GCBBpqkidNsU_tLLYz23P9oW22LiHn6dzWkRqnBK5wckOTFTle9qlbPQc4alq5Gb73uc2aOd6eiEEEIJi7whV8ySnCABPTe6_UvlztTTMIs85K=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM4vKZ4Z2aK6O-C2dv-xK-08xwU_0_xyc581rVeuOjzOoeXAnUP3GkIz8fducpGUeAOXRQh0-vE0P71cBY_K9r6Zz_0BJOuxQL9r7KIszRHM9otFufSZ4NuOrRoFyE60qlia6BnTkjWu3Jd=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNVJxHTpYFtlHXBiISpcIaFk7KA07hA2Y94Qg16XmxwRdaknygM0MywVv2TGfq5K9SCdFNimRda03In-3OrnwIXgewbE5beqqqnvyD5F4sWlm4kkzmcliyPXAjFPD0RcWM-5dhHGvp7k4Ok=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO9K4eaah6SWoIN4YIesLi2h78y0uDX4Q-tzQMPCDuT1dpGgW74DTxj7621IaDIK0QHMbLgl5cMdcudtHUZ_0AmWlK9lErmTjMbWVSRkOQ6YZHL0UZA4FN5fS0zCnsQwXtZ4nH6gRpsizkM=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPRbzUbXxg0yGH797aXgrwJAsKIBml7xydXL3UpfUTl_9t7UpfOp9arGSUNlDsH5SgsXQRUukO9_yHSyW9MFTsZv8KFOT4hJiN48G1yd-pGqIYNHRaFdMH7ebpRubYjweDz-aMCljwjDVU=k-no"],"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25ocFpVRk9TVWxxV1d0UllUSm9SVEpSTW5ob01tYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113912304134955388539/reviews?hl=en-GB","posted_at_unix_micros":1777737587999239,"updated_at_unix_micros":1777751331993367,"language":"en","translated_lang":"","text_original":"I absolutely adore this 1rebel branch!! I’ve been to more than half the studios in London but this is my fav for sure!! All the instructors are lovely, (Bronte is amazing!) the workouts are the perfect level of challenging and well paced (but not to the point where I feel like imma pass out), I always feel the burn!! And then feel great after!! The interior is gorgeous \u0026 dog friendly too! Plus the shakes are always the cherry on the top of every workout! Jordan \u0026 Sarine make such great shakes every time!! Big shoutout to them","text_translated":"","published_at":"2026-05-02T15:59:47.999239Z"},{"Name":"GiGi","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUnJwC2N6vaJwUxwv3JKpy0ycinkJ-Cg07RW-AyUbXprq8Iz_Q=s120-c-rp-mo-br100","Rating":5,"Description":"Staff was friendly and welcoming, space is clean and stocked with amenities like reusable water bottles and cold towels.\n\nAttended the reformer class, although it was challenging really enjoyed it thank you!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOZFTIKlrsfOQWPDswP5pMpgTRmhXAIYgm370hFAE5tnBqynEcz4Iv1xNqUpReyacODkMDhVE6heG4ekTU6qHrtPrEuwfVe7-QFPFdv21ghDdtyRIrg9ImNtI9TRxyNU1E4jQSEFv5F7MA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO4zhXnKBSJafgRp5ZgTY20UzcRYak0yl19ZaGWmClZlMGmd56GAhRLxNT1csiO68EnfyCwc9ZZfV7YMqzTfUhjuDrMZ4kiAI3eShZTwrL63Yp6t_TEkpWrv54sX4aDLUXNt9Z9wfXsujwy=k-no"],"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25WSGFuWjBRVGhWYUhNeVZIaE5lVzVUYWxsTU4yYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102316668455443256162/reviews?hl=en-GB","posted_at_unix_micros":1784378023605843,"updated_at_unix_micros":1784378023605843,"language":"en","translated_lang":"","text_original":"Staff was friendly and welcoming, space is clean and stocked with amenities like reusable water bottles and cold towels.\n\nAttended the reformer class, although it was challenging really enjoyed it thank you!","text_translated":"","published_at":"2026-07-18T12:33:43.605843Z"},{"Name":"Augustin Mallon","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWOK73Q-4d9wMZMTBXllVQzPm7m3wfH-RrtACcrw8Dw-AhXapEgxA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great infrastructure. Showers and locker rooms super clean and safe. Great spin classes. The room is very cool! Similar to a boiler room, dark and buzzing with music.\n\nWonderful sauna \u0026 ice bath. Very unique in nature: it fits 4 people and is very well lit. Optimal for chatting or quieter times reading a book. The ice baths are constantly pristine cold - that after about 20 or so visits. Never a flaw!\n\nStaff are very friendly. Fast paced customer support. All you’d want from a boutique fitness studio!\n\nThey also listen to feedback and are forward looking which is very appreciated.\nThank you 1Rebel for some great workouts!!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNAwXi63pOoayJTCF_qLhQ-_VB60qho1P0nk1X4LlEGgY9WZpTvq-9k-pPjeAbsOtlpEvQdTeVyN8Tmd-XkRR9Wi5BHKx9-U7iiGm15TD5RRvIaqX418BfuF4u0mZJQbtSUraJuR4Dr-WU=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmN02cON-11p627Abo4V_rvEMvRS5A98F2gSav9u1ouBex9YmSq_Is0ERw9bR2hjYuuKfJody-R5MsG1spwVgc-3_T6gCz6QbzDVxSINjgud7mwLILLWqCV1mxq9cmVAYUxOqIx4TwPioCE=k-no"],"When":"Edited a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2t0R0xUSlBWVFZ4TkhSclEzZFhabkJvTTJZeVNIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109399166163230993905/reviews?hl=en-GB","posted_at_unix_micros":1756899925560798,"updated_at_unix_micros":1757536537878857,"language":"en","translated_lang":"","text_original":"Great infrastructure. Showers and locker rooms super clean and safe. Great spin classes. The room is very cool! Similar to a boiler room, dark and buzzing with music.\n\nWonderful sauna \u0026 ice bath. Very unique in nature: it fits 4 people and is very well lit. Optimal for chatting or quieter times reading a book. The ice baths are constantly pristine cold - that after about 20 or so visits. Never a flaw!\n\nStaff are very friendly. Fast paced customer support. All you’d want from a boutique fitness studio!\n\nThey also listen to feedback and are forward looking which is very appreciated.\nThank you 1Rebel for some great workouts!!","text_translated":"","published_at":"2025-09-03T11:45:25.560798Z"},{"Name":"Alaska Tegi","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocI6XlbUd7QVeouymRhw4_ZM-0ng0ZHcd2FCy0f8IMXU_z1_CA=s120-c-rp-mo-br100","Rating":5,"Description":"I want to sincerely thank Sarine and Yazmine for being so incredibly accommodating and kind! Their presence always lights up the studio and I am always greeted with the most warmest smiles! I spilt my protein shake and Sarine made me another one and didn’t make me feel embarrassed at all 🥹❤️ She even gave me a stamp card after to make me feel better! I am so touched by their kindness and spirit! I’ve truly never felt so uplifted and moved by two incredible people! I urge everyone to go to 1Rebel on High Str. Kens! Sarine and Yazmine’s kindness goes above and beyond! They are truly incredible human beings and it’s such a pleasure to come to a gym with the best and most positive spirit! 🥹❤️❤️❤️","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT200dFFTMWpRMGxEUnkxMlYwTmxURzB6ZFZWUk5sRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105714636901668867882/reviews?hl=en-GB","posted_at_unix_micros":1780127770971514,"updated_at_unix_micros":1780127770971514,"language":"en","translated_lang":"","text_original":"I want to sincerely thank Sarine and Yazmine for being so incredibly accommodating and kind! Their presence always lights up the studio and I am always greeted with the most warmest smiles! I spilt my protein shake and Sarine made me another one and didn’t make me feel embarrassed at all 🥹❤️ She even gave me a stamp card after to make me feel better! I am so touched by their kindness and spirit! I’ve truly never felt so uplifted and moved by two incredible people! I urge everyone to go to 1Rebel on High Str. Kens! Sarine and Yazmine’s kindness goes above and beyond! They are truly incredible human beings and it’s such a pleasure to come to a gym with the best and most positive spirit! 🥹❤️❤️❤️","text_translated":"","published_at":"2026-05-30T07:56:10.971514Z"},{"Name":"Sophie Lapointe","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocL4ScaATIknLiDK6xYVHCpubXEUCiTkEDqC0vhA9XxYzLp-DQc=s120-c-rp-mo-br100","Rating":5,"Description":"Serene,Yasmin ,Alex always make everyone at OneRebel such a great experience. They are consistently friendly, kind, welcoming, and bring such positive energy to the studio. They make everyone feel comfortable the moment you walk in. Their professionalism and warmth truly stand out. Well done to both of you  it never goes unnoticed.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xoTmFUQnJURVJJTkhkMGJqTnJWSGxxYmxaMlNXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106795114463278298867/reviews?hl=en-GB","posted_at_unix_micros":1779456216663202,"updated_at_unix_micros":1779456216663202,"language":"en","translated_lang":"","text_original":"Serene,Yasmin ,Alex always make everyone at OneRebel such a great experience. They are consistently friendly, kind, welcoming, and bring such positive energy to the studio. They make everyone feel comfortable the moment you walk in. Their professionalism and warmth truly stand out. Well done to both of you  it never goes unnoticed.","text_translated":"","published_at":"2026-05-22T13:23:36.663202Z"}]</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>13</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hitio+Gym+Hoxton/data=!4m7!3m6!1s0x48761db8d88e4fa5:0xce17d48f87664fed!8m2!3d51.5361547!4d-0.0888535!16s%2Fg%2F11j0jj13wp!19sChIJpU-O2LgddkgR7U9mh4_UF84</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Hitio Gym Hoxton</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Gainsborough Studio, 1 Poole St, London N1 5EB, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:30 am–10 pm"],"Monday":["6:30 am–10 pm"],"Saturday":["8 am–7 pm"],"Sunday":["10 am–6 pm"],"Thursday":["6:30 am–10 pm"],"Tuesday":["6:30 am–10 pm"],"Wednesday":["6:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hitiogym.com/gym/hoxton</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>+44 20 3746 7630</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>GWP6+FF London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>366</v>
+      </c>
+      <c r="O77" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>{"1":8,"2":2,"3":5,"4":6,"5":345}</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>51.536155</v>
+      </c>
+      <c r="R77" t="n">
+        <v>-0.088854</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>14850572009194541037</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm_YN6hMo-Ahh6VAm0p6IUP7PN4Wl2GKi4BR58nwUQ8_3gaaCogspscajVBuuAdba9R9p5D2LKieZePVuh2BHcR5AUkhxdxi8bxsU4p7hk-xGFAeZ8DI3ueFQ5GhGaR-kqOxZ4=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>0x48761db8d88e4fa5:0xce17d48f87664fed</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>ChIJpU-O2LgddkgR7U9mh4_UF84</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.hitiogym.com/gym/hoxton/","source":"hitiogym.com"}]</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>{"id":"103044316553674149660","name":"Hitio Gym Hoxton (Owner)","link":"https://www.google.com/maps/contrib/103044316553674149660"}</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Gainsborough Studio, 1 Poole St","city":"London","postal_code":"N1 5EB","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>[{"Name":"Sarah Stoutamire","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIh9-RgRrVpWF-lTelkRjG9GBr18U6-SNfxUsHH_PUtWrfPmto=s120-c-rp-mo-br100","Rating":5,"Description":"Amazing gym! Tim truly cares about community feedback and always strives to improve the range of equipment, really listening to members’ requests, so much so that I think he may have gone a little too far with my request for more StairMasters 😅","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMlW9YxccjpLpH-9N-Ca9RRSsPBlYRADT__jUA_JgKrKvKiuo0_ZG9Wvis975GhlPCV_26tZp8j_hAqlh7T2z4cS0zt6CR04Po-VgQ2dmrykuqI-HO_qCgC_KlgBfuEz6Hj9N2KdGhzJI8=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPbzaMJWhFTFqde9yTH1-X9RfKKZxqKYc7rpItYvui8jaFs6ygsiKGRmHoW8GO67GnucAVn3tZWk9w_WUx8uaQgEOEAsCIryQ5JOyCBvwPZGGmGG8E8pqD3TVydo6ZxZZcNwYumda77yC8=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOtRsZVtrk7a2O6nEiMeviR4hEKV79cDBgRoAF-z2Lx_IAJJf8bR_-VhgkWsgV5WOOcDdqhka8HgspXg4N2junUhPhimysQDzjcflFS-iFMxOXz5WwTPZxyZfsaBgeIk_-MaUptZnzAkSLf=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT205S1ExRXRVV2hrWmtWWFZVdFNRMFZrTUVjek1uYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110607857774672147498/reviews?hl=en-GB","posted_at_unix_micros":1775046158772208,"updated_at_unix_micros":1775046158772208,"language":"en","translated_lang":"","text_original":"Amazing gym! Tim truly cares about community feedback and always strives to improve the range of equipment, really listening to members’ requests, so much so that I think he may have gone a little too far with my request for more StairMasters 😅","text_translated":"","reply_text_original":"Hi Sarah,\nLoving the pictures very much.\nWhat this space more developments coming this year \n😊","reply_language":"en","reply_posted_at_unix_micros":1777985104000000,"reply_updated_at_unix_micros":1777985104000000,"published_at":"2026-04-01T12:22:38.772208Z"},{"Name":"Tammy Goodger","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLTz9n3YBE5rgAz0jSsRID2hE1JvFv7LMntGCsvz0aFvwSlWQ=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve recently left a well known gym to join Hitio gym! I found a plan that worked for me in no time. The variety of plans are suitable for all and didn’t feel overwhelming. Sauna and steam room was just the win for me and of course the multiple classes they have to offer! Along with the wide range of equipment. It is a friendly and welcoming environment I highly recommend hitio gym! (Also a stunning location!)","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tGZlQwRmpZMVptYVVGV2NWOUVYMk5uYW1RNWRYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106216752997113771383/reviews?hl=en-GB","posted_at_unix_micros":1781819384474060,"updated_at_unix_micros":1781819384474060,"language":"en","translated_lang":"","text_original":"I’ve recently left a well known gym to join Hitio gym! I found a plan that worked for me in no time. The variety of plans are suitable for all and didn’t feel overwhelming. Sauna and steam room was just the win for me and of course the multiple classes they have to offer! Along with the wide range of equipment. It is a friendly and welcoming environment I highly recommend hitio gym! (Also a stunning location!)","text_translated":"","reply_text_original":"Hey Tammy\nThank you for your kind words \nGlad your part of the family now\nThanks again \nTim \u0026 Matt ","reply_language":"en","reply_posted_at_unix_micros":1782559201000000,"reply_updated_at_unix_micros":1782559201000000,"published_at":"2026-06-18T21:49:44.47406Z"},{"Name":"Olivia Beighton","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLrmZom1mp3KDf88UtFYLqrZqptTjzqI7WR3XqzzpCoopmj2g=s120-c-rp-mo-br100","Rating":5,"Description":"Hands down the best gym in London, couldn’t recommend more highly. The gym has all the equipment you could need, from strength to cardio. The owner, Tim, and the trainers are the friendliest, most welcoming team who create such a sense of community within the gym. Tim is constantly upgrading the equipment from peloton, to new plates and new machines. The gym is always kept super clean throughout, including the changing rooms which also have sauna and steam rooms. HITIO has a great range of classes from low intensity yoga and Pilates to boxing and HIIT training, in addition to all of this the gym offers free friends Friday and regular freebies throughout. If you’re looking for a gorgeous, independent gym with a lovely bunch of people, HITIO is your answer!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tkVGJqVk1aa05vTUhFd1Z6ZG1TbTV4Wm5SYVprRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110854070863821240125/reviews?hl=en-GB","posted_at_unix_micros":1773427919859542,"updated_at_unix_micros":1773427919859542,"language":"en","translated_lang":"","text_original":"Hands down the best gym in London, couldn’t recommend more highly. The gym has all the equipment you could need, from strength to cardio. The owner, Tim, and the trainers are the friendliest, most welcoming team who create such a sense of community within the gym. Tim is constantly upgrading the equipment from peloton, to new plates and new machines. The gym is always kept super clean throughout, including the changing rooms which also have sauna and steam rooms. HITIO has a great range of classes from low intensity yoga and Pilates to boxing and HIIT training, in addition to all of this the gym offers free friends Friday and regular freebies throughout. If you’re looking for a gorgeous, independent gym with a lovely bunch of people, HITIO is your answer!","text_translated":"","reply_text_original":"Hey Olivia,\nThis is so lovely, thank you for leaving such an amazing review.\nThe team will be delighted with such feedback.\nBest Wishes\nTim\n","reply_language":"en","reply_posted_at_unix_micros":1773666594000000,"reply_updated_at_unix_micros":1773666594000000,"published_at":"2026-03-13T18:51:59.859542Z"},{"Name":"Jack Crumlin","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWZs0GUL_6QwX0iA94Czhaw4b_HOWcKPw8O4kU8YqkWoOvjWn4I=s120-c-rp-mo-br100","Rating":5,"Description":"Olavi is the best PT I’ve ever had! Incredibly knowledgeable and highly skilled coach, and excellent at motivating. Being trained by Olavi has made me more fit, healthy and strong than I have ever been. I can’t recommend working with Olavi highly enough!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2t4eFNtMUpUMFppVlU5bVpXWjRSRTlLVkZSdFVHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101094508768100853705/reviews?hl=en-GB","posted_at_unix_micros":1785847766692876,"updated_at_unix_micros":1785847766692876,"language":"en","translated_lang":"","text_original":"Olavi is the best PT I’ve ever had! Incredibly knowledgeable and highly skilled coach, and excellent at motivating. Being trained by Olavi has made me more fit, healthy and strong than I have ever been. I can’t recommend working with Olavi highly enough!","text_translated":"","reply_text_original":"Hey Jack,\nWe are so pleased we have Olavi here, myself and Olavi are super proud.\nThank you\nTim","reply_language":"en","reply_posted_at_unix_micros":1785849018000000,"reply_updated_at_unix_micros":1785849018000000,"published_at":"2026-08-04T12:49:26.692876Z"},{"Name":"Joshua James Armstrong","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLwPt-iQVxalnytxseb24w-MSOuQPl8tJY_g8n_0feh2LTR7Q=s120-c-rp-mo-br100","Rating":5,"Description":"Such an awesome gym! The owners are so passionate about the gym and bringing value to their clients. Just super genuine people. The space and the equipment are top notch too. Honestly not a bad thing to say about this gym and the staff. Highly recommend this place!","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSRVgzWjBWRUZFTUdwVWVEVkVhR2t6TlV0aU1IYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109304200093275761226/reviews?hl=en-GB","posted_at_unix_micros":1770815894034530,"updated_at_unix_micros":1770815894034530,"language":"en","translated_lang":"","text_original":"Such an awesome gym! The owners are so passionate about the gym and bringing value to their clients. Just super genuine people. The space and the equipment are top notch too. Honestly not a bad thing to say about this gym and the staff. Highly recommend this place!","text_translated":"","reply_text_original":"Hi Joshua,\nThis is awesome, from behave of myself,, Matt and the team and massive thank you. Really glad your happy, with what we are trying to do.","reply_language":"en","reply_posted_at_unix_micros":1770900274000000,"reply_updated_at_unix_micros":1770900274000000,"published_at":"2026-02-11T13:18:14.03453Z"}]</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>13</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Tempo+301+-+SE17+%7C+Elephant+and+Castle/data=!4m7!3m6!1s0x48761ce7c63f7817:0xd7fcfec82f1639a7!8m2!3d51.4941126!4d-0.0972382!16s%2Fg%2F1tdcfvw1!19sChIJF3g_xuccdkgRpzkWL8j-_Nc</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tempo 301 - SE17 | Elephant and Castle</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pilates studio</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2 Ash Ave, London SE17 1GQ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>{"Friday":["7 am–3 pm","5–9 pm"],"Monday":["7 am–2 pm","5–9 pm"],"Saturday":["8 am–4 pm"],"Sunday":["8 am–4 pm"],"Thursday":["7 am–2 pm","4:30–8:30 pm"],"Tuesday":["7 am–2 pm","4:30–8:30 pm"],"Wednesday":["7 am–2 pm","5–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>http://tempo301.co.uk/</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>+44 7881 746243</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>FWV3+J4 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>296</v>
+      </c>
+      <c r="O78" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>{"1":9,"2":2,"3":3,"4":6,"5":276}</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>51.494113</v>
+      </c>
+      <c r="R78" t="n">
+        <v>-0.097238</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>15563594548022491559</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn3SO1QX8C0N9Hht8orp3C-_MYiOXNZsf0MOAZxCz19lw3AgPFsVCZ3LKGKoIK7I_wWa1TwjAUUbfiTLyqhJusX7QDyvHwbsebGKTpeCFZffNVJLBNIJ_Ppt7cta2ZWka42WF6exFk37oNF=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>0x48761ce7c63f7817:0xd7fcfec82f1639a7</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>ChIJF3g_xuccdkgRpzkWL8j-_Nc</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>[{"link":"https://tempo301.co.uk/studios/london-se17-elephant-park/","source":"tempo301.co.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>{"id":"104154309176677326683","name":"Tempo 301 - SE17 | Elephant and Castle (Owner)","link":"https://www.google.com/maps/contrib/104154309176677326683"}</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"2 Ash Ave","city":"London","postal_code":"SE17 1GQ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>[{"Name":"Anna","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJIoBtsWy6rHrmbT3EgntzPqkiwa-oqxvMYWh32-GRzh5mjCu0=s120-c-rp-mo-br100","Rating":5,"Description":"Genuinely lovely space! I had my first ever pilates session here today, the instructor was supportive and kind, and the whole place is super clean and has everything you need to\nstart pilates. Would definitely recommend!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tkSWFVSnJRelpDY1RJNE0yRkJPSFUzZDFocFduYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113799439078766834896/reviews?hl=en-GB","posted_at_unix_micros":1786050057692477,"updated_at_unix_micros":1786050057692477,"language":"en","translated_lang":"","text_original":"Genuinely lovely space! I had my first ever pilates session here today, the instructor was supportive and kind, and the whole place is super clean and has everything you need to\nstart pilates. Would definitely recommend!","text_translated":"","reply_text_original":"Thank you for your wonderful review! We’re so glad you enjoyed your first Pilates session with us and found the space clean, well-equipped, and welcoming. We hope to see you again soon!\nThe Tempo 301 Team","reply_language":"en","reply_posted_at_unix_micros":1787054023000000,"reply_updated_at_unix_micros":1787054023000000,"published_at":"2026-08-06T21:00:57.692477Z"},{"Name":"Katie Moore","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXDOQ3mVYx7UmVZ6WfCO3V3vkZKDHS0W4vKZvRAxy76aGch1_hP=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I’ve been going to this studio for a couple of years now multiple times a week and I can’t say enough good things about it!\n\nI’ve done reformer, jump board and mat Pilates as well as their strength classes. Every instructor has been super friendly and knowledgable.\n\nSpecial shout outs to Pérola, Isabella and Deinny who I’ve continued to be taught by throughout my pregnancy - they are so attentive and I feel very well taken care of so I can keep exercising well into my 3rd trimester!\n\nThe front desk employees are also incredibly helpful and friendly as well - makes for a great atmosphere.\n\nThe facilities are super clean and I think the promotional packages they run are good value for money.\n\nMy only complaint would have been the lack of memberships for classes but they’ve just introduced them so now it’s an easy 5/5!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xkUGNFVndjV1pPYkZSMVNFYzFaMmhaVDFSMVNWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115216502881935565415/reviews?hl=en-GB","posted_at_unix_micros":1779212708089783,"updated_at_unix_micros":1779212708089783,"language":"en","translated_lang":"","text_original":"I’ve been going to this studio for a couple of years now multiple times a week and I can’t say enough good things about it!\n\nI’ve done reformer, jump board and mat Pilates as well as their strength classes. Every instructor has been super friendly and knowledgable.\n\nSpecial shout outs to Pérola, Isabella and Deinny who I’ve continued to be taught by throughout my pregnancy - they are so attentive and I feel very well taken care of so I can keep exercising well into my 3rd trimester!\n\nThe front desk employees are also incredibly helpful and friendly as well - makes for a great atmosphere.\n\nThe facilities are super clean and I think the promotional packages they run are good value for money.\n\nMy only complaint would have been the lack of memberships for classes but they’ve just introduced them so now it’s an easy 5/5!","text_translated":"","reply_text_original":"Thank you so much for this incredibly thoughtful review, Katie!  💛  \n\nWe’re so happy to hear that you’ve been enjoying a variety of our classes over the past couple of years, and it means a lot to know our team has made you feel welcome and supported throughout your journey.\n\nAnd yes - we’re so excited to finally offer memberships! Thank you for being part of our studio community \u0026 we look forward to seeing you in class :) \n\nTempo 301 team","reply_language":"en","reply_posted_at_unix_micros":1780050970000000,"reply_updated_at_unix_micros":1780050970000000,"published_at":"2026-05-19T17:45:08.089783Z"},{"Name":"Darina Nedeva","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVvRGrB_vOdZEz1ov9BzouTyUdNYLugTxiwXUgYRUdBds5FpeLz=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I had such a fantastic experience at this Pilates studio last Friday! I attended a class with Filiz, and she was absolutely amazing. Her energy level was incredibly high in the best way—it really kept the whole class motivated and engaged from start to finish. She made sure to interact with everyone and created such a positive and inclusive atmosphere. What I appreciated most was how clearly she demonstrated each movement; everything was explained in a way that was easy to understand, no matter your level.\n\nA special mention also goes to Leila at reception, who made my visit even more enjoyable. She greeted me with such a warm, friendly smile and took the time to show me around the studio, which immediately made me feel comfortable and welcome.\n\nOverall, it was a wonderful experience, and I genuinely look forward to my next class. Highly recommend!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2kxNlJYVTJOakJyVjJWM2VWazRkbFZaZFZaT1JsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110586845421102966220/reviews?hl=en-GB","posted_at_unix_micros":1775560320736996,"updated_at_unix_micros":1775560320736996,"language":"en","translated_lang":"","text_original":"I had such a fantastic experience at this Pilates studio last Friday! I attended a class with Filiz, and she was absolutely amazing. Her energy level was incredibly high in the best way—it really kept the whole class motivated and engaged from start to finish. She made sure to interact with everyone and created such a positive and inclusive atmosphere. What I appreciated most was how clearly she demonstrated each movement; everything was explained in a way that was easy to understand, no matter your level.\n\nA special mention also goes to Leila at reception, who made my visit even more enjoyable. She greeted me with such a warm, friendly smile and took the time to show me around the studio, which immediately made me feel comfortable and welcome.\n\nOverall, it was a wonderful experience, and I genuinely look forward to my next class. Highly recommend!","text_translated":"","reply_text_original":"Hi Darina, thank you so much for your kind review. We really appreciate you taking the time to share your experience, and your lovely words about Filiz and Leyla mean a lot to us. We’ll be sure to pass them on to both of them.\n\nWe look forward to seeing you soon.\nThe Tempo 301 team","reply_language":"en","reply_posted_at_unix_micros":1776164646000000,"reply_updated_at_unix_micros":1776164646000000,"published_at":"2026-04-07T11:12:00.736996Z"},{"Name":"Lexi Williams","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIhS6xf1KRk9DDyRBnxfpbgFNNzVre1Z0oNgW6TBRmKZ6sGvQ=s120-c-rp-mo-br100","Rating":5,"Description":"This was my first Barre class and Esme the instructor was amazing. Her high energy and bubbly personality put me right at ease and was a great was to kickstart the day along with an early morning workout. I felt challenged but able to complete the moves and had a good sweat at the end of it. The teaching group was small too which meant a good level of attention was paid to each member of the class. 10/10 would recommend both Esme and the Barre class","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pBMWFsWklURmd0Y1VkUk9HRjZOMjlLUVV4RVFsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117105271988788583755/reviews?hl=en-GB","posted_at_unix_micros":1775760739726541,"updated_at_unix_micros":1775760739726541,"language":"en","translated_lang":"","text_original":"This was my first Barre class and Esme the instructor was amazing. Her high energy and bubbly personality put me right at ease and was a great was to kickstart the day along with an early morning workout. I felt challenged but able to complete the moves and had a good sweat at the end of it. The teaching group was small too which meant a good level of attention was paid to each member of the class. 10/10 would recommend both Esme and the Barre class","text_translated":"","reply_text_original":"Thank you so much for your wonderful review! We’re thrilled to hear you enjoyed your first Barre class and that Esme made you feel so welcome and supported. It’s great to know you found the class both challenging and fun, and that the small group setting helped you feel well looked after.\n\nWe really appreciate your recommendation and look forward to seeing you again soon.\nKind regards,\nTempo 301 Team","reply_language":"en","reply_posted_at_unix_micros":1776164675000000,"reply_updated_at_unix_micros":1776164675000000,"published_at":"2026-04-09T18:52:19.726541Z"},{"Name":"Tajda","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLaGaATxbmvN_ejneYPmQeCrX1h3j86HxlhLUkiefqfCOBfEnA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"One of my favorite studios! Knowledgeable instructors with great cueing and exercises. I like their different levels classes systems. I've been training with Demi and Ines. Definitely recommend! I wish I lived in London to be able to go there often! Also their interior is chic and clean.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmM6HUfeEKQszO90ryN940PFzk6NjtohFOz5dGxRMLyhuVq61zuXe_T_4jbAO8duCU0yaGqHoaNKft8bb4odM9VRXyGj6y0AQB0ueBIM8vqgLgQtSIWE56MPln8h1V8y3ag0Tn6y=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmP_rp448vKhX5QhZii1K82Yz0wTA75iN1Ytz34WV5xKNNsvf4PIYcAehwtZXWDwcL4NjdDzjfnAODnSl7mjScnpYwx2BwofNi7C-mKnTsVdgkRc7oA3rEjGcfrgGjuivebIUVjsTA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMyml-6Fx98HPcdY8V0sSO3Te9BhCpERA-tmrHi1MT_l7cJXd83nm-_MMw9tsnGoFgWqYWAMXI71u9stql6iLF_sbfglkrdxIV2W5V820Yiz6oYhOfKD1QHhQLyCpjXJM845Hk=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPUYCEXkQeVE9oPNJ9gDIB1-TmxnY3b1jVK9aiHfK6ShAe5ESUoJfxmMmDPuHlZ9l7ijbOTLZBR41WGTHoAEgSjnGXn1BrMpZOe7a-E5h7BWHNP6L6Vu2Jcul1GJMBXsVmDj5mydQ=k-no"],"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnTURRdThpOXlnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103508309621958435444/reviews?hl=en-GB","posted_at_unix_micros":1741967552961548,"updated_at_unix_micros":1741967552961548,"language":"en","translated_lang":"","text_original":"One of my favorite studios! Knowledgeable instructors with great cueing and exercises. I like their different levels classes systems. I've been training with Demi and Ines. Definitely recommend! I wish I lived in London to be able to go there often! Also their interior is chic and clean.","text_translated":"","reply_text_original":"Hi Tajda, thank you for taking the time to leave such a lovely review of our studio. We're so pleased you enjoy our classes, facilities, and staff, and we're pleased to hear Demi and Ines stand out to you as such strong instructors. We hope to see you when you return to London! Thanks, The Tempo 301 Team","reply_language":"en","reply_posted_at_unix_micros":1742471131000000,"reply_updated_at_unix_micros":1742471131000000,"published_at":"2025-03-14T15:52:32.961548Z"}]</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>13</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Barry%27s+London+East/data=!4m7!3m6!1s0x48761caedd530497:0x3c47ace9c073f358!8m2!3d51.5218253!4d-0.086814!16s%2Fg%2F11b7xq0p10!19sChIJlwRT3a4cdkgRWPNzwOmsRzw</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Barry's London East</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2 Worship St, City Rd, London EC2A 1AH, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:45 am–9:30 pm"],"Monday":["5:45 am–9:30 pm"],"Saturday":["7 am–3:30 pm"],"Sunday":["8:15 am–3:30 pm"],"Thursday":["5:45 am–9:30 pm"],"Tuesday":["5:45 am–9:30 pm"],"Wednesday":["5:45 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>http://www.barrysbootcamp.com/studio/london-east/</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>+44 20 7045 2530</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>GWC7+P7 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>287</v>
+      </c>
+      <c r="O79" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>{"1":11,"2":7,"3":8,"4":28,"5":233}</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>51.521825</v>
+      </c>
+      <c r="R79" t="n">
+        <v>-0.086814</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>4343630485578314584</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmiJlNzGNc1zhGj3rSWftRF8KfMcK8M2_iaDTsRonF-g1k39w4nLl7FMoPmylNGDGxzKwMZRnjuFmZbgDpPBjRxq6ogzPFXWHZEi8SQEaYjLA6Tu0V6EUUyAR_OvjH2KZKf-vbJ=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>0x48761caedd530497:0x3c47ace9c073f358</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>ChIJlwRT3a4cdkgRWPNzwOmsRzw</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.ubereats.com/gb/store/barrys-london-east/iWDy2xIdV4Sa6jyjIiRIOQ?diningMode=PICKUP\u0026utm_campaign=CM2508147-search-free-nonbrand-google-pas_e_all_acq_Global\u0026utm_medium=search-free-nonbrand\u0026utm_source=google-pas\u0026rwg_token=AE37R_hESEYlc0ZCssR_ldlfyAwlbEqhiJSZTtjybeV7fDBVCCc_qlwu1jsWxr4d-_z__ilJlj82qNLNFvde4gQ6HqBVQeWDDwGAoVFKfnZNJmpeRITiUew%3D","source":"ubereats.com"},{"link":"https://deliveroo.co.uk/menu/london/shoreditch/barrys-east?utm_medium=affiliate\u0026utm_source=google_maps_link\u0026fulfillment_type=DELIVERY\u0026rwg_token=AE37R_hZtLfLl8lPqLEFYqmOcrdHI0jcmU_-m9DzWox0KIJ_CoClXMyW-tXCS1Nd58reB9pLk-dJx_Smrl9ia-ZhZJhytYpxyW9vf1y9OfpIBw5DIwT1lMQ%3D","source":"deliveroo.co.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>{"id":"103846971124022100495","name":"Barry's London East (Owner)","link":"https://www.google.com/maps/contrib/103846971124022100495"}</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"2 Worship St, City Rd","city":"London","postal_code":"EC2A 1AH","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>[{"Name":"Daisy Ashford-Russell","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKH4WKqPzfdYQAgSrJWju-ZZSqJuL8sLoFvYTsjotrca1LWWQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Best workout in London, absolutely LOVE every Barry's class! All the trainers are amazing but Jake is incredible! So clear and encouraging!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tsTVVHUTNSRFZ2YjFOa1MwOHhRVVZUYkdkaWJHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108085727768258213702/reviews?hl=en-GB","posted_at_unix_micros":1779463783855867,"updated_at_unix_micros":1779463783855867,"language":"en","translated_lang":"","text_original":"Best workout in London, absolutely LOVE every Barry's class! All the trainers are amazing but Jake is incredible! So clear and encouraging!","text_translated":"","reply_text_original":"Thanks for the feedback!","reply_language":"en","reply_posted_at_unix_micros":1779791234000000,"reply_updated_at_unix_micros":1779791234000000,"published_at":"2026-05-22T15:29:43.855867Z"},{"Name":"Emma Still","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVzkKPPFF3t5Dc1vZ0dHSzjx7hqtE38OxDb2QHG0-FNhKfU1ik=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Came here today for my first visit, did total body with Jake.\nI was a bit nervous with it being my first time but all the staff were so lovely.\nJake was amazing, really brought such amazing energy to the class, and definitely pushed me to workout super hard!\nThanks so much will definitely be back!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tJeVh6bHdkMmRHTmtvMVFreHZUamRXVlZSMFVYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114315661431318877527/reviews?hl=en-GB","posted_at_unix_micros":1778256967402295,"updated_at_unix_micros":1778256967402295,"language":"en","translated_lang":"","text_original":"Came here today for my first visit, did total body with Jake.\nI was a bit nervous with it being my first time but all the staff were so lovely.\nJake was amazing, really brought such amazing energy to the class, and definitely pushed me to workout super hard!\nThanks so much will definitely be back!","text_translated":"","reply_text_original":"Thanks for the feedback!","reply_language":"en","reply_posted_at_unix_micros":1778620991000000,"reply_updated_at_unix_micros":1778620991000000,"published_at":"2026-05-08T16:16:07.402295Z"},{"Name":"Nikki Sx","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKbC2qE6n8nKPToVjKZhYLLmkpiQie09VWv_KLQArFtMSeoNxTZ=s120-c-rp-mo-ba12-br100","Rating":2,"Description":"Went in early morning to buy some leggings and a sports bra. Girl on the counter so so rude, wanted to let everyone and could not be bothered serving me, another girl served me. Absolutely terrible service and will never go again","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pWb2Jsa3lRbUV0ZUU1aFEycENSV05mWm5sbmRIYxAB","source":"Google","rating_scale":5,"rating_float":2,"author_url":"https://www.google.com/maps/contrib/102388165188787079061/reviews?hl=en-GB","posted_at_unix_micros":1784700655745102,"updated_at_unix_micros":1784700655745102,"language":"en","translated_lang":"","text_original":"Went in early morning to buy some leggings and a sports bra. Girl on the counter so so rude, wanted to let everyone and could not be bothered serving me, another girl served me. Absolutely terrible service and will never go again","text_translated":"","reply_text_original":"Hey Nikki, could you please email j.subohon@barrys.com so we can understand the situation better and ensure we can improve on this.\n\nThanks","reply_language":"en","reply_posted_at_unix_micros":1785744295000000,"reply_updated_at_unix_micros":1785744295000000,"published_at":"2026-07-22T06:10:55.745102Z"},{"Name":"Jessica A","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJqQ8wCmAXrozjb19IqWgPQvzGEMZsj02o32zIkQMNpHYu-WA=s120-c-rp-mo-br100","Rating":5,"Description":"Came here for my first Barry’s experience and loved it. Staff on reception were so incredibly helpful and friendly, Panos (instructor) was brilliant and changing/shower facilities were great! Not a single bad thing to note. The class really pushed me but in the best way possible, I didn’t realise I had that much endurance. I’ll be adding Barry’s into my exercise rotation based of this experience alone. 10/10","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2t3eE1ubHhSbVY0VkZWVmNWaG5VV3BWZUdKelNFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115707818255184523366/reviews?hl=en-GB","posted_at_unix_micros":1766338171483375,"updated_at_unix_micros":1766338171483375,"language":"en","translated_lang":"","text_original":"Came here for my first Barry’s experience and loved it. Staff on reception were so incredibly helpful and friendly, Panos (instructor) was brilliant and changing/shower facilities were great! Not a single bad thing to note. The class really pushed me but in the best way possible, I didn’t realise I had that much endurance. I’ll be adding Barry’s into my exercise rotation based of this experience alone. 10/10","text_translated":"","reply_text_original":"Thanks for the feedback","reply_language":"en","reply_posted_at_unix_micros":1767624388000000,"reply_updated_at_unix_micros":1767624388000000,"published_at":"2025-12-21T17:29:31.483375Z"},{"Name":"Kay Loves Food","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWNI9VfBhuBwCNAx5asemhVBiLVhVu2QFi8Wtbj88QLCswET7Y=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Had a great first experience at Barry’s in Barry’s East! The staff at the desk were helpful in their explanation and let us sit and wait for our friends to join. We found the towels and facilities organised and clean, albeit a bit cramped. The session was great, with an enthusiastic trainer. Enjoyed a shower and the products, as well as a smoothie each afterwards. This is a great place to go in your own or with a couple mates.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMfMIMzSQDDM4XPYZyILbaM74KMaUq9tDNryVqXTHRiES8FjkRRrmSccKE0MhyVYIm0aZh_PVeFo0ORntCJb_wrvobEhfs4bwHok7vJ1SvpfrFx0eV2PinJVDgPtOpVVcXekQpH=k-no"],"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnTURRbTdIbzZ3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108984869787822884122/reviews?hl=en-GB","posted_at_unix_micros":1741958678135781,"updated_at_unix_micros":1741958678135781,"language":"en","translated_lang":"","text_original":"Had a great first experience at Barry’s in Barry’s East! The staff at the desk were helpful in their explanation and let us sit and wait for our friends to join. We found the towels and facilities organised and clean, albeit a bit cramped. The session was great, with an enthusiastic trainer. Enjoyed a shower and the products, as well as a smoothie each afterwards. This is a great place to go in your own or with a couple mates.","text_translated":"","reply_text_original":"Thanks for your feedback!","reply_language":"en","reply_posted_at_unix_micros":1742200525000000,"reply_updated_at_unix_micros":1742200525000000,"published_at":"2025-03-14T13:24:38.135781Z"}]</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>13</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Victus+Soul+Aldgate/data=!4m7!3m6!1s0x4876035ed1d8e3c5:0xacc93da31d19ba5!8m2!3d51.5120918!4d-0.0732666!16s%2Fg%2F11fhw12f0t!19sChIJxePY0V4DdkgRpZvRMdqTzAo</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Victus Soul Aldgate</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Victus Soul, 90 Mansell St, London E1 8AL, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9:30 pm"],"Monday":["6 am–9:30 pm"],"Saturday":["8 am–5 pm"],"Sunday":["8 am–3 pm"],"Thursday":["6 am–9:30 pm"],"Tuesday":["6 am–9:30 pm"],"Wednesday":["6 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>http://www.victus-soul.com/</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>+44 20 7481 0896</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>GW6G+RM London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>278</v>
+      </c>
+      <c r="O80" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>{"1":40,"2":2,"3":6,"4":14,"5":216}</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>51.512092</v>
+      </c>
+      <c r="R80" t="n">
+        <v>-0.073267</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>778159400976227237</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmtoBYRe0FNnMYxH3wHmjWTv6FmCV47UyxwGfhttO6BNy9Z8qQ9P6vBxOMoXsr7wHVoxU7ueuqP_ugVZ3DU0waC5e8sjrrXPSino0QbGn3D0tlbVLM3T6aFkRaCWGkCcLVToJw=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>0x4876035ed1d8e3c5:0xacc93da31d19ba5</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>ChIJxePY0V4DdkgRpZvRMdqTzAo</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.victus-soul.com/vs/#/schedule/site/1/st/1764f8fd-b538-43ac-9255-c8e9a85ad783","source":"victus-soul.com"}]</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>{"id":"114279441160247791140","name":"Victus Soul Aldgate (Owner)","link":"https://www.google.com/maps/contrib/114279441160247791140"}</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Victus Soul, 90 Mansell St","city":"London","postal_code":"E1 8AL","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>[{"Name":"Adeline Gillet","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXk5S1XToa4Cc2CVK_dQzsku0nhirnO7wlwKSwmnGDYyIR15chU5A=s120-c-rp-mo-br100","Rating":5,"Description":"I have been coming to Victus Soul for a few years now, and I’m so grateful to have such an incredible, stylish, clean Reformer Pilates studio nearby. The teachers are not only lovely but also attentive and supportive, always helping you improve. A special thank you to Poppy, Mel, and Sydney, as well as Maddie, Jayda, and Alejandro at reception, who are always so welcoming and helpful. Five stars aren't enough for Victus Soul!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tKQlJXcFdlSHBYUkhOUVlrTldTMGgyU0d3eE5tYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103337709525739145860/reviews?hl=en-GB","posted_at_unix_micros":1785856149350409,"updated_at_unix_micros":1785856149350409,"language":"en","translated_lang":"","text_original":"I have been coming to Victus Soul for a few years now, and I’m so grateful to have such an incredible, stylish, clean Reformer Pilates studio nearby. The teachers are not only lovely but also attentive and supportive, always helping you improve. A special thank you to Poppy, Mel, and Sydney, as well as Maddie, Jayda, and Alejandro at reception, who are always so welcoming and helpful. Five stars aren't enough for Victus Soul!","text_translated":"","published_at":"2026-08-04T15:09:09.350409Z"},{"Name":"Lara Archer","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXqfKzlMQeJAA8TJ5wSoDMAxpqV1R5TW88wWfFzB7ruHEuRaBQ=s120-c-rp-mo-br100","Rating":5,"Description":"Had a brilliant experience at Victus Soul Aldgate yesterday. There was a little admin mishap meaning me and my group of friends weren’t notified about a timetable change, but the staff were amazing and called in an absolutely incredible instructor, called G, to take our class. G was such good fun, she had so much energy and kept us laughing and motivated throughout, she even let us choose the music to workout to and happily became a photographer for us at the end too! Thank you so much for such a wonderful class.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tWak1EVmxTVVJzUjBsMlRHeEJZMVpmVkVoVGFuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105706508264472858647/reviews?hl=en-GB","posted_at_unix_micros":1779052474085480,"updated_at_unix_micros":1779052474085480,"language":"en","translated_lang":"","text_original":"Had a brilliant experience at Victus Soul Aldgate yesterday. There was a little admin mishap meaning me and my group of friends weren’t notified about a timetable change, but the staff were amazing and called in an absolutely incredible instructor, called G, to take our class. G was such good fun, she had so much energy and kept us laughing and motivated throughout, she even let us choose the music to workout to and happily became a photographer for us at the end too! Thank you so much for such a wonderful class.","text_translated":"","published_at":"2026-05-17T21:14:34.08548Z"},{"Name":"James D","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK08wsL6RuBqYxnbqVJd-ht4hYlme6IWs1w5HZjZMC_bJ9fvQ=s120-c-rp-mo-br100","Rating":1,"Description":"Extremely disappointed by the decision of removing HIIT\u0026BOX classes after March.\nThe classes were always fully booked, and it was a unique opportunity in the Aldagate area to do heavybag workout with HIIT.\n\nThis could have been a 5 star review but thanks to this decision the gym will loose customers and I am aware that I am not the only one.\n\nHope they will understand how this decision will only push customers away.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xkbk5EWkVXVVpsWnpoeGRsTjZkVVpQUzJsb2NIYxAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/113053608301618424821/reviews?hl=en-GB","posted_at_unix_micros":1772651936311218,"updated_at_unix_micros":1772651936311218,"language":"en","translated_lang":"","text_original":"Extremely disappointed by the decision of removing HIIT\u0026BOX classes after March.\nThe classes were always fully booked, and it was a unique opportunity in the Aldagate area to do heavybag workout with HIIT.\n\nThis could have been a 5 star review but thanks to this decision the gym will loose customers and I am aware that I am not the only one.\n\nHope they will understand how this decision will only push customers away.","text_translated":"","published_at":"2026-03-04T19:18:56.311218Z"},{"Name":"Aaliyah Estrada","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXe-rtLsNVgQfN7g4fb77bbcrYzL00ckI4r_UqrXS6g5i0slphP=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Had my first reformer Pilates class here and was amazed by the focus the instructors had on me during the class helping me at any points I was lost. Loved her energy and the motivation she gave. Also loved the showers and amenities will be coming back!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmN1ms6uvhdyhqh_Y9JGbOe5eesQgO1c6XJq1XBCWxWbt6EFhKPGgmObFiVzFCNaA0xntdpkHCc__eI6TiZ0QTPcFD__DQuZT2gskwLsR2tsefO1Eqzta6URczHpk0jju-ka68QhdA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOCnYjU4GQGNeVJlF6hCC8y4gevLU5qHL1yfgpLltWYVAfLsZh24w5Z3qrNaAvOFmh3At6IMfcNtSz4Uc5mErFlhkCgK__7gbPII8dlfTHmzBbiG7jWoRvzflTZxEt_VmPDG6Go=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMXTKYDQ2UDPGX_DXIO0joIdXv_I_w7fSDofF2TzB6rwQzWdnl3IH7GEJOHnq-20xtm4l_iGmna1Zyu3_GanmPMJ-wqme6VAma3nda9Fs7b1FXTfOHuolRI17YO0_f6UOOdGz8RPA=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnTUNZOUpfTEtnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114026350604617403371/reviews?hl=en-GB","posted_at_unix_micros":1746143797341111,"updated_at_unix_micros":1746143797341111,"language":"en","translated_lang":"","text_original":"Had my first reformer Pilates class here and was amazed by the focus the instructors had on me during the class helping me at any points I was lost. Loved her energy and the motivation she gave. Also loved the showers and amenities will be coming back!","text_translated":"","published_at":"2025-05-01T23:56:37.341111Z"},{"Name":"Arielle","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVshgzk_5Fhe7GxwRa2pbnpGTSG_cM6QXm8WauKo7GmY9AkPXoo=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Really enjoyed the workout at this spot! We did the hit and run which was well structured, instructed, and fun. The studio is spacious and the workout facility/equipment felt new. The change rooms and amenities had everything you needed to get ready for the day. Will be back soon!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNSbHlDo4W86UnAj9ZyaG8MM5pSA1AMdOTmoMtB22clA3t4MGy1qSERtbA2Dn0FKbvZECI-4_upPXMe3vVqSe_JoC8qjpQTLy7ZEkPQdWhtA8gQZdx2q0ChS1O2zFX55j9SAfreuw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOjFFRY_X1UpqEXjsbuBP06Dav4MFokQCec72rZkcZH521I_yYkFCaFce48z_J-l0H67w4mjd0NXX4dknSn1VQcXLmEzIcxVQvpNOS1fidYm-0g8ZUmPPHhxz2NG77hYk1ulVGc=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMgciH-qjYnGuZC3pIkM9h0KLhfahzuTY8VM8Qym1LA6aIvpRq8xyYcAJ2kvZIaZ-oDh_BDQn8hHoGdTDZgp1K6eFjF5KVpduZGyTRO8AdshTvg6N8yvPKBzHt80Ds6gnCxHKtZsw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMm5TqC4AO3UMdijIJ8FaVF-J2gUEQUxODTgX3tpNFC7SLQ4WO0B-xuTKxY_FfcgaxwBJjmTFMkOHzDwvNUyK4GPSKLIVctVhj3uOWsRHvXJlLJaz_WAyEc9v8xfYvra-hiiHc=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMTj0PJkX90880Pcf6b-i5JP4RelOI-LxI12GGEMiY4TLXexlXUA3wvO-9rlp4k7jpZfqixKpHQjCAQ5NENRgO6mHI7EnHcx19lv1otI-cv9R_l8qzN254GOlVwFo6SAMsZIEad=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOOzO_HQ-wRwIg008HfIVqrH2sY6gs7G-magXkNfSdsyR7uw_vTINjwdz1fODQ7L0mbwHyPhHR6Dmdr-l5CM7aVjDcROEQmQID-qqcFhfLVQKSexf4AluiHaJosX5RNY99siQ=k-no"],"When":"2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNaLTdhSW53RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102506547161608577480/reviews?hl=en-GB","posted_at_unix_micros":1695105230676384,"updated_at_unix_micros":1695105230676384,"language":"en","translated_lang":"","text_original":"Really enjoyed the workout at this spot! We did the hit and run which was well structured, instructed, and fun. The studio is spacious and the workout facility/equipment felt new. The change rooms and amenities had everything you needed to get ready for the day. Will be back soon!","text_translated":"","published_at":"2023-09-19T06:33:50.676384Z"}]</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>13</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/ONE+LDN+%7C+High-Performance+Gym+%26+Fitness+Classes/data=!4m7!3m6!1s0x4876057f4506b915:0x32d74c9a3671a5cb!8m2!3d51.4736824!4d-0.1825503!16s%2Fg%2F11bwqfyds2!19sChIJFbkGRX8FdkgRy6VxNppM1zI</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ONE LDN | High-Performance Gym &amp; Fitness Classes</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Imperial Wharf the Boulevard, Imperial Wharf, 3 The Blvd, London SW6 2UB, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–8 pm"],"Monday":["6 am–9:30 pm"],"Saturday":["8 am–8 pm"],"Sunday":["8 am–8 pm"],"Thursday":["6 am–9:30 pm"],"Tuesday":["6 am–9:30 pm"],"Wednesday":["6 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>http://oneldn.com/</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>+44 20 3841 4401</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>FRF8+FX London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>274</v>
+      </c>
+      <c r="O81" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>{"1":32,"2":4,"3":8,"4":21,"5":209}</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>51.473682</v>
+      </c>
+      <c r="R81" t="n">
+        <v>-0.18255</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>3663481047111280075</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Modern gym with specialty classes</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Fitness center with equipment, personal training &amp; an array of classes, including yoga &amp; boxing.</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlfDwZTCVcFsyXvGQpi7WeyeGPew0LmTxORsFXfCGa1DYWRQCbYG2klUyAm4IT8XuPlQNRHd5qZcW4jBlCabsFENECrUkJ1f-TvBuNzNoRV2LBwLG7JffE4XQlPH6Ro_EXmRmQegRgtoqcw=w408-h612-k-no</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>0x4876057f4506b915:0x32d74c9a3671a5cb</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>ChIJFbkGRX8FdkgRy6VxNppM1zI</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>[{"link":"http://oneldn.com/book","source":"oneldn.com"}]</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>{"id":"113982121171669995101","name":"ONE LDN | High-Performance Gym \u0026 Fitness Classes (Owner)","link":"https://www.google.com/maps/contrib/113982121171669995101"}</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Imperial Wharf the Boulevard, Imperial Wharf, 3 The Blvd","city":"London","postal_code":"SW6 2UB","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>[{"Name":"TMA Kampfkunstschule","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVxDDBMyW_DepyTJG0J1R8BjvelZd7EXiCgBJb4HBsuXS4c4sANaQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I had the chance to train at ONE LDN and attended several classes, including HYROX, CrossFit, and Yoga. I can honestly say I was impressed across the board.\nThe coaching quality is outstanding. Every coach I trained with was knowledgeable, attentive, and excellent at explaining movements and techniques. Whether it was a high-intensity HYROX session, a challenging CrossFit workout, or a Yoga class, the instruction was always clear, professional, and motivating.\nWhat really stands out is the incredible value for money. The range of facilities and services available is remarkable. The gym is extremely well equipped, with everything you could possibly need for strength training, functional fitness, conditioning, and athletic performance. In fact, the equipment selection is even better than the photos suggest. When you see it in person, you realize just how much thought has gone into creating a complete training environment.\nI also made regular use of the recovery facilities, which were fantastic. The sauna gets properly hot, the two cold plunge pools are excellent, and the changing rooms and showers were consistently clean and well maintained.\nAnother highlight is the atmosphere. The staff are genuinely friendly and welcoming, and the members create a great culture. There’s no unnecessary ego or intimidating vibe. Instead, people are supportive, respectful, and focused on improving themselves while encouraging others to do the same.\nI also tried several of the shakes, and the selection was excellent—another nice touch that adds to the overall experience.\nI've trained in many gyms around the world, and ONE LDN is genuinely one of the best all-around fitness facilities I've visited. Great coaching, world-class equipment, excellent recovery options, a positive community, and exceptional value for what you get.\nHighly recommended. If you're looking for a place to train, recover, and be part of a strong fitness community, this is it. 💪🔥","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOT1B1KFsz6JO-KfzV8tGykcdXUl4lmRTLEjlqHx4PyNytSjyiJOcL5TIc3fltE1r-PQ0_cb5NdNZ3LGRiuHbPNk4tlXLxJSGO3yULBxngJMpqyQwJohdNFLAOHQTFTAERaCcBToANUhgUq=k-no"],"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT201bFFVcDZaVjh4U25wdU9YQktNa2gwWWxWRlMxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104078290538434765079/reviews?hl=en-GB","posted_at_unix_micros":1781509767618467,"updated_at_unix_micros":1781509767618467,"language":"en","translated_lang":"","text_original":"I had the chance to train at ONE LDN and attended several classes, including HYROX, CrossFit, and Yoga. I can honestly say I was impressed across the board.\nThe coaching quality is outstanding. Every coach I trained with was knowledgeable, attentive, and excellent at explaining movements and techniques. Whether it was a high-intensity HYROX session, a challenging CrossFit workout, or a Yoga class, the instruction was always clear, professional, and motivating.\nWhat really stands out is the incredible value for money. The range of facilities and services available is remarkable. The gym is extremely well equipped, with everything you could possibly need for strength training, functional fitness, conditioning, and athletic performance. In fact, the equipment selection is even better than the photos suggest. When you see it in person, you realize just how much thought has gone into creating a complete training environment.\nI also made regular use of the recovery facilities, which were fantastic. The sauna gets properly hot, the two cold plunge pools are excellent, and the changing rooms and showers were consistently clean and well maintained.\nAnother highlight is the atmosphere. The staff are genuinely friendly and welcoming, and the members create a great culture. There’s no unnecessary ego or intimidating vibe. Instead, people are supportive, respectful, and focused on improving themselves while encouraging others to do the same.\nI also tried several of the shakes, and the selection was excellent—another nice touch that adds to the overall experience.\nI've trained in many gyms around the world, and ONE LDN is genuinely one of the best all-around fitness facilities I've visited. Great coaching, world-class equipment, excellent recovery options, a positive community, and exceptional value for what you get.\nHighly recommended. If you're looking for a place to train, recover, and be part of a strong fitness community, this is it. 💪🔥","text_translated":"","reply_text_original":"Thanks for the incredible review! We love that you experienced exactly what ONE LDN is all about; elite coaching, world-class facilities, and a club where no trains alone.\n\nHopefully, we'll see you again to see next time you're in London!\n\nONE LDN\n","reply_language":"en","reply_posted_at_unix_micros":1782228144000000,"reply_updated_at_unix_micros":1782228144000000,"published_at":"2026-06-15T07:49:27.618467Z"},{"Name":"Bin Kallan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWAjZWT7rj61uxxy5gTprMLeYGHgl6gwtmv2UydVdvEfDurE-L9=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I was visiting for work from the States and the hotel next door doesn't have a gym. They recommended this place.\n\nI've been around many gyms and this one is one of the better ones. Lots of equipment, friendly staff, and people ACTUALLY working out!\n\nIt was refreshing and a delight to get my reps in.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOhHrtgtnnWncXPBLQyP2KHe8k68zsG9BMNEu5R-28GQt9G9il34kydkuFgT_VFdjSnvdXUzvL4a1F61Hhw7LMNxqLu7M5760hFimuxEcwTbttaSuVKrqxo8ijXabGVwm5EGNxA599YS0uO=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMKZZfl_nAVYHcP3t7IMHPqUz7a8dZhr0sOlzSZduzSMubBbm3ODA_Tmmw9utjg5MrIneVBuhak8cGKB0CxOwWqBdCqFfBl2Woei9EoYjo1c2Q7gvd1xs256ZE4dcu9gd1k_dd2gMZdlzjn=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNfqVg0tgm0fHI49bpMw9NOmWZ8atcFhmcsuEHtz9BNbywu1AlR7R_fiHHo_oD_Qym0E14LbjW2hrULuDfeNve3NtQYxNXdo4mT6YGE4AXF1PnVnYLprpnDtZYNjbGy3FcpGi6egj96dJAB=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2kxMlIwSlRhVkJpWkhoNVRFUkJObWd6Ym05SVNGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111548516183216616337/reviews?hl=en-GB","posted_at_unix_micros":1775666611834530,"updated_at_unix_micros":1775666611834530,"language":"en","translated_lang":"","text_original":"I was visiting for work from the States and the hotel next door doesn't have a gym. They recommended this place.\n\nI've been around many gyms and this one is one of the better ones. Lots of equipment, friendly staff, and people ACTUALLY working out!\n\nIt was refreshing and a delight to get my reps in.","text_translated":"","reply_text_original":"Hi Bin,\n\nThanks so much for this.\n\nWe love that you enjoyed using the gym - it's shame you were just passing through, but hopefully we'll see you again next time you're here!\n\nONE LDN\n\n","reply_language":"en","reply_posted_at_unix_micros":1783674989000000,"reply_updated_at_unix_micros":1783674989000000,"published_at":"2026-04-08T16:43:31.83453Z"},{"Name":"F P","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLUe2GERay2dpCYEgw7CRQzmfQq8KWpbbtbwF0kl4QnrE1f4g=s120-c-rp-mo-br100","Rating":5,"Description":"Joining this gym was my best decision after moving in London. Here you meet great people, from the staff to the athletes you train with. Everything is so smooth! From the membership management (big cheers to Sam, always available and super friendly) to the classes booking!!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tsVFV6ZGpSbWRtU2tGMmNrOTBjRVkyUzJjMVUwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111413807053935525215/reviews?hl=en-GB","posted_at_unix_micros":1783583501228328,"updated_at_unix_micros":1783583501228328,"language":"en","translated_lang":"","text_original":"Joining this gym was my best decision after moving in London. Here you meet great people, from the staff to the athletes you train with. Everything is so smooth! From the membership management (big cheers to Sam, always available and super friendly) to the classes booking!!","text_translated":"","reply_text_original":"Hey,\n\nThanks so much for leaving your review. We can't argue with you, Sam is great and we are lucky to have him!\n\nReally glad to hear that you've been having such a great experience at the gym, and we appreciate you sharing it.\n\nONE LDN","reply_language":"en","reply_posted_at_unix_micros":1783674706000000,"reply_updated_at_unix_micros":1783674706000000,"published_at":"2026-07-09T07:51:41.228328Z"},{"Name":"Maria","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXFUYn4XTxb4GA5jy_uPVwXOmg9nh_gnvu7pAmPFs_e92d19oUd9w=s120-c-rp-mo-br100","Rating":1,"Description":"The membership team sent me a cancellation of membership confirmation and then charged me over the cancellation contract date again which is actually illegal. When I contacted them they did not even tell me when I get my money back. I would stay away unless you want to deal with fraudulent charge cases after.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pKT2RVdFlZMmRWYWw4eU1FczBNR1ZLVFhFNVJWRRAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/111688440058408583576/reviews?hl=en-GB","posted_at_unix_micros":1782907208763620,"updated_at_unix_micros":1782907208763620,"language":"en","translated_lang":"","text_original":"The membership team sent me a cancellation of membership confirmation and then charged me over the cancellation contract date again which is actually illegal. When I contacted them they did not even tell me when I get my money back. I would stay away unless you want to deal with fraudulent charge cases after.","text_translated":"","reply_text_original":"Hi Maria,\n\nAs we’ve explained over email, there was a miscommunication on your cancellation date due to human error. Once you flagged this, we responded on the same day and processed your refund immediately too. Unfortunately, this review doesn’t fairly represent what happened.\n\nBest,\nONE LDN","reply_language":"en","reply_posted_at_unix_micros":1783598461000000,"reply_updated_at_unix_micros":1783598461000000,"published_at":"2026-07-01T12:00:08.76362Z"},{"Name":"Robert Crookall","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIgZNgA3mIyFU-6WOkI0qYYjzQzYqyhP6ekQG9B8BKcwkMJdw=s120-c-rp-mo-br100","Rating":5,"Description":"This gym is one of the best places to train in SW London. It has a huge range of equipment and motivational PT’s (not compulsory.) OneLDN caters for everyone, with numerous Hyrox and strength based, Pilates and yoga classes. There is a really inclusive, non intimidating atmosphere. The teachers are very experienced and the front desk and staff are friendly and most helpful. The ice baths and saunas are an additional bonus.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tzemMzVXhabVYzTW1Ka1JUQjJNM1JPZUVSaVYxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110334965480793011512/reviews?hl=en-GB","posted_at_unix_micros":1770288223670424,"updated_at_unix_micros":1770288223670424,"language":"en","translated_lang":"","text_original":"This gym is one of the best places to train in SW London. It has a huge range of equipment and motivational PT’s (not compulsory.) OneLDN caters for everyone, with numerous Hyrox and strength based, Pilates and yoga classes. There is a really inclusive, non intimidating atmosphere. The teachers are very experienced and the front desk and staff are friendly and most helpful. The ice baths and saunas are an additional bonus.","text_translated":"","reply_text_original":"Thanks so much for your review, and for being such a fantastic member Rob. Always a pleasure chatting to you at the club. We hope your training for London Olympia HYROX is going well, it's great to see you putting in the work - we’ll be there to support!\nONE LDN Team","reply_language":"en","reply_posted_at_unix_micros":1770647549000000,"reply_updated_at_unix_micros":1770739901000000,"published_at":"2026-02-05T10:43:43.670424Z"}]</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>13</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>c2406c1e-2fba-4c5c-8ab2-a599af517682</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Bootcamp+SE16/data=!4m7!3m6!1s0x487602dbd707b933:0x1bd4bf7d4ff48a6d!8m2!3d51.5012529!4d-0.0410821!16s%2Fg%2F11g6myv11g!19sChIJM7kH19sCdkgRbYr0T32_1Bs</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Bootcamp SE16</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Boot camp</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Dock Hill Ave, London SE16 6AX, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>{"Friday":["9 am–8 pm"],"Monday":["9 am–8 pm"],"Saturday":["9:30 am–4:30 pm"],"Sunday":["10 am–12 pm"],"Thursday":["9 am–8 pm"],"Tuesday":["9 am–8 pm"],"Wednesday":["9 am–8 pm"]}</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bootcampse16.co.uk/</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>+44 7496 871663</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>GX25+GH London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>270</v>
+      </c>
+      <c r="O82" t="n">
+        <v>5</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":1,"3":0,"4":2,"5":266}</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>51.501253</v>
+      </c>
+      <c r="R82" t="n">
+        <v>-0.041082</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>2005438279019956845</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnlotaOIRXLu9DucbbIGtXcKaaV18gxbfTchAv8lnOl_NVxG7yIuvLQeG6Y0Lmlvgu5Fp6geEpVVYLyC9NDCSvyItPnf1fJ55WDHfKO2tut39gaNrWN4q5t7j69dhGz9GuIlcH7Rw=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>0x487602dbd707b933:0x1bd4bf7d4ff48a6d</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>ChIJM7kH19sCdkgRbYr0T32_1Bs</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>[{"link":"https://go.acr.fit/widget/bookings/stephj","source":"acr.fit"}]</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>{"id":"108792915174556116848","name":"Bootcamp SE16 (Owner)","link":"https://www.google.com/maps/contrib/108792915174556116848"}</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Dock Hill Ave","city":"London","postal_code":"SE16 6AX","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>[{"Name":"Rita Base","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKEf2cJdQ3q_6SRoW06pDl3PWAZ2z1ZhyDhSOZH_nK0vKo82g=s120-c-rp-mo-br100","Rating":5,"Description":"I joined Bootcamp SE16 while on maternity leave because I wanted to get my body back, and the morning sessions were perfectly timed for my newborn's outdoor naps. More than two years later, I can honestly say it was one of the best decisions I've made.\n\nThe coaches are incredibly supportive and motivating, the sessions are challenging but suitable for all fitness levels, and the community is so welcoming. Every workout leaves me feeling stronger, fitter, and looking forward to the next one. I couldn't recommend Bootcamp SE16 more highly!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s0d1QzRnJYMjAxV0VwSlFrWXlXR3ByYzB0ME1uYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102727350197119873391/reviews?hl=en-GB","posted_at_unix_micros":1782981341262174,"updated_at_unix_micros":1782981341262174,"language":"en","translated_lang":"","text_original":"I joined Bootcamp SE16 while on maternity leave because I wanted to get my body back, and the morning sessions were perfectly timed for my newborn's outdoor naps. More than two years later, I can honestly say it was one of the best decisions I've made.\n\nThe coaches are incredibly supportive and motivating, the sessions are challenging but suitable for all fitness levels, and the community is so welcoming. Every workout leaves me feeling stronger, fitter, and looking forward to the next one. I couldn't recommend Bootcamp SE16 more highly!","text_translated":"","reply_text_original":"Thank you so much for this wonderful review, Rita. We’re thrilled Bootcamp SE16 fit perfectly into your maternity leave routine and that our morning sessions worked with your newborn’s naps. It’s great to hear the coaches, workouts, and community have supported your progress over the past two years. Your recommendation means so much and we look forward to many more sessions with you.","reply_language":"en","reply_posted_at_unix_micros":1782997254000000,"reply_updated_at_unix_micros":1782997254000000,"published_at":"2026-07-02T08:35:41.262174Z"},{"Name":"Daniela Melo","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXgJq4cv_hKdtA-Db7yW8LWBPHPHti9U4B5fmQpOfZLCiiktxM4=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"The energy from the coaches and the whole group is fantastic. Everyone has such a positive attitude, which makes every session really enjoyable.\n\nWhat I’ve liked the most so far is that the coach pays close attention to make sure you’re doing the exercises correctly. That way, you can avoid injuries and feel much more confident while training.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT20wek4zQk1ObE5aYUdJMFYwNWZkbFpQYzIxdWMzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115137725091670439700/reviews?hl=en-GB","posted_at_unix_micros":1783081378486936,"updated_at_unix_micros":1783081378486936,"language":"en","translated_lang":"","text_original":"The energy from the coaches and the whole group is fantastic. Everyone has such a positive attitude, which makes every session really enjoyable.\n\nWhat I’ve liked the most so far is that the coach pays close attention to make sure you’re doing the exercises correctly. That way, you can avoid injuries and feel much more confident while training.","text_translated":"","reply_text_original":"Thank you so much for the lovely review Daniela. We are really glad that you’re enjoying the sessions!","reply_language":"en","reply_posted_at_unix_micros":1783155170000000,"reply_updated_at_unix_micros":1783155170000000,"published_at":"2026-07-03T12:22:58.486936Z"},{"Name":"Linh Nguyen","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXMufFTTBzamg2agxziaaT-o3x20rd-dFRbFistxo4ZfZrdlAl7=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I finished my trial and have started my monthly membership with Bootcamp SE16 now. I’ve really enjoyed all the sessions I’ve been in so far, all the instructors are so kind and supportive.\nI needed help with my discipline and a structure for my routine, and the bootcamp really has given me motivation to get out and exercise. A hug bonus is that it also shows a big sense of community where everyone can work out at their own pace while being so encouraging towards others.\nLooking forward to seeing more results as I take more sessions ❤️.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2toQ2RGaDVjekYzTFZoS0xYSkVaMFpHYkRFMVRsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114636118794564738201/reviews?hl=en-GB","posted_at_unix_micros":1779285746215609,"updated_at_unix_micros":1779285746215609,"language":"en","translated_lang":"","text_original":"I finished my trial and have started my monthly membership with Bootcamp SE16 now. I’ve really enjoyed all the sessions I’ve been in so far, all the instructors are so kind and supportive.\nI needed help with my discipline and a structure for my routine, and the bootcamp really has given me motivation to get out and exercise. A hug bonus is that it also shows a big sense of community where everyone can work out at their own pace while being so encouraging towards others.\nLooking forward to seeing more results as I take more sessions ❤️.","text_translated":"","published_at":"2026-05-20T14:02:26.215609Z"},{"Name":"Liam McLeavey","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJkIkwW0u2i6H2zI_ebAfSpXCMkBNwsp7Fr19uekBMARdyqNkQ=s120-c-rp-mo-br100","Rating":5,"Description":"I genuinely can’t recommend Bootcamp highly enough. I’ve done around 10 classes now and I am honestly shocked at how much better I feel, both physically and mentally. I noticed a difference within the first couple of sessions, which really surprised me.\n\nThe onboarding experience with the amazing owner Steph is seamless and professional, and the instructors are incredibly knowledgeable, supportive, and motivating. Every class is thoughtfully structured so that different muscle groups are challenged each time, meaning your body is constantly progressing rather than plateauing. It’s a fabulous community of lots of different lovely people who are also supportive.\n\nThe value for money is excellent, especially considering the level of technical expertise and personal attention you receive. PT without the price tag I say! I’ve found the sessions far more productive than working out on my own in a traditional gym.\n\nIf you’re looking for something that will genuinely improve your fitness, energy, and mindset, Bootcamp is an outstanding choice 💪","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s5WFRtdzNhRmxZTlRkUFVGOTNjVFIwU1ZCUlEyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105954292247037120797/reviews?hl=en-GB","posted_at_unix_micros":1774706051420273,"updated_at_unix_micros":1774706051420273,"language":"en","translated_lang":"","text_original":"I genuinely can’t recommend Bootcamp highly enough. I’ve done around 10 classes now and I am honestly shocked at how much better I feel, both physically and mentally. I noticed a difference within the first couple of sessions, which really surprised me.\n\nThe onboarding experience with the amazing owner Steph is seamless and professional, and the instructors are incredibly knowledgeable, supportive, and motivating. Every class is thoughtfully structured so that different muscle groups are challenged each time, meaning your body is constantly progressing rather than plateauing. It’s a fabulous community of lots of different lovely people who are also supportive.\n\nThe value for money is excellent, especially considering the level of technical expertise and personal attention you receive. PT without the price tag I say! I’ve found the sessions far more productive than working out on my own in a traditional gym.\n\nIf you’re looking for something that will genuinely improve your fitness, energy, and mindset, Bootcamp is an outstanding choice 💪","text_translated":"","published_at":"2026-03-28T13:54:11.420273Z"},{"Name":"Suzie Cory","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJlgkLGMaSbf48PWMMugFIqUJ6BBngtEBPocPyFNsBtMtUikw=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I’ve been joining sessions now for about a month, I started in the 2 week trial. Steph and the team are really friendly and welcoming. They really give you the personal touch and make joining up easy and not intimidating. The classes are varied and as challenging as you make them - if you need to take it easier you can but the trainers also push you and encourage you to build and grow. Everyone at the sessions have been super welcoming, most people I e met so far have been going for anything between months and years! The session packages are also really flexible, I got the 2 weekly but have had to miss a couple weeks due to holiday and injury and it’s really easy to tack on sessions, you don’t lose your money which is great! Top tip, get gloves before your first session! Bear crawls up the park path are not fun on bare hands!!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25CZlpISnBTRE40UWxKSFlqSnJjelZ2TUZkU1pGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111875764159425722268/reviews?hl=en-GB","posted_at_unix_micros":1782319262953910,"updated_at_unix_micros":1782319262953910,"language":"en","translated_lang":"","text_original":"I’ve been joining sessions now for about a month, I started in the 2 week trial. Steph and the team are really friendly and welcoming. They really give you the personal touch and make joining up easy and not intimidating. The classes are varied and as challenging as you make them - if you need to take it easier you can but the trainers also push you and encourage you to build and grow. Everyone at the sessions have been super welcoming, most people I e met so far have been going for anything between months and years! The session packages are also really flexible, I got the 2 weekly but have had to miss a couple weeks due to holiday and injury and it’s really easy to tack on sessions, you don’t lose your money which is great! Top tip, get gloves before your first session! Bear crawls up the park path are not fun on bare hands!!","text_translated":"","reply_text_original":"Thank you so much for the wonderful review, Suzie. We’re thrilled the team made your trial and first month welcoming and that you find the classes adaptable and encouraging. It’s great to hear the flexible session packages worked well when you needed to miss time, and thanks for the gloves tip—bear crawls are definitely easier with them. We hope your injury has healed and look forward to seeing you back in sessions soon.","reply_language":"en","reply_posted_at_unix_micros":1782326092000000,"reply_updated_at_unix_micros":1782326092000000,"published_at":"2026-06-24T16:41:02.95391Z"}]</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>13</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/1Rebel+Broadgate/data=!4m7!3m6!1s0x48761cadbd97654f:0x3b75d58096a1ecd1!8m2!3d51.5184369!4d-0.0835825!16s%2Fg%2F11ckq_11hj!19sChIJT2WXva0cdkgR0eyhloDVdTs</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1Rebel Broadgate</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>31, 1Rebel Broadgate, 32 Lower Circle, Broadgate, London EC2M 2QS, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9 pm"],"Monday":["6 am–10 pm"],"Saturday":["7:30 am–6:30 pm"],"Sunday":["8 am–6:30 pm"],"Thursday":["6 am–10 pm"],"Tuesday":["6 am–10 pm"],"Wednesday":["6 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1rebel.com/en-gb</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>+44 20 3876 8719</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>GW98+9H London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>267</v>
+      </c>
+      <c r="O83" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>{"1":28,"2":10,"3":13,"4":29,"5":187}</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>51.518437</v>
+      </c>
+      <c r="R83" t="n">
+        <v>-0.083582</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>4284565368772619473</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk0WtErYzStrAVGQ1wQ7gjrUU1RooKhrezyEFq4aVqCtjUNYokgGBY_Mt4UaXAfNJB2TplxTI63_UsDrbu2mNb6pyQxQB71zPzZ71lCfMfjzQ1OC4gdr67shLAamKuTL2JihyPJwA=w408-h271-k-no</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>0x48761cadbd97654f:0x3b75d58096a1ecd1</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>ChIJT2WXva0cdkgR0eyhloDVdTs</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.1rebel.com/reserve/index.cfm?action=Reserve.chooseClass\u0026site=2","source":"1rebel.com"}]</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>{"id":"104638428080958750634","name":"1Rebel Broadgate (Owner)","link":"https://www.google.com/maps/contrib/104638428080958750634"}</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"31, 32 Lower Circle, Broadgate","city":"London","postal_code":"EC2M 2QS","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>[{"Name":"Theresa Carthy","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLIBLwoDGjaN3gI56j8lXNCqCS7QpOkBFEOpM7nEriODTGaJQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"1Rbeel has great workout classes! They are fun and challenging. This studio in particular has large changing rooms and plenty of space in both the Reshape and Reformer studios. They do enforce a strict punctuality policy as many reviews mention. When I've been late, the team has been very courteous about finding me another class even though I book through WellHub which is above and beyond.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pWUE1FcGhVVkExWms5S2N6Uk1VRzFVUjA1bFFYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110940466785142793994/reviews?hl=en-GB","posted_at_unix_micros":1775887785917568,"updated_at_unix_micros":1775887785917568,"language":"en","translated_lang":"","text_original":"1Rbeel has great workout classes! They are fun and challenging. This studio in particular has large changing rooms and plenty of space in both the Reshape and Reformer studios. They do enforce a strict punctuality policy as many reviews mention. When I've been late, the team has been very courteous about finding me another class even though I book through WellHub which is above and beyond.","text_translated":"","reply_text_original":"Hi Theresa, thank you for your lovely review, we look forward to seeing you again.","reply_language":"en","reply_posted_at_unix_micros":1775990244000000,"reply_updated_at_unix_micros":1775990244000000,"published_at":"2026-04-11T06:09:45.917568Z"},{"Name":"Joel C","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUkbju6DHIgtv31dfIQuGk7YAtvuPfWl22dsJHEI4Fb-mmYe8FM=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Amazing circuit workout, I enjoy ‘Reshape’ a lot. It emphasises not only physical strength but mental agility. Love the session.\n\nThe place is clean and tidy, lots of lockers. Towels are free, and they even do mint infused cold towel in the fridge which is free as well.\n\n45mins session, you would burn at least 600 calorie. Really addicted to reshape. The drinks are very delicious too, ranges from £5.5 to £7/£8 (if you customise).\n\nOne down side, the music may be too loud sometimes.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNLukMwSxW8xU-VxCD509hEZ22ISsHefVUrRaXBNaqvCM8Cq3Gft-cG1vTsP-7-z6YX-g7OuJdNJh2E0z61I4u-f6RsJNxGC-azE32sbrwtdM6iseWxhBypNTiv6zMxEvt01EaN=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMOs13JJ6bBFGay4uS-LY24Jx2EMflJawwPVmMYjqJebxGf4e55cZNQz6dN82uBdKpwFPU1-qiXAh6JehDjvslMT7yhwUsOljnjSoUCGgwxKjw_H_wKS8ct2AjzPeqZMqpsCedYEQ=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOWXCXKSNPWU4V5tImY5ESPKWUhCayq_V--yJ2Wr_yHGrSx_bhPPZBbYdUbz6YMazsGSQ70V6298umg74wZU9kFoPNKwPJhzbAfOVJ6qdhI_jpOC_cJpI8-jb1WoNuHJKrc3rPV=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNHLlkrRcrNHMp4u3ryHNyj3VGDaIlpBIBe4OqlSFwQ9OZ2vDoyrFXvCkz4kj2-sVjSZ0junvorScOs4VJLG1HvELfNaJ82u3lgmxTQFP2waG1EooqNFP9CKCrI5JuQabvYsT_Rlw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNRoT7ahUrsF_Ao8SI5W-U64YdUEm26cqvLHbpqdosdq6FwjiPuYqurQNQjskCvmTNQ7F4YUy6doVllUGPQOKLcrW52VLIKCv_8SUnKfIbzHzwUBYoxWDp2juvXUFEMZIz2I8c=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNcxc7PYzrC2aqnsbtqLoDQHh2V-IvoiMEggHACMztB5yhV6qLw5x38V-uqY7yTHYSbf5KvMnrY7LUtPU47F6S0drg_otDFQTSKMYIz_tqhyytGQaYmnoQs03IHtnW4HmZm4zxFgw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMfXSIWtN0vuV-eTC1CrWT2iBYS7CiRBHJSWsQ2HMxdoThRBGOZxBB2pqv018_E7zXE8E_zwE0hgQUgcfsv3OSx-hCvBLXhZAEyhS5WkdEPXSBVTivKdpDyyc2A6eUT075fNKSO=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURYdUplYU1REAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107056879959485563491/reviews?hl=en-GB","posted_at_unix_micros":1729733335729011,"updated_at_unix_micros":1729733335729011,"language":"en","translated_lang":"","text_original":"Amazing circuit workout, I enjoy ‘Reshape’ a lot. It emphasises not only physical strength but mental agility. Love the session.\n\nThe place is clean and tidy, lots of lockers. Towels are free, and they even do mint infused cold towel in the fridge which is free as well.\n\n45mins session, you would burn at least 600 calorie. Really addicted to reshape. The drinks are very delicious too, ranges from £5.5 to £7/£8 (if you customise).\n\nOne down side, the music may be too loud sometimes.","text_translated":"","reply_text_original":"Thank you for taking the time to write this wonderful review. We hope to see you back in the studio soon Joel!","reply_language":"en","reply_posted_at_unix_micros":1729846084000000,"reply_updated_at_unix_micros":1729846084000000,"published_at":"2024-10-24T01:28:55.729011Z"},{"Name":"Maria P","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVICWEPfKdXQtLcdxpQvnRJwhR92aHexq90la4Cm_83MX9V-ws=s120-c-rp-mo-br100","Rating":1,"Description":"It’s nearly impossible to get into classes in this gym unless you book 20 days in advance, so you’re basically paying a premium to sit on a waiting list. The bathrooms are smelly, poorly lit, and hot water is unreliable. A high-end gym should deliver high-end services, and this one falls well short.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25KVVFsTkNOa3h3T1dFMFR6QTFaV2R0WjJ0V1oyYxAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/116895165579310148207/reviews?hl=en-GB","posted_at_unix_micros":1770070452016285,"updated_at_unix_micros":1770070452016285,"language":"en","translated_lang":"","text_original":"It’s nearly impossible to get into classes in this gym unless you book 20 days in advance, so you’re basically paying a premium to sit on a waiting list. The bathrooms are smelly, poorly lit, and hot water is unreliable. A high-end gym should deliver high-end services, and this one falls well short.","text_translated":"","published_at":"2026-02-02T22:14:12.016285Z"},{"Name":"Libby Wales","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWAH021qC2CGXLH_Nx1aeMUNGi1NbojxkQjJQ6Yo7kjjWeUhmLS=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"First experience of 1rebel and it was great. Reshape with sanchez. Such a nice instructor and even though i was the only first timer he took the time to explain everything to me. Gave different levels for beginner to advance, music was great and as a runner it was perfect for strength \u0026 conditioning alongside interval work on the treadmill.  Changing rooms are really nice and spacious. Bike storage inside (bottom of the stairs before reception) which was great for peace of mind.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMzZebvYWGzF4PDwxWCB0ViP8m_bBJCEmpHaUJ1HZLoQuGd_h0ImznODtJIQSnrWj3rlgjOxHU9HbpFYUcj2koK3hE3ARorxTC_xcOG3KZ2DfXvPA0z2gXSCnr8Xf3eo7t7Ifc7-A=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNfdGZLbFp3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118146622056773770980/reviews?hl=en-GB","posted_at_unix_micros":1737154859669198,"updated_at_unix_micros":1737154859669198,"language":"en","translated_lang":"","text_original":"First experience of 1rebel and it was great. Reshape with sanchez. Such a nice instructor and even though i was the only first timer he took the time to explain everything to me. Gave different levels for beginner to advance, music was great and as a runner it was perfect for strength \u0026 conditioning alongside interval work on the treadmill.  Changing rooms are really nice and spacious. Bike storage inside (bottom of the stairs before reception) which was great for peace of mind.","text_translated":"","reply_text_original":"Thank you for taking the time to write this lovely feedback Libby. We hope to welcome you back in the studio soon! ","reply_language":"en","reply_posted_at_unix_micros":1737399031000000,"reply_updated_at_unix_micros":1737399031000000,"published_at":"2025-01-17T23:00:59.669198Z"},{"Name":"Blake Cronyn","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXFoWaQFRDM6EBMqqHkmEmTzKe9JFFNQv1QFT9rf2naChAYjhfhnA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"One of my favourite workouts in London. Whether it’s a treadmill workout (reshape) or boxing (rumble), it is always a great workout and sweat. I love mixing weights with cardio, so 1Rebel hits the spot! I also love being in Broadgate, so I can grab a pint after (if weather is nice) or watch a movie at Everyman Cinemas. Work hard, play hard!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMZVvGj6X7nBU1iBNZKeUjvcNwJwipeJ-dSI7RywYqzEEnB5PWY7O57yZbCh0azin__eoOxLQE_hGCRw5dhB71Oq7xCw95g90KkzakeLG_ycUwyVF2qmXvCuVtksFL36IjEH6tt=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOwofI6EtCgqPJ5zjn7I5EuwTar60UOumQkA5X3qd47ebah-44dwv7dkG6vEJZIYVtqHF-mgP_pYbq2ALiqaHRoGfxUJx99SFCLpTxzLejJIwrgBZpSp8n-O1C1WHMJ3NMXEkUNbw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM0qzY_hG3PYbW3fPPmpzkkPTU0lLuqFQ8tkkBw74M3-NREcgVU2Wv_Uab6YMHNaX2CqFvmSWekkFMpWPYcAf9bgXY_-cmsTHmLjHZwU5K7Zi-vjNVZ-BF3IJljvirv1VkRHgiq=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPpAij_4CwxP6FaRuhpbzc2_Z99f1UAVz672HZKPLogLJKMiPhJSrde2j8iWIERR_w9XKFIkQcvPuitBfaunRSYGN4jx17zHzU3_dSLQDMpFfcVQB8bIWUFa1t1CvMCp1QlCRb6gg=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPRrcMr9LtmayK-OCLrRb3BP-O7jTPUqumRMc9TzRfMKKaABMkVAH7WKnR3XDVzGBV750mjgXNMJOtxae3DRZlZAmo4_8uNIWp_rLVHBW0GirnbtJFEqRZp4TDAaQlAx8ypDF2S=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmN7nHK3Ka4X20Ud4PhzS_JYmGVrb8vXsr-AMuJjlS2WlqALXVa5L8UhAjDRnBSGnFWbDEPj0gEzAg4DEatZsajCZxxLYYWpqfUqwAMUChT1BRtOt5F6OslLHei06M7kH58mpD0zOw=k-no"],"When":"Edited 2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURwMi1tRFpnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103976262501546427886/reviews?hl=en-GB","posted_at_unix_micros":1693337723683043,"updated_at_unix_micros":1694765723224228,"language":"en","translated_lang":"","text_original":"One of my favourite workouts in London. Whether it’s a treadmill workout (reshape) or boxing (rumble), it is always a great workout and sweat. I love mixing weights with cardio, so 1Rebel hits the spot! I also love being in Broadgate, so I can grab a pint after (if weather is nice) or watch a movie at Everyman Cinemas. Work hard, play hard!","text_translated":"","reply_text_original":"Hi Blake. Thank you for this great rating and review. We look forward to seeing you again soon.","reply_language":"en","reply_posted_at_unix_micros":1694879630000000,"reply_updated_at_unix_micros":1694879630000000,"published_at":"2023-08-29T19:35:23.683043Z"}]</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>13</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6758c484-00e9-4c1c-a81f-56f19a65c71b</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Fitness+Lab/data=!4m7!3m6!1s0x487604e17e18728d:0x69f757fe062f1390!8m2!3d51.516607!4d-0.133026!16s%2Fg%2F11fzf7lckg!19sChIJjXIYfuEEdkgRkBMvBv5X92k</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Fitness Lab</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>5 Evelyn Yard, Rathbone Pl, London W1T 1HJ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9 pm"],"Monday":["6 am–9 pm"],"Saturday":["8 am–6 pm"],"Sunday":["8 am–6 pm"],"Thursday":["6 am–9 pm"],"Tuesday":["6 am–9 pm"],"Wednesday":["6 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>http://www.fitnesslab.fit/</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>+44 20 3494 4200</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>GV88+JQ London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>266</v>
+      </c>
+      <c r="O84" t="n">
+        <v>5</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":1,"4":2,"5":263}</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>51.516607</v>
+      </c>
+      <c r="R84" t="n">
+        <v>-0.133026</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>7635668441767023504</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkeAJBXQ_rkxEfI-R4cOdxH5Hop4wqUilu-y6FhRmCxHJ9VQZF99DT2NYSzhQiTgAIhPMwB3be91pYdYIalKXP7aPaQzhvBLPyiMJc7WnkUoul9FzdDJXNGf1iovzLjYe4oqbUnUvvvok5M=w432-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>0x487604e17e18728d:0x69f757fe062f1390</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>ChIJjXIYfuEEdkgRkBMvBv5X92k</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>[{"link":"https://fitnesslab.fit/contact-us/","source":"fitnesslab.fit"}]</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>{"id":"101511534820592771410","name":"Fitness Lab (Owner)","link":"https://www.google.com/maps/contrib/101511534820592771410"}</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"5 Evelyn Yard, Rathbone Pl","city":"London","postal_code":"W1T 1HJ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>[{"Name":"Senam D","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVNJ1fyiKBiMfPhJIKtG-PEmrohPZ0M7xMJQux_JyTtbtcCWPo=s120-c-rp-mo-br100","Rating":5,"Description":"I have felt fully supported by the team at Fitness Lab and couldn't recommend it more!\n\nEach session feels tailored to your individual needs, whether you’re just starting out or looking to push your limits.\n\nWhat I appreciate most is how supportive and encouraging my trainer is which makes a big difference in staying consistent and, most importantly, building confidence.\n\nThe overall atmosphere is friendly and I would definitely recommend this company to anyone looking for high-quality personal training and a great fitness environment!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xsaGVraHBSVzlDVVVOUk5EQjRiVjlSY21ocVVtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109553514946026082652/reviews?hl=en-GB","posted_at_unix_micros":1776157031548694,"updated_at_unix_micros":1776157031548694,"language":"en","translated_lang":"","text_original":"I have felt fully supported by the team at Fitness Lab and couldn't recommend it more!\n\nEach session feels tailored to your individual needs, whether you’re just starting out or looking to push your limits.\n\nWhat I appreciate most is how supportive and encouraging my trainer is which makes a big difference in staying consistent and, most importantly, building confidence.\n\nThe overall atmosphere is friendly and I would definitely recommend this company to anyone looking for high-quality personal training and a great fitness environment!","text_translated":"","reply_text_original":"Hi Senam, thank you so much for your review - we really, really appreciate it. We’re so pleased that your personal training experience has been positive. Looking forward to seeing you in the Fitzrovia PT studio again soon. All the best from the entire personal trainer team at Fitness Lab 🙏","reply_language":"en","reply_posted_at_unix_micros":1776167359000000,"reply_updated_at_unix_micros":1776167359000000,"published_at":"2026-04-14T08:57:11.548694Z"},{"Name":"Firaas Rashid","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJL4n59-e0CuxOz58yWnyeKMp_sUljGGqD_sz0VfjBkIRipjmt4=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I have been training here for a few months and love the facility. Jack the owner personally checks in and is very quick at handling any questions or issues. Training with Dan has been awesome and I am very pleased to have made a lot of progress in fitness and health.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tacGExVkpNMjlYWVdsRmNuRlhjVzQ1VGpGVlozYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112104795402497611332/reviews?hl=en-GB","posted_at_unix_micros":1783085271170053,"updated_at_unix_micros":1783085271170053,"language":"en","translated_lang":"","text_original":"I have been training here for a few months and love the facility. Jack the owner personally checks in and is very quick at handling any questions or issues. Training with Dan has been awesome and I am very pleased to have made a lot of progress in fitness and health.","text_translated":"","reply_text_original":"Hi Firaas, thank you so much for the review, we really appreciate it. We’re so pleased that your personal training experience with us at Fitness Lab in Fitzrovia has been positive. Looking forward to seeing you in the studio soon. All the best from the entire personal trainer team at Fitness Lab 🙏💪🙏","reply_language":"en","reply_posted_at_unix_micros":1783090434000000,"reply_updated_at_unix_micros":1783090434000000,"published_at":"2026-07-03T13:27:51.170053Z"},{"Name":"Abby Dunlavy","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX6ru_Tc4a_8XnNnLsYCRDin9bFiOmE4vWVgsLsaB3oBoA5riKF=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I trained with Tom in Fitzrovia and couldn’t recommend him more! He tailored everything to my specific goals and worked around various injuries that have all gotten much better through our training. If you’re considering training with him or at Fitness Lab in general do!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psdlgxOXpjbGROUjA5YVdYWkVSM2d4Um1WRVFXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102461198535808677387/reviews?hl=en-GB","posted_at_unix_micros":1784381928872925,"updated_at_unix_micros":1784381928872925,"language":"en","translated_lang":"","text_original":"I trained with Tom in Fitzrovia and couldn’t recommend him more! He tailored everything to my specific goals and worked around various injuries that have all gotten much better through our training. If you’re considering training with him or at Fitness Lab in general do!","text_translated":"","reply_text_original":"Hi Abby, we can’t thank you enough for your review and we’re so pleased that your personal training experience with us has been positive. We know your personal trainer Tom loves seeing you for your regular PT sessions. Looking forward to seeing you in the studio soon. All the best from the entire team at Fitness Lab 🙏💪🙏","reply_language":"en","reply_posted_at_unix_micros":1784383454000000,"reply_updated_at_unix_micros":1784383454000000,"published_at":"2026-07-18T13:38:48.872925Z"},{"Name":"Rosie","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWmO0nIxobmocsn-1xG6iJQ0NjATa5Yc_1zW4pjLJxFcFTpxEiy-w=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"The Fitness Lab team really know what they’re doing! I’ve had previous personal trainers, but not at this level with attention to detail and support. It’s been so easy to fit it into my routine, and I’ve found that this is the most consistent with training I’ve been. The private spaces mean you don’t have the overbearing equipment sharing struggles that you find in commercial gyms, so I look forward to my session every time. Really recommend them","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSWFVUZFdhRzl5ZEZGemFWcEpVRmhrUkV0NU5VRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103950646266773701383/reviews?hl=en-GB","posted_at_unix_micros":1776764194180087,"updated_at_unix_micros":1776764194180087,"language":"en","translated_lang":"","text_original":"The Fitness Lab team really know what they’re doing! I’ve had previous personal trainers, but not at this level with attention to detail and support. It’s been so easy to fit it into my routine, and I’ve found that this is the most consistent with training I’ve been. The private spaces mean you don’t have the overbearing equipment sharing struggles that you find in commercial gyms, so I look forward to my session every time. Really recommend them","text_translated":"","reply_text_original":"Hi Rosie, thank you SO much for your review. We’re so happy that your personal training experience has been great. Looking forward to seeing you at Fitness Lab for more PT soon. Thanks again 🙏💪","reply_language":"en","reply_posted_at_unix_micros":1776774006000000,"reply_updated_at_unix_micros":1776774006000000,"published_at":"2026-04-21T09:36:34.180087Z"},{"Name":"Laura Cansdale","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIa9mROZnA0NnJxime7YbNIZlW-NDF2p-ZVmFJqK92_2yWFlw=s120-c-rp-mo-br100","Rating":5,"Description":"Miguel is an incredible PT - I could not rate him more. Having never been inside a gym before, I was immediately put at ease. I am now look forward to working out and my friends are very confused by this transformation!\n\nI cannot rate Miguel any higher. I am constantly impressed by his training methods and his knowledge. I am empowered by his support, his positivity and his motivation. I should’ve started working out with Miguel years ago. My body and my outlook on my health is being transformed.\n\nThe facilities and equipment are excellent, the prices are very reasonable for the area and he is popular with his dedicated client base. I hope to work out with Miguel for years to come.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT210UVRqTXlRMTlxYlV0cGRWSm5kVEJyY1RCdVdYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100965273231627264238/reviews?hl=en-GB","posted_at_unix_micros":1769807790063089,"updated_at_unix_micros":1769807790063089,"language":"en","translated_lang":"","text_original":"Miguel is an incredible PT - I could not rate him more. Having never been inside a gym before, I was immediately put at ease. I am now look forward to working out and my friends are very confused by this transformation!\n\nI cannot rate Miguel any higher. I am constantly impressed by his training methods and his knowledge. I am empowered by his support, his positivity and his motivation. I should’ve started working out with Miguel years ago. My body and my outlook on my health is being transformed.\n\nThe facilities and equipment are excellent, the prices are very reasonable for the area and he is popular with his dedicated client base. I hope to work out with Miguel for years to come.","text_translated":"","reply_text_original":"Thank you for the kind review.","reply_language":"en","reply_posted_at_unix_micros":1777557684000000,"reply_updated_at_unix_micros":1777557684000000,"published_at":"2026-01-30T21:16:30.063089Z"}]</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>13</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>c2406c1e-2fba-4c5c-8ab2-a599af517682</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Barry%27s+London+SW1/data=!4m7!3m6!1s0x487605220f793bc9:0x364b92a37a4ca81c!8m2!3d51.4938005!4d-0.1485074!16s%2Fg%2F11gf9pmnd4!19sChIJyTt5DyIFdkgRHKhMeqOSSzY</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Barry's London SW1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>16 Eccleston Yards, London SW1W 9AZ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–9:30 pm"],"Monday":["5:30 am–9:30 pm"],"Saturday":["7 am–7:30 pm"],"Sunday":["7 am–7:30 pm"],"Thursday":["5:30 am–9:30 pm"],"Tuesday":["5:30 am–9:30 pm"],"Wednesday":["5:30 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barrysbootcamp.com/studio/barrys-bootcamp-sw1/</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>+44 20 3954 2074</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>FVV2+GH London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>260</v>
+      </c>
+      <c r="O85" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>{"1":13,"2":12,"3":4,"4":21,"5":210}</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>51.4938</v>
+      </c>
+      <c r="R85" t="n">
+        <v>-0.148507</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>3912381932130576412</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlpPAelEZ1Q_n-n0A8bj8Cuq9psLdmZFAaon41Kf5uHnJ_qMXqWJx9184YDmHRNUDERUl2j9dk3oJOLYjAL-QYYc9K0Hgl6L5YUN-bWokhmaYLVtHYxTT5aGcfYc1S9VWoUJo5v=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>0x487605220f793bc9:0x364b92a37a4ca81c</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>ChIJyTt5DyIFdkgRHKhMeqOSSzY</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>[{"link":"https://deliveroo.co.uk/menu/london/belgravia/barrys-sw1w?utm_medium=affiliate\u0026utm_source=google_maps_link\u0026fulfillment_type=DELIVERY\u0026rwg_token=AE37R_gQwzW72duMXVn2yYLays9nw8BDNFgKMRp5HV-NHJrcWx8ZYNXWtMy2-Y7qWCq3ZsJiF6OrLSa-ltXTfJOThkmz1AaptqL1Lu3kWVIPpTUuSZTPQmk%3D","source":"deliveroo.co.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>{"id":"114294244276684048028","name":"Barry's London SW1 (Owner)","link":"https://www.google.com/maps/contrib/114294244276684048028"}</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"16 Eccleston Yards","city":"London","postal_code":"SW1W 9AZ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>[{"Name":"Sarah Murphy","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIVjPOIDs72SKIZ4ZT405afM83o6CBfXFUStanlHyfP65_wmQ=s120-c-rp-mo-ba12-br100","Rating":4,"Description":"Loved our class with Lu. But had an awful class with Amelie and would never do one of her classes again. Very difficult to understand and doesn’t enunciate. Timings throughout her class were incorrect eg saying a run would be 60s and ending it at 35-40s. And the floor portion of the workout was chaotic and like she had not prepared. Perhaps she is new to the classes but I Wouldn’t recommend her classes, and if it hadn’t been for Lus class I wouldn’t recommend the studio.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNgXLNfY_YcJbWwrkZx-5n3Alj2iupe_zo9aR21pKiO2qj8xyA4ZkNXdXO-s4aM_OMrf17CseiX01itYrLU9KtaIIveSIEBoG6iWF8mcN152EsUnAQvLQKMmM7mBGOumROlAZZNh8vInTxN=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xOcVpEaFdUR0o2UmxGSVVFSldOWHBETkZjdFNGRRAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/112144014657091050208/reviews?hl=en-GB","posted_at_unix_micros":1771241345123155,"updated_at_unix_micros":1771241345123155,"language":"en","translated_lang":"","text_original":"Loved our class with Lu. But had an awful class with Amelie and would never do one of her classes again. Very difficult to understand and doesn’t enunciate. Timings throughout her class were incorrect eg saying a run would be 60s and ending it at 35-40s. And the floor portion of the workout was chaotic and like she had not prepared. Perhaps she is new to the classes but I Wouldn’t recommend her classes, and if it hadn’t been for Lus class I wouldn’t recommend the studio.","text_translated":"","reply_text_original":"Thanks for the feedback! Sorry to hear you didn't enjoy Amelie's class as she's an incredible trainer. We will touch base with the team to ensure the feedback has been passed on.","reply_language":"en","reply_posted_at_unix_micros":1771251452000000,"reply_updated_at_unix_micros":1771251452000000,"published_at":"2026-02-16T11:29:05.123155Z"},{"Name":"Catie Mc Nama","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV1-Uq8XLwqAZbeFtzLXPFV1ceNdzZrUsaAma6b1E_u4tF7ggYf=s120-c-rp-mo-br100","Rating":5,"Description":"Barry’s SW1 is hands down my favourite place to workout in London! I have tried many different studios and companies but this particular studio is my favourite - it is very spacious and clean, so you never feel overcrowded, which is a real plus in London. The classes are incredibly high-energy, and the instructors are fantastic - motivating, attentive, and accommodating to all fitness levels. The front desk team is lovely and welcoming, making you feel right at home from the moment you walk in. The whole vibe, from the music to the atmosphere, is unmatched. Barry’s SW1 is literally a dream😍","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPuN757UxZCcGs13yv1nuFmcPipusrMZTTHTCnW_wCbnpVxwb3AhvhcGmEbCh1RpYGwKXuEMvUrivD75UfS-c45Vx_JQDiRnwZP34wX3BAy5YJBmgg2H-kH2l0pAEgalBck42-g=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmP4jd6QbYMYvWLDnXMoZp3IrmTg5SJ5Pc95GACwWHZartcLEpL5coLk2CpMIZg4soZs9JaWMpqTgSj2EZOhfnDpP2u6Hdt7a0tNnzwKoqDV2xePVkG31KZh9wFULJmkQD1BlR1G=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO1_x0gPyrFbqECfeN4ANHwLFK_5dr6ltxl9MJIzPowIlTP1ycL5oDPnwku-ltdF5pXBDCvSRaSIHiWHJEM0pR83Xh5EnzkYe7cQQc4sfL0gBtQ9u7RtF7R16g1PX5uCK3SYmpH=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUQzMXRTMFpBEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101238632217661335711/reviews?hl=en-GB","posted_at_unix_micros":1731620687881432,"updated_at_unix_micros":1731620687881432,"language":"en","translated_lang":"","text_original":"Barry’s SW1 is hands down my favourite place to workout in London! I have tried many different studios and companies but this particular studio is my favourite - it is very spacious and clean, so you never feel overcrowded, which is a real plus in London. The classes are incredibly high-energy, and the instructors are fantastic - motivating, attentive, and accommodating to all fitness levels. The front desk team is lovely and welcoming, making you feel right at home from the moment you walk in. The whole vibe, from the music to the atmosphere, is unmatched. Barry’s SW1 is literally a dream😍","text_translated":"","reply_text_original":"Thanks so much for the feedback!","reply_language":"en","reply_posted_at_unix_micros":1731680635000000,"reply_updated_at_unix_micros":1731680635000000,"published_at":"2024-11-14T21:44:47.881432Z"},{"Name":"Sherman Bok [IG shermeenator]","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUIwoEq1jHKSTUq-HJplAILUY0bZaG_jBofoJL9y8uziK5PB5M=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great location, near Victoria Coach station and rather central, but still enclosed cosily in a small courtyard.\n\nInstructors were also good, consistent with Barrys globally, and staff were also welcoming.\n\nFacilities all well maintained and spacious.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMOTxrR9j3to0Iccp7ODr9p9PsFjnelc456wBkqBDEh-BVDQKo3rLwh_2hTt4KLuTnQONqwEf7CkIHPZmrOiecXIagUFRTTHcMQixE4fOkX1MPSE6Ira6hdLw3r62Rca9VeUTmWzA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOqcLAAcEOSClLKZa8WV_TV1nXOOMiZ0ByaB-a-YcBgCs3NT17BA4tBci4mVBM1Q4QGpp96tWsAbpUe_4wCu8_MePFJLrKFYefcbuR2MrpJ6JnOzLOp9ANKY20299rvmzU69hi6=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPZbLIDluzUzdA0-jgCxNqK3RkrDJakMTceCXTR4vmFYhXK4Mm7CxEtuEUo0JFL6hyyv4vKEq91qUMcxojRV1hFh4ecHN9yVCo-i6pSSVwxf9lUjs8rmFXqbU7ljNhWRSny4Alx=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOiiqd_m5Ob0RdeYAdnw3_MsBNf8lEx46GFvllVwIUWOO-y617yAGHeJFAz9_uQ_AtL9w7_VllhsEvV8fkzekhthPLGVL-SJbcprY_6AfSRSIX5pbD3-DGW0fjlveFQm6cMYgWR=k-no"],"When":"Edited 3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURSLTZuTUlREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101219516959550521307/reviews?hl=en-GB","posted_at_unix_micros":1683234738423077,"updated_at_unix_micros":1688748780572926,"language":"en","translated_lang":"","text_original":"Great location, near Victoria Coach station and rather central, but still enclosed cosily in a small courtyard.\n\nInstructors were also good, consistent with Barrys globally, and staff were also welcoming.\n\nFacilities all well maintained and spacious.","text_translated":"","published_at":"2023-05-04T21:12:18.423077Z"},{"Name":"Adrianna Rokit","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLfV9nYGCdaBiJ1OiKoeZUyx_qLWPeFvl6dh5PcESDM7oLVmQ=s120-c-rp-mo-br100","Rating":1,"Description":"The receptionists working on 26th March (PM) were so unprofessional and wouldn’t stop glaring, making fun of clients’ appearance while laughing hysterically and face-palming. It is quite evident that their parents failed to educate them on the Golden Rule. Any reasonable person would know that the common areas are a space for clients to relax and/or be productive and it is impossible to do that with these eye-sore receptionists that aren’t even trying to be discreet. I was not informed that this was a pre-school and not a gym. I could make fun of them as well but I won’t do so as I was brought up to treat others with respect and decency.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSVU1EUkdaMjlIWm0xaFpUaG5OSFZXUmt3dFpGRRAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/115127119212420578276/reviews?hl=en-GB","posted_at_unix_micros":1774568642607305,"updated_at_unix_micros":1774568672029299,"language":"en","translated_lang":"","text_original":"The receptionists working on 26th March (PM) were so unprofessional and wouldn’t stop glaring, making fun of clients’ appearance while laughing hysterically and face-palming. It is quite evident that their parents failed to educate them on the Golden Rule. Any reasonable person would know that the common areas are a space for clients to relax and/or be productive and it is impossible to do that with these eye-sore receptionists that aren’t even trying to be discreet. I was not informed that this was a pre-school and not a gym. I could make fun of them as well but I won’t do so as I was brought up to treat others with respect and decency.","text_translated":"","reply_text_original":"Hey Adriana,\n\nI’m so sorry to hear about your recent experience at Barry's UK. Our SW1 team is incredibly thoughtful, and I hope there may have been a miscommunication during your visit.Unfortunately, I can't find anyone on our system matching the name specified in your review, but I would love to speak with you further to understand what happened. Please email me at k.khanna@barrys.com so we can speak on this matter further and hopefully make it up to you.Thank you for bringing this to our attention, and we look forward to resolving it.\n\nThanks\n\nBarry's UK","reply_language":"en","reply_posted_at_unix_micros":1774603688000000,"reply_updated_at_unix_micros":1774603688000000,"published_at":"2026-03-26T23:44:02.607305Z"},{"Name":"Andrew Curtis","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUJg1vQUwK-5Y8cXZz3hzoGd9C4oJ_vOE_lNMLCJv0kBhDSMfsfKg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Fantastic session with Emma today — really motivating, clear coaching and a great balance of treadmill and strength work. Pushed me in the right way and left feeling energised. Will definitely be back. 🏃‍♂️🥵💪","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwRGFUWTNVa3h5WTJwa2Jtd3hhVVp6WW1zMWQzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106164615921908622057/reviews?hl=en-GB","posted_at_unix_micros":1775911895361483,"updated_at_unix_micros":1775911895361483,"language":"en","translated_lang":"","text_original":"Fantastic session with Emma today — really motivating, clear coaching and a great balance of treadmill and strength work. Pushed me in the right way and left feeling energised. Will definitely be back. 🏃‍♂️🥵💪","text_translated":"","reply_text_original":"Thanks for the feedback!","reply_language":"en","reply_posted_at_unix_micros":1776069503000000,"reply_updated_at_unix_micros":1776069503000000,"published_at":"2026-04-11T12:51:35.361483Z"}]</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="inlineStr"/>
+      <c r="AN85" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>13</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Barry%27s+London+Central/data=!4m7!3m6!1s0x48761b2516995329:0x175f66d48275afc2!8m2!3d51.5270351!4d-0.1310268!16s%2Fg%2F1pp2x6hg1!19sChIJKVOZFiUbdkgRwq91gtRmXxc</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Barry's London Central</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>163 Euston Rd., London NW1 2BH, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–8:30 pm"],"Monday":["5:30 am–8:30 pm"],"Saturday":["7 am–3:30 pm"],"Sunday":["7 am–3:30 pm"],"Thursday":["5:30 am–8:30 pm"],"Tuesday":["5:30 am–8:30 pm"],"Wednesday":["5:30 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barrysbootcamp.com/studio/london-central/</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>+44 20 7387 7001</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>GVG9+RH London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>246</v>
+      </c>
+      <c r="O86" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>{"1":12,"2":3,"3":11,"4":23,"5":197}</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>51.527035</v>
+      </c>
+      <c r="R86" t="n">
+        <v>-0.131027</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1684177848567705538</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnITMgHlzkhSGf3Ichig7Yy5CF2AJ5Pj2tc9tZcidIEKnCXD3RIsOxo12n77-8TAPG5puqEFPjLYrdXYRoe3zmWt304Ii185BLxi1smT6154WRywodqbyZAY6L8gu6EGAbjJvo=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>0x48761b2516995329:0x175f66d48275afc2</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>ChIJKVOZFiUbdkgRwq91gtRmXxc</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.ubereats.com/gb/store/barrys-london-central/Skj_zAjZXMKN67pBqRp8Ww?diningMode=PICKUP\u0026utm_campaign=CM2508147-search-free-nonbrand-google-pas_e_all_acq_Global\u0026utm_medium=search-free-nonbrand\u0026utm_source=google-pas\u0026rwg_token=AE37R_ivwBSIVXToGEakPFNqe6tUOYHVcHwKuATdUYHOtsrXU_4Di6F9ughdVzQPBNPR2c76Y7D95JKxSlHGYPCvPgmiVQwiOw%3D%3D","source":"ubereats.com"},{"link":"https://deliveroo.co.uk/menu/london/bloomsbury/barrys-central?utm_medium=affiliate\u0026utm_source=google_maps_link\u0026fulfillment_type=DELIVERY\u0026rwg_token=AE37R_jU6xR-eaXse3P3qCquMZSO9rHkS3UuWepHwg_9_uFK5sHTX67DtMhnaU74AQViHy_sq8PsXAlTYmwdUHWuMKfAxm4J8Q%3D%3D","source":"deliveroo.co.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>{"id":"114569297044798154202","name":"Barry's London Central (Owner)","link":"https://www.google.com/maps/contrib/114569297044798154202"}</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"163 Euston Rd.","city":"London","postal_code":"NW1 2BH","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>[{"Name":"Jason Parmar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWgRIUKqHCqTkkK0kIiiwdeG4qQNfwCUa-2TUtjOH2MSFq1ckAL_w=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Honestly one of the best workouts anywhere, we even went the morning of our wedding! 😂💪\nWe kept pretty fit before but started going a month before marriage to get “wedding fit” and it’s the real deal. The “OG” and “best workout in the world” is factual and ultimately worth the extra price premium vs the alternatives.\nThe staff \u0026 instructors are awesome, facilities are top notch and workout is unbeatable!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNqF8s6oi1ljY-tOhGJ_4gF0GKTI3dozNwx0H6MZvti4DfyX1MLoiYTkXpuhEwNaLQQLGXIOywa5RlAaRZpx1FShhdFN-uK8rVV69V-91e13KX6iaqNskzPDgnmPb_rPWXGBxthX3HikXM=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNTRin9Xesk7CYuXM-rb1A3iV9ns-LmMYKu-703Wsd045mSyJ2twQ_LLbR_P1xMCOwEyvJ4nwKiOKjRrGg5XuCv0Cxar62wa447Irl3w2TTbQzFKQQ-f9Q99ar874RGiQYqoDqE1fQ3Xasj=k-no"],"When":"Edited a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25GWFJESk9XWFE1UkhjM1NucGpRMWROT0c5ZmRYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110390738897622726957/reviews?hl=en-GB","posted_at_unix_micros":1753372993759435,"updated_at_unix_micros":1756032271147363,"language":"en","translated_lang":"","text_original":"Honestly one of the best workouts anywhere, we even went the morning of our wedding! 😂💪\nWe kept pretty fit before but started going a month before marriage to get “wedding fit” and it’s the real deal. The “OG” and “best workout in the world” is factual and ultimately worth the extra price premium vs the alternatives.\nThe staff \u0026 instructors are awesome, facilities are top notch and workout is unbeatable!","text_translated":"","reply_text_original":"Thanks for the feedback!","reply_language":"en","reply_posted_at_unix_micros":1754398054000000,"reply_updated_at_unix_micros":1754398054000000,"published_at":"2025-07-24T16:03:13.759435Z"},{"Name":"Danielle Louise","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVmKd7dXDsng9_ukjsV5QhfJviR4cZj51y997meY4KdzHevu8c=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Best workout of my life! Love that it’s dark with red lights, music is loud, instructions are clear and there’s no judgement - it’s just you vs you. Intensely hard work cardio and weights. Instructors are awesome, super friendly but they push you, are motivating and encouraging even for first timers. Showers and changing room area is lovely - towels provided, Malin \u0026 Goetz toiletries, hairdryers and straighteners. I did a class then got ready to go out. Loved it!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPkJCYL_Ph4EaCFDcXIjr3d6VgNMY19gZPbtsDGJZM30-gZ-t_uD3Nj1sH8UftIIjrOxELkUbyPHFzPoTERWzmEprojWO2hc1YjxpRqIdv5JBwE1YfI1QHuXqPiW29kGicC9EIHKA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMWvibZE2XAkTZCrUZWtk3Fqf8yq5jgPzXnXB2EPsGBTLDz3GCdAjeT4tFtkHbiW9wsC0n4a5Vhtn8ucQUdZxp4igAtaZosdpJqv68zkvH2bz6Yug6KB0r74ZjJED1JTHS4WIse=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNjTYgnpNuj1miyn8gk30sMlRehtnkvnsp9wHWnP-1VDylZ2oN-e0AHgDSBjmC_Qtofir8p4dzsyJaUub93SRKHdq6p9yglSTyxV3Nlvun0GOdehP8lOwfo8fQlvxPWfkH41_auUg=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOi_gHZY0A0joXibjL7sHEKUxi2lm7gXrgFNS8wQV3OrVgTkgbB6kH6i517Mw4V4NdnfREAFz79hbadrDEFULfHxiyDe8KTabJ1PP7DJNOAjtMZxXM3KpL0ck4ndoaFJR_EOCvO=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnTURneC1TNUFnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107276765642000968053/reviews?hl=en-GB","posted_at_unix_micros":1740702407958412,"updated_at_unix_micros":1740702407958412,"language":"en","translated_lang":"","text_original":"Best workout of my life! Love that it’s dark with red lights, music is loud, instructions are clear and there’s no judgement - it’s just you vs you. Intensely hard work cardio and weights. Instructors are awesome, super friendly but they push you, are motivating and encouraging even for first timers. Showers and changing room area is lovely - towels provided, Malin \u0026 Goetz toiletries, hairdryers and straighteners. I did a class then got ready to go out. Loved it!","text_translated":"","reply_text_original":"Thanks so much for the feedback!","reply_language":"en","reply_posted_at_unix_micros":1742200972000000,"reply_updated_at_unix_micros":1742200972000000,"published_at":"2025-02-28T00:26:47.958412Z"},{"Name":"Matilda Young","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJW1rtiSRs97wyG-W9s9BqaSZX_xnqnlwfjdea6SwE9AYJvMA=s120-c-rp-mo-br100","Rating":5,"Description":"Never had a bad experience. The workout is always top tier and I leave booking my next. All the trainers I have had (Dottie and Craig in particular) are so motivating even on a Friday evening. Highly recommend, much better than their ‘competitors’ who offer a much more transactional experience with little substance.","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25aelZrSjNlWEZFY0RodmJXVXRPREpZWTNFeVRuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117754249473721233209/reviews?hl=en-GB","posted_at_unix_micros":1767688004007044,"updated_at_unix_micros":1767688004007044,"language":"en","translated_lang":"","text_original":"Never had a bad experience. The workout is always top tier and I leave booking my next. All the trainers I have had (Dottie and Craig in particular) are so motivating even on a Friday evening. Highly recommend, much better than their ‘competitors’ who offer a much more transactional experience with little substance.","text_translated":"","reply_text_original":"Hey Matilda, thanks for the feedback! Dottie, Craig and all our central crew are fab!","reply_language":"en","reply_posted_at_unix_micros":1768484135000000,"reply_updated_at_unix_micros":1768484135000000,"published_at":"2026-01-06T08:26:44.007044Z"},{"Name":"isabelu1991","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLO2-zQFC-3l6wwAMeGCodMINJtt7Kryjpmk_YWKR32bxr48A=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I love it!\nI was a little bit worried before coming here because I have never done a workout like this before. BUT it was such a great experience!\nThe instructor named Jemma was sooo good! She explained everything before the course started. Sometimes I didn’t know what to do but she and everyone else was so nice and caring that I felt very comfortable. The course is very challenging but super fun.\nCan‘t recommend enough!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNhvu61FstrSrlYMgCsU8tiNx0yGyUERuSLPW1YbeE_P4WrWpMSt1SFrRLKiAIdlqcBuQeWHImjCZtX2JDiZOHsuZLb2IiR3EHxMXisY_F_-DSezB7-mUW_HPytQeN_kp8Ut6Ns=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPhVqUcBeniR4ixjd_5yaVNF7AjO7g0jHbZqQ849B_si0_hFsbE_7sDFwABhMDKQJ0o_gS0DHkZKtxDhVVRfTi4klo2mHnyWKgnHe5F8BEPvjghvwDQgjl2Nbnv47cAs38CfvIA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPWwgQO_q4ljI4UT3Fz04vFvta2K1I2qn6XtcUsAzr_ZWwQfzMh5GiadrBuBb3mp_SMOsSqg1JisIeJkZDdfvF0sk8Xxp-3mwA8HizAmCMF8BXIAeddIZ2TAAFB0qw1GCBS2dk=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMI1woD5QfrALjEZw5ipkGbjo_pIgg8Opxhr9rNMuBd0AgZ26DTF49joEwwddfEYehUOLo8bqQQan_6G581XWuZdZDt28GSIzc5lGCDnEkAtvJFxVvmMnOudyS_fsH5PUq7YUE-Jw=k-no"],"When":"4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURtb18zNmt3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103164460168345898497/reviews?hl=en-GB","posted_at_unix_micros":1644268341286701,"updated_at_unix_micros":1644268341286701,"language":"en","translated_lang":"","text_original":"I love it!\nI was a little bit worried before coming here because I have never done a workout like this before. BUT it was such a great experience!\nThe instructor named Jemma was sooo good! She explained everything before the course started. Sometimes I didn’t know what to do but she and everyone else was so nice and caring that I felt very comfortable. The course is very challenging but super fun.\nCan‘t recommend enough!","text_translated":"","reply_text_original":"Can't wait to see you in the Red Room again soon!","reply_language":"en","reply_posted_at_unix_micros":1649176464000000,"reply_updated_at_unix_micros":1649176464000000,"published_at":"2022-02-07T21:12:21.286701Z"},{"Name":"X Y","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJVRDTD6zC8YI6e56SGO0Eo3TyYrldtcg-ks4CekZET2yTLDg=s120-c-rp-mo-ba12-br100","Rating":4,"Description":"Nice club with big airy (male, anyway) changing room. Sound system in the red room can be a little variable and there are floor spots around the corner at the back where you'll struggle to see/ be seen by the instructor (some may see this as a positive!)\n\nBarry's UK founders / co-owners Anya and Sandy have 'residency'-style fixed classes at 08.20 and 09.30 respectively each weekday that are considered essential/iconic by hard-core fans.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMNeYjasgaBw1ELbLdK8uDPPAEHdL4G-lGRKk2-oicQUmfo1yi_q6_oCd2yoOXDmCfwbbdG_BwBEzrIM0M457jegcKoyXW1mRPwnZ1vxKn7CTJigTMmypBI6G__J3ZitaOgXWfg=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmN60UoQiHLICnKnG8QrNBnZp8BSrlZRow6i2jAfpg5eym2HUxp2jU6NWLtbHjN1-_9xTEzBaVi_wvA-ZwLjkak5zZoBay-lCxfzRVWAvP92AKRDaEpFbQ7bipOXH0u_i_J6djoc=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNAwG1O9qbKFofb_XEhlTs8_yIJ3OPabfv7gjegnTudc95u97xkQoq_nDVIs9KDdp3ImXkkA0jIE1FPQFQQk8dP2tcrqR7-n-WrvPNbTKsnGYU-xfwtJyqAKUWOTn51jyLpE05N=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMl7IbZnsyiFYPd7dLuF6XqWobKT0opdxhloAV2erS6Cu1jgoQiQjwpVffUc1dAEFyQn9hDu31Ng6DlWlVOrAjP-x0vtgTpVwVlMjFv8N0eNvjQQBHbNPF7xUtCIHoOp0QYtSkNBw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmN390LlDiV-IZs9oWwXqt5NecljIUGWgU5nfbX4aosvtSY_HJjI8fdV10XC6o6cKshQnfvTGjSGFBvOf6tI5ad0Bcvylbm7mNQKxKODfgYqPA9IppOIq0fwMhn7ma107oE0dTc=k-no"],"When":"4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUR1X002RGlBRRAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/108105588886618587257/reviews?hl=en-GB","posted_at_unix_micros":1660642416085504,"updated_at_unix_micros":1660642416085504,"language":"en","translated_lang":"","text_original":"Nice club with big airy (male, anyway) changing room. Sound system in the red room can be a little variable and there are floor spots around the corner at the back where you'll struggle to see/ be seen by the instructor (some may see this as a positive!)\n\nBarry's UK founders / co-owners Anya and Sandy have 'residency'-style fixed classes at 08.20 and 09.30 respectively each weekday that are considered essential/iconic by hard-core fans.","text_translated":"","reply_text_original":"Thanks for the great feedback!","reply_language":"en","reply_posted_at_unix_micros":1660644776000000,"reply_updated_at_unix_micros":1660644776000000,"published_at":"2022-08-16T09:33:36.085504Z"}]</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>13</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>c2406c1e-2fba-4c5c-8ab2-a599af517682</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Diesel+Gym+London/data=!4m7!3m6!1s0x487602d46bae62a1:0x70d1bc4f90ce101a!8m2!3d51.5428082!4d0.0004277!16s%2Fg%2F1tcxj798!19sChIJoWKua9QCdkgRGhDOkE-80XA</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Diesel Gym London</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Martial arts school</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2, Diesel Gym London, Gerry Raffles Square, London E15 1BG, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>{"Friday":["7 am–9:30 pm"],"Monday":["7 am–9:30 pm"],"Saturday":["9 am–3 pm"],"Sunday":["9 am–2 pm"],"Thursday":["7 am–9:30 pm"],"Tuesday":["10 am–9:30 pm"],"Wednesday":["7 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>http://www.dieselgym.co.uk/</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>+44 7765 243012</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>G2V2+45 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>243</v>
+      </c>
+      <c r="O87" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":2,"3":3,"4":7,"5":230}</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>51.542808</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0.000428</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>8129485852298317850</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkfXCAIG2ooyXiCHZaRc3xKCNoZuNuC6sAAiRqpODixIbPkOklOcprjdWkR9o3jSoHivyi0nKiAxBy30f0hMalNR75Mf77mCAbV2L6OgjDm3v8QIz0ky1xlZ_RNGU3sMhszGdh9=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>0x487602d46bae62a1:0x70d1bc4f90ce101a</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>ChIJoWKua9QCdkgRGhDOkE-80XA</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>{"id":"108863763477758381301","name":"Diesel Gym London (Owner)","link":"https://www.google.com/maps/contrib/108863763477758381301"}</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"2, Gerry Raffles Square","city":"London","postal_code":"E15 1BG","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible seating","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>[{"Name":"BILLY GAVIGAN","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU33JYVGC52RCrSTeoqNEiMknsGr2x48eX4QEPF09QLXK6tU6k=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Judo London Open arrival and  Prep in East London — Diesel Gym Delivered When It Mattered Most\n\nI’m in East London competing in the London Open Veterans Judo Tournament, representing Team USA as a National Champion — and if you know the sport, you know weigh-ins aren’t just a formality… they’re everything. Managing weight before competition is one of the most stressful parts of the process, and having access to an accurate scale can make or break your mindset going into fight day.\n\nI stopped into Diesel Gym London needing a quick check — and what I got was way more than that.\n\nFrom the moment I walked in, the team was welcoming, professional, and completely dialed in. They had a spot-on digital scale, and without hesitation, they let me use it. No hassle, no attitude — just genuine support for an athlete in the middle of prep.\n\nThe facility itself has a serious, high-performance energy — the kind of place where people are there to work, improve, and compete. You can feel it immediately. The coaches and members carry that same mindset: focused, respectful, and driven.\n\nThat quick stop took a huge weight off my shoulders (literally and mentally) heading into tomorrow.\n\nMassive shoutout to the Diesel Gym team for stepping up when it counted. If you’re a fighter, competitor, or anyone serious about training in London — this is a spot you want in your corner.\n\nHighly recommend if you’re this part of London ! Thanks Cliff \u0026 The Coaches\n\n⭐⭐⭐⭐⭐\n\n#BillyEats #BillyDrinks #BarScout #FoodieLife #TopGoogleReviewer #GlobalBites #judo #MMA #Eastlondon","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOMQDt5j2j8_nHwyXvsBat4i8uAUcIwpd_pI_iYAb-U6IcGlsUzxYxshF9MwcLqFsfR1upmth0fBfBXlmoEK-RShgLHisJdtB-4u3NEYPCcSWLnleCOZsXPDxz3P6MppIJifgwN8WN-SdJb=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPs0m7FxhtzZgM_lkfzJGFWi-B13alYtXpCXjinfj374vjE8kEgGN9fSYPurzB3sAmCNJSuIw3VywkRYiV0Wt3pnVw2OfAypgslSm2EImqYDYwW7hcyTYdDgYElaeYcqwyg8Fwb31-54uEd=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25GelVWOUNhMUIxTUhRMlVXZG5RV05TYmpVM1NuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103730805771631900179/reviews?hl=en-GB","posted_at_unix_micros":1774534462728352,"updated_at_unix_micros":1774607732216409,"language":"en","translated_lang":"","text_original":"Judo London Open arrival and  Prep in East London — Diesel Gym Delivered When It Mattered Most\n\nI’m in East London competing in the London Open Veterans Judo Tournament, representing Team USA as a National Champion — and if you know the sport, you know weigh-ins aren’t just a formality… they’re everything. Managing weight before competition is one of the most stressful parts of the process, and having access to an accurate scale can make or break your mindset going into fight day.\n\nI stopped into Diesel Gym London needing a quick check — and what I got was way more than that.\n\nFrom the moment I walked in, the team was welcoming, professional, and completely dialed in. They had a spot-on digital scale, and without hesitation, they let me use it. No hassle, no attitude — just genuine support for an athlete in the middle of prep.\n\nThe facility itself has a serious, high-performance energy — the kind of place where people are there to work, improve, and compete. You can feel it immediately. The coaches and members carry that same mindset: focused, respectful, and driven.\n\nThat quick stop took a huge weight off my shoulders (literally and mentally) heading into tomorrow.\n\nMassive shoutout to the Diesel Gym team for stepping up when it counted. If you’re a fighter, competitor, or anyone serious about training in London — this is a spot you want in your corner.\n\nHighly recommend if you’re this part of London ! Thanks Cliff \u0026 The Coaches\n\n⭐⭐⭐⭐⭐\n\n#BillyEats #BillyDrinks #BarScout #FoodieLife #TopGoogleReviewer #GlobalBites #judo #MMA #Eastlondon","text_translated":"","reply_text_original":"Billy, thank you for the incredible review and for stopping by Diesel Gym. We’re honored to have supported a Team USA National Champion and glad the scale and atmosphere helped ease the pre-competition stress. It means a lot to hear our team and members created the focused environment you needed. Best of luck at the London Open Veterans and you’re welcome back anytime.  We all wish you all of the very best with the tournament.\n\n","reply_language":"en","reply_posted_at_unix_micros":1774541698000000,"reply_updated_at_unix_micros":1774542458000000,"published_at":"2026-03-26T14:14:22.728352Z"},{"Name":"Eliza Yuan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKjodSO_R2zjbWzTfyE5FvnY5ohnmmuk7f60UqcfFZHMJYzUKqv=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My daughter has trained at Diesel Gym for over two and a half years, and it's been a fantastic experience. Her confidence, discipline, fitness and martial arts skills have all improved so much during her time there.\n\nThe coaches are knowledgeable, supportive and genuinely care about helping every child develop and reach their potential. The atmosphere is welcoming, encouraging and motivating, making it a great place for children to learn and grow.\n\nI highly recommend it to anyone looking for high-quality martial arts training for their children.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xOblZtbzFibUY2VTNwTGRtUlBZMUJJU205bmVXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114465831584309748494/reviews?hl=en-GB","posted_at_unix_micros":1784047666719493,"updated_at_unix_micros":1784047704759407,"language":"en","translated_lang":"","text_original":"My daughter has trained at Diesel Gym for over two and a half years, and it's been a fantastic experience. Her confidence, discipline, fitness and martial arts skills have all improved so much during her time there.\n\nThe coaches are knowledgeable, supportive and genuinely care about helping every child develop and reach their potential. The atmosphere is welcoming, encouraging and motivating, making it a great place for children to learn and grow.\n\nI highly recommend it to anyone looking for high-quality martial arts training for their children.","text_translated":"","reply_text_original":"What a wonderful review,  thanks Eliza","reply_language":"en","reply_posted_at_unix_micros":1784052057000000,"reply_updated_at_unix_micros":1784052092000000,"published_at":"2026-07-14T16:47:46.719493Z"},{"Name":"Bowen Zhang","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIffrsOdQN3pdo35ndDdQkRTqizkBDhDzO3hWhaOelIqnur=s120-c-rp-mo-br100","Rating":5,"Description":"I would 100% recommend this gym to anyone looking to start training or improve their skills. The atmosphere is friendly, professional, and very welcoming to beginners. The coaches are knowledgeable, supportive, and clearly passionate about what they do. The membership is also very reasonably priced for the quality of training and facilities on offer. Overall, it has been a 10/10 experience for me :)","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25keldsQXRNWGszTFUxS1pFOUpTVVV3VERRd1RHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109323270690509084381/reviews?hl=en-GB","posted_at_unix_micros":1784042254756433,"updated_at_unix_micros":1784042254756433,"language":"en","translated_lang":"","text_original":"I would 100% recommend this gym to anyone looking to start training or improve their skills. The atmosphere is friendly, professional, and very welcoming to beginners. The coaches are knowledgeable, supportive, and clearly passionate about what they do. The membership is also very reasonably priced for the quality of training and facilities on offer. Overall, it has been a 10/10 experience for me :)","text_translated":"","reply_text_original":"Thanks  Bowe, great review","reply_language":"en","reply_posted_at_unix_micros":1784051987000000,"reply_updated_at_unix_micros":1784051987000000,"published_at":"2026-07-14T15:17:34.756433Z"},{"Name":"Nayana Mena","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUSO-U3tTPZqAkLGjrxfFisBMNTW6Yt1u1Q8XC73xlgektx5UrQvw=s120-c-rp-mo-br100","Rating":5,"Description":"Absolutely love attending Lauren’s group PT sessions on a Wednesday evening.\n\nSuch an empowering and motivating bunch of women.\n\nWould recommend!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNcGZaN8XytLE_S3lTicvnImj-IKmKS4TSOnmOKQH8A0HMtWH9c5DC7NUzkbkhuqWwZARbeYwSTOBcXU1i4O1niqiKhkqYQhj6XdYAQWh3gdsKlU3AZMiTOc9TMmaPuL2bPaFhW6oJr744K=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21sdWNWcFlNWEpzYW1kM1NGTnZZa2hoYldZM1EzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107547586795020176093/reviews?hl=en-GB","posted_at_unix_micros":1778839319270346,"updated_at_unix_micros":1778839319270346,"language":"en","translated_lang":"","text_original":"Absolutely love attending Lauren’s group PT sessions on a Wednesday evening.\n\nSuch an empowering and motivating bunch of women.\n\nWould recommend!","text_translated":"","reply_text_original":"Thank you Nayana.  Lauren is amazing","reply_language":"en","reply_posted_at_unix_micros":1778860587000000,"reply_updated_at_unix_micros":1778860587000000,"published_at":"2026-05-15T10:01:59.270346Z"},{"Name":"Karen Lee","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLMCDuL6hBF9Hz5TpuMQEVa8cL1uByx2rGp6-Qe1_SZOx57=s120-c-rp-mo-br100","Rating":5,"Description":"I can't recommend Lauren enough! What makes her truly special isn't just her expertise as a personal trainer — it's her incredible generosity and energy! Every Tuesday and Sunday, she gives up her own time to train women completely free of charge, and that says everything about the kind of person and coach she is.\n\nHer sessions are energetic, well-structured, and genuinely fun. She has a real gift for making every woman feel capable and confident, no matter their fitness level. She pushes you just the right amount and always makes sure you feel supported rather than intimidated.\n\nIf you're looking for a trainer who is skilled, passionate, and genuinely invested in the women she works with, look no further. Follow her on Instagram @laurens.pt. You can find success stories of her clients there.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2toMmRUbGFlRzFuWWsxeWJqWTJWMDFhV0hWUVUyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112150285001428651759/reviews?hl=en-GB","posted_at_unix_micros":1778879792789961,"updated_at_unix_micros":1778879792789961,"language":"en","translated_lang":"","text_original":"I can't recommend Lauren enough! What makes her truly special isn't just her expertise as a personal trainer — it's her incredible generosity and energy! Every Tuesday and Sunday, she gives up her own time to train women completely free of charge, and that says everything about the kind of person and coach she is.\n\nHer sessions are energetic, well-structured, and genuinely fun. She has a real gift for making every woman feel capable and confident, no matter their fitness level. She pushes you just the right amount and always makes sure you feel supported rather than intimidated.\n\nIf you're looking for a trainer who is skilled, passionate, and genuinely invested in the women she works with, look no further. Follow her on Instagram @laurens.pt. You can find success stories of her clients there.","text_translated":"","reply_text_original":"Incredible review.  Thanks Karen","reply_language":"en","reply_posted_at_unix_micros":1779002124000000,"reply_updated_at_unix_micros":1779002124000000,"published_at":"2026-05-15T21:16:32.789961Z"}]</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>13</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Barry%27s+SOHO/data=!4m7!3m6!1s0x487605efcf47fe0f:0x4c0ec6c2972a7226!8m2!3d51.5127417!4d-0.1396881!16s%2Fg%2F11jrcmtb0g!19sChIJD_5Hz-8FdkgRJnIql8LGDkw</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Barry's SOHO</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>59 Kingly St, London W1B 5QL, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–8:30 pm"],"Monday":["5:30 am–9:30 pm"],"Saturday":["7 am–4:45 pm"],"Sunday":["7 am–4:45 pm"],"Thursday":["5:30 am–9:30 pm"],"Tuesday":["5:30 am–9:30 pm"],"Wednesday":["5:30 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>http://www.barrys.com/</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>+44 20 4511 6206</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>GV76+34 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>232</v>
+      </c>
+      <c r="O88" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>{"1":11,"2":5,"3":6,"4":17,"5":193}</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>51.512742</v>
+      </c>
+      <c r="R88" t="n">
+        <v>-0.139688</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>5480536335618568742</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWli8NDq4_DkyZErnneBMawFXBLyXTIdZnxqIt28dMplC4jmPokC3rnXQ4C9wCmvChjTGdh7Si9J4ges0QBEg-4tfHTGzI0zobwIUbKVWXoiCQL8NDOWy88LE12DDnCccBL3ozgL=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>0x487605efcf47fe0f:0x4c0ec6c2972a7226</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>ChIJD_5Hz-8FdkgRJnIql8LGDkw</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>[{"link":"https://deliveroo.co.uk/menu/london/soho/barrys-soho?utm_medium=affiliate\u0026utm_source=google_maps_link\u0026fulfillment_type=DELIVERY\u0026rwg_token=AE37R_g_f8rAfuPSY_uG46mKrW-42NUUVrewTmuXaf77kNih3qgemBJf7kHFAEwtxXeE-GLBr_h-8nYj1yao5aX6rdPt2t_jVnrWCgDwzPkud_4loE8_G30%3D","source":"deliveroo.co.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>{"id":"112361818612005514338","name":"Barry's SOHO (Owner)","link":"https://www.google.com/maps/contrib/112361818612005514338"}</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"59 Kingly St","city":"London","postal_code":"W1B 5QL","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>[{"Name":"Holly Keyse","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKVVyF7Sb7m_g5xMBTWI2Gb-8xm6fYr3iCZ0HZT6MeUq9rNfg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great experience always love a Barry’s. All staff very friendly and helpful. Great class. Showers and changing rooms clean and good space","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNiJN-xcjPCotgQSAQlxGKJ-itrWxkSI6Zvlchn4q4zjeEFeMyHJEOC4QTPoh1d3NgpeLmI9c16uxpuVObxnztE8AzpU8hHoRvJqjTJH3o314MqWoQwPnouzqgt2wPVENC7b99MrclevWgQ=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMsIC_b-UItbCgEizNkegWyOi1LRSpqbM_wQnc_VCcZi15kdggisJaIBS74L0OmMONkpAOn5S6dszf0ddCz98sudV-IkKdy0Z8Lx-kOasiPQuFK6frPYUo5iAHQ67EjjUMmM-lF9ok6rGY=k-no"],"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xGUmNUUXRhR0pPZEdoeGRHVklhMWxsWkVNek1XYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115571965249771542152/reviews?hl=en-GB","posted_at_unix_micros":1786135079900279,"updated_at_unix_micros":1786135079900279,"language":"en","translated_lang":"","text_original":"Great experience always love a Barry’s. All staff very friendly and helpful. Great class. Showers and changing rooms clean and good space","text_translated":"","reply_text_original":"Thanks for the feedback!","reply_language":"en","reply_posted_at_unix_micros":1787837764000000,"reply_updated_at_unix_micros":1787837764000000,"published_at":"2026-08-07T20:37:59.900279Z"},{"Name":"Michelle BL","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX7SdQTlmVsrIsYGk64pOFGRLUDSly4Np1m0ozrDkHyaqPJqa0=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My weekend morning ritual! I always feel so much fitter and brighter after every Barry's session: the Run X Lift classes are my go-to, plus the fresh amenities and showers as well as the friendly atmosphere make it worth each session. A bootcamp inspired workout that keeps me coming back :)","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOpCtOEeMYj2p6ndttqA84VixUOFF9KXr0E2U6WN_0kSTjQh9EHcabCm4fY34RlAbKA9dBCo7dE2Li3_YSfEB5wmDAYkiKFHjs6PoW3fLJVGwaNJB2NGw-Yv9PGGcJgtaZ_JDY7LhWT9z4=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNLLgv3yGYfyyHNFlZxo5iN3lfiuTLR55WO0IpW_NEi2pRtluN8-QTJRpgM2mUnOPjcXdgShSqRUMYfCofmMYmwiUV-BWThfF8pxkdsP_bBddMqcndDwIga3Vw-Ng6P1OjbZzX4N2LVb-_4=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMEhstmjP9UjDxOZRLzt_vDeP2J8nSGKeqBj_PwSRYSsMPJvU3_3pdivZdu9EaEyx3nU0pPl7mo8fsQI12p8rOjFqKanMEGvFayJI_BvD_7lTtenmCM2z3RYDxFO7rNBGrIBEH_xjto2BV4=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25ScGEwSXRTVEZmUnpaTU4wTnZVMHhRV0V4RFduYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107692764229228526605/reviews?hl=en-GB","posted_at_unix_micros":1771183215432206,"updated_at_unix_micros":1771183215432206,"language":"en","translated_lang":"","text_original":"My weekend morning ritual! I always feel so much fitter and brighter after every Barry's session: the Run X Lift classes are my go-to, plus the fresh amenities and showers as well as the friendly atmosphere make it worth each session. A bootcamp inspired workout that keeps me coming back :)","text_translated":"","published_at":"2026-02-15T19:20:15.432206Z"},{"Name":"Irene García Morillo","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW1iabEBrXuJfd8LjjQnPrLMyxgzolBa7mkGvP_TIEp3IQml2vxmQ=s120-c-rp-mo-ba12-br100","Rating":2,"Description":"I had my first session today and frankly, I don’t get the hype. It was a terrible work out class. Usually after I work out I’d leave feeling relaxed and accomplished, at Barry’s I left stressed and with a headache…\n\nFirst of all, the music is so so incredibly loud and so is the instructors microphone. My Apple watch was going off constantly with “dangerously loud environment” warnings. The instructor spends the entire hour shouting at you and it’s so chaotic and loud you can barely follow what you’re supposed to do. They darken the room so much at times I couldn’t even see my feet or the buttons I was supposed to press on the treadmill and felt genuinely unsafe running in the absolute dark. In the bench, I felt we were encouraged to do the exercises as quickly as possible which is a recipe for injury when manipulating weights, as it’s harder to keep good form. In fact, nobody’s form was corrected at all. The only good thing is that the facilities are nice, spacious and well equipped changing rooms so I did enjoy my shower afterwards and the smoothie I got was tasty. Other than that, the worst workout class I’ve done in a long time.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2toSVRUSm9aR2xMYjJseGN6ZElOV3d0UkZaV1RWRRAB","source":"Google","rating_scale":5,"rating_float":2,"author_url":"https://www.google.com/maps/contrib/108292740394373623131/reviews?hl=en-GB","posted_at_unix_micros":1776497357269979,"updated_at_unix_micros":1776497427530826,"language":"en","translated_lang":"","text_original":"I had my first session today and frankly, I don’t get the hype. It was a terrible work out class. Usually after I work out I’d leave feeling relaxed and accomplished, at Barry’s I left stressed and with a headache…\n\nFirst of all, the music is so so incredibly loud and so is the instructors microphone. My Apple watch was going off constantly with “dangerously loud environment” warnings. The instructor spends the entire hour shouting at you and it’s so chaotic and loud you can barely follow what you’re supposed to do. They darken the room so much at times I couldn’t even see my feet or the buttons I was supposed to press on the treadmill and felt genuinely unsafe running in the absolute dark. In the bench, I felt we were encouraged to do the exercises as quickly as possible which is a recipe for injury when manipulating weights, as it’s harder to keep good form. In fact, nobody’s form was corrected at all. The only good thing is that the facilities are nice, spacious and well equipped changing rooms so I did enjoy my shower afterwards and the smoothie I got was tasty. Other than that, the worst workout class I’ve done in a long time.","text_translated":"","reply_text_original":"Thanks for sharing your experience, we’re really sorry to hear it wasn’t what you were hoping for, especially for your first class.\n\nBarry’s is intentionally a very high-energy environment, designed to feel a bit like a nightclub mixed with fitness. That said, we completely get that the volume, lighting and pace can feel intense, particularly if you’re new to it.\n\nJust to mention, we do have complimentary earplugs available in all of our studios if the music feels too loud, feel free to grab some next time or ask the team.\n\nWe’re also sorry to hear you felt uncomfortable or unsafe at points, especially on the treadmill and floor. That’s not how anyone should feel in class, and we’ll definitely pass this on to the team to look into.\n\nReally glad to hear you enjoyed the facilities, though, always a win with the showers and smoothies.\n\nThanks again for taking the time to be honest with us, we do appreciate it.\n\nBarry's UK","reply_language":"en","reply_posted_at_unix_micros":1776675337000000,"reply_updated_at_unix_micros":1776675337000000,"published_at":"2026-04-18T07:29:17.269979Z"},{"Name":"Phai Dip","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXCyF0SQS3WscDMYEeXyFNgyrG8Od_arS_OjKlvng1C_3BGDrHG=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"One of my favourite Barry’s studio in London, it is the only one (I believe) that has a ‘lift’ class. So there’s a lot more time slots available to suit different needs. They even occasionally have skin care products and other samples for their customers. Great dealers and excellent trainers, as you’d expect from the worlds best gym.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMlIMXIVuhVSrEIQboNXdiLOhDd8LvfW7rGbMZ6dnRTQvpCWsqkRkyl0JA3f-b3R1TaP2EeuRpPZjQyQHEUCBwE670wGQgizH7Qco1pOeJuL-xT6B8Nk85xVDGu9m0OafnSAfE=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM_oBdiuaVVkpAsdq13IS5sN5AX7tUSFw6eY9IdPeN3pn13ldgjG-QU5VhbzANG7JgWCThM_UYylVvI7S1aWcFdm53TCcz76GmYpmwnWLs0RPr61B5HinNxCUSDvNPNO9MEMnADcA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOWiiQjTpuFduCNy_TaDc1wNF91SzeUVVXNYhEaJzdH_U3VFarn_6D6csjY1jm6dAPM5VMoF0t-T2yqMMl3gh3MykWjwpAgydmtARAarsRJ2EFuKx_Ykm10nnVjuisXuwoSdRVh=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOI_cd7ms8RRFXB4wT9OcP7qoQTYgTWmSk_-jTOH1nw3ZICL9TNZ8KFGAbiTP9i5MSk_VwEKTOituv3ONNH_e2eOjQdQGUeoBWlK9DbKz7pl17ga-4xG8cz93JrywMn3oCnshu1rg=k-no"],"When":"3 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURoOTRlSnB3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104322396302701862348/reviews?hl=en-GB","posted_at_unix_micros":1679321688271623,"updated_at_unix_micros":1679321688271623,"language":"en","translated_lang":"","text_original":"One of my favourite Barry’s studio in London, it is the only one (I believe) that has a ‘lift’ class. So there’s a lot more time slots available to suit different needs. They even occasionally have skin care products and other samples for their customers. Great dealers and excellent trainers, as you’d expect from the worlds best gym.","text_translated":"","published_at":"2023-03-20T14:14:48.271623Z"},{"Name":"Shalishah Kay","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWYU-Kft1UBuD_BJHVliy1AXgTnKwvZvLdObtQwAC8yCkdF1ohH=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I had an amazing time doing the lower body focus class! Facilities are A1 and our instructor Craig was an absolute star- explained everything as we went on  and kept the group extremely motivated with their great vibes and positive energy. If you are looking to establish a great workout routine and or wanting something more challenging this class is suitable for all levels of fitness. I know I definitely will be back and loved the fact I could help myself to a tasty but healthy smoothie after my workout class. Barry is unmatched!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNe5xfKtR23ZYE_xPLutmva3s1uCkmffqQwWfvY3oAc83Rz8KQSDh6uoTG9R8H5UyBdIkPoVK8-E-KJ4jcSlC3e0nYA-NKVl0VYP0FBpaj26qEEtMymBayqIqCLFOKF6JgRYJTs=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO-ujCesDXxeYvuHN9p7kHB1tWMSv8E7RFZFLFkrZC7yvMXYc4JFYgvolv85NiW4lVW7Iqmr0paRs8hldRLCVZ7MO5yCy1wtN_qA2GIq5C0baMK96RZmtIcgVTQrDtzXFZgmV-H9w=k-no"],"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUQzd283aHpnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116662331268098364050/reviews?hl=en-GB","posted_at_unix_micros":1731500653479568,"updated_at_unix_micros":1731500653479568,"language":"en","translated_lang":"","text_original":"I had an amazing time doing the lower body focus class! Facilities are A1 and our instructor Craig was an absolute star- explained everything as we went on  and kept the group extremely motivated with their great vibes and positive energy. If you are looking to establish a great workout routine and or wanting something more challenging this class is suitable for all levels of fitness. I know I definitely will be back and loved the fact I could help myself to a tasty but healthy smoothie after my workout class. Barry is unmatched!","text_translated":"","reply_text_original":"Thankyou, and can't wait to see you again!","reply_language":"en","reply_posted_at_unix_micros":1731681286000000,"reply_updated_at_unix_micros":1731681286000000,"published_at":"2024-11-13T12:24:13.479568Z"}]</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>13</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/1Rebel+St+John%27s+Wood/data=!4m7!3m6!1s0x48761bcc0a87f661:0x7d92313bd9429697!8m2!3d51.533326!4d-0.1706983!16s%2Fg%2F11h844n21x!19sChIJYfaHCswbdkgRl5ZC2Tsxkn0</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1Rebel St John's Wood</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>51 St John's Wood High St, London NW8 7NJ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:15 am–9 pm"],"Monday":["6:15 am–10 pm"],"Saturday":["7:45 am–7 pm"],"Sunday":["7:45 am–5:45 pm"],"Thursday":["6:15 am–10 pm"],"Tuesday":["6:15 am–10 pm"],"Wednesday":["6:15 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1rebel.com/en-gb</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>+44 20 7036 9889</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>GRMH+8P London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>229</v>
+      </c>
+      <c r="O89" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>{"1":33,"2":3,"3":10,"4":9,"5":174}</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>51.533326</v>
+      </c>
+      <c r="R89" t="n">
+        <v>-0.170698</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>9048348734458599063</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl58GLNrX2bWfAOOsEviFkn_yh2oQ7CihfNIIVZpeRpJjSl_nsoR8Kd73mMVtwUfoqxSQJohUC1RIiIy7aNbViLIbuQHqwSy1jtcFlA17Qkpp6DxtNVeFMYtRGxRTJXHzlFacsottbJm6dK=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>0x48761bcc0a87f661:0x7d92313bd9429697</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>ChIJYfaHCswbdkgRl5ZC2Tsxkn0</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>{"id":"101375051581046556566","name":"1Rebel St John's Wood (Owner)","link":"https://www.google.com/maps/contrib/101375051581046556566"}</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"51 St John's Wood High St","city":"London","postal_code":"NW8 7NJ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>[{"Name":"Stephano","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWQlYCIZHTn8JSKeTEDBQW5lRjx1tafaCyojKm4FMThqlXU4v2egA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Absolutely love the St John’s Wood studio! The facilities are always immaculate and the energy is unmatched, but what really makes it is the team. A huge shoutout to the lovely Ella and Bronte, who are always so welcoming and helpful—they make every visit a brilliant experience. Whether you're there for a savage sweat or a stretch, the trainers and staff are top-tier. Highly recommend!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPQCc_ioBb3MUQP-iYNjl9KX2KeAmz_4rOb7ZqrzxK-CfzIma_3FwS3PA_oh46XZaQJ_dlIAShRPxSI2ollKQybille7W-G-wpYrAb5u1ff3HBEHh1BjDjiQe48kIAnUAOYl5qbBogM9UrB=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xObGRrTmhTV0V4VEZoTVVFaFNlbEIwYjNkcGRVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109575421183503578125/reviews?hl=en-GB","posted_at_unix_micros":1779779291539023,"updated_at_unix_micros":1779779291539023,"language":"en","translated_lang":"","text_original":"Absolutely love the St John’s Wood studio! The facilities are always immaculate and the energy is unmatched, but what really makes it is the team. A huge shoutout to the lovely Ella and Bronte, who are always so welcoming and helpful—they make every visit a brilliant experience. Whether you're there for a savage sweat or a stretch, the trainers and staff are top-tier. Highly recommend!","text_translated":"","reply_text_original":"Thankyou for your 5* review. We look forward to welcoming you back to 1Rebel St John's Wood soon.","reply_language":"en","reply_posted_at_unix_micros":1780082918000000,"reply_updated_at_unix_micros":1780082918000000,"published_at":"2026-05-26T07:08:11.539023Z"},{"Name":"Vik \u0026 Bina","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKXZGYyl3Upt21GaMypcxhncBTGiTAAM8HwzWXgfSSb4o6inw=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been a member at 1Rebel since they’ve opened in SJW a few years ago. The reformer and reshape classes are top notch and I love that the trainers aren’t just knowledgeable and helpful but so personable (esp Alex K 🥳)!\n\nWhat sets 1 rebel apart from most gyms is the incredible super friendly and efficient front of House team! Massive shout out to all esp Ella and Brontë and of course Nick who manages the studio with ease! Reception is never chaotic,and you always have a few minutes for a quick chat!! Well done guys! Thank you 🙏🏼 xx","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25Jd2RIVkRWVXBDZFRkTGNFTlJZVzFzYTFKNFNrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114649557778369232795/reviews?hl=en-GB","posted_at_unix_micros":1778055106962029,"updated_at_unix_micros":1778055106962029,"language":"en","translated_lang":"","text_original":"I’ve been a member at 1Rebel since they’ve opened in SJW a few years ago. The reformer and reshape classes are top notch and I love that the trainers aren’t just knowledgeable and helpful but so personable (esp Alex K 🥳)!\n\nWhat sets 1 rebel apart from most gyms is the incredible super friendly and efficient front of House team! Massive shout out to all esp Ella and Brontë and of course Nick who manages the studio with ease! Reception is never chaotic,and you always have a few minutes for a quick chat!! Well done guys! Thank you 🙏🏼 xx","text_translated":"","reply_text_original":"Thankyou for your 5* review. We look forward to welcoming you back to 1Rebel St John's Wood soon. ","reply_language":"en","reply_posted_at_unix_micros":1778835191000000,"reply_updated_at_unix_micros":1778835191000000,"published_at":"2026-05-06T08:11:46.962029Z"},{"Name":"Trevir Burns","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocI9otnb5O4hM663DpKDuCjgFuhVAFU-MwG4zEZWGd_MGX-V1Q=s120-c-rp-mo-br100","Rating":5,"Description":"I had an absolutely fantastic time at 1Rebel. At first I didn’t quite feel like working out from a whole day of work , but I stepped into reception and was immediately greeted by friendly front desk staff Jodie and Equiana! Got my water bottles and will reward myself with a long shower at the end.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tOcGIyZGhNakF6V1U5T1RuUm9TSGR2WWxGd1JFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106851053093473192053/reviews?hl=en-GB","posted_at_unix_micros":1778150025368519,"updated_at_unix_micros":1778150025368519,"language":"en","translated_lang":"","text_original":"I had an absolutely fantastic time at 1Rebel. At first I didn’t quite feel like working out from a whole day of work , but I stepped into reception and was immediately greeted by friendly front desk staff Jodie and Equiana! Got my water bottles and will reward myself with a long shower at the end.","text_translated":"","reply_text_original":"Thankyou for your 5* review. We look forward to welcoming you back to 1Rebel St John's Wood soon. ","reply_language":"en","reply_posted_at_unix_micros":1778835174000000,"reply_updated_at_unix_micros":1778835174000000,"published_at":"2026-05-07T10:33:45.368519Z"},{"Name":"cansu demir","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVjkp_WUz30V1UOkYcZ1JYB49p6WFk_6HJsOGU2sFxIOIm332ktiQ=s120-c-rp-mo-ba12-br100","Rating":1,"Description":"I would never recommend you to go this place. I arrived for the 6:15 AM Reformer by class by Jabez fully prepared, only to be asked to leave because the instructor incorrectly assumed it was my first class and behaved as though I wouldn’t understand the setup. I have attended Reformer classes many times before and was perfectly familiar with the process.\n\nThe way this situation was handled was extremely unprofessional, dismissive, and frankly disrespectful. Instead of listening, the instructor made assumptions and spoke to me in a patronising manner. As someone with a busy work schedule, mornings are the only time I have available to exercise, and having that time wasted due to someone else’s poor judgement was incredibly frustrating.\n\nWhat made matters worse was that no alternative, replacement class, or any form of compensation was offered. A business that values its clients should know better. Staff should be properly trained to communicate respectfully, assess situations accurately, and resolve issues professionally. This experience fell far below an acceptable standard.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMYx4ESvVuYJLBf1qdF_Y-65o616M4YEesFOKgbYpbF4nevkDDlte6d637QBYX8Bc4C4LvSz4aSipPhdzvlvhJhab3ifF0UwIn92hgWd56r91qj646dwjWL-2BPFrPbr1VhA3qzPnFVkaMn=k-no"],"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xKR0xTMVNXRmR1YVRKeE9XMVpSRWt5ZDBWdVNFRRAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/118200278574542187800/reviews?hl=en-GB","posted_at_unix_micros":1777614098513911,"updated_at_unix_micros":1777614098513911,"language":"en","translated_lang":"","text_original":"I would never recommend you to go this place. I arrived for the 6:15 AM Reformer by class by Jabez fully prepared, only to be asked to leave because the instructor incorrectly assumed it was my first class and behaved as though I wouldn’t understand the setup. I have attended Reformer classes many times before and was perfectly familiar with the process.\n\nThe way this situation was handled was extremely unprofessional, dismissive, and frankly disrespectful. Instead of listening, the instructor made assumptions and spoke to me in a patronising manner. As someone with a busy work schedule, mornings are the only time I have available to exercise, and having that time wasted due to someone else’s poor judgement was incredibly frustrating.\n\nWhat made matters worse was that no alternative, replacement class, or any form of compensation was offered. A business that values its clients should know better. Staff should be properly trained to communicate respectfully, assess situations accurately, and resolve issues professionally. This experience fell far below an acceptable standard.","text_translated":"","reply_text_original":"Morning Cansu,\n\nThank you for taking the time to share your experience. We’re very sorry to hear about what happened during your visit.\n\nPlease email us at stjohnswood@1rebel.com, and we’ll be happy to discuss this further.\n\nThank you again for bringing this to our attention.\n","reply_language":"en","reply_posted_at_unix_micros":1777628588000000,"reply_updated_at_unix_micros":1777628588000000,"published_at":"2026-05-01T05:41:38.513911Z"},{"Name":"Riya \u0026 Jimmy Thomas","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKcBq4SsGsELTGEIgMMf8_duoIFYxTOQ2-RVpJMpHDBuhKo0w=s120-c-rp-mo-ba12-br100","Rating":1,"Description":"Spoke to a member of staff on Thursday just gone (when it was 35 degrees!) to reschedule a spin class as I was struggling with the heatwave. I was told initially that it'll be OK if I emailed but later during the day the request was denied unless I supplied a doctors note. The people who run this place have no perspective. Given the pressure NHS is under I'm not calling the GP to ask for a medical note to reschedule a spin class. I'm happy to lose the class but hopefully the business can exercise some common sense going forward..","Images":null,"When":"Edited 2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwSlVESjRiamwyV0VRMmQzVk9UemhuY1dWRVYzYxAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/103388703416917303580/reviews?hl=en-GB","posted_at_unix_micros":1782403610581169,"updated_at_unix_micros":1782638551577026,"language":"en","translated_lang":"","text_original":"Spoke to a member of staff on Thursday just gone (when it was 35 degrees!) to reschedule a spin class as I was struggling with the heatwave. I was told initially that it'll be OK if I emailed but later during the day the request was denied unless I supplied a doctors note. The people who run this place have no perspective. Given the pressure NHS is under I'm not calling the GP to ask for a medical note to reschedule a spin class. I'm happy to lose the class but hopefully the business can exercise some common sense going forward..","text_translated":"","reply_text_original":"Morning Riya,\n\nSorry to hear that you did not enjoy your experience. If you could reach out to Stjohnswood@1rebel.com with further details so we can explore options. \n","reply_language":"en","reply_posted_at_unix_micros":1783933260000000,"reply_updated_at_unix_micros":1783933260000000,"published_at":"2026-06-25T16:06:50.581169Z"}]</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>13</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>c2406c1e-2fba-4c5c-8ab2-a599af517682</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Collective+Pilates+%28previously+Bootcamp+Pilates+Notting+Hill%29/data=!4m7!3m6!1s0x48761aaa8531531b:0xb8ee98942d90db93!8m2!3d51.5184963!4d-0.1888857!16s%2Fg%2F1tkc1ln_!19sChIJG1MxhaoadkgRk9uQLZSY7rg</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Collective Pilates (previously Bootcamp Pilates Notting Hill)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pilates studio</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>64 Porchester Rd, London W2 6ET, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>{"Friday":["7 am–7 pm"],"Monday":["7 am–8:30 pm"],"Saturday":["9 am–1 pm"],"Sunday":["9 am–1 pm"],"Thursday":["7:30 am–8:30 pm"],"Tuesday":["7:30 am–8:30 pm"],"Wednesday":["7 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.collectivepilates.com/</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>+44 20 7034 0000</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>GR96+9C London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>228</v>
+      </c>
+      <c r="O90" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>{"1":6,"2":1,"3":2,"4":1,"5":218}</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>51.518496</v>
+      </c>
+      <c r="R90" t="n">
+        <v>-0.188886</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>13325756109622926227</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl7by1zzzjWSryzLe2mGZMI1RoMJopIT1Zk_tjgs3uJiwMz8YdjnQ_6jks4TDJLvQg_5e1rPeSl4IC5cN8KozHM_FnODw0L93ZmnFX7TERv3NLHaRHYoOTVbnvbcq0IDAdqtb3o=w408-h271-k-no</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>0x48761aaa8531531b:0xb8ee98942d90db93</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>ChIJG1MxhaoadkgRk9uQLZSY7rg</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.collectivepilates.com/schedule","source":"collectivepilates.com"}]</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>{"id":"114657118972962384807","name":"Collective Pilates (previously Bootcamp Pilates Notting Hill) (Owner)","link":"https://www.google.com/maps/contrib/114657118972962384807"}</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"64 Porchester Rd","city":"London","postal_code":"W2 6ET","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>[{"Name":"Linda Lowy","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKQw3iBufWOTRHMztplQ0IZOvF2aSIMdlIZq01Gasu1oPATsA=s120-c-rp-mo-br100","Rating":5,"Description":"I absolutely love coming to Collective Pilates in West Hampstead. The studio is bright, modern and really welcoming, and the classes strike a great balance between being challenging and enjoyable. The instructors are knowledgeable, supportive and always take the time to give helpful corrections, so you feel like you are improving with every session. It’s such a friendly atmosphere, and I always leave feeling stronger, more energised and looking forward to my next class. I would highly recommend it to anyone, whether you are completely new to reformer Pilates or have been doing it for years.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT20wdFFqRmpZbUpuU20xVVYzUTNNSGxNZEhaV1pXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108559354632547058279/reviews?hl=en-GB","posted_at_unix_micros":1783084469776536,"updated_at_unix_micros":1783084469776536,"language":"en","translated_lang":"","text_original":"I absolutely love coming to Collective Pilates in West Hampstead. The studio is bright, modern and really welcoming, and the classes strike a great balance between being challenging and enjoyable. The instructors are knowledgeable, supportive and always take the time to give helpful corrections, so you feel like you are improving with every session. It’s such a friendly atmosphere, and I always leave feeling stronger, more energised and looking forward to my next class. I would highly recommend it to anyone, whether you are completely new to reformer Pilates or have been doing it for years.","text_translated":"","published_at":"2026-07-03T13:14:29.776536Z"},{"Name":"Megan Galizia","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUtRqMoDi2DEN43JO8gwhcmZVukFewhlADNw2eL4en0-7RC3_nr=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve had a wonderful experience at Collective Pilates. The studio is clean, welcoming, and equipped with excellent reformers, making every class feel comfortable and well run.\n\nA special shoutout to Babette, who has been incredible as I’ve returned to exercise postpartum. She consistently offers thoughtful modifications, meets you where you are, and creates an encouraging environment that feels both supportive and challenging. Her energy is contagious, and she brings such a positive attitude to every class.\n\nI always leave feeling stronger, energized, and motivated to come back. Highly recommend Collective Pilates for anyone looking for great instruction, a positive community, and a fantastic workout.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT210UWREbHJiSFYyYTJWRlNHcHVOSGRCZEhONk1XYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114317678657168290740/reviews?hl=en-GB","posted_at_unix_micros":1783671955360144,"updated_at_unix_micros":1783676418941183,"language":"en","translated_lang":"","text_original":"I’ve had a wonderful experience at Collective Pilates. The studio is clean, welcoming, and equipped with excellent reformers, making every class feel comfortable and well run.\n\nA special shoutout to Babette, who has been incredible as I’ve returned to exercise postpartum. She consistently offers thoughtful modifications, meets you where you are, and creates an encouraging environment that feels both supportive and challenging. Her energy is contagious, and she brings such a positive attitude to every class.\n\nI always leave feeling stronger, energized, and motivated to come back. Highly recommend Collective Pilates for anyone looking for great instruction, a positive community, and a fantastic workout.","text_translated":"","published_at":"2026-07-10T08:25:55.360144Z"},{"Name":"Mérédith Heinrich","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLvIOON-T61LWsqScCKKF7Uu199LLsX420-XdJzlEuDr-7nXw=s120-c-rp-mo-br100","Rating":5,"Description":"As someone chronically afraid of everything fitness and sport, I was a bit anxious heading into my first class at Collective Pilates. Thankfully, my first Pilates experience was chaperoned by the incredibly kind and patient Adelya and instead of running away from a second class, I was quickly lured into doing it again! Since then, I have had the chance to do multiple Fundamental classes with Sarah-Ann, Dannie, and of course, Adelya, and they have all been phenomenal, each with their own strengths which make them so unique!! I have felt constantly challenged physically but always supported emotionally! The instructors will regularly crack jokes, adjust your form (and ask before doing so!) and what makes the difference: remember who you are! Although I’ve only done a couple of classes with Adelya, she recently mentioned to me that she was positively impressed at my progress doing a specific exercise. This type of positive reinforcement is incredibly motivating when you’re a beginner and aren’t really sure if you’re progressing or not! And I was really touched she not only noticed but also took the time to tell me after class 🥹 I’m one of many students at Collective but it really doesn’t feel like the staff (reception or teachers) view me as one. On that note, a very very special shoutout to Whitney and Sarah working at the reception, who are nothing but warm and personable! They always ask you how your class went (although it’s usually met with some incoherent nonsense from me as the blood isn’t flowing to my brain properly) and they’ve always been incredibly helpful helping me book classes, sending me this review link, or even giving me food recommendations for plans later in my day haha!\n\nAll and all, if I had to recommend any Pilates studio, it would 100000% be Collective Pilates! Whether you’re already a certified Pilates baddie or an afraid beginner like me, the staff is here to make your legs tremble and make you leave with a happy feeling!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21aVmMzcGtiVXBLVTFaVmVGZEZZbU5FWm14WmVIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100379369933615814710/reviews?hl=en-GB","posted_at_unix_micros":1779393402904521,"updated_at_unix_micros":1779393402904521,"language":"en","translated_lang":"","text_original":"As someone chronically afraid of everything fitness and sport, I was a bit anxious heading into my first class at Collective Pilates. Thankfully, my first Pilates experience was chaperoned by the incredibly kind and patient Adelya and instead of running away from a second class, I was quickly lured into doing it again! Since then, I have had the chance to do multiple Fundamental classes with Sarah-Ann, Dannie, and of course, Adelya, and they have all been phenomenal, each with their own strengths which make them so unique!! I have felt constantly challenged physically but always supported emotionally! The instructors will regularly crack jokes, adjust your form (and ask before doing so!) and what makes the difference: remember who you are! Although I’ve only done a couple of classes with Adelya, she recently mentioned to me that she was positively impressed at my progress doing a specific exercise. This type of positive reinforcement is incredibly motivating when you’re a beginner and aren’t really sure if you’re progressing or not! And I was really touched she not only noticed but also took the time to tell me after class 🥹 I’m one of many students at Collective but it really doesn’t feel like the staff (reception or teachers) view me as one. On that note, a very very special shoutout to Whitney and Sarah working at the reception, who are nothing but warm and personable! They always ask you how your class went (although it’s usually met with some incoherent nonsense from me as the blood isn’t flowing to my brain properly) and they’ve always been incredibly helpful helping me book classes, sending me this review link, or even giving me food recommendations for plans later in my day haha!\n\nAll and all, if I had to recommend any Pilates studio, it would 100000% be Collective Pilates! Whether you’re already a certified Pilates baddie or an afraid beginner like me, the staff is here to make your legs tremble and make you leave with a happy feeling!","text_translated":"","published_at":"2026-05-21T19:56:42.904521Z"},{"Name":"Ellen M","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocI1F8jA4Ekf2vO1MLIvvJcQd7b1m4ttyEDC4_YEvmOTsshFpA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My favorite Pilates studio! Always so welcoming when you arrive and love the teachers! Dannie, Babette and James are def my favorite classes and highly recommend this studio if you want a good Pilates workout for all levels!❤️","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT20wNVUxSnJYMFJaWlZFd2FIRkNVamhaT0ROcWNrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108673811386886184898/reviews?hl=en-GB","posted_at_unix_micros":1784579603463932,"updated_at_unix_micros":1784579603463932,"language":"en","translated_lang":"","text_original":"My favorite Pilates studio! Always so welcoming when you arrive and love the teachers! Dannie, Babette and James are def my favorite classes and highly recommend this studio if you want a good Pilates workout for all levels!❤️","text_translated":"","published_at":"2026-07-20T20:33:23.463932Z"},{"Name":"Lucy Francis","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLdMDxqmS_n0O8V09a_SWp0tYYWtksrUTtjVEdlbXixukPxzQ=s120-c-rp-mo-br100","Rating":5,"Description":"Excellent teachers, i've been coming here for years and it wins on having a super-friendly team and quality of classes. Highly recommended - no fancy showers or products but not what reformer's really about, for me.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psTlpraE1hMEZqVGxCRWVFdFJWa2hET0hOSmNFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109208472658937020746/reviews?hl=en-GB","posted_at_unix_micros":1784646454228131,"updated_at_unix_micros":1784646454228131,"language":"en","translated_lang":"","text_original":"Excellent teachers, i've been coming here for years and it wins on having a super-friendly team and quality of classes. Highly recommended - no fancy showers or products but not what reformer's really about, for me.","text_translated":"","published_at":"2026-07-21T15:07:34.228131Z"}]</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>13</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Barry%27s+London+West/data=!4m7!3m6!1s0x48760555ed8abda9:0x14beb9ed82b3f44c!8m2!3d51.5107652!4d-0.1872483!16s%2Fg%2F11c804_l5v!19sChIJqb2K7VUFdkgRTPSzgu25vhQ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Barry's London West</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>9A Queensway, London W2 4QJ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–9:30 pm"],"Monday":["5 am–9:30 pm"],"Saturday":["7 am–6:30 pm"],"Sunday":["7 am–4 pm"],"Thursday":["5 am–9:30 pm"],"Tuesday":["5 am–9:30 pm"],"Wednesday":["5 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barrysbootcamp.com/studio/london-west/</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>+44 20 7045 9911</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>GR67+84 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>225</v>
+      </c>
+      <c r="O91" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>{"1":9,"2":4,"3":8,"4":23,"5":181}</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>51.510765</v>
+      </c>
+      <c r="R91" t="n">
+        <v>-0.187248</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1494836556084802636</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXS42WkrcRdo5h5VmRi0boYPoRV92JL6KgsMuk2U1TTMeYDMq8YELJa3z4ECSsf54UuL8EfNd8897-34v8zbLh_-s7HVwwPK0jEeXtZsfUzdNb7UPAGpZS5e69PiTcqHa041UG=w408-h339-k-no</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>0x48760555ed8abda9:0x14beb9ed82b3f44c</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>ChIJqb2K7VUFdkgRTPSzgu25vhQ</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.ubereats.com/gb/store/barrys-london-west/HgW596K4UveEES2IpffGYg?diningMode=PICKUP\u0026utm_campaign=CM2508147-search-free-nonbrand-google-pas_e_all_acq_Global\u0026utm_medium=search-free-nonbrand\u0026utm_source=google-pas\u0026rwg_token=AE37R_htgJpzOZny9X4jrNDiU6j23O8hVWxrO0kwC8D8lk1WLyQq36Qc7PichRqY6T9Eo_fME_xmJSzQtsjmBGNV8Ts48Z36GwN_k3p6q2Fes5YuF6nSBjw%3D","source":"ubereats.com"},{"link":"https://deliveroo.co.uk/menu/london/bayswater/barrys-west?utm_medium=affiliate\u0026utm_source=google_maps_link\u0026fulfillment_type=DELIVERY\u0026rwg_token=AE37R_gMh1swNt9IvbfVY66vHzRrTPy1fEmtSslRArGkP8GqiJ1Fa_RACogihHqgTHd1MyBUxXtJSTz824GGamNMxd1UnY8zscFiqSN9TuCAjqwdp7uSKiA%3D","source":"deliveroo.co.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>{"id":"102143987946980503237","name":"Barry's London West (Owner)","link":"https://www.google.com/maps/contrib/102143987946980503237"}</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"9A Queensway","city":"London","postal_code":"W2 4QJ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>[{"Name":"Khaled Alsabej","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJKSqnrYVotKnRX1NlS18XYb1q1TencIsftd1HPzhIsAho--w=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Been training here the past few weeks and the energy here is amazing, and what coach Johan Duncan Alleyne handle the class makes you agree with the gym’s slogan (The best workout in the world) ;)!\nEveryone at the gym is kind and friendly from the receptionist and instructors.\n*** CBPB protein shake is amazing!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21Sb1NVOVlaekZ1VTJKc00xbFdZaTExY0hCVFlsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114025292979052063653/reviews?hl=en-GB","posted_at_unix_micros":1771459148922329,"updated_at_unix_micros":1771459148922329,"language":"en","translated_lang":"","text_original":"Been training here the past few weeks and the energy here is amazing, and what coach Johan Duncan Alleyne handle the class makes you agree with the gym’s slogan (The best workout in the world) ;)!\nEveryone at the gym is kind and friendly from the receptionist and instructors.\n*** CBPB protein shake is amazing!","text_translated":"","published_at":"2026-02-18T23:59:08.922329Z"},{"Name":"Supersmartkids Supersmartkids","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLzJU1CCAgEMmVNmAMGkDCg_rQstbG9KlgioAqqLjk7iUb-=s120-c-rp-mo-ba12-br100","Rating":1,"Description":"Not sure if this is a good class for\nBeginners. Sadly our class teacher (Sam?) was very rude to me and my friend.\nWe were far away from the other participants so I asked her if she can show us the exercises in front of us as we didn’t have any glasses and really couldn’t see from far. She said NO :-(\nAnd she really didn’t care if we understood the exercise and did it right or wrong, she just passed us blabbering on.\nI would say, only come here if you are a pro!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNTLSl21aR9fdHABTmehRSuw_6ywoOXxu7F4h9Wu-Sfvdqyl1hIww33RI-4-1nvXNlZX1iwUMASn1PlioHD47ex-Lo7J0twVU5tuuOHrwWpiV_tbw1Har1VzItCVzAs6VRUHbeEpHZL6yKQ=k-no"],"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT214MWFIcGtMV1JtWVdKRlEwNVpjSFJQV2pGWmFIYxAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/106954255514637946388/reviews?hl=en-GB","posted_at_unix_micros":1770307655533703,"updated_at_unix_micros":1770307655533703,"language":"en","translated_lang":"","text_original":"Not sure if this is a good class for\nBeginners. Sadly our class teacher (Sam?) was very rude to me and my friend.\nWe were far away from the other participants so I asked her if she can show us the exercises in front of us as we didn’t have any glasses and really couldn’t see from far. She said NO :-(\nAnd she really didn’t care if we understood the exercise and did it right or wrong, she just passed us blabbering on.\nI would say, only come here if you are a pro!","text_translated":"","reply_text_original":"Hey,\n\nThanks for your feedback. We believe that Barry’s is an inclusive space for all fitness levels, with a wide range of weights and speed options available. We really appreciate you sharing this feedback and will be reviewing it with the team, including speaking directly with the trainer.","reply_language":"en","reply_posted_at_unix_micros":1770373364000000,"reply_updated_at_unix_micros":1770373364000000,"published_at":"2026-02-05T16:07:35.533703Z"},{"Name":"Chewielicious T","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVJ9eQfY99_SozTX73--RZaDHi3GUy9FYM9dWfomC5ps1dd-GSvBQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Intense, Energizing, and Absolutely Worth It!\n\nOne of the most enjoyable workout sessions I’ve had in London. The studio is immaculately clean, with a refreshing signature scent that sets the mood the moment you walk in. The instructor was incredible—motivating, pushing you to your absolute limits, but also knowing exactly when to pull back so you don’t burn out.\n\nThe energy in the room is electric, and the location itself adds to the experience—absolutely love this neighborhood! Gotta burn some calories given the amount that I’m eating.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOAylP36MLgjYrk9Qs3UV26djlmyW8cWRiF9bXP6pmTkiGmFDUGVcsji25THubUwgbKqeRzMSNrv4F2K6C8pyLebRMPO0bKrZlhT_8WR2oO_sQeTwb0Z4iGAdbVPTcCyej6uAd2PQ=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPVCgex6SSDh4pvdBS5xbwRkJVVNtbsiiGMxNT5U6rMkONMWImrrnJ3NzRBQFYj4DSk6hZDxCsv5PQmUeIK7YNcbKKV98MSKixfzzFrhMwBHpeNoc75n2lCN74QcF4Q8iUavXJ5=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMB29uemRdXj7ysJCBj5E6YMvtmLl9TWslbqO_JZE-76DpqzNqOtCHbmbi7MxxENe9b9T8tEfexJAu0EJFTAMBm_RHefc2ZJ-wQwJK9QgVS3VZZ2Xh0KxsbQ4DYlJskjTgBwPet7w=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnTURRMXJfcFV3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112973732117339181795/reviews?hl=en-GB","posted_at_unix_micros":1741654183481181,"updated_at_unix_micros":1741654183481181,"language":"en","translated_lang":"","text_original":"Intense, Energizing, and Absolutely Worth It!\n\nOne of the most enjoyable workout sessions I’ve had in London. The studio is immaculately clean, with a refreshing signature scent that sets the mood the moment you walk in. The instructor was incredible—motivating, pushing you to your absolute limits, but also knowing exactly when to pull back so you don’t burn out.\n\nThe energy in the room is electric, and the location itself adds to the experience—absolutely love this neighborhood! Gotta burn some calories given the amount that I’m eating.","text_translated":"","published_at":"2025-03-11T00:49:43.481181Z"},{"Name":"Dilnoza Irismetova","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUMDVuYtMNnOVhIL6HvvrTPYKrXlL5uvjVzrnpaFAu0IQTpeYy-=s120-c-rp-mo-ba12-br100","Rating":2,"Description":"I was really looking forward to trying Barry’s London West, especially after great experiences in other locations like SW1. Unfortunately, this visit left me quite disappointed.\n\nFirst, when we arrived, we were told we were on stand-by - which was a surprise. I had switched my booking from East to West, and nowhere in the confirmation email was it mentioned that we were on a waitlist. It simply said the class was booked.\n\nSecond, there was no introduction for newcomers (I even approached Harry to make an intro, he said he will pass by and he never did). In other Barry’s studios, the coach usually asks if anyone’s new and gives a quick explanation about the treadmills and floor exercises. Here, nothing.\n\nThird, the atmosphere at the front desk was far from welcoming. The reception team seemed cold, distracted, and not very open to conversation, even when I tried to ask basic questions.\n\nOthee Barry’s studios made me feel excited and part of the community - but sadly, not this one.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOoKXt3_sVectzHaYuJ1lbCrjN75fSpy8Me3wUj-iw_KPTp68C0vYlC1xruRhd30lYn7FvP03dSkQiQonWLVPNjUdcsw0DW6kQwzemuDprK9lGPezOipRAEZUReou2BJRMZBjb-G-Sd7VZd=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOH261f4XJfCY7U_axSz8noP-8IVMdoYh5xeuHVfsXFc-Yu4KWiprVqMUuPVPm-IFHuQOYJTjWyV8Ivr4EPhbM1BnjfrVhXYNnornrdItvcW4-ZNJde6wY96ACMuFwIr_e4xBkO8MzszJgn=k-no"],"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xFMlFtVkhOMlJsYW1Sb2RDMWlRVGRoUVc5cVkwRRAB","source":"Google","rating_scale":5,"rating_float":2,"author_url":"https://www.google.com/maps/contrib/117098873009970961259/reviews?hl=en-GB","posted_at_unix_micros":1750714339924248,"updated_at_unix_micros":1750714339924248,"language":"en","translated_lang":"","text_original":"I was really looking forward to trying Barry’s London West, especially after great experiences in other locations like SW1. Unfortunately, this visit left me quite disappointed.\n\nFirst, when we arrived, we were told we were on stand-by - which was a surprise. I had switched my booking from East to West, and nowhere in the confirmation email was it mentioned that we were on a waitlist. It simply said the class was booked.\n\nSecond, there was no introduction for newcomers (I even approached Harry to make an intro, he said he will pass by and he never did). In other Barry’s studios, the coach usually asks if anyone’s new and gives a quick explanation about the treadmills and floor exercises. Here, nothing.\n\nThird, the atmosphere at the front desk was far from welcoming. The reception team seemed cold, distracted, and not very open to conversation, even when I tried to ask basic questions.\n\nOthee Barry’s studios made me feel excited and part of the community - but sadly, not this one.","text_translated":"","reply_text_original":"Hi Dilnoza, \n\nwe are sorry to hear this was your experience in our studio. Please could you email us at clientexperienceuk@barrys.com with these details and we will look into this for you. \n\nBest Wishes \n\nBarry's UK ","reply_language":"en","reply_posted_at_unix_micros":1750849176000000,"reply_updated_at_unix_micros":1750849176000000,"published_at":"2025-06-23T21:32:19.924248Z"},{"Name":"Sammy","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWPIecibFw3PZRdwZC_gq3vBx0rnAd54XHFODYrhHD5Wtb-WH4=s120-c-rp-mo-br100","Rating":5,"Description":"Hey, Supersmart kids, Sam here. As advised to your friend after three visual demonstrations and three further personal instructions I suggested that you put your phone down whilst I demonstrated the exercises. Every other participant was watching, listening and performing the class at a range of abilities. Phones are not permitted in class, but if you chose to take one in, maybe put it aside when the demonstrations and instructions are being performed. Barry’s is a an all inclusive place with a positive and supportive atmosphere. Good vibes only!","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25wamFtZGlRMGN0YVdaWFpVVjFaRVZIWDNONFlYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115112643533496186720/reviews?hl=en-GB","posted_at_unix_micros":1770314882150235,"updated_at_unix_micros":1770314882150235,"language":"en","translated_lang":"","text_original":"Hey, Supersmart kids, Sam here. As advised to your friend after three visual demonstrations and three further personal instructions I suggested that you put your phone down whilst I demonstrated the exercises. Every other participant was watching, listening and performing the class at a range of abilities. Phones are not permitted in class, but if you chose to take one in, maybe put it aside when the demonstrations and instructions are being performed. Barry’s is a an all inclusive place with a positive and supportive atmosphere. Good vibes only!","text_translated":"","published_at":"2026-02-05T18:08:02.150235Z"}]</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr"/>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>13</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Evolution+Fitness+London/data=!4m7!3m6!1s0x48760e8bd2c48deb:0x55b0e42857e7e975!8m2!3d51.4666504!4d-0.2670485!16s%2Fg%2F11gds5f205!19sChIJ643E0osOdkgRdennVyjksFU</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Evolution Fitness London</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>40 Sheen Ln, London SW14 8LW, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–8:30 pm"],"Monday":["6 am–8:30 pm"],"Saturday":["8:30 am–12:30 pm"],"Sunday":["8:30 am–12:30 pm"],"Thursday":["6 am–8:30 pm"],"Tuesday":["6 am–8:30 pm"],"Wednesday":["6 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>https://evolutionldn.com/</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>+44 7446 156992</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>FP8M+M5 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>218</v>
+      </c>
+      <c r="O92" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>{"1":3,"2":1,"3":0,"4":3,"5":211}</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>51.46665</v>
+      </c>
+      <c r="R92" t="n">
+        <v>-0.267048</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>6174685951049591157</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnlDmbn0LTU9NQDG3EI1ucAiIeHP6vCnFRbFbfFP-jS57y9wvU6ApdJqNsGx4N1_aswt0r1UCr7vPg4oCCfuJTsB6nAtH9QZc7yd41JBPg6k6axlO1qeZ-kDJsSKQPJrIAh6zXbr_deb69w=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>0x48760e8bd2c48deb:0x55b0e42857e7e975</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>ChIJ643E0osOdkgRdennVyjksFU</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>[{"link":"https://evolutionldn.com/reserve#/schedule/site/1","source":"evolutionldn.com"}]</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>{"id":"117862018472203123790","name":"Evolution Fitness London (Owner)","link":"https://www.google.com/maps/contrib/117862018472203123790"}</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"40 Sheen Ln","city":"London","postal_code":"SW14 8LW","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>[{"Name":"Rim Ahmadieh","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVpf9CY44DAL44vxC6BIgyjZeLcIsHiYHKMwHpVsKn7yc-T0K2a=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Evolution Gym in East Sheen is, without a doubt, the best gym I’ve ever been a member of. If you often feel lost on the gym floor without a personal trainer or a clear workout plan, this is the perfect place for you.\n\nWhat I love most is their structured small-group personal training sessions—you simply show up, and they take care of the rest, in only 6 weeks I lost around 5kgs and 2.4% of my body fat. As for my muscles and core strength they improved significantly. Their cardio classes are fantastic too, from Move to Breathe to Sweat, all designed to work at your own pace while improving your heart health and overall fitness. The Pilates classes are equally impressive.\n\nThe team deserves five stars—they’re incredibly knowledgeable, kind, and genuinely supportive.\n\nIt’s an amazing environment to train in, where you can achieve great results while actually enjoying the process and receiving plenty of encouragement and guidance along the way.\n\nThey also offer trial sessions—and honestly, once you try it, you won’t want to leave!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmO-bHbZBY8hkxvuOCGe8dBQ94iwEWiax1BuSAg7Kr_t7vbgE3GiiytBUkrjWFX7jiHYNKfVvN309DLbfU88qzyEPZMRiKUjJwSIO8m9-TqsARnr6mvRH-uN86_5-a8WC_bZledvFTsoRTS1=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tkSE9HMTNjMHQzWW1WclJHbGZXVkJGVEZOSWFFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106776823958205098122/reviews?hl=en-GB","posted_at_unix_micros":1774717621235433,"updated_at_unix_micros":1774717954875067,"language":"en","translated_lang":"","text_original":"Evolution Gym in East Sheen is, without a doubt, the best gym I’ve ever been a member of. If you often feel lost on the gym floor without a personal trainer or a clear workout plan, this is the perfect place for you.\n\nWhat I love most is their structured small-group personal training sessions—you simply show up, and they take care of the rest, in only 6 weeks I lost around 5kgs and 2.4% of my body fat. As for my muscles and core strength they improved significantly. Their cardio classes are fantastic too, from Move to Breathe to Sweat, all designed to work at your own pace while improving your heart health and overall fitness. The Pilates classes are equally impressive.\n\nThe team deserves five stars—they’re incredibly knowledgeable, kind, and genuinely supportive.\n\nIt’s an amazing environment to train in, where you can achieve great results while actually enjoying the process and receiving plenty of encouragement and guidance along the way.\n\nThey also offer trial sessions—and honestly, once you try it, you won’t want to leave!","text_translated":"","published_at":"2026-03-28T17:07:01.235433Z"},{"Name":"Jenny Ryan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWcPUdASMK535TfRVAU2lHbWBVutBTZhLN7Sh0BtB3C58NH-xOB=s120-c-rp-mo-br100","Rating":5,"Description":"I've just finished my first 6 week introductory course at Evolution Fitness London, and I'm absolutely loving it.\n\nThe coaches are fantastic - they really focus on proper form and take the time to explain why you're doing each exercise, which has made me feel more confident and helped me improve much faster.\n\nThe community is another huge highlight. Everyone is genuinely welcoming, supportive, and interested in each other's progress. It's such a positive environment that makes showing up easy.\n\nThe class times fit perfectly with my schedule, the gym is well equipped, and every session is challenging in the best way. Most importantly, they've made working out something I actually look forward to.\n\nIf you're looking for a gym with knowledgeable coaches, an amazing community, and a fun, supportive atmosphere, I highly recommend Evolution Fitness London.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xBeFlqaFhOM1ZrVDBscGJ6SlRhRWh3V1VkVFUzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109714124447054956232/reviews?hl=en-GB","posted_at_unix_micros":1783368456347008,"updated_at_unix_micros":1783368456347008,"language":"en","translated_lang":"","text_original":"I've just finished my first 6 week introductory course at Evolution Fitness London, and I'm absolutely loving it.\n\nThe coaches are fantastic - they really focus on proper form and take the time to explain why you're doing each exercise, which has made me feel more confident and helped me improve much faster.\n\nThe community is another huge highlight. Everyone is genuinely welcoming, supportive, and interested in each other's progress. It's such a positive environment that makes showing up easy.\n\nThe class times fit perfectly with my schedule, the gym is well equipped, and every session is challenging in the best way. Most importantly, they've made working out something I actually look forward to.\n\nIf you're looking for a gym with knowledgeable coaches, an amazing community, and a fun, supportive atmosphere, I highly recommend Evolution Fitness London.","text_translated":"","published_at":"2026-07-06T20:07:36.347008Z"},{"Name":"Jo Peck","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVc7B-TymBu1HoGiF_KGnfwIhqPhIxAD5n-WrIESTb9QDDUd8M=s120-c-rp-mo-br100","Rating":5,"Description":"I joined Evolution in April on their 6-week trial programme, and it has been fantastic from day one. In such a short space of time, I've gone from being a complete beginner to weight training three times a week, and I can already feel a noticeable difference in my strength and fitness.\n\nWhat really sets Evolution apart is the amazing team of coaches. They are incredibly friendly, supportive, and knowledgeable, always taking the time to ensure you're training safely and effectively. The atmosphere is welcoming and motivating, and the sense of community is brilliant.\n\nAn added bonus is that I get to train alongside my best friend, which makes every session even more enjoyable and helps keep us both accountable.\n\nI would highly recommend Evolution Gym to anyone looking to get stronger, build confidence, and be part of a great community!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pSaVNsOUpTbFF0UlZGQk0ySkJVVjlSTkc5NVgyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100784256989504873441/reviews?hl=en-GB","posted_at_unix_micros":1781701334905309,"updated_at_unix_micros":1781701334905309,"language":"en","translated_lang":"","text_original":"I joined Evolution in April on their 6-week trial programme, and it has been fantastic from day one. In such a short space of time, I've gone from being a complete beginner to weight training three times a week, and I can already feel a noticeable difference in my strength and fitness.\n\nWhat really sets Evolution apart is the amazing team of coaches. They are incredibly friendly, supportive, and knowledgeable, always taking the time to ensure you're training safely and effectively. The atmosphere is welcoming and motivating, and the sense of community is brilliant.\n\nAn added bonus is that I get to train alongside my best friend, which makes every session even more enjoyable and helps keep us both accountable.\n\nI would highly recommend Evolution Gym to anyone looking to get stronger, build confidence, and be part of a great community!","text_translated":"","published_at":"2026-06-17T13:02:14.905309Z"},{"Name":"Nolo Masemola","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJdod8x-GHQH5irieHstEuIsAPCYfTRXeX6IzerO_oOkXA9tWim=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve just finished the 6-week programme at Evolution and really enjoyed it. We started with an InBody scan and went through my goals, then put together a plan to work towards them.\nThe programme is great for building momentum, and the coaches were always encouraging me to push a little harder than I thought I could. The PT sessions were really helpful, and the whole team is friendly, professional, and supportive.\nWhat I liked most is that it doesn’t just feel like a gym – it feels like a community. I’d definitely recommend it to anyone looking to get fitter and stay motivated.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25BeGFqTndTRTlDVGtoT2EwRkNabE5MUjA1UVVIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101172199889503178008/reviews?hl=en-GB","posted_at_unix_micros":1783678303573787,"updated_at_unix_micros":1783678303573787,"language":"en","translated_lang":"","text_original":"I’ve just finished the 6-week programme at Evolution and really enjoyed it. We started with an InBody scan and went through my goals, then put together a plan to work towards them.\nThe programme is great for building momentum, and the coaches were always encouraging me to push a little harder than I thought I could. The PT sessions were really helpful, and the whole team is friendly, professional, and supportive.\nWhat I liked most is that it doesn’t just feel like a gym – it feels like a community. I’d definitely recommend it to anyone looking to get fitter and stay motivated.","text_translated":"","published_at":"2026-07-10T10:11:43.573787Z"},{"Name":"ELLA COLEMAN","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJL8u3QJgyZoczcSEFpEAMom-tJvyXdttfRt2MGw5drFOftIQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"We all hear about how we should be doing strength training, but there was just no appeal to be one of those gung-ho weight lifters sweating it out in a gym... until I went on holiday a few months ago and realised my exercise routine of long walks and yoga wasn't quite hacking it. I signed up for the 6-week programme at EVO and was surprised at how much I enjoyed the sessions! I've gone on to become a full-time member.\n\nEVO is set up in a unique way, with small groups so you get a lot of help for every step/squat/lift. All the personal trainers are super friendly and incredibly helpful - they can spot my bad form a mile off and are very kind in the way they correct me. I am feeling so much stronger and more mobile - I think strength training combined with yoga is getting my body back in bikini shape - whoo hoo!\n\nThanks to the lovely crew who make EVO such a welcoming and fun place. Who would have thought I'd be so proud and happy to be a gung-ho gym bunny!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xCc1UwcExkM3BXZHpWc1FrOWpVR1JGVEROQ1dGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106495525009027976802/reviews?hl=en-GB","posted_at_unix_micros":1781701003299209,"updated_at_unix_micros":1781763926615191,"language":"en","translated_lang":"","text_original":"We all hear about how we should be doing strength training, but there was just no appeal to be one of those gung-ho weight lifters sweating it out in a gym... until I went on holiday a few months ago and realised my exercise routine of long walks and yoga wasn't quite hacking it. I signed up for the 6-week programme at EVO and was surprised at how much I enjoyed the sessions! I've gone on to become a full-time member.\n\nEVO is set up in a unique way, with small groups so you get a lot of help for every step/squat/lift. All the personal trainers are super friendly and incredibly helpful - they can spot my bad form a mile off and are very kind in the way they correct me. I am feeling so much stronger and more mobile - I think strength training combined with yoga is getting my body back in bikini shape - whoo hoo!\n\nThanks to the lovely crew who make EVO such a welcoming and fun place. Who would have thought I'd be so proud and happy to be a gung-ho gym bunny!","text_translated":"","published_at":"2026-06-17T12:56:43.299209Z"}]</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>13</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/1Rebel+Bayswater/data=!4m7!3m6!1s0x48761aaa9ba11e2f:0xe99c1f51aa96cda2!8m2!3d51.5165573!4d-0.1875276!16s%2Fg%2F11ggrm07n9!19sChIJLx6hm6oadkgRos2WqlEfnOk</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1Rebel Bayswater</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>34 Porchester Rd, London W2 6ES, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9 pm"],"Monday":["6 am–10 pm"],"Saturday":["7:30 am–7 pm"],"Sunday":["8:15 am–7 pm"],"Thursday":["6 am–9 pm"],"Tuesday":["6 am–10 pm"],"Wednesday":["6 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1rebel.com/en-gb</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>+44 20 3800 0990</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>GR86+JX London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>211</v>
+      </c>
+      <c r="O93" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>{"1":21,"2":2,"3":4,"4":9,"5":175}</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>51.516557</v>
+      </c>
+      <c r="R93" t="n">
+        <v>-0.187528</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>16833363942818893218</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnNvLt0gq5MKiRyUxRk-0jsm312Tx7o0oucadDkgyEEGCkzUtdJUgUH0AeEaCOIoT7YZyDwFPCY7pviE6StSZwBLb7feJ1ABMkpwH8gHxpyb_QehJWqxMxlltdJ4Ym9KtqhWZ4N=w408-h333-k-no</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>0x48761aaa9ba11e2f:0xe99c1f51aa96cda2</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>ChIJLx6hm6oadkgRos2WqlEfnOk</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>{"id":"111768540935874191719","name":"1Rebel Bayswater (Owner)","link":"https://www.google.com/maps/contrib/111768540935874191719"}</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"34 Porchester Rd","city":"London","postal_code":"W2 6ES","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>[{"Name":"Bowen Su","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJIK0ogpLWBBHlUmYd28wlwjiX7GJkKiJaBpriJr82fQ1OuRw=s120-c-rp-mo-br100","Rating":5,"Description":"My favourite Chinese hotpot in London; Sour spicy soup base is highly recommended! Currently have all you can eat offer!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMBzNYPlsobCnYxjICtFyek6_Zd-JBjQ0W-C5a9SXLUIEgsTJBjxUMOGNv0U6Bv2t0GhepRzpPgLDKIaVAr5jZsB_czlR9SKHPSye-iLaWXHwp0OuC4Edj7cKb5FofsRfnuEzOjfjwhhPE=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPgyFRolJFKZ2AeQwtcb5o_p-WBc2JP1NI-N3h6winqCuLIeQ-XmgGwC8vb2xHUQ3HZopq-bJedA9wJjKIjRusOggRT6I5CttcxnWzHTPTBZu_Qe8eOiySFAzgu7--idGz5O0Xdaq-ZzV4=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPybVzq8xCbDevIE7eJ1avRSb79CZVCHwRg0sDGw8ADpF17Gc1Lr5dFH75F3H4hxOJdAwZvcD92eTL5jqHw3UsHDpwjxEUgmGZZEDJ71QKyZT7q4SsVKDkq4OlrvH42hZS3i2B5r3bHe0gX=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNsjPeBuEk_vxbJjTo0o3u0xDAVcJL2WrHfgh546Zdd_nYkHSAU7p9UIAqwW18bprGN6nYdMSRO5rjBDoNKNQxglokj1eUGF2b6T0JIAViNL4bksA4gUOxVAJ9jPxsfNXkLCJVqx64WCmDp=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM3dcepg1NAp7H4Q3ixRpYjCMIZdtIrzEUt22erBVjQwfweCQNro8si1RWqVbcK4QiBjeOLOV08Ydm-egD_IKlMNkmiRojB66UIlx0Dq8zK6ALDjePGDYYC0yAU8gJou7oV-vRjMG50lQVU=k-no"],"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s5TVZXZzFhR05zTWpCWE4xcFZNMVE1UVhVMGNsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113499657522389780649/reviews?hl=en-GB","posted_at_unix_micros":1777897442415438,"updated_at_unix_micros":1777897519174343,"language":"en","translated_lang":"","text_original":"My favourite Chinese hotpot in London; Sour spicy soup base is highly recommended! Currently have all you can eat offer!","text_translated":"","published_at":"2026-05-04T12:24:02.415438Z"},{"Name":"Viviana Agostinho","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWUZGnlMwM7xGPdtxl4gtcGS_TeitCuJLqPuz7Nl2w0udbHAGFs=s120-c-rp-mo-br100","Rating":5,"Description":"I was never a gym rat but 1Rebel Bayswater changed that: it has become pretty much my second home! The classes are super fun, very inclusive and challenging. I particularly enjoy their Reformer classes — amazing instructors, clean equipments, lots of new props and modifications that suit every body and level. They also have the most welcoming, friendliest staff (Ash, Maddie, Sydney… ❤️). I can’t think of working out anywhere else.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tSMGFUZG1WbVYzVlU1UWVqbFlURlF4TVVGVlRWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113976489189244214206/reviews?hl=en-GB","posted_at_unix_micros":1779871492921807,"updated_at_unix_micros":1779871492921807,"language":"en","translated_lang":"","text_original":"I was never a gym rat but 1Rebel Bayswater changed that: it has become pretty much my second home! The classes are super fun, very inclusive and challenging. I particularly enjoy their Reformer classes — amazing instructors, clean equipments, lots of new props and modifications that suit every body and level. They also have the most welcoming, friendliest staff (Ash, Maddie, Sydney… ❤️). I can’t think of working out anywhere else.","text_translated":"","published_at":"2026-05-27T08:44:52.921807Z"},{"Name":"Reem","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK7-Up-SgTdCyB654n7KJA2sKg17dmUL_yyQAPcfiLCCNhesXY=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Im a huge 1rebel fan but Bayswater has to be the most elite!! The entire team are so adorable. Sirene is SUCH A GEM!! and Khalid always good vibes. All the Instructors are all amazing, Charlotte and Rosie are UN-REAL!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xObGFGOVliM2hZYjJGQ2RFTlBZMWt4VkhKWE5YYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108773616837730175008/reviews?hl=en-GB","posted_at_unix_micros":1780152486674840,"updated_at_unix_micros":1780152486674840,"language":"en","translated_lang":"","text_original":"Im a huge 1rebel fan but Bayswater has to be the most elite!! The entire team are so adorable. Sirene is SUCH A GEM!! and Khalid always good vibes. All the Instructors are all amazing, Charlotte and Rosie are UN-REAL!","text_translated":"","published_at":"2026-05-30T14:48:06.67484Z"},{"Name":"Kirty Patel","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJIQeQRTIy2cnVWvzMTbp9_uscWE4SBewTpagxWj87e_NsdAw=s120-c-rp-mo-br100","Rating":5,"Description":"Bayswater - my fave 1Rebel studio!\n\nThe FoH team always welcome you with so much energy and make you feel fab. You’re all amazing - Ash, Hannah, Maddie and not forgetting everyone else including the trainers (Camila, Andy, Libby). You always bring such a great vibe 🤍","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tWWU5XSk5Xa2t5YzB3NVF5MUtaREJmTldaU1VGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106207096904937511253/reviews?hl=en-GB","posted_at_unix_micros":1779875456947736,"updated_at_unix_micros":1779875456947736,"language":"en","translated_lang":"","text_original":"Bayswater - my fave 1Rebel studio!\n\nThe FoH team always welcome you with so much energy and make you feel fab. You’re all amazing - Ash, Hannah, Maddie and not forgetting everyone else including the trainers (Camila, Andy, Libby). You always bring such a great vibe 🤍","text_translated":"","published_at":"2026-05-27T09:50:56.947736Z"},{"Name":"Beth Farnsworth","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJeS_jzk1C85Y2ccUjv6Ew__3jIl08LcUjd6AnBruKW7C4_9w=s120-c-rp-mo-br100","Rating":5,"Description":"Love the range of workouts you can do at 1Rebel, with the most wonderful, positive, instructors that make it a joy. The front of house team at Bayswater set it apart from other clubs - always so friendly, welcoming and helpful. Shoutout to Ash and Sorcha who are just amazing!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT20xd01VRkljM2MwVXpaa2EydEhUVU5PYm5Wd1JHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106488132662284991749/reviews?hl=en-GB","posted_at_unix_micros":1780133725758702,"updated_at_unix_micros":1780133725758702,"language":"en","translated_lang":"","text_original":"Love the range of workouts you can do at 1Rebel, with the most wonderful, positive, instructors that make it a joy. The front of house team at Bayswater set it apart from other clubs - always so friendly, welcoming and helpful. Shoutout to Ash and Sorcha who are just amazing!","text_translated":"","published_at":"2026-05-30T09:35:25.758702Z"}]</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>13</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/1Rebel+South+Bank/data=!4m7!3m6!1s0x487604ae2799e9d5:0x90b3404d7eb6047a!8m2!3d51.5080033!4d-0.1058553!16s%2Fg%2F11gf8dw37t!19sChIJ1emZJ64EdkgRegS2fk1As5A</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1Rebel South Bank</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>7 Upper Ground, London SE1 9LP, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–8:45 pm"],"Monday":["6 am–9:45 pm"],"Saturday":["7:30 am–4:30 pm"],"Sunday":["7:30 am–4:30 pm"],"Thursday":["6 am–9:45 pm"],"Tuesday":["6 am–9:45 pm"],"Wednesday":["6 am–9:45 pm"]}</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1rebel.com/en-gb</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>+44 20 3800 1800</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>GV5V+6M London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>208</v>
+      </c>
+      <c r="O94" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>{"1":15,"2":4,"3":11,"4":23,"5":155}</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>51.508003</v>
+      </c>
+      <c r="R94" t="n">
+        <v>-0.105855</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>10426748263875347578</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmGabqNvJwiqzsWLw5c1kOSl-efb95otTG4ZG8aTdbZvsTdrQL1QlnXB_pHVoEc2icUhJYNsuy6S2_o1k5unu6mFJUR2Q1I2ppJRS_JiE4sceldixRebpwOKrOqDUtmoJlc3dgQ=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>0x487604ae2799e9d5:0x90b3404d7eb6047a</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>ChIJ1emZJ64EdkgRegS2fk1As5A</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>{"id":"113093597105005772374","name":"1Rebel South Bank (Owner)","link":"https://www.google.com/maps/contrib/113093597105005772374"}</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"7 Upper Ground","city":"London","postal_code":"SE1 9LP","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>[{"Name":"Florencia Moreno","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWH9aAKl10GwbPGxoz5Gegz0wYAUEW23aXpq2lfMuelRQ-Jj_j_=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I was impressed the moment I walked in — the place feels very high-end. When I checked in, a really friendly blonde little dude gave me all the info I needed: where to sit, my bed number, and how long to wait.\n\nMy reformer class was with Jack D, and it was honestly one of the most complete classes I’ve ever taken. He’s not only funny and a great showman, but he also really pays attention to every student and corrects posture. He demonstrates everything himself and gives extra attention to beginners and non-native speakers. He chooses his words carefully, reminds you to be grateful to be there, and even makes you reflect on yourself. He truly covers every aspect (and more) that a class can offer.\n\nAfter my first class, I left feeling emotional and told to a very nice girl at front desk they have a truly special instructor. One of kind dude. She said ‘you should comeback’ and I felt she knew what I talking about.\nThe shakes are excellent too. I had ‘the glow up’ and ‘the recovery’.\nI would recommend 1Rebel Southbank a thousand times.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmN9BM_itk_eeUd3y7tjn15G2ciD2ikvYFp5_D4Eu5RkbNgCj6CuodFd6PUqRKYOm2MFzHg-5tfpB1T1FKHk_fKk2wnRL8s8T8AFSSL0bsC0HQDpOYmkakQd7sW5ijtnhGLeNp2AbC2JGu0=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tsQ1lsaFJiMms1VVVKbVVFNTFOalY1TVhCaGVXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108930475348842762139/reviews?hl=en-GB","posted_at_unix_micros":1771404821499735,"updated_at_unix_micros":1771405027224270,"language":"en","translated_lang":"","text_original":"I was impressed the moment I walked in — the place feels very high-end. When I checked in, a really friendly blonde little dude gave me all the info I needed: where to sit, my bed number, and how long to wait.\n\nMy reformer class was with Jack D, and it was honestly one of the most complete classes I’ve ever taken. He’s not only funny and a great showman, but he also really pays attention to every student and corrects posture. He demonstrates everything himself and gives extra attention to beginners and non-native speakers. He chooses his words carefully, reminds you to be grateful to be there, and even makes you reflect on yourself. He truly covers every aspect (and more) that a class can offer.\n\nAfter my first class, I left feeling emotional and told to a very nice girl at front desk they have a truly special instructor. One of kind dude. She said ‘you should comeback’ and I felt she knew what I talking about.\nThe shakes are excellent too. I had ‘the glow up’ and ‘the recovery’.\nI would recommend 1Rebel Southbank a thousand times.","text_translated":"","published_at":"2026-02-18T08:53:41.499735Z"},{"Name":"Amy Playfair","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXIZ9WnM8u-QcGjJAJ3SI5JaXTMxbOPPTe_RrZ9zusa3nO-lVY=s120-c-rp-mo-br100","Rating":5,"Description":"Love this place!! I had an amazing workout today with Bryony -such a great session. A special shoutout as well to Catherine and Tash on front of house, who very kindly granted me a credit back after a flare-up of my chronic illness earlier this week. That level of understanding and care really means a lot.\n\nI’d recommend a membership here to anyone and everyone!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25weVlucDZOSHBHU2tSV1YybHhTbkkxYUVob1ltYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117653227499379491586/reviews?hl=en-GB","posted_at_unix_micros":1771511835161240,"updated_at_unix_micros":1771511835161240,"language":"en","translated_lang":"","text_original":"Love this place!! I had an amazing workout today with Bryony -such a great session. A special shoutout as well to Catherine and Tash on front of house, who very kindly granted me a credit back after a flare-up of my chronic illness earlier this week. That level of understanding and care really means a lot.\n\nI’d recommend a membership here to anyone and everyone!","text_translated":"","published_at":"2026-02-19T14:37:15.16124Z"},{"Name":"Vincent P","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJaPIPiSq5o5GEqrCKNYdhDfwgw7G0Qp-hfiGXSWVD33U-2SZc=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My go-to gym for the past three months! 1Rebel’s have great energy, the staff is always welcoming, and the instructors are great. I would only suggest lowering the volume a bit or wearing some earplugs as it can sometimes be a bit too loud!\n\nEDIT: this continues to be my favourite 1Rebel club. I have been to many, including more recently built ones, but South Bank remains the best, especially due to the kindness of the staff. Can only recommend!","Images":null,"When":"Edited 3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xkaFZuWjZWVlJhVW5OV2JYQnNSRGxzYW5ScE0wRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110772735475205981045/reviews?hl=en-GB","posted_at_unix_micros":1763813688879349,"updated_at_unix_micros":1779725450417378,"language":"en","translated_lang":"","text_original":"My go-to gym for the past three months! 1Rebel’s have great energy, the staff is always welcoming, and the instructors are great. I would only suggest lowering the volume a bit or wearing some earplugs as it can sometimes be a bit too loud!\n\nEDIT: this continues to be my favourite 1Rebel club. I have been to many, including more recently built ones, but South Bank remains the best, especially due to the kindness of the staff. Can only recommend!","text_translated":"","reply_text_original":"Hi Vincent, \n\nThank you so much for the 5 stars and we're happy to hear you're enjoying your experience at Southbank :) \n\nThank you for taking the time to pass along your feedback and we can't wait to see you in the studio soon. \n\nBest wishes, \n1Rebel Southbank ","reply_language":"en","reply_posted_at_unix_micros":1766144156000000,"reply_updated_at_unix_micros":1766144156000000,"published_at":"2025-11-22T12:14:48.879349Z"},{"Name":"Henry Wadsworth","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXn3kHh79IQrhJ4HSAr39hAJ48nUwcX_rE4GdM41Pl_oaAOWruz=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"A big THANK YOU to Yanilda, Morgan and Tara on the front desk at 1Rebel Broadgate for the amazing service they gave my mate and I earlier this week. They always greet you with the loveliest smiles, no matter what time of day it is, and they’re one of the many reasons I love working out at 1Rebel. Such a lovely group of girls - they’re an absolute asset to the company!","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tSUlFWZFliVmxsZFZRMGRXWmliREJvWm5Fd1RrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103781595832735585221/reviews?hl=en-GB","posted_at_unix_micros":1769066965201883,"updated_at_unix_micros":1769066965201883,"language":"en","translated_lang":"","text_original":"A big THANK YOU to Yanilda, Morgan and Tara on the front desk at 1Rebel Broadgate for the amazing service they gave my mate and I earlier this week. They always greet you with the loveliest smiles, no matter what time of day it is, and they’re one of the many reasons I love working out at 1Rebel. Such a lovely group of girls - they’re an absolute asset to the company!","text_translated":"","published_at":"2026-01-22T07:29:25.201883Z"},{"Name":"Laura Estrada","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIaQsF5t-ZGgugAUFy_tZHWnXpEPjpFXTRIN8H4dbcg-Ee3fA=s120-c-rp-mo-br100","Rating":5,"Description":"Great facilities and amenities the staff are always going far and beyond. I’ve been to many studios and this has to be one of my favourite due to the quality of the classes and all its staff members from reception to instructors.","Images":null,"When":"Edited 5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tGU1NWRlBiVXRYY0ZSSWFWbDNkR2x0UlZOTmVYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102323264374224973359/reviews?hl=en-GB","posted_at_unix_micros":1775339583543240,"updated_at_unix_micros":1775579875709572,"language":"en","translated_lang":"","text_original":"Great facilities and amenities the staff are always going far and beyond. I’ve been to many studios and this has to be one of my favourite due to the quality of the classes and all its staff members from reception to instructors.","text_translated":"","published_at":"2026-04-04T21:53:03.54324Z"}]</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr"/>
+      <c r="AM94" t="inlineStr"/>
+      <c r="AN94" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>13</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>6758c484-00e9-4c1c-a81f-56f19a65c71b</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Vita+Boutique+Fitness/data=!4m7!3m6!1s0x487605f240fb9345:0x861c1e32844c024!8m2!3d51.4921391!4d-0.1578784!16s%2Fg%2F11j1k8r7b7!19sChIJRZP7QPIFdkgRJMBEKOPBYQg</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vita Boutique Fitness</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Pilates studio</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>31 Sloane Square, London SW1W 8AQ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>{"Friday":["7:30 am–7:30 pm"],"Monday":["7:30 am–8:30 pm"],"Saturday":["9:30 am–5:30 pm"],"Sunday":["9:30 am–5:30 pm"],"Thursday":["7:30 am–8:30 pm"],"Tuesday":["7:30 am–8:30 pm"],"Wednesday":["7:30 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>https://vitaboutiquefitness.com/</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>+44 20 7730 4814</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>FRRR+VR London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>206</v>
+      </c>
+      <c r="O95" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>{"1":34,"2":6,"3":3,"4":5,"5":158}</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>51.492139</v>
+      </c>
+      <c r="R95" t="n">
+        <v>-0.157878</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>603977006421688356</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkI3g13md9JG2iqxBQ2SFWFajhEwHA1TmYMhgRoXXdmDCvhm3rvvoTscM_v4rXo11syPwEz0kUZQJ9CdSXgmkoOFuoMPsoco0FwtHD8wm-DgLsvEcODv0l42YnpIc3ksimVO2izgg=w408-h408-k-no</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>0x487605f240fb9345:0x861c1e32844c024</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>ChIJRZP7QPIFdkgRJMBEKOPBYQg</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr"/>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.fresha.com/book-now/vita-head-body-spa-b563er21/all-offer?id=1548406\u0026pId=1469528\u0026rwg_token=AE37R_iHyaBgOq0PZLrttoam54uLXP04Czypy0zgF-LT0vIPgEeDMKWLbxjezJOm5DI2EV7Y7DI_LOuNz7w0taMszrmdXW0oyS7pe0fgL67U5drOblc01z8%3D","source":"fresha.com"}]</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>{"id":"114597903224818866324","name":"Vita Boutique Fitness (Owner)","link":"https://www.google.com/maps/contrib/114597903224818866324"}</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"31 Sloane Square","city":"London","postal_code":"SW1W 8AQ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>[{"Name":"Emilia Struss","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIcFPMd7_SLvBZLeataT4wOjJ2Oz-6dqDnzINr7qnKAJfg5RQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"You HAVE to try Vita in Sloane Square.\nI went for Pilates but was also impressed by everything else they offer.\nThey’ve got the Glow Bar Cafe, head spa, Emsculpt, and a lymphatic roller treatment that looks super interesting!\n\nIt’s so wellness-focused and not gym-y at all. You work out then actually feel refreshed after. Also the staff is super lovely!\nPerfect if you want fitness + beauty + recovery in one place.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSeFVWbG9SMnB0UVRCbFFqZFFkM281ZUZwaldtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112884927793477510202/reviews?hl=en-GB","posted_at_unix_micros":1783454516406542,"updated_at_unix_micros":1783454516406542,"language":"en","translated_lang":"","text_original":"You HAVE to try Vita in Sloane Square.\nI went for Pilates but was also impressed by everything else they offer.\nThey’ve got the Glow Bar Cafe, head spa, Emsculpt, and a lymphatic roller treatment that looks super interesting!\n\nIt’s so wellness-focused and not gym-y at all. You work out then actually feel refreshed after. Also the staff is super lovely!\nPerfect if you want fitness + beauty + recovery in one place.","text_translated":"","published_at":"2026-07-07T20:01:56.406542Z"},{"Name":"Tracy Sedino","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJPe-aN1yP4HCUF_mEUqBQJRCfnAzdWm7Rf66ObsB08Mz4bSg=s120-c-rp-mo-br100","Rating":5,"Description":"Incredible space and location, most importantly great classes and teachers. I absolutely love the infrared classes and that they have multiple other services such as EMSculpt and a head spa! Whats not to like, also serve my fav Ube Coconut Matcha 🤍","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOT-iwEE7v8Kmdfy5fT0a4nsae69cMmiWUNDDkx6T6vMwgSwdh3ifNCkM8El-xsGwt2Tywm1GDKNekzJVmjqD6HU7-_vxDROqIue6MpIzsBWCNO00a3zTqGznWrrb9e7GahHi-4Lyf83SCj=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmN9ceuRLpqWrGjcN6OFpMJCct6g_tsKZzrt1Fc52XYEEoMoEZUwxBpUEr5Q_3nHkMP_R4oHzQSzQ160ZZz0aVsBjx-XWeZ6e0Jr4DaJvQM0QBB3HVSbDPnpzwUImMMFXTMeBwMzFUgBZE9E=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPvuIy0E3K7tOmlsz2gDpP-A3ET8OdUCEOriMwMDnXdFWfetLlOd0uOICgCvhNygFtwOAYXEOHeHaf1TFO8CEbgLlOLgTRf42048fj7O5N2SEEb-vrWSd7A7AQ_AFkcOo1splJDHJk8O9b8=k-no"],"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psaFluQmFjVU5sUWpaa1NGQXhNRlpMVWs1MmFVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109755833795200597099/reviews?hl=en-GB","posted_at_unix_micros":1770287018243713,"updated_at_unix_micros":1770287018243713,"language":"en","translated_lang":"","text_original":"Incredible space and location, most importantly great classes and teachers. I absolutely love the infrared classes and that they have multiple other services such as EMSculpt and a head spa! Whats not to like, also serve my fav Ube Coconut Matcha 🤍","text_translated":"","published_at":"2026-02-05T10:23:38.243713Z"},{"Name":"Abby Haber","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK6oWdOK4ko2JQRUxyUoHTh8ansVKNVi8mPKhFeG0nuiAmbfA=s120-c-rp-mo-br100","Rating":5,"Description":"I had a great experience at Vita Boutique Fitness in Sloane Square. The space is beautiful, clean, and welcoming, and it feels like a perfect mix of boutique fitness and wellness. I really liked that they offer Pilates along with treatments like the lymphatic body roller and Emsculpt. The Glow Bar Cafe is also such a nice touch for matcha or coffee after a session. Definitely recommend for anyone in Chelsea looking for a health and wellness spot.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2poZmIyMWFORGw1YUhweE0yOUZOMjFoV0Uxd1IzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116497246609018571632/reviews?hl=en-GB","posted_at_unix_micros":1783437516507815,"updated_at_unix_micros":1783437519172093,"language":"en","translated_lang":"","text_original":"I had a great experience at Vita Boutique Fitness in Sloane Square. The space is beautiful, clean, and welcoming, and it feels like a perfect mix of boutique fitness and wellness. I really liked that they offer Pilates along with treatments like the lymphatic body roller and Emsculpt. The Glow Bar Cafe is also such a nice touch for matcha or coffee after a session. Definitely recommend for anyone in Chelsea looking for a health and wellness spot.","text_translated":"","published_at":"2026-07-07T15:18:36.507815Z"},{"Name":"Brooke Ketterer","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJwZR18ijRCKb47c0Q8NQVq9zPg2p5kqvh6ipyYPtDUNdtShA=s120-c-rp-mo-br100","Rating":5,"Description":"Vita Boutique Fitness is such a great wellness spot in Chelsea. The Pilates classes are enjoyable, the studio is beautiful and welcoming, and I love that everything is in one place. Grabbing a matcha from the Glow Bar Cafe after class is the perfect way to finish a workout. Definitely a great choice if you're looking for boutique fitness near Sloane Square.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pGTE1uZFBTa1oxVVhCRmFETkxObWhUUTBST1VVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112792840455873255803/reviews?hl=en-GB","posted_at_unix_micros":1783518667162451,"updated_at_unix_micros":1783518667162451,"language":"en","translated_lang":"","text_original":"Vita Boutique Fitness is such a great wellness spot in Chelsea. The Pilates classes are enjoyable, the studio is beautiful and welcoming, and I love that everything is in one place. Grabbing a matcha from the Glow Bar Cafe after class is the perfect way to finish a workout. Definitely a great choice if you're looking for boutique fitness near Sloane Square.","text_translated":"","published_at":"2026-07-08T13:51:07.162451Z"},{"Name":"Ava Saalfeld","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLLJFibm9m5NiSuksGhXloaTwwDrVWK0rs1Pzfq1VArukmpsA=s120-c-rp-mo-br100","Rating":5,"Description":"I had such a great experience at Vita Boutique Fitness! The Pilates class was challenging in the best way and the instructor made everyone feel comfortable, no matter their experience level. The studio is gorgeous, clean, and has such a relaxing atmosphere. Everyone at the front desk was incredibly welcoming, and I loved being able to grab a drink from the Café after class. It’s such a unique wellness space, and I would recommend it to anyone in the area!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xNMmRFWkJlV3c0TjJaelZrTlphbEkxUW1SbmFFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114487541365839457052/reviews?hl=en-GB","posted_at_unix_micros":1783538617355983,"updated_at_unix_micros":1783538617355983,"language":"en","translated_lang":"","text_original":"I had such a great experience at Vita Boutique Fitness! The Pilates class was challenging in the best way and the instructor made everyone feel comfortable, no matter their experience level. The studio is gorgeous, clean, and has such a relaxing atmosphere. Everyone at the front desk was incredibly welcoming, and I loved being able to grab a drink from the Café after class. It’s such a unique wellness space, and I would recommend it to anyone in the area!","text_translated":"","published_at":"2026-07-08T19:23:37.355983Z"}]</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="inlineStr"/>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>13</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Gym+On+London/data=!4m7!3m6!1s0x487605d2081a3803:0xf6d5f960176b2d9!8m2!3d51.4655311!4d-0.181197!16s%2Fg%2F11fmgzbmq1!19sChIJAzgaCNIFdkgR2bJ2AZZfbQ8</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Gym On London</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2 Chatfield Rd, London SW11 3SD, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–10 pm"],"Monday":["6 am–10 pm"],"Saturday":["8 am–5 pm"],"Sunday":["8 am–5 pm"],"Thursday":["6 am–10 pm"],"Tuesday":["6 am–10 pm"],"Wednesday":["6 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>http://www.gymonlondon.com/</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>+44 20 8063 5939</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>FR89+6G London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>198</v>
+      </c>
+      <c r="O96" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>{"1":4,"2":1,"3":2,"4":7,"5":184}</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>51.465531</v>
+      </c>
+      <c r="R96" t="n">
+        <v>-0.181197</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1111649780904669913</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn47-zS-2vh5MR9XeGnk1wEZYMa6VRkj53rJBFp7EqCEXJoinb9aYqB2RVOXEkvGdFd9oRBlI_YzwsUdhcZF-x446Wul13tnPwFgdSWhl8FLs7OxGQYvgYUluEusVXofxnV64rV7eOFzpPo=w408-h274-k-no</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>0x487605d2081a3803:0xf6d5f960176b2d9</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>ChIJAzgaCNIFdkgR2bJ2AZZfbQ8</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>{"id":"106149042961676229776","name":"Gym On London (Owner)","link":"https://www.google.com/maps/contrib/106149042961676229776"}</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"2 Chatfield Rd","city":"London","postal_code":"SW11 3SD","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>[{"Name":"Raeesa Hussain","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIm3DTwtmt43y7TSHoktjSPQ6COKBnlelNIZ0H8YxagNHruEVU=s120-c-rp-mo-br100","Rating":4,"Description":"Great gym! Been coming here consistently for a few months and it has all the equipment you need and machines are normally free to use.\nMy only negative is that the equipment has not really been maintained when it has broken or become dirty whilst I have been here, and a lot of the machines are dusty on top.\nOther than that, the gym is lovely and the staff are very welcoming.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2kxUmVYRk5kRFphTUVNeFl6SkZhMGREYW5WU1NXYxAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/118251435791238402776/reviews?hl=en-GB","posted_at_unix_micros":1770320266971326,"updated_at_unix_micros":1770320266971326,"language":"en","translated_lang":"","text_original":"Great gym! Been coming here consistently for a few months and it has all the equipment you need and machines are normally free to use.\nMy only negative is that the equipment has not really been maintained when it has broken or become dirty whilst I have been here, and a lot of the machines are dusty on top.\nOther than that, the gym is lovely and the staff are very welcoming.","text_translated":"","published_at":"2026-02-05T19:37:46.971326Z"},{"Name":"Flavie Delahaut","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKye4-9oq1TIjtkazlKYBztEO6WSZLM78N1qwIO6hMfKHD9xA=s120-c-rp-mo-br100","Rating":5,"Description":"I absolutely love this gym! The coaches are super friendly and always adapt the workouts to each person’s needs. The atmosphere is great, everyone is welcoming and there’s always a good vibe. The equipment is top quality, and there’s always enough space to do your workout comfortably. And if you’re in the mood for a little coffee after your session, they even have a super nice coffee shop with amazing drinks. Highly recommend!","Images":null,"When":"10 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT201d2ExRjROa2RLVjFSQlEzaGlZak51YURWdFJtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101997686566745383045/reviews?hl=en-GB","posted_at_unix_micros":1761900679316960,"updated_at_unix_micros":1761900679316960,"language":"en","translated_lang":"","text_original":"I absolutely love this gym! The coaches are super friendly and always adapt the workouts to each person’s needs. The atmosphere is great, everyone is welcoming and there’s always a good vibe. The equipment is top quality, and there’s always enough space to do your workout comfortably. And if you’re in the mood for a little coffee after your session, they even have a super nice coffee shop with amazing drinks. Highly recommend!","text_translated":"","published_at":"2025-10-31T08:51:19.31696Z"},{"Name":"Katie Partridge","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWeDsLYotrdUwo70XPosKe0kelT92pnm7QHG_Qdt9rC2g1U-CLGNw=s120-c-rp-mo-br100","Rating":5,"Description":"Such a nice community gym, with the loveliest staff 💪🏼. Coffee beans from Doppia are elite \u0026 nice latte art too (always needed for an early gym sesh…). Would definitely recommend :)","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOa08nRfEiBfiXNV0gxw2NLNOUkKfk_amOqL6AmEYC4bwu4VV4Xbx5plem-VeQoQnqbNbVrNM4q8F2HBKdlqGUjtD--7T_ZoRXtLh1TJFQQ-E7UJ0uTGcL203M9ggXX_yswAZAXmqaNQUga=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2taWFpIZE5aa1JLYmtoMmRuZFFkRTg0ZW5aU2EwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107526945068629958404/reviews?hl=en-GB","posted_at_unix_micros":1771496932260832,"updated_at_unix_micros":1771496973535612,"language":"en","translated_lang":"","text_original":"Such a nice community gym, with the loveliest staff 💪🏼. Coffee beans from Doppia are elite \u0026 nice latte art too (always needed for an early gym sesh…). Would definitely recommend :)","text_translated":"","published_at":"2026-02-19T10:28:52.260832Z"},{"Name":"Monika Trawińska","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLXBkF4_0jWzFe6tCaRlPb7R6RhZ8foguz69qY-d47y0VGVTSk=s120-c-rp-mo-br100","Rating":5,"Description":"Great place with a vibe of local club. Cheerful community, very welcoming service. All equipment available when needed. Energetic morning classes. And the best part - coffee in the little cafe corner. Absolutely favourite!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tRemEwdGxhbkpUUmpSVmMzRlNkVVJYWjFCMmFFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110877342861362505906/reviews?hl=en-GB","posted_at_unix_micros":1771332628602953,"updated_at_unix_micros":1771332628602953,"language":"en","translated_lang":"","text_original":"Great place with a vibe of local club. Cheerful community, very welcoming service. All equipment available when needed. Energetic morning classes. And the best part - coffee in the little cafe corner. Absolutely favourite!","text_translated":"","published_at":"2026-02-17T12:50:28.602953Z"},{"Name":"Abigail Boxall","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJXkix9JrPJI2wr_01UUYzPX9vSqj4AM8Y8PyhsNgM8lhzpRxZw=s120-c-rp-mo-br100","Rating":5,"Description":"A fantastic gym! I have been coming to Gym On consistently for 9 months, it has a welcoming atmosphere and the staff are super friendly and helpful. The gym is never too crowded (even at peak times) and as a woman in my 20’s, I have always felt safe and comfortable!","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25CclVrNUdjRk15YmtaRlF6QlhjMmMwZGxnNVdIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112400691833872034327/reviews?hl=en-GB","posted_at_unix_micros":1756990924502487,"updated_at_unix_micros":1756990924502487,"language":"en","translated_lang":"","text_original":"A fantastic gym! I have been coming to Gym On consistently for 9 months, it has a welcoming atmosphere and the staff are super friendly and helpful. The gym is never too crowded (even at peak times) and as a woman in my 20’s, I have always felt safe and comfortable!","text_translated":"","published_at":"2025-09-04T13:02:04.502487Z"}]</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="inlineStr"/>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>13</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/INYO+Fit+-+UK+Branch/data=!4m7!3m6!1s0x487611d800f433b9:0x13ec7aba02badd07!8m2!3d51.5021452!4d-0.099806!16s%2Fg%2F11k_4j6mmk!19sChIJuTP0ANgRdkgRB926Arp67BM</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>INYO Fit - UK Branch</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>MOONRAKER point, 1 Pocock St, London SE1 0FN, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:30 am–5 pm"],"Monday":["6:30 am–6 pm"],"Saturday":["8 am–2 pm"],"Sunday":["Closed"],"Thursday":["6:30 am–6 pm"],"Tuesday":["6:30 am–6 pm"],"Wednesday":["6:30 am–6 pm"]}</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>http://www.inyofit.com/</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>+44 7480 459649</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>GW22+V3 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>189</v>
+      </c>
+      <c r="O97" t="n">
+        <v>5</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":0,"5":189}</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>51.502145</v>
+      </c>
+      <c r="R97" t="n">
+        <v>-0.09980600000000001</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1435657320552652039</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnopQX75pTa3aQAKl8Agc8urKH9wLh8eUXYyYdTuPTp63sB7Xr_lpP4iAw0TZo1hv02em8xf7oi6DvoctLjT1kiY2fk2w9w37tnu8nR6s51rI3ppde3Vv0zFt4CXCmjSsVFBUc3X4ai9g-G=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>0x487611d800f433b9:0x13ec7aba02badd07</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>ChIJuTP0ANgRdkgRB926Arp67BM</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr"/>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>[{"link":"https://go.oncehub.com/CarmenRosa","source":"oncehub.com"}]</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>{"id":"100328087974435623904","name":"INYO Fit - UK Branch (Owner)","link":"https://www.google.com/maps/contrib/100328087974435623904"}</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"MOONRAKER point, 1 Pocock St","city":"London","postal_code":"SE1 0FN","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible seating","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>[{"Name":"Narta Voca","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUsQUYQLw8yuSEPYdl9P5_DxYOBrZmleqgH9sgvZNLeV-enIW1c=s120-c-rp-mo-br100","Rating":5,"Description":"I just took my first breathwork and mindfulness class with Rosa at my local gym and it was a great experience! She has such a calm, grounding presence, and the breathing techniques she guided me through left me feeling like I’d just had a full-body massage. I walked out feeling so much lighter.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21ONlkzRjFUemM1VFdkWU15MUVablIxWmtobFdXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110696349093180341327/reviews?hl=en-GB","posted_at_unix_micros":1785234949298733,"updated_at_unix_micros":1785234949298733,"language":"en","translated_lang":"","text_original":"I just took my first breathwork and mindfulness class with Rosa at my local gym and it was a great experience! She has such a calm, grounding presence, and the breathing techniques she guided me through left me feeling like I’d just had a full-body massage. I walked out feeling so much lighter.","text_translated":"","reply_text_original":"The best kind of feedback! Appreciate you taking the time to leave me this review and I hope you keep up your mindfulness and breathwork practice in and out the studio x","reply_language":"en","reply_posted_at_unix_micros":1785954257000000,"reply_updated_at_unix_micros":1785954257000000,"published_at":"2026-07-28T10:35:49.298733Z"},{"Name":"Nate","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUrrFfwHMdNeQWlvwhq8QPskjQgsyZqky0kIY4yRrJadAER3uM_qw=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Very knowledgeable and supportive trainer. Rosa gave clear instructions throughout the session and explained not only what we were doing, but why each stretch was important. We identified tightness in my quads, hips, and shoulders, and I left feeling like I had the support I needed. I now have a much better understanding of what I need to work on to improve my mobility and overall fitness.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xadlpISjZObkpWU0VGb016TTJWbkpvVGxGS1MwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111899651741116785889/reviews?hl=en-GB","posted_at_unix_micros":1783448193545128,"updated_at_unix_micros":1783453983464781,"language":"en","translated_lang":"","text_original":"Very knowledgeable and supportive trainer. Rosa gave clear instructions throughout the session and explained not only what we were doing, but why each stretch was important. We identified tightness in my quads, hips, and shoulders, and I left feeling like I had the support I needed. I now have a much better understanding of what I need to work on to improve my mobility and overall fitness.","text_translated":"","reply_text_original":"Thank you for your kind and detailed feedback, very happy you got the treatment and tools you needed to keep up with your cycling demands and feel great within your body!","reply_language":"en","reply_posted_at_unix_micros":1784535530000000,"reply_updated_at_unix_micros":1784535530000000,"published_at":"2026-07-07T18:16:33.545128Z"},{"Name":"E J","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVM-q5VFMAl-xMwQcEsz2chpRx4U6GPn7HKQiQJ0m-wlDOcJPTl=s120-c-rp-mo-br100","Rating":5,"Description":"As an individual that sits in front of a desk for long hours, that runs and goes for hikes often, my body retain a lot of tension and becomes rigid, that's why I like to 'stretch' on a daily basis... Let me tell that after the stretch therapy with Carmen Rosa the definition I had of 'stretching' has been completely redefined. The attention to detail and knowledge behind every stretch and move is paramount. I stretched areas that I don't think has been stretch in my entire life. I like to be pushed and she adapted and applied the exact force needed and even allowed to rediscover my body limitation and help me surpass it. It felt like nothing I've experienced before when it comes to a fitness professional working on my body. I would highly recommend working Carmen Rosa, she showed extensive knowledge and care. (and she was very bright and cheerful) nothing beats someone working on you with a big smile!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25VdE1FSnVNR2h2TUVGNU5qQnBNMWRwZEdObWJXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102483528949266184754/reviews?hl=en-GB","posted_at_unix_micros":1776382569778454,"updated_at_unix_micros":1776382569778454,"language":"en","translated_lang":"","text_original":"As an individual that sits in front of a desk for long hours, that runs and goes for hikes often, my body retain a lot of tension and becomes rigid, that's why I like to 'stretch' on a daily basis... Let me tell that after the stretch therapy with Carmen Rosa the definition I had of 'stretching' has been completely redefined. The attention to detail and knowledge behind every stretch and move is paramount. I stretched areas that I don't think has been stretch in my entire life. I like to be pushed and she adapted and applied the exact force needed and even allowed to rediscover my body limitation and help me surpass it. It felt like nothing I've experienced before when it comes to a fitness professional working on my body. I would highly recommend working Carmen Rosa, she showed extensive knowledge and care. (and she was very bright and cheerful) nothing beats someone working on you with a big smile!","text_translated":"","reply_text_original":"Thank you for such a thoughtful review. I love helping people discover that mobility and stretch therapy can be so much more than traditional stretching. It was a pleasure working with you and tailoring the session to your needs and goals. I’m delighted you felt challenged, supported and able to move beyond previous limitations!","reply_language":"en","reply_posted_at_unix_micros":1781763338000000,"reply_updated_at_unix_micros":1781763338000000,"published_at":"2026-04-16T23:36:09.778454Z"},{"Name":"Mahnoor Jamal","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVtXdPY8rynL6aSW5Sdn6zN3G3qdLZxBFhZrEen_1gpu7JBRCdl=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Rosa is so amazing! She has a very uplifting and motivating presence thus helping me to cross my limits and do things I never believed I could do like a handstand. I also attended a yoga class of hers recently and her encouragement helped me do some tricky stretches and I left feeling super zen. If you want to spice up your training beyond weights this is the place to be. 💞🔥","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21wamFIWnJXbmx3TlU1U1pFVkJWak5qTVMxSE1HYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104912444744815107107/reviews?hl=en-GB","posted_at_unix_micros":1778180747049275,"updated_at_unix_micros":1778180747049275,"language":"en","translated_lang":"","text_original":"Rosa is so amazing! She has a very uplifting and motivating presence thus helping me to cross my limits and do things I never believed I could do like a handstand. I also attended a yoga class of hers recently and her encouragement helped me do some tricky stretches and I left feeling super zen. If you want to spice up your training beyond weights this is the place to be. 💞🔥","text_translated":"","reply_text_original":"Thank you Mahnoor! Your kind words mean so much. It has been a pleasure helping you build confidence in your movement and explore new challenges like handstands. I’m delighted you enjoyed both the yoga and mobility work, and that you left feeling strong, capable and relaxed. Thank you for your support!","reply_language":"en","reply_posted_at_unix_micros":1781764886000000,"reply_updated_at_unix_micros":1781764886000000,"published_at":"2026-05-07T19:05:47.049275Z"},{"Name":"Elvis Sachas","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIJNLbUPZg1Cn6MzRMvW3bf-Fj2vpxSosPU30Osj7EMerYQgw=s120-c-rp-mo-br100","Rating":5,"Description":"When I first started coming to Rosa, I was very stiff, lacked mobility, and was regularly picking up hamstring and ankle injuries as a football player. Since working with her, I’ve noticed a huge improvement in both my mobility and overall movement.\n\nRosa has genuinely made me feel like a new person. I feel much looser, quicker, and more agile, both on the football pitch and in my day-to-day life. The difference has been massive, and I’ve been able to perform better while feeling less restricted and more confident in my body.\n\nI can’t recommend Rosa enough to any athlete or anyone looking to improve their mobility, reduce injuries, and move better overall.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2w5alNpMVdSM2hVZWpKSFRubGxhRkZMYkhaRU0zYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113588311269824542529/reviews?hl=en-GB","posted_at_unix_micros":1779975478196615,"updated_at_unix_micros":1779975478196615,"language":"en","translated_lang":"","text_original":"When I first started coming to Rosa, I was very stiff, lacked mobility, and was regularly picking up hamstring and ankle injuries as a football player. Since working with her, I’ve noticed a huge improvement in both my mobility and overall movement.\n\nRosa has genuinely made me feel like a new person. I feel much looser, quicker, and more agile, both on the football pitch and in my day-to-day life. The difference has been massive, and I’ve been able to perform better while feeling less restricted and more confident in my body.\n\nI can’t recommend Rosa enough to any athlete or anyone looking to improve their mobility, reduce injuries, and move better overall.","text_translated":"","reply_text_original":"Thank you Elvis! It’s been fantastic seeing your progress over time. I’m so pleased you’ve noticed improvements in your mobility, movement quality and confidence both on and off the football pitch. Your dedication and consistency have played a huge part in those results, and I appreciate your recommendation and support.","reply_language":"en","reply_posted_at_unix_micros":1781764167000000,"reply_updated_at_unix_micros":1781764167000000,"published_at":"2026-05-28T13:37:58.196615Z"}]</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="inlineStr"/>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>13</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/KXU/data=!4m7!3m6!1s0x48760515e2ea03f5:0xbe68e87b37e260e8!8m2!3d51.4936512!4d-0.1585152!16s%2Fg%2F11g9qcbgf2!19sChIJ9QPq4hUFdkgR6GDiN3voaL4</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>KXU</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>241 Pavilion Rd, London SW1X 0BP, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9 pm"],"Monday":["6 am–9 pm"],"Saturday":["9 am–6 pm"],"Sunday":["9 am–6 pm"],"Thursday":["6 am–9 pm"],"Tuesday":["6 am–9 pm"],"Wednesday":["6 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kxu.co.uk/pricing/</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>+44 20 3948 3840</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>FRVR+FH London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>188</v>
+      </c>
+      <c r="O98" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>{"1":23,"2":6,"3":12,"4":13,"5":134}</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>51.493651</v>
+      </c>
+      <c r="R98" t="n">
+        <v>-0.158515</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>13720471880700420328</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Hip gym with treatment rooms &amp; snack bar</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Pay-as-you-use gym offer classes &amp; PT sessions, spa treatments, a cryotherapy chamber &amp; snack bar.</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmXLAU14dUrd4r4lMzFX759wsQj6zuHrMYesu7TCGNxHOw2ZiMEBfEQad4ugr_8L0LGn7RgRID_BTZB7WkeXTwbwNIy8hT3ROsGv7OjedhAfbK7p65-NPy770epiCwLok_xuiaH7Q=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>0x48760515e2ea03f5:0xbe68e87b37e260e8</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>ChIJ9QPq4hUFdkgR6GDiN3voaL4</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.mindbodyonline.com/explore/locations/kxu?rwg_token=AE37R_jBsipykyqmideTEUQkQdw-sZwM5h0-Oj7l-ckAG4xcZz0GA0nwMWVioNHMEXmh1gpj_KYX7D-R5dY-MYFk1yCZePq55GBGf_AElnmSJZZHLFugHRw%3D","source":"mindbodyonline.com"}]</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>{"id":"116450814441483002717","name":"KXU (Owner)","link":"https://www.google.com/maps/contrib/116450814441483002717"}</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"241 Pavilion Rd","city":"London","postal_code":"SW1X 0BP","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>[{"Name":"Lara Accison","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKQBlB8tr8YOesC2IcQPJkwintIKTAUjB96T0i8XUS23SVyUQ=s120-c-rp-mo-br100","Rating":5,"Description":"I recently attended an event with Backstage and had a fantastic experience overall. One of the standout elements of the activation was the dedicated spa area, which was thoughtfully designed and incredibly well organised. The space felt calm and welcoming, providing a perfect contrast to the busier parts of the event.\n\nThere was a great variety of treatments available, allowing guests to choose from several relaxing options. Each station was clearly set up, and the staff were professional, friendly, and attentive, making the whole experience feel seamless and enjoyable. The flow of the space worked really well, so even with multiple treatments taking place, everything felt structured and easy to navigate.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25sdE1HeFVNR1E0VmpFNWJVOUtiV2xYZVVZNVFWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106952692935379866122/reviews?hl=en-GB","posted_at_unix_micros":1773470805492590,"updated_at_unix_micros":1773470805492590,"language":"en","translated_lang":"","text_original":"I recently attended an event with Backstage and had a fantastic experience overall. One of the standout elements of the activation was the dedicated spa area, which was thoughtfully designed and incredibly well organised. The space felt calm and welcoming, providing a perfect contrast to the busier parts of the event.\n\nThere was a great variety of treatments available, allowing guests to choose from several relaxing options. Each station was clearly set up, and the staff were professional, friendly, and attentive, making the whole experience feel seamless and enjoyable. The flow of the space worked really well, so even with multiple treatments taking place, everything felt structured and easy to navigate.","text_translated":"","published_at":"2026-03-14T06:46:45.49259Z"},{"Name":"Carl van Heerden","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW2wEgA92oHhSF4fNV5u2sERK_254hafrC_--y1Yb2NMM9W4TZE=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This gym has the best trainers. Experienced coaches, well planned sessions, attention to detail - they’ve nailed it. The cafe also has a great vibe, coffee and smoothies for post workout catch-ups. I’d 💯 recommend their spin class - leaderboard for extra motivation!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21kYVdGWnlTbVl6TFhJdFNrRm1XSEp3VEdsTVYzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113830980143768728525/reviews?hl=en-GB","posted_at_unix_micros":1773236986592043,"updated_at_unix_micros":1773236986592043,"language":"en","translated_lang":"","text_original":"This gym has the best trainers. Experienced coaches, well planned sessions, attention to detail - they’ve nailed it. The cafe also has a great vibe, coffee and smoothies for post workout catch-ups. I’d 💯 recommend their spin class - leaderboard for extra motivation!","text_translated":"","published_at":"2026-03-11T13:49:46.592043Z"},{"Name":"Thea Peterson","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLy6rq82V89u4oqf5SKcpfCITruL7BcjavL_BhE54d_S8hNvw=s120-c-rp-mo-br100","Rating":3,"Description":"I’ve been coming regularly and love the cycle classes, instructors are phenomenal! However increasingly the equipment has been sub par. Cycle shoes with loose hardware clip ins (dangerous!), broken bikes from adjustment knobs to the cyclocomputer, instructor mics shorting and popping, sometimes sound system not working…\n\nFor the cost this is so unacceptable. Invest in the studio!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tGM1ZVUnphVFpYUWtRNVUzZEtiV055WDNWSlZXYxAB","source":"Google","rating_scale":5,"rating_float":3,"author_url":"https://www.google.com/maps/contrib/111559375880235308933/reviews?hl=en-GB","posted_at_unix_micros":1775814582717738,"updated_at_unix_micros":1775814582717738,"language":"en","translated_lang":"","text_original":"I’ve been coming regularly and love the cycle classes, instructors are phenomenal! However increasingly the equipment has been sub par. Cycle shoes with loose hardware clip ins (dangerous!), broken bikes from adjustment knobs to the cyclocomputer, instructor mics shorting and popping, sometimes sound system not working…\n\nFor the cost this is so unacceptable. Invest in the studio!","text_translated":"","published_at":"2026-04-10T09:49:42.717738Z"},{"Name":"MISS FOX","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVovPVpNr0aSoL6NEXcjOQe2iGNolcRA9uI22OOf9OmLNnh1mP3pw=s120-c-rp-mo-br100","Rating":1,"Description":"What am absolute shambles this place is. Filthy dirty, skeleton staff and the management just sit watching the guests struggle to even order a protein shake or make a relatively simple booking. An infrared sauna with NO red light and according to the KXU spa team, the red light is purely for 'VIBES' .. this place would serve better as a dingy, dirty, warehouse nightclub NOT. How it is associated with KX Gym is an embarrassment, many years ago it was incredible, but I'll be surprised if this place is even still there in 12 months time.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT214UWJXUkJOblZJUTBOSGRHOTJNMWxOUTNabFFVRRAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/112824283994450172831/reviews?hl=en-GB","posted_at_unix_micros":1777385458538882,"updated_at_unix_micros":1777385523294276,"language":"en","translated_lang":"","text_original":"What am absolute shambles this place is. Filthy dirty, skeleton staff and the management just sit watching the guests struggle to even order a protein shake or make a relatively simple booking. An infrared sauna with NO red light and according to the KXU spa team, the red light is purely for 'VIBES' .. this place would serve better as a dingy, dirty, warehouse nightclub NOT. How it is associated with KX Gym is an embarrassment, many years ago it was incredible, but I'll be surprised if this place is even still there in 12 months time.","text_translated":"","published_at":"2026-04-28T14:10:58.538882Z"},{"Name":"anastasia davelopoulou","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK80DWhl28lha8bwOA1esN7PIcRepD5haJjYqa1Xv5GpfeaoA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Attended an amazing event last week at KXU in collaboration with Backstage. I loved the mix of different elements and activations throughout the evening — everything was thoughtfully curated and kept the experience engaging from start to finish.\nThe hosts were fantastic, and the attention to detail really stood out. A great example of how to create an immersive and memorable event. Looking forward to the next one!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25scFUyZFhTMWhPVUY4NWNrUnJkRTVzTVZkMUxVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115840595860587365089/reviews?hl=en-GB","posted_at_unix_micros":1773410631486640,"updated_at_unix_micros":1773410631486640,"language":"en","translated_lang":"","text_original":"Attended an amazing event last week at KXU in collaboration with Backstage. I loved the mix of different elements and activations throughout the evening — everything was thoughtfully curated and kept the experience engaging from start to finish.\nThe hosts were fantastic, and the attention to detail really stood out. A great example of how to create an immersive and memorable event. Looking forward to the next one!","text_translated":"","published_at":"2026-03-13T14:03:51.48664Z"}]</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="inlineStr"/>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>13</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Peloton+Studios+London/data=!4m7!3m6!1s0x487605dab2e9b687:0x2ceeb0cde99aac1b!8m2!3d51.5124194!4d-0.1241853!16s%2Fg%2F11gnhl4z3y!19sChIJh7bpstoFdkgRG6ya6c2w7iw</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Peloton Studios London</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>11 Floral St, London WC2E 9DH, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30–9 pm"],"Monday":["Closed"],"Saturday":["8:30 am–5 pm"],"Sunday":["9 am–5 pm"],"Thursday":["Closed"],"Tuesday":["Closed"],"Wednesday":["Closed"]}</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>https://studio.onepeloton.co.uk/</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>+44 20 3031 6251</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>GV6G+X8 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>179</v>
+      </c>
+      <c r="O99" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>{"1":3,"2":1,"3":0,"4":5,"5":170}</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>51.512419</v>
+      </c>
+      <c r="R99" t="n">
+        <v>-0.124185</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>3237719580559977499</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmRfBVjwfjHxKlWtEjzZ4bUfxe3jmcoKl5tRTuMb9ahED2S4Ej8aivRyznfLRZSJRlbBGDltYTjXKX7vYT10kCBdXEfssd0RCjeCoo6jXrcLNAVzPVWGaf8onTnZhlL7cLgkEpA=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>0x487605dab2e9b687:0x2ceeb0cde99aac1b</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>ChIJh7bpstoFdkgRG6ya6c2w7iw</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>{"id":"103748441772574480030","name":"Peloton Studios London (Owner)","link":"https://www.google.com/maps/contrib/103748441772574480030"}</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"11 Floral St","city":"London","postal_code":"WC2E 9DH","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>[{"Name":"Ben","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWhd9S85KuSFmkMCuOAbowexBIv5aCF9TsvEjybYhY1sEYJz3AeBg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I did a live ride at Peloton Studios London with Sam Yo and it was an amazing experience from start to finish.\n\nThe staff were incredibly helpful and accommodating, which made everything feel really easy and welcoming. The facilities were spotless and really modern, especially the showers, changing rooms, and toilets.\n\nThe whole vibe in the studio was incredible. It was super well organised but still had loads of energy. There’s also a small shop, but it honestly has everything you’d realistically want.\n\nWhat really stood out to me was how different it feels compared to riding at home. It is a completely different experience and, for me, a much better one. You really get a sense of how strong and open the Peloton community is, and I didn’t expect that difference to be so big.\n\nThe only small thing they could improve is providing bigger towels in the class, although you can probably just bring your own anyway.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNAvsjG2wzVlFf4yxjhAmDYNIGDhYoR1cnkGJSd4ecqLrRL7SWSKuFJpr2W13pHO5AMJH6wYQLtD4E0oQs60BEm_SWPcXkN87JwFT93SbIWxmcb6bi5mLQ7GhdK7zshIsCv4t5Secj3o_g=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMGD_U9FBGDCjYfS8YpgzFjdSR9pemGjqoBf5CRjfxcsdS0sTspB1HgyI1gbT-FIcKfsTfgGWqT8sSC5LHPOWWIfxmA7FUM9RmCjaaBpc2vDLflhlYV88qdZZtyh4Xb7VboS_XgZs0t9uk=k-no"],"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21GUFkyNU5NRWx3YmtJdFprTm9kWHBhVUdkNWVYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100118510722062816213/reviews?hl=en-GB","posted_at_unix_micros":1781559205865135,"updated_at_unix_micros":1781559205865135,"language":"en","translated_lang":"","text_original":"I did a live ride at Peloton Studios London with Sam Yo and it was an amazing experience from start to finish.\n\nThe staff were incredibly helpful and accommodating, which made everything feel really easy and welcoming. The facilities were spotless and really modern, especially the showers, changing rooms, and toilets.\n\nThe whole vibe in the studio was incredible. It was super well organised but still had loads of energy. There’s also a small shop, but it honestly has everything you’d realistically want.\n\nWhat really stood out to me was how different it feels compared to riding at home. It is a completely different experience and, for me, a much better one. You really get a sense of how strong and open the Peloton community is, and I didn’t expect that difference to be so big.\n\nThe only small thing they could improve is providing bigger towels in the class, although you can probably just bring your own anyway.","text_translated":"","published_at":"2026-06-15T21:33:25.865135Z"},{"Name":"Sophia Heitzig","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKSP0pI2_mzxwLUAB0hmCa7NOjdQitdo20wKS32SwAZxWUYhg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Peloton does everything to the highest level of quality and Peloton Studios London is no exception. The facility itself is beautiful, and super clean and well kept. The team was incredible, attentive, and kept everything running smoothly. We were celebrating two big events and after learning that only one of us got a space in a class, the team reached out personally, and provided a seat once someone had dropped. It was such a special experience. We also loved browsing the store afterwards and found some amazing deals. 10/10 experience! Thank you Peloton!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25KT1YwczRaR1puUkZSdVZFZG9MWFJTVUc0M2NVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113409994556747256602/reviews?hl=en-GB","posted_at_unix_micros":1786135312037450,"updated_at_unix_micros":1786135312037450,"language":"en","translated_lang":"","text_original":"Peloton does everything to the highest level of quality and Peloton Studios London is no exception. The facility itself is beautiful, and super clean and well kept. The team was incredible, attentive, and kept everything running smoothly. We were celebrating two big events and after learning that only one of us got a space in a class, the team reached out personally, and provided a seat once someone had dropped. It was such a special experience. We also loved browsing the store afterwards and found some amazing deals. 10/10 experience! Thank you Peloton!","text_translated":"","published_at":"2026-08-07T20:41:52.03745Z"},{"Name":"J","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXILuCTBAWBzg5VKX-DJ7epjkBZcdZZH3FYbCv97th-N7WDpso=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I am a huge Peloton fan and I am so happy to say I made it into a class with my dad in 2023 and 2024! Hopefully I will get to go again someday! The studio is beautiful and I have also been to the New York studio. I will say the London studio is smaller, but honestly a more beautiful space. It is well organized, clean, in the bathrooms are well stocked! The staff and instructors are all extremely kind and happy for you to be there!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOfPV9iEeIv0jOMmiliF5rQc48w_XzewHutmT6d8NGjIpmZ15HEOa5PRI1WS5VH3XW42mRR9CvT82M1WjI92Vvs4zwp3_SXFlclJEwsC_a5nByrodDTAeqcZDv5dMUIAfaHOSGRwHWcql4o=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOba1aRGC9tdgDAaD7Betob-Bfv7N4mo6Z0JCLRv7fLsRcEu0RNJZRVXTM6ljqxOWKRXre2b-2FVRnapdt0niWa1IEQeZrlcRLFRIi9TCy_qnZROUujMK2fn8nf-6ojS9SALWFw0OTP_JY=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOzHZI2W3JEBNSiltU8XA7j3XMaMAyelb7adinKSgo4WdB8iX9QieTseGJXxW4E3C-BWyNO-15wQMqsB_h0ogBrFJvpfjvHMCRxvhYPrA6NbS4iUA4UyYTF2osRO3hcL9hfUJ9Xaowz35v2=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNRJXYLMrkl_fuYNQMb8GizvbI7_jnxs50MEL5RKgCRqTYf1TbGww5VyhXfDpB6j-mfwsw0Fr3DnQ6QAOFYiB2HcxZBCC3__QNe0TMmHZKbNeZ8UWRB_MUK-eUgSs1w6K1RjgB8COwEdVjO=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOkC-bWzx4Ror3hF4EF1MT4vjGeNBcV98Rt4vjDy_gAJZ5L1tOW-7g7_YZNlOnP4jDFRdy-_HKygRsrtrjej9LwBUZzLawQzBx3kpGjz1CWBJ2tCQ53hdm3GcDcXoiEesVfQjt1wwal191l=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOmNxU86hx9A5U5KvC7oRSbDW__zI0W1ULmcV01eNmWvBCjDlOWN1x-a01Ma1Ns88Y5_PtA4XcgE-x67PQhifx2-o5dODsHHdl9EIjDgvGBo7jg9F4taUNnXw4x5MG9rRGoHPX9O7TBqyEz=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmN5TSOQwcngDDskxA_e5zFcxfT5EYJ7reGJ0zZqM25Q4Wz0dIB-hbfQuWVmoccC0Ofki7D87LVwe1wX1utGnkJPW_TdLColm2Io8Xh4PM-1btNYs1nk_Fmie5QQLhp2pW_bESrKiSZX1aaH=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNDu_5FvhdkJe-Le1qeUguinZivQRq4s2SgF6Sznu9y2MlHuyAcbcE9219S7hiBNRTKMsS-Fil1XiIlhav1sps3S1VxO8FnkDljlsxSgMmeADpypgHX0RSVJdD9rZQw4lReEvUiLZDPiVEs=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmN_5nG0e3OdP9RwIzRPzk5ngeVb5vscNs1cb-ukFqY6XBzGaOj_XTyn74S0LUm9wpjH7Ox-rV-CvH9jQIOtMwwJHXvPZynLoHUIGpzN-wM2tHRoLkG-9XQBWq4wyLjzDk-AAMxhmqs5VMqo=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOSeX6bnhM_hjwY-5qa2V7roFtuy_RDfWhMAXsRxbm4DogVdm3iW4bsAvgYiK4fMUOyRztztTuZgGuRj4vdL-lBTj5ZminceeqRNlUtc_kJfPCc_F06aoh36K72CxM2ToaFxnqP0UlcJzep=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOeMoB_obJU3WJniFMqYXi61vXN20KNpn49WIK-ZpdL0n5jxwOsYHjRzY_Bfcmw4F1Po5sMAY9z55i9E2VN8qMfsg5rLSZVKgzoEZYqaCTisZep2QfTWeKpwN2V-VlTFYYrGRqKwk8GMAEC=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMYVljd0zCdpA0ET49N_jmsoBmdg8dSYjTrsaLzfMb7zJxObIXQnQiKbsfAzcKqAT4ho9iyMKVf3AOXvVuFrcIWL1jGm38O0qHem4qtU09urEm9DmwTfSOVzwbdngPGdkF2DR4xPWGs_d9o=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNlb8cx9Q_sYb9NPVNrhed2Kg1t9Xug1QjnGQEff0OFzQMfL1l2puqTeVItakBjSGHHx3sVaQTxe1nN5oFyiwuVQaE04J05ZVX8NJlN8FmqQm-DIgu8BYqA0J7FTD-0KE_KZ2Onk3A4C_rd=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMzbKOPyi_W6IqB1Ui48oLiDsVXUubfQM7iaG1WHQx8ALrccXQOY7kZ-6_yCrJ18QjVBzBxi7y_lxsoBxUs1l82xeyI0UhihZ1b21s2i-Ts3pgQYz6F9zzZobJt005fiKj2jzjcjxFxiG5h=k-no"],"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21SSWJuVjNZMHRmZHkxVGMySnFkR2RwZVRCS2JHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111280456884542185704/reviews?hl=en-GB","posted_at_unix_micros":1763048323190813,"updated_at_unix_micros":1763048362319835,"language":"en","translated_lang":"","text_original":"I am a huge Peloton fan and I am so happy to say I made it into a class with my dad in 2023 and 2024! Hopefully I will get to go again someday! The studio is beautiful and I have also been to the New York studio. I will say the London studio is smaller, but honestly a more beautiful space. It is well organized, clean, in the bathrooms are well stocked! The staff and instructors are all extremely kind and happy for you to be there!","text_translated":"","published_at":"2025-11-13T15:38:43.190813Z"},{"Name":"Hayley Goldner","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKDf-_bz38n2fW4nYPZmCPHqOLkj9SjMsSWPUCfk-s6JjH_SL8=s120-c-rp-mo-br100","Rating":5,"Description":"Amazing time at the Peloton London studio for a live class. Every employee from start to finish was beyond welcoming and friendly. Extra special shout out to our group host Tiana who went above and beyond for us. We can't wait to come back!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT201T09VaFRlRTlwY0haR1MyOXdSbnBzVlhGSmQzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108185999057541119958/reviews?hl=en-GB","posted_at_unix_micros":1783968784525082,"updated_at_unix_micros":1783968784525082,"language":"en","translated_lang":"","text_original":"Amazing time at the Peloton London studio for a live class. Every employee from start to finish was beyond welcoming and friendly. Extra special shout out to our group host Tiana who went above and beyond for us. We can't wait to come back!","text_translated":"","published_at":"2026-07-13T18:53:04.525082Z"},{"Name":"Derek Andrews","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUQ3mi0LzGYTAk9cskhjgYbW6VADjR6Dc2rxVIwpQeqqZ4xwJ-p=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My wife and I lucked out getting into a 30 min 2010s pop run with Susie while visiting from the US. The entire experience was excellent. All around, London is better than the NYC studio. The whole crew, especially Wale, were all super kind and accommodating. Will definitely come back on our next trip.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25BNFkweGFRWEYxTUhNM2ExOW1Za0ZFYlRGTFluYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110282578366751381579/reviews?hl=en-GB","posted_at_unix_micros":1783847146808292,"updated_at_unix_micros":1783847146808292,"language":"en","translated_lang":"","text_original":"My wife and I lucked out getting into a 30 min 2010s pop run with Susie while visiting from the US. The entire experience was excellent. All around, London is better than the NYC studio. The whole crew, especially Wale, were all super kind and accommodating. Will definitely come back on our next trip.","text_translated":"","published_at":"2026-07-12T09:05:46.808292Z"}]</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr"/>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>13</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>6758c484-00e9-4c1c-a81f-56f19a65c71b</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Fitness+Lab/data=!4m7!3m6!1s0x487604d345f84e39:0x894c5197c71a83d!8m2!3d51.5142957!4d-0.1339984!16s%2Fg%2F11bytsgk2n!19sChIJOU74RdMEdkgRPahxfBnFlAg</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Fitness Lab</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>9-12 St Anne's Ct, London W1F 0BB, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9 pm"],"Monday":["6 am–9 pm"],"Saturday":["8 am–6 pm"],"Sunday":["8 am–6 pm"],"Thursday":["6 am–9 pm"],"Tuesday":["6 am–9 pm"],"Wednesday":["6 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>http://www.fitnesslab.fit/</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>+44 20 3494 4200</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>GV78+PC London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>174</v>
+      </c>
+      <c r="O100" t="n">
+        <v>5</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":1,"5":173}</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>51.514296</v>
+      </c>
+      <c r="R100" t="n">
+        <v>-0.133998</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>618335762109278269</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkLf2t8BRHIJhblnTQpAFt5778RY_aNnVOkkLdTeAv51_kLOWRVPDlvNgJ5GI5rQCU0hYGjG9BCnzapJB1SZzRPbZyfhuR96nZqAi2mRVoUCS7bIEGQWQIEJNRCryQBMTsEvvqqwXK6SEE=w408-h264-k-no</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>0x487604d345f84e39:0x894c5197c71a83d</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>ChIJOU74RdMEdkgRPahxfBnFlAg</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>{"id":"107631594597572965077","name":"Fitness Lab (Owner)","link":"https://www.google.com/maps/contrib/107631594597572965077"}</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"9-12 St Anne's Ct","city":"London","postal_code":"W1F 0BB","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>[{"Name":"Gonzalo Garcia","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV0sXIWkI1cxf8QJCUY2eO7-q_FTuw9XzEaBtoEBiyHjzHIWXlM=s120-c-rp-mo-br100","Rating":5,"Description":"I've been training with Ash for nearly 5 years now doing 1 or 2 sessions a week. It has been completely transformative! For a start, the private gym is very well equipped and it's amazing never having to wait for things to free up. Then Ash is always super on top of my training programme, the weights for each exercise, target reps, any specifics to work around/avoid... I just show up and lift without needing to worry about anything else. And I've seen the results very clearly in my own strength and body composition. Highly recommend!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tzMVJFSjVOMWxhZFZwbVJrOVpOa3d5VkVaRWJtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107382619361056135275/reviews?hl=en-GB","posted_at_unix_micros":1776762631656466,"updated_at_unix_micros":1776762631656466,"language":"en","translated_lang":"","text_original":"I've been training with Ash for nearly 5 years now doing 1 or 2 sessions a week. It has been completely transformative! For a start, the private gym is very well equipped and it's amazing never having to wait for things to free up. Then Ash is always super on top of my training programme, the weights for each exercise, target reps, any specifics to work around/avoid... I just show up and lift without needing to worry about anything else. And I've seen the results very clearly in my own strength and body composition. Highly recommend!","text_translated":"","reply_text_original":"Hi Gonzalo, we can’t thank you enough for your review. Your PT Ash loves seeing you each week for personal training and we’re so pleased you are happy with the service. All the best from the entire personal trainer team at Fitness Lab 🙏💪","reply_language":"en","reply_posted_at_unix_micros":1776774368000000,"reply_updated_at_unix_micros":1776774368000000,"published_at":"2026-04-21T09:10:31.656466Z"},{"Name":"Felix Gabriel Mance","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUUxkBasJiaMKqckspD4aLI4lKQMopQ1v_0DlOPkcoNrzs3xk0=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been training with Ash from FitnessLab Soho for around 3 years, and the impact has been huge. I went from being skinny-fat and lacking confidence to becoming much stronger, leaner and more comfortable in myself, to the point that a lot of people have commented on my transformation.\nWhat I value a lot is that Ash helps me manage the full picture of fitness, not just the workouts themselves, but also makes sure the nutrition and recovery are structured properly, and he keeps me focused on a sustainable, long term progress, rather than quick fixes.\nAlso what I really like, and I think this sets him apart, is that he has very deep knowledge about the science of muscle building and training, keeps up with the latest research in the field, and uses that knowledge to provide the most effective workout for my goals.\nOn top of that, he is also very friendly and easy to get on with, which makes training something I actually look forward to! Couldn’t recommend him enough!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psNFRWRk9ZMmQ1Tms1SGJUbHdSSFpTVm5WdlUwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105044123512156488626/reviews?hl=en-GB","posted_at_unix_micros":1776804973734109,"updated_at_unix_micros":1776804973734109,"language":"en","translated_lang":"","text_original":"I’ve been training with Ash from FitnessLab Soho for around 3 years, and the impact has been huge. I went from being skinny-fat and lacking confidence to becoming much stronger, leaner and more comfortable in myself, to the point that a lot of people have commented on my transformation.\nWhat I value a lot is that Ash helps me manage the full picture of fitness, not just the workouts themselves, but also makes sure the nutrition and recovery are structured properly, and he keeps me focused on a sustainable, long term progress, rather than quick fixes.\nAlso what I really like, and I think this sets him apart, is that he has very deep knowledge about the science of muscle building and training, keeps up with the latest research in the field, and uses that knowledge to provide the most effective workout for my goals.\nOn top of that, he is also very friendly and easy to get on with, which makes training something I actually look forward to! Couldn’t recommend him enough!","text_translated":"","reply_text_original":"Hi Felix, thank you SO much for the review, we are SO happy that you are happy with your personal training experience with Ash at Fitness Lab. I now that Ash looks forward to each and every PT session you have together and is so committed to ensuring you constantly achieve your goals. Looking forward to seeing you at Fitness Lab Soho soon. All the best from the entire personal trainer team at Fitness Lab 🙏💪","reply_language":"en","reply_posted_at_unix_micros":1776872054000000,"reply_updated_at_unix_micros":1776872054000000,"published_at":"2026-04-21T20:56:13.734109Z"},{"Name":"Rosie","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWmO0nIxobmocsn-1xG6iJQ0NjATa5Yc_1zW4pjLJxFcFTpxEiy-w=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I can’t recommend Fitness Lab enough, the team are all so welcoming. When I went for my consultation I was impressed with their dedication to supporting me with meeting my goals. Their studio was spotless and I appreciated the privacy. The training I’ve been given has meant I’m achieving my goals and seeing results already - I love the push they give, and the fact there’s no hidden costs with the membership. What you see is what you get, which is very high quality!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25Gc1R6Rk5MV0o2TWpsWlYzRXdXWGhGY1Znd1JXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103950646266773701383/reviews?hl=en-GB","posted_at_unix_micros":1776764066632959,"updated_at_unix_micros":1776764066632959,"language":"en","translated_lang":"","text_original":"I can’t recommend Fitness Lab enough, the team are all so welcoming. When I went for my consultation I was impressed with their dedication to supporting me with meeting my goals. Their studio was spotless and I appreciated the privacy. The training I’ve been given has meant I’m achieving my goals and seeing results already - I love the push they give, and the fact there’s no hidden costs with the membership. What you see is what you get, which is very high quality!","text_translated":"","reply_text_original":"Hi Rosie, thanks so much for the review. We’re so pleased that your PT experience has been great. Looking forward to seeing you in the studio for more PT soon. All the best from the entire personal trainer team at Fitness Lab 🙏💪","reply_language":"en","reply_posted_at_unix_micros":1776774273000000,"reply_updated_at_unix_micros":1776774273000000,"published_at":"2026-04-21T09:34:26.632959Z"},{"Name":"Louise Ford","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWh09wi0mHwCOYcK9jnW6BRg2_piy2YHXVuntyA2Jo4D9_CX8S8=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve worked regularly with personal trainers for the past 6 years, both at Equinox in New York and Third Space in London, but the trainers at Fitness Lab are by far the best-qualified and most invested in their clients’ progress. It’s super well-run by people who actually give a damn about doing a good job. I’m not interested in group classes, so the fact that you only pay for your PT sessions (which are priced on a par with the big chains mentioned), and there’s no monthly fee is also a nice bonus. Would highly recommend.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25ST00ycHZVbFptU0hSeU1IZFpVRWR2Y1VnNWNWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100464899341895652517/reviews?hl=en-GB","posted_at_unix_micros":1771341655915754,"updated_at_unix_micros":1771341655915754,"language":"en","translated_lang":"","text_original":"I’ve worked regularly with personal trainers for the past 6 years, both at Equinox in New York and Third Space in London, but the trainers at Fitness Lab are by far the best-qualified and most invested in their clients’ progress. It’s super well-run by people who actually give a damn about doing a good job. I’m not interested in group classes, so the fact that you only pay for your PT sessions (which are priced on a par with the big chains mentioned), and there’s no monthly fee is also a nice bonus. Would highly recommend.","text_translated":"","reply_text_original":"Hi Louise, thank you so much for your review, we really appreciate it. We’re so happy that your personal training experience with us at Fitness Lab has been positive. Looking forward to seeing you in the PT studio soon. All the best from the entire personal trainer team at Fitness Lab 🙏💪","reply_language":"en","reply_posted_at_unix_micros":1771360477000000,"reply_updated_at_unix_micros":1771360477000000,"published_at":"2026-02-17T15:20:55.915754Z"},{"Name":"Chris P","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKUY7MstP8JTdcl0blaG5eEeBShLGEJkSTiNAL8BdfX_LSIhg=s120-c-rp-mo-br100","Rating":5,"Description":"16 sessions in and I am seeing loads of progress in strength, fitness and flexibility - and most importantly am enjoying it and thoroughly looking forward to each session. The gym itself is great. Clean facilities, plenty of space and superb equipment. My PT, Mantas, keeps the training fun, varied and relevant to what I am trying to achieve. He is knowledgeable and has a great sense of the right level of intensity to hit. Wish I’d found this place earlier.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xoRU9WTlVVV3R0UkRkeExTMDRYM2RQUVdKRFRWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118221897001660624302/reviews?hl=en-GB","posted_at_unix_micros":1773306312258414,"updated_at_unix_micros":1773306312258414,"language":"en","translated_lang":"","text_original":"16 sessions in and I am seeing loads of progress in strength, fitness and flexibility - and most importantly am enjoying it and thoroughly looking forward to each session. The gym itself is great. Clean facilities, plenty of space and superb equipment. My PT, Mantas, keeps the training fun, varied and relevant to what I am trying to achieve. He is knowledgeable and has a great sense of the right level of intensity to hit. Wish I’d found this place earlier.","text_translated":"","reply_text_original":"Hi Chris, can’t thank you enough for your review. We love having you with us and I know Mantas is really enjoying training you. We’re so pleased that your personal training experience at Fitness Lab Soho is going well. Thanks again for the review and see you in the studio soon.  All the best from the entire personal trainer team at fitness Lab 🙏","reply_language":"en","reply_posted_at_unix_micros":1773328535000000,"reply_updated_at_unix_micros":1773328535000000,"published_at":"2026-03-12T09:05:12.258414Z"}]</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr"/>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>13</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/F45+Training+Clapham+Junction/data=!4m7!3m6!1s0x487605abd524506d:0x279e701e5b535e2c!8m2!3d51.4617585!4d-0.1737996!16s%2Fg%2F11syz42k76!19sChIJbVAk1asFdkgRLF5TWx5wnic</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>F45 Training Clapham Junction</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>72 St John's Hl, London SW11 1SF, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:45 am–7:15 pm"],"Monday":["5:45 am–8:15 pm"],"Saturday":["8:15 am–12:30 pm"],"Sunday":["8:45 am–12:15 pm"],"Thursday":["5:45 am–8:15 pm"],"Tuesday":["5:45 am–8:15 pm"],"Wednesday":["5:45 am–8:15 pm"]}</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>https://f45training.co.uk/claphamjunction/home</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>+44 7778 250071</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>FR6G+PF London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>170</v>
+      </c>
+      <c r="O101" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>{"1":3,"2":0,"3":1,"4":4,"5":162}</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>51.461758</v>
+      </c>
+      <c r="R101" t="n">
+        <v>-0.1738</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2854842489482993196</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnka3ICKXXaC2qB2JvMvdoCtc4l9ucCzf8H1rP2xXtRuv19j-SOM4CssWcbld9TGSW6aFL3q7_wM531EGU1iHL5H4CjAmykC7a8Rodwna0jDOesh-k1ZTgD_obVo5fQCGevlctc3jzfBkCk=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>0x487605abd524506d:0x279e701e5b535e2c</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>ChIJbVAk1asFdkgRLF5TWx5wnic</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>[{"link":"https://f45training.com/uk/studio/claphamjunction/#schedule","source":"f45training.com"}]</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>{"id":"105637181838879527196","name":"F45 Training Clapham Junction (Owner)","link":"https://www.google.com/maps/contrib/105637181838879527196"}</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"72 St John's Hl","city":"London","postal_code":"SW11 1SF","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>[{"Name":"Annie HU","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ5nO1eooIPXmCFTFxvFNRykZYBd4bQ_P2ZKLPknMy43H8dXA=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve really enjoyed my experience at the gym so far. The service is excellent, and the coaches are always helpful, fun, and professional. Every week’s classes are different and engaging, which keeps me motivated and encourages me to try new things. Over time, I’ve realised that I’ve genuinely started to enjoy going to the gym, and I can feel my strength and overall fitness gradually improving.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25oYWFEZHJVVGxZYW5CcWVrUlVUMU5DZW5kQ0xVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118073091625631396931/reviews?hl=en-GB","posted_at_unix_micros":1778334406632748,"updated_at_unix_micros":1778334406632748,"language":"en","translated_lang":"","text_original":"I’ve really enjoyed my experience at the gym so far. The service is excellent, and the coaches are always helpful, fun, and professional. Every week’s classes are different and engaging, which keeps me motivated and encourages me to try new things. Over time, I’ve realised that I’ve genuinely started to enjoy going to the gym, and I can feel my strength and overall fitness gradually improving.","text_translated":"","reply_text_original":"Thank you so much, Annie, for your lovely review! We’re so happy to hear that you’ve been enjoying your experience with us and that the variety in our classes is keeping you motivated. It’s especially rewarding to know you’re feeling stronger and genuinely enjoying coming to the gym, that’s exactly what we aim for at F45 Clapham Junction.\nOur team really appreciates your kind words, and we can’t wait to keep supporting you on your fitness journey 💪😊","reply_language":"en","reply_posted_at_unix_micros":1778520660000000,"reply_updated_at_unix_micros":1778520660000000,"published_at":"2026-05-09T13:46:46.632748Z"},{"Name":"Essy Es (Essyes)","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXhsreiT5Gl5Bi1NlLdPtuwUgj4ZoSShG14fdfjAMIhl5lY7N39=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I’ve tried several F45 branches, and Clapham Junction is by far the best!\nThe energy, the coaches, and the overall vibe are amazing.\n\nI’ve only been training here for 2 weeks and I can already see a real  change feeling stronger and in better shape than ever. I signed up for a 9-month membership right after my trial session because I knew this was the right place for me. Highly recommend! 💪🔥 Also the manager is super helpful and kind 🥰","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPj7XwpiKT1qJRAlvIVhxtnVRMEcuvmGsUW58vqFYe998yGispyFEm5q4-Duinx7gm30W6QYBfR0q7r6PqVY2Iil93Zk5pYUCeOYeaWruJwbvxLiGkkYpRAaoOc8k2NGIjbncyCbU6WG3Yv=k-no"],"When":"10 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xOYWFHRkZXRmhYZEVaemNrNDFWazAyVFdSNGMwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113490210577423840563/reviews?hl=en-GB","posted_at_unix_micros":1761381977424425,"updated_at_unix_micros":1761381977424425,"language":"en","translated_lang":"","text_original":"I’ve tried several F45 branches, and Clapham Junction is by far the best!\nThe energy, the coaches, and the overall vibe are amazing.\n\nI’ve only been training here for 2 weeks and I can already see a real  change feeling stronger and in better shape than ever. I signed up for a 9-month membership right after my trial session because I knew this was the right place for me. Highly recommend! 💪🔥 Also the manager is super helpful and kind 🥰","text_translated":"","reply_text_original":"Thank you Esra for your kind words. We love having you as a member :)","reply_language":"en","reply_posted_at_unix_micros":1763140372000000,"reply_updated_at_unix_micros":1763140372000000,"published_at":"2025-10-25T08:46:17.424425Z"},{"Name":"Christopher Welch","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUZ3W6JpkHhjMvitpnkW8GlAOFBdjhpQhWaKLyK5E4UaMCMigRA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"F45 Clapham Junction has very warm, motivating, fun trainers and the community and environment feels safe and welcoming. The workouts are programmed well, diverse, effective and enjoyable. Also the staff have communicated very well as I navigated an injury situation that took place in the wider world and accommodated expertly. High marks.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21SUVVHdzJXRmN5UTJGak5tcHRWbVJpWWt0MGNIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105391322220032275420/reviews?hl=en-GB","posted_at_unix_micros":1774873034179035,"updated_at_unix_micros":1774873034179035,"language":"en","translated_lang":"","text_original":"F45 Clapham Junction has very warm, motivating, fun trainers and the community and environment feels safe and welcoming. The workouts are programmed well, diverse, effective and enjoyable. Also the staff have communicated very well as I navigated an injury situation that took place in the wider world and accommodated expertly. High marks.","text_translated":"","reply_text_original":"Thank you for the amazing feedback, Christopher! We’re really glad you’ve felt supported by both the coaching team and the community, especially while managing your injury. Helping members train safely and confidently is always our priority. We appreciate your kind words about the programming and atmosphere, and we’re looking forward to seeing you continue to progress in the studio! 🙏","reply_language":"en","reply_posted_at_unix_micros":1775894495000000,"reply_updated_at_unix_micros":1775894495000000,"published_at":"2026-03-30T12:17:14.179035Z"},{"Name":"Anthony William Catt","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXP2i2kJjoBSc8GyycgWIQxBeQ5Tbjio9oNIxqRHh9Ep8cBtVXW=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been going to F45 in Clapham Junction this summer, and I’ve got to say, it’s been a blast! The workouts are solid, intense, but fun and perfect for all fitness levels. But what really makes it great place to train is the community vibe. The team is super friendly and supportive, and they’ve created a great atmosphere where everyone feels welcome 🙌🏼\n\nBig shout out to the amazing Julia and her mega team of Shaina, Chris, Lydia, Tyler,  Kirsty, Cameron and James. Also, for coffee lovers, Birdhouse which is a stones throw away is a great spot for afters.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOxkGelN13BNW9fpvZrNa6jKLYx1K91DSONT5ZYGMIUG4H9FBz-A424C3d213JEl3sK0U8og4Y7WOKJVrz0RE_tvHQ1Jfl_cWx4rbseHNuP0EVmEbe4kEwp63Z_lmEtNXKYQO-q=k-no"],"When":"Edited a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURuaGEyZmlnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116163538936959867280/reviews?hl=en-GB","posted_at_unix_micros":1728333779276445,"updated_at_unix_micros":1736842055160235,"language":"en","translated_lang":"","text_original":"I’ve been going to F45 in Clapham Junction this summer, and I’ve got to say, it’s been a blast! The workouts are solid, intense, but fun and perfect for all fitness levels. But what really makes it great place to train is the community vibe. The team is super friendly and supportive, and they’ve created a great atmosphere where everyone feels welcome 🙌🏼\n\nBig shout out to the amazing Julia and her mega team of Shaina, Chris, Lydia, Tyler,  Kirsty, Cameron and James. Also, for coffee lovers, Birdhouse which is a stones throw away is a great spot for afters.","text_translated":"","published_at":"2024-10-07T20:42:59.276445Z"},{"Name":"Hao Zhou","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVvoENVhueb2SuB323zneay9qU8G0DUMMgBtquo0EPJrfyLf20=s120-c-rp-mo-br100","Rating":1,"Description":"I strongly advise against giving them your actual name, email and phone number. Julia will stop at nothing to what'sapp you for months while email data breaches are a common occurrence. Last night 80 names and email addresses were leaked. You have coaches, now you need someone for GDPR. Is Julia doing anything other than creating traffic signing everyone in on an ipad (which everyone is perfectly capable of doing themselves) and messaging above levels of elegance?","Images":null,"When":"10 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSdFgxVklhRTVvVWpJeFdtaFlSazVzZFVNMFUzYxAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/106850140461843247682/reviews?hl=en-GB","posted_at_unix_micros":1761641521827632,"updated_at_unix_micros":1761641741629296,"language":"en","translated_lang":"","text_original":"I strongly advise against giving them your actual name, email and phone number. Julia will stop at nothing to what'sapp you for months while email data breaches are a common occurrence. Last night 80 names and email addresses were leaked. You have coaches, now you need someone for GDPR. Is Julia doing anything other than creating traffic signing everyone in on an ipad (which everyone is perfectly capable of doing themselves) and messaging above levels of elegance?","text_translated":"","reply_text_original":"Thank you for your review. We have checked our records and can confirm that you are not on our contact list and have never been registered with our studio. As such, we are unable to verify the situation described.","reply_language":"en","reply_posted_at_unix_micros":1763140072000000,"reply_updated_at_unix_micros":1763140072000000,"published_at":"2025-10-28T08:52:01.827632Z"}]</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>13</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/MPowered+Indoor+Cycling+Certification/data=!4m7!3m6!1s0x48761baa0761fb43:0x8566aed1251d68db!8m2!3d51.5129483!4d-0.0876553!16s%2Fg%2F11gk6zds40!19sChIJQ_thB6obdkgR22gdJdGuZoU</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>MPowered Indoor Cycling Certification</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Training provider</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Gymbox, 71 Lombard St, London EC3V 9AY, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>{"Friday":["Open 24 hours"],"Monday":["Open 24 hours"],"Saturday":["Open 24 hours"],"Sunday":["Open 24 hours"],"Thursday":["Open 24 hours"],"Tuesday":["Open 24 hours"],"Wednesday":["Open 24 hours"]}</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>https://melissapower.co.uk/about-academy</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>+44 20 3051 5401</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>GW76+5W London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>163</v>
+      </c>
+      <c r="O102" t="n">
+        <v>5</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":1,"4":0,"5":162}</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>51.512948</v>
+      </c>
+      <c r="R102" t="n">
+        <v>-0.087655</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>9612562667962984667</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm2iKBZee7BPPioam37WAM_VhvojuUE72sceTlUnZ6_x4gvsQdHJYEgujgvarOgIy2QB-uZP_64uBgLg65kOAeb_PKMnfVzzjTYMqWjTzomq2Vdn-ipj251BqMqJfM6JIfD6ZB0xQhvWz6-=w408-h291-k-no</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>0x48761baa0761fb43:0x8566aed1251d68db</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>ChIJQ_thB6obdkgR22gdJdGuZoU</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>{"id":"107292454124174150173","name":"MPowered Indoor Cycling Certification (Owner)","link":"https://www.google.com/maps/contrib/107292454124174150173"}</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Gymbox, 71 Lombard St","city":"London","postal_code":"EC3V 9AY","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>[{"Name":"Emilia Pistilli","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUwyzyGT2VXvJjsBVTUPAivDikWxQAHF65lm0W8RybvWJf6Nnoy=s120-c-rp-mo-br100","Rating":5,"Description":"I recently completed my Indoor Cycling qualification with Melissa, and I couldn't recommend the experience more! Melissa was really supportive, encouraging, and knowledgeable throughout.\n\nThe course day itself was super fun, with a brilliant atmosphere and hands on experience that helped me learn about how much goes into being a great instructor in a really interesting way.\n\nI feeling genuinely excited to start teaching and continue developing as an instructor. Thank you for such a positive and memorable experience!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tGaFN6Rm5NWFZJY21aWGVXTXpiVFJuWkZaUFptYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104594436189744024367/reviews?hl=en-GB","posted_at_unix_micros":1782826260567046,"updated_at_unix_micros":1782826260567046,"language":"en","translated_lang":"","text_original":"I recently completed my Indoor Cycling qualification with Melissa, and I couldn't recommend the experience more! Melissa was really supportive, encouraging, and knowledgeable throughout.\n\nThe course day itself was super fun, with a brilliant atmosphere and hands on experience that helped me learn about how much goes into being a great instructor in a really interesting way.\n\nI feeling genuinely excited to start teaching and continue developing as an instructor. Thank you for such a positive and memorable experience!","text_translated":"","published_at":"2026-06-30T13:31:00.567046Z"},{"Name":"Bhavin Shah","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWf2jKCuWS_75pGbidZ062pu7QqILWIj3r5sbuJMvhWy9VVvX65nw=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Melissa is an outstanding indoor cycling instructor in her own right *and* a coach for aspiring instructors. Her all day course was thorough, insightful, well-structured and genuinely enjoyable! It's clear the course is highly respected in the indoor cycling community. For the assessment, Melissa provided detailed guidance before and feedback after. Her years/decades of experience really comes through in everything she teaches and all the materials you're given. Thank you Melissa!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tzeVExQTVhMFpRZEVwdGRFdFRkSEo0YzIxNVVHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107025246190345999802/reviews?hl=en-GB","posted_at_unix_micros":1778048699132637,"updated_at_unix_micros":1778048699132637,"language":"en","translated_lang":"","text_original":"Melissa is an outstanding indoor cycling instructor in her own right *and* a coach for aspiring instructors. Her all day course was thorough, insightful, well-structured and genuinely enjoyable! It's clear the course is highly respected in the indoor cycling community. For the assessment, Melissa provided detailed guidance before and feedback after. Her years/decades of experience really comes through in everything she teaches and all the materials you're given. Thank you Melissa!","text_translated":"","published_at":"2026-05-06T06:24:59.132637Z"},{"Name":"Sophie Jones","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWo7YHO7hTUuUDAyNGHkoKtqvgxwbraGf8N3xKOCe6H7tvA5R8h=s120-c-rp-mo-br100","Rating":5,"Description":"Melissa is an excellent coach. Her training day was fantastic. Informative \u0026 incredibly insightful.\n\nHer approach to indoor cycling is the approach to learn from, especially if you're wanting to teach it. The training day focused on how make indoor cycling classes inclusive, safe, effective and most of all, fun for everyone ,whether you're a complete beginner or have been doing spin indoor cycling for years.\n\nMelissa was someone who was recommended to me by multiple spin instructors, and I totally understand why. She was knowledgeable, incredibly approachable, and lots of fun. No question was a silly question.\n\nWith Melissa's teaching, I feel very confident that I can teach a very effective indoor cycling class.\n\n10/10 would recommend. Great value \u0026 passionate teaching!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT20weFJUQndPREJNTUY5QlkyUmlOVlJDUkhGVVFVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104114218343806685065/reviews?hl=en-GB","posted_at_unix_micros":1777538011764339,"updated_at_unix_micros":1777538011764339,"language":"en","translated_lang":"","text_original":"Melissa is an excellent coach. Her training day was fantastic. Informative \u0026 incredibly insightful.\n\nHer approach to indoor cycling is the approach to learn from, especially if you're wanting to teach it. The training day focused on how make indoor cycling classes inclusive, safe, effective and most of all, fun for everyone ,whether you're a complete beginner or have been doing spin indoor cycling for years.\n\nMelissa was someone who was recommended to me by multiple spin instructors, and I totally understand why. She was knowledgeable, incredibly approachable, and lots of fun. No question was a silly question.\n\nWith Melissa's teaching, I feel very confident that I can teach a very effective indoor cycling class.\n\n10/10 would recommend. Great value \u0026 passionate teaching!","text_translated":"","published_at":"2026-04-30T08:33:31.764339Z"},{"Name":"Deb Rankin","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVPTs-DFpXWRwnYiy4VkF6W2rqn9e3_5_82dWKn_ONzUJwbV3ys=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I recently purchased Melissa’s online version of the indoor cycling course. I found it extremely informative and easy to follow, packed with useful tips and I would highly recommend this course to anyone looking for a side career as an instructor. Following the course I have begun instructing at a local studio.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNOsuWKMi6kfj9AsYZqhgEjoTB4doii9_fyf9SJJ02w6GfLemkAf6vxTbUGlF_nBl4qWzQTc9IzGsemzhj_Ce9m-WxahQPaebBhPmPlkbp7S7O6s8aZvdXRt8uEi0Rz7-QShViipR8IDfoK=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s1U1VHdEdVMjF6Tnpsb016QnRiVWxmTTNaNVEwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112552999333937833905/reviews?hl=en-GB","posted_at_unix_micros":1771084887072510,"updated_at_unix_micros":1771084887072510,"language":"en","translated_lang":"","text_original":"I recently purchased Melissa’s online version of the indoor cycling course. I found it extremely informative and easy to follow, packed with useful tips and I would highly recommend this course to anyone looking for a side career as an instructor. Following the course I have begun instructing at a local studio.","text_translated":"","published_at":"2026-02-14T16:01:27.07251Z"},{"Name":"Ellie MacDonald","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUoli7CSTNMAED60LluTrWer7nzJeRwNTDNjU2AszS4Xi-BI9c1=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Highly recommend Melissa's course!\n\nIt was an exciting yet informative day in London, she answered all the questions we had and kept us engaged all day. From learning the moves on the bike, to a sample class into a theory filled afternoon, you come away feeling full of knowledge ready to start your career. You are given all the information for the theory written test and then a practical submitted via video, she is on hand to answer questions and help with a very fast response on her marking.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25kVUxURTRWaTF1V0hCclozZzJURk5aUzE5YU5YYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116008269054119536840/reviews?hl=en-GB","posted_at_unix_micros":1781094450573767,"updated_at_unix_micros":1781094450573767,"language":"en","translated_lang":"","text_original":"Highly recommend Melissa's course!\n\nIt was an exciting yet informative day in London, she answered all the questions we had and kept us engaged all day. From learning the moves on the bike, to a sample class into a theory filled afternoon, you come away feeling full of knowledge ready to start your career. You are given all the information for the theory written test and then a practical submitted via video, she is on hand to answer questions and help with a very fast response on her marking.","text_translated":"","published_at":"2026-06-10T12:27:30.573767Z"}]</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>13</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Boom+Cycle+-+Battersea/data=!4m7!3m6!1s0x48760504abfaf785:0xe9a48df2b3cfc2a1!8m2!3d51.4831853!4d-0.1468449!16s%2Fg%2F11g9vlnyx9!19sChIJhff6qwQFdkgRocLPs_KNpOk</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Boom Cycle - Battersea</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Indoor cycling</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1 &amp; 3 Arches Ln, Station Circus, Nine Elms, London SW11 8AB, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>{"Friday":["7 am–7:30 pm"],"Monday":["7 am–8:30 pm"],"Saturday":["8:30 am–5:30 pm"],"Sunday":["8 am–4:30 pm"],"Thursday":["7 am–8:30 pm"],"Tuesday":["7 am–8:30 pm"],"Wednesday":["7 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>http://thecommonbond.co/boom-cycle</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>+44 20 3034 0711</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>FVM3+77 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>163</v>
+      </c>
+      <c r="O103" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>{"1":6,"2":6,"3":1,"4":10,"5":140}</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>51.483185</v>
+      </c>
+      <c r="R103" t="n">
+        <v>-0.146845</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>16835737380556096161</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlknK4GXnryTxbbdsQTgdratrozpqCOkD6FB55yyZjtTEkafReployQjBfSip3cQbq1Gpow9XhaHQ3Zsfjyv_afKQzNttXXx6XGiLpPt8R6ALFy89OfQ1Oi3jtuOg7gzYEcZi7P5A=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>0x48760504abfaf785:0xe9a48df2b3cfc2a1</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>ChIJhff6qwQFdkgRocLPs_KNpOk</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.mindbodyonline.com/explore/locations/boom-cycle-battersea?rwg_token=AE37R_inkD_xhW5aDUMyVCum-GUf3GBtpIILP4sbqmiKPXPJToWckvaXqTXsHkGuXFh3WXX7MyaCuCnj_n0cUg9GSpnVEoMJ0FPDm7x4GuNHq3_QNT9cokE%3D","source":"mindbodyonline.com"}]</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>{"id":"109974947649841178824","name":"Boom Cycle - Battersea (Owner)","link":"https://www.google.com/maps/contrib/109974947649841178824"}</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>{"borough":"Nine Elms","street":"1 \u0026 3 Arches Ln, Station Circus","city":"London","postal_code":"SW11 8AB","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>[{"Name":"Isobel Camm","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLYA4x8y7PsLwsXc4pv8EjOd8zMYLyQPeg6FGVcyg-otf8O1g=s120-c-rp-mo-br100","Rating":5,"Description":"The best spin In London! I’ve been coming to this studio since it opened in 2018 and tried other classes… these trump every time!! Best team, beautiful studio, guaranteed sweat. Thank you team for always looking after the studio and us so well 🙏🏻😊","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNll3neFpse8cO6rHKUxEiYtgy5U29qHIFnqNxZ0h_dJEi_nEeh18wxD8KTqRZ3BPGxcXC9Ytbn8JOLOO_z87z8BLwtEivNfJg4avc0_POJvvoPOXSgEXuBm7zbazhA6T34zhaV__2PQVSR=k-no"],"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pOd01taHlhMmx1VEhCaFNraHRjbkJRY0U1RVRrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117658025529395231613/reviews?hl=en-GB","posted_at_unix_micros":1769023503734164,"updated_at_unix_micros":1769023503734164,"language":"en","translated_lang":"","text_original":"The best spin In London! I’ve been coming to this studio since it opened in 2018 and tried other classes… these trump every time!! Best team, beautiful studio, guaranteed sweat. Thank you team for always looking after the studio and us so well 🙏🏻😊","text_translated":"","reply_text_original":"What a wonderful review! Thank you for sharing the love! Looking forward to seeing you back in the studio soon :D","reply_language":"en","reply_posted_at_unix_micros":1770643697000000,"reply_updated_at_unix_micros":1770643697000000,"published_at":"2026-01-21T19:25:03.734164Z"},{"Name":"Wei Yong","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLd1_0i42bcBxf3omAPS3xJKfyPVsrHTiWR_-Fnp0jukLJ_k-o=s120-c-rp-mo-br100","Rating":5,"Description":"We’ve done an intro offer for the cycling. We did classes with Martina, Amy, and Jess. Izzy helped us set up when we had trouble. Unfortunately we will miss her 300th ride. We’d enjoyed all the rides. Will come back soon.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNMGTyZojzVXfJrrbOi0BkegsLWHrNNrzXUR19dYDnj_2NHjgST06NWtj_uw8YgexHno80ZM4aMtRqCKiKnUDqcIlBNp2-7kIf13GsYQgyNDM8itstiezY9Yc7T1Y3bWugw1MG5ntU53s2k=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSMlYzTXdlRlZXUVRRMWVIQkRNMnBTT1dGb2NIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115701980463838571977/reviews?hl=en-GB","posted_at_unix_micros":1772881197776544,"updated_at_unix_micros":1772881197776544,"language":"en","translated_lang":"","text_original":"We’ve done an intro offer for the cycling. We did classes with Martina, Amy, and Jess. Izzy helped us set up when we had trouble. Unfortunately we will miss her 300th ride. We’d enjoyed all the rides. Will come back soon.","text_translated":"","reply_text_original":"Thank you so much for your lovely review and for joining us for your intro offer Wei!\n\nWe’re really happy to hear you enjoyed your classes with Martina, Amy, and Jess, and that Izzy was able to help you get set up — we’ll be sure to pass on your kind words to the whole team.\n\nWe’re sorry you missed Izzy’s 300th ride, but we really look forward to welcoming you back again soon for more rides with us 🚴‍♀️","reply_language":"en","reply_posted_at_unix_micros":1778838835000000,"reply_updated_at_unix_micros":1778838835000000,"published_at":"2026-03-07T10:59:57.776544Z"},{"Name":"Sheila Boswell","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUOs4ssPY1URBlRAY8VGTdfd0KXaCgarPa0y_QmGFuZfEaAsQc=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Estela subbed the spin class, and she was fantastic! The energy, music, and overall vibe were amazing—the whole class seemed to really enjoy it.\nThe ride was a great mix of speed and well-executed choreography, and the music selection was fun and motivating throughout. Estela created an engaging atmosphere that kept everyone energized from start to finish.\nI would absolutely love to have Estela back at Battersea again!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xkUU16aEVPVk5LZFdSRmNsZHJiRkk1ZW5aeVRsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104057111266318989726/reviews?hl=en-GB","posted_at_unix_micros":1780747832932598,"updated_at_unix_micros":1780747832932598,"language":"en","translated_lang":"","text_original":"Estela subbed the spin class, and she was fantastic! The energy, music, and overall vibe were amazing—the whole class seemed to really enjoy it.\nThe ride was a great mix of speed and well-executed choreography, and the music selection was fun and motivating throughout. Estela created an engaging atmosphere that kept everyone energized from start to finish.\nI would absolutely love to have Estela back at Battersea again!","text_translated":"","reply_text_original":"Thank you so much for your fantastic review! We're delighted to hear that you enjoyed Estela's class so much. She brings such incredible energy to every ride, and it's wonderful to know that her music, coaching, and atmosphere made such a positive impact on your experience.\n\nWe're especially pleased that you enjoyed the balance of speed, choreography, and motivation throughout the class. Creating an engaging and uplifting environment is exactly what we aim for, and it sounds like Estela delivered just that!\n\nWe'll be sure to pass along your kind words to Estela, and we'll certainly take your feedback on board. We hope to welcome you back to another ride at Battersea very soon!","reply_language":"en","reply_posted_at_unix_micros":1781175790000000,"reply_updated_at_unix_micros":1781175790000000,"published_at":"2026-06-06T12:10:32.932598Z"},{"Name":"Federica Accorinti","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJvqO6e3iVY_ftFMbWkiPZCFGTBlKWpoSkt_J05HYMEbLod7Q=s120-c-rp-mo-br100","Rating":5,"Description":"Mu favourite place for a fun and energetic spinning class! The staff are always friendly and helpful, the themed classes are so much fun and the coreos are challenging but rewarding. You can go as hard as you want and feel good with yourself without anyone judging. The changing rooms are also lovely, well equipped and very clean. Would totally recommend","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2toa1kwVllRVloxVTFGaVkwdFlSMHBHZUVGWFlVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107607352448849870188/reviews?hl=en-GB","posted_at_unix_micros":1775037292565443,"updated_at_unix_micros":1775037292565443,"language":"en","translated_lang":"","text_original":"Mu favourite place for a fun and energetic spinning class! The staff are always friendly and helpful, the themed classes are so much fun and the coreos are challenging but rewarding. You can go as hard as you want and feel good with yourself without anyone judging. The changing rooms are also lovely, well equipped and very clean. Would totally recommend","text_translated":"","reply_text_original":"Thank you so much for this fantastic review Federica! We’re thrilled to hear that our spinning classes are your favourite place for a fun, energetic workout.\n\nIt’s wonderful to know you’re enjoying the themed rides, challenging choreography, and the supportive, non-judgmental atmosphere — that’s exactly what we aim to create. We’re also really glad you’re happy with the changing rooms and facilities.\n\nWe truly appreciate your recommendation and look forward to seeing you back in the studio soon! 🚴‍♀️","reply_language":"en","reply_posted_at_unix_micros":1778838589000000,"reply_updated_at_unix_micros":1778838589000000,"published_at":"2026-04-01T09:54:52.565443Z"},{"Name":"sarah-jessica rose","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK3DPbThkqyzWJeEG-j0id5ejTTOskoYKGREB7Rc1dRW2CLVabw=s120-c-rp-mo-br100","Rating":2,"Description":"Two and a half out of 5\n\nWas deliberating posting but this is the 5th class of Amy Shooters I’ve heard and the playlists and energy needs adjusting .\n\nI’ve been trying a few studios in the area over the past couple of weeks and was really looking forward to finding a great spin class. Unfortunately, the class hosted by Amy was disappointing enough that I considered leaving early several times.\n\nThe main issue was the music and playlist selection. Rather than being motivating or energising, it felt overwhelmingly loud and chaotic throughout the session. The vibe leaned heavily into 90s British rock/punk, which just didn’t work for me in a spin environment.\n\nBefore moving to the area, I regularly attended classes at SoulCycle and 1Rebel, where the playlists really enhanced the experience and kept the energy high. In comparison, this class felt more stressful than motivating.\n\nSadly, because of the overall experience, I won’t be returning.\n\nGood points :\n\nGreat chill zone before class\nNice changing rooms\nWater refill tank is nice\nReformer was good","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xoSWMxZENZbE5TU0VaS1EzaGFWRWcwUjJoWmVuYxAB","source":"Google","rating_scale":5,"rating_float":2,"author_url":"https://www.google.com/maps/contrib/109790318280957126063/reviews?hl=en-GB","posted_at_unix_micros":1779701088123770,"updated_at_unix_micros":1779701088123770,"language":"en","translated_lang":"","text_original":"Two and a half out of 5\n\nWas deliberating posting but this is the 5th class of Amy Shooters I’ve heard and the playlists and energy needs adjusting .\n\nI’ve been trying a few studios in the area over the past couple of weeks and was really looking forward to finding a great spin class. Unfortunately, the class hosted by Amy was disappointing enough that I considered leaving early several times.\n\nThe main issue was the music and playlist selection. Rather than being motivating or energising, it felt overwhelmingly loud and chaotic throughout the session. The vibe leaned heavily into 90s British rock/punk, which just didn’t work for me in a spin environment.\n\nBefore moving to the area, I regularly attended classes at SoulCycle and 1Rebel, where the playlists really enhanced the experience and kept the energy high. In comparison, this class felt more stressful than motivating.\n\nSadly, because of the overall experience, I won’t be returning.\n\nGood points :\n\nGreat chill zone before class\nNice changing rooms\nWater refill tank is nice\nReformer was good","text_translated":"","reply_text_original":"Thank you for taking the time to share your feedback. We’re really pleased to hear you enjoyed the chill zone, changing facilities, water station, and reformer experience.\n\nWe’re sorry to hear the spin class with Amy didn’t meet your expectations. Music and energy are such a personal part of the ride experience, and we appreciate your honest comments regarding the playlist style and atmosphere. Amy’s classes do have a distinctive music taste and coaching style that many riders enjoy, but we understand it won’t resonate with everyone.\n\nWe always value constructive feedback and will certainly take your comments on board as we continue refining our class experience across the timetable. We appreciate you giving us a try and wish you all the best in finding the right studio fit for you.","reply_language":"en","reply_posted_at_unix_micros":1779716826000000,"reply_updated_at_unix_micros":1779716826000000,"published_at":"2026-05-25T09:24:48.12377Z"}]</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>13</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>c2406c1e-2fba-4c5c-8ab2-a599af517682</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/HIT35+Bootcamp/data=!4m7!3m6!1s0x48760a569d3c592f:0x1f9ff79498737742!8m2!3d51.3880121!4d-0.3205624!16s%2Fg%2F11fy_n5v_s!19sChIJL1k8nVYKdkgRQndzmJT3nx8</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>HIT35 Bootcamp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Windmill Ln, Long Ditton, Surbiton KT6 5JT, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–8:30 pm"],"Monday":["5:30 am–8:30 pm"],"Saturday":["5:30 am–8:30 pm"],"Sunday":["7 am–12 pm"],"Thursday":["5:30 am–8:30 pm"],"Tuesday":["5:30 am–8:30 pm"],"Wednesday":["5:30 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>http://www.hit35.co.uk/</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>+44 7557 221663</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>9MQH+6Q Surbiton, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>162</v>
+      </c>
+      <c r="O104" t="n">
+        <v>5</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":0,"3":0,"4":0,"5":161}</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>51.388012</v>
+      </c>
+      <c r="R104" t="n">
+        <v>-0.320562</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>2278812154057684802</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlk7Gob6DZZjRulTAiGzFO0T1pcG36xAELvHoeAfpwtZNAoFUdsIhKDjZYrmAbqfCQqdD2LM-boHaYZt1w-75WlORGXBBW4GIX31F3rp8m2mDim5v2H2mMt5Flz4yXVGKq_MHWRWg=w408-h271-k-no</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>0x48760a569d3c592f:0x1f9ff79498737742</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>ChIJL1k8nVYKdkgRQndzmJT3nx8</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>[{"link":"http://www.hit35.co.uk/book-your-free-intro","source":"hit35.co.uk"},{"link":"https://www.wellnessliving.com/rwg/booking/request?query=X8VdOUztd22xTwiEzpcBeV87jcSbH5AP3LyHF6FJGLsK7ObQnO4jO\u0026rwg_token=AE37R_jjrKJaxTxkhNM03SgooYcRCBZRObsaoioV8N1Wt7ReQayFWAxxrIP-6AFkp0h5nz7A9hsYdyam2tmHAefAIvlbJjupyYXgNsQoRQ3uEHBunh-6uP8%3D","source":"wellnessliving.com"}]</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>{"id":"100424183178393908062","name":"HIT35 Bootcamp (Owner)","link":"https://www.google.com/maps/contrib/100424183178393908062"}</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>{"borough":"Long Ditton","street":"HIT35 Bootcamp, Windmill Ln","city":"Surbiton","postal_code":"KT6 5JT","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible seating","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>[{"Name":"Louise","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKdAUXc4dXWElFnpM-TjgooK5aL7Cu8VyLiXkYbhXvEqQSmFA=s120-c-rp-mo-br100","Rating":5,"Description":"I started going to HIT35 in February 2023  and cannot recommend them enough. It sounds clichéd but it's true. The instructors are so professional and each has their own style when taking a class, ranging from humour (that's you David), to pure motivation and support. They are all eagle-eyed, so no matter how many of you there are in a class (max 15), you always receive individual attention. All the trainers are knowledgeable and approachable. Not having had any previous gym experience, I always feel safe carrying out new tasks. It feels as though great care is taken when hiring new trainers, and it shows. The classes are fun, welcoming and the diary system on the app makes booking or swapping very easy. I'm reluctantly taking a break due to personal reasons, Ali and the team have been so supportive. Thank you everyone and I hope to return in due course!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21GUlRIaE5TRWRrYlRSNmVtMUlNWGhpYUVkVmMxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104816781502948175110/reviews?hl=en-GB","posted_at_unix_micros":1776706749843838,"updated_at_unix_micros":1776706749843838,"language":"en","translated_lang":"","text_original":"I started going to HIT35 in February 2023  and cannot recommend them enough. It sounds clichéd but it's true. The instructors are so professional and each has their own style when taking a class, ranging from humour (that's you David), to pure motivation and support. They are all eagle-eyed, so no matter how many of you there are in a class (max 15), you always receive individual attention. All the trainers are knowledgeable and approachable. Not having had any previous gym experience, I always feel safe carrying out new tasks. It feels as though great care is taken when hiring new trainers, and it shows. The classes are fun, welcoming and the diary system on the app makes booking or swapping very easy. I'm reluctantly taking a break due to personal reasons, Ali and the team have been so supportive. Thank you everyone and I hope to return in due course!","text_translated":"","reply_text_original":"Thats so lovely to hear, thank you Louise. Try not to stay away for too long 😊","reply_language":"en","reply_posted_at_unix_micros":1776760740000000,"reply_updated_at_unix_micros":1776760740000000,"published_at":"2026-04-20T17:39:09.843838Z"},{"Name":"Jas Madia","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKcgLHoWwsgiBVbds2fXcD2YJWFYm2lZZmRRnIZBbaUpYXlIg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"HIT35 Bootcamp has been my fitness home from 2018 to 2024, and I can confidently say it’s one of the most effective and well-rounded gyms I’ve ever been part of.\n\nThe 35-minute workout format is incredibly efficient — perfect for busy schedules yet packed with intensity and variety to deliver real results. Every session is designed to challenge you while being tailored to your fitness level, making it both approachable and powerful.\n\nI also did personal training here with a few of their trainers, and each one brought a depth of knowledge, support, and motivation that kept me consistently progressing. The coaching approach goes beyond workouts — they truly focus on the full picture, including nutrition, lifestyle habits, and mindset, all aligned to help you hit your goals and sustain them.\n\nWhat really sets HIT35 apart, though, is the community. Over the years, I’ve made some lifelong friends — the kind who cheer you on inside the gym and stay connected outside of it too.\n\nIf you’re looking for an efficient, results-driven, and community-oriented gym, HIT35 Bootcamp is the place. Can’t recommend it highly enough.\n\nEven though I’ve moved away from London, I don’t miss a chance to drop in for a few sessions when around Surbiton.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOEiGxqAWqBmxitnfUdH8vj-xe3b70tW51JCNmU1xWVLfonWEupqbH7QnHroDuFe1JlojfnZNsQ_xceTP9lLLGK-E2AxFjh7dsomoe1-jpNobl6a2kevOR41MA7OGvoTmfT4B8XAatMwhnR=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNIRwT7w6Y-8Le_OvDu-X6O7ZfMUqbV5Uwy2eJlXOuP6zDkAFyc28tMEP32DHvodOaVfaFLULCcKaoRMElwkZfQFDE1If9jhwfwJYWRXeFDxExmC2L76FfSZmsROZEj0XmNa006of09Xnvq=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNPoml8GmiFWjBZ7MqgZCaV9noLjnAhobBkoeLsI1gBa0IjLUJ3xCu-F8uZ5aVuq5y63PHK1S6VHD3dItL6F3GU4IbMv1DWEBtyFhxZYt5AonHThxMYmNltJk1O5VGzJQdULzVGjRKORwfU=k-no"],"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pSdGVHZHdjRUpHUjBSUGFUbFljbWxKY1hrd1pXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117471640198606193379/reviews?hl=en-GB","posted_at_unix_micros":1753781537014941,"updated_at_unix_micros":1753781779142651,"language":"en","translated_lang":"","text_original":"HIT35 Bootcamp has been my fitness home from 2018 to 2024, and I can confidently say it’s one of the most effective and well-rounded gyms I’ve ever been part of.\n\nThe 35-minute workout format is incredibly efficient — perfect for busy schedules yet packed with intensity and variety to deliver real results. Every session is designed to challenge you while being tailored to your fitness level, making it both approachable and powerful.\n\nI also did personal training here with a few of their trainers, and each one brought a depth of knowledge, support, and motivation that kept me consistently progressing. The coaching approach goes beyond workouts — they truly focus on the full picture, including nutrition, lifestyle habits, and mindset, all aligned to help you hit your goals and sustain them.\n\nWhat really sets HIT35 apart, though, is the community. Over the years, I’ve made some lifelong friends — the kind who cheer you on inside the gym and stay connected outside of it too.\n\nIf you’re looking for an efficient, results-driven, and community-oriented gym, HIT35 Bootcamp is the place. Can’t recommend it highly enough.\n\nEven though I’ve moved away from London, I don’t miss a chance to drop in for a few sessions when around Surbiton.","text_translated":"","reply_text_original":"WE MISS YOU JAS, COME BAAAACK! ","reply_language":"en","reply_posted_at_unix_micros":1765961087000000,"reply_updated_at_unix_micros":1765961087000000,"published_at":"2025-07-29T09:32:17.014941Z"},{"Name":"Anna Bootle","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK8SOTGBx2h_hdVA5LVwRPLzn6kv5OeThB9S-jBum_GffJjUQ=s120-c-rp-mo-br100","Rating":5,"Description":"I have really enjoyed my first three months at HIT35 Surbiton, every class is different and as they are only 35 minutes long it’s easy to fit into your day. David and the instructors are really friendly, welcoming and motivating and ensure your doing the exercises correctly, would highly recommend anyone to join!","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25wd01IRnlNbVkzVkRsM1kwazNWWG81ZFhGS0xVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100146411591439836940/reviews?hl=en-GB","posted_at_unix_micros":1770463079367812,"updated_at_unix_micros":1770463079367812,"language":"en","translated_lang":"","text_original":"I have really enjoyed my first three months at HIT35 Surbiton, every class is different and as they are only 35 minutes long it’s easy to fit into your day. David and the instructors are really friendly, welcoming and motivating and ensure your doing the exercises correctly, would highly recommend anyone to join!","text_translated":"","reply_text_original":"Thanks Anna! Great to have you with us 😊","reply_language":"en","reply_posted_at_unix_micros":1770496220000000,"reply_updated_at_unix_micros":1770496220000000,"published_at":"2026-02-07T11:17:59.367812Z"},{"Name":"Carolyn Bagnell","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJpIi1qMEXreO2nzzzlo3-75hhbEMIBklGvziDSgi_VIM6Vkw=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve had a great experience since joining this gym and can’t recommend it enough to anyone looking for effective workouts in a friendly, supportive environment. Classes are only 35 minutes so I can easily fit them into my schedule. A big plus is that the workouts vary so I never get bored! The coaches are constantly encouraging everyone in the class and I appreciate when they push me to work harder. Overall this is simply just a great space to workout and meet new people.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT210NWFtbGxUbDlqV0hFemFuSmZhek53ZUdWc1luYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106164838521491799690/reviews?hl=en-GB","posted_at_unix_micros":1773150695985113,"updated_at_unix_micros":1773150695985113,"language":"en","translated_lang":"","text_original":"I’ve had a great experience since joining this gym and can’t recommend it enough to anyone looking for effective workouts in a friendly, supportive environment. Classes are only 35 minutes so I can easily fit them into my schedule. A big plus is that the workouts vary so I never get bored! The coaches are constantly encouraging everyone in the class and I appreciate when they push me to work harder. Overall this is simply just a great space to workout and meet new people.","text_translated":"","reply_text_original":"Carolyn you have been an absolute PLEASURE to have with us. Here's to more years to come 😊🎉🥂","reply_language":"en","reply_posted_at_unix_micros":1773158784000000,"reply_updated_at_unix_micros":1773158784000000,"published_at":"2026-03-10T13:51:35.985113Z"},{"Name":"Delyth Gadd","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLYKbOD1gkBESRD2LrY5VaLUPi6qar0Ju5MkjSW4IbWiiVpnQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I’ve been a member since 2019 and I love it. The trainers are enthusiastic and the members are fun and the work outs have made me a fitter and stronger. The timetable of sessions fits around busy schedules and it really has become an important part of my week. I never ever thought I’d enjoy exercise and get up early on a Saturday morning to do it but I do and I walk away with a smile.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMu-WrGtXbf7onV2FdYNrrr03tBS42epaqLkfMaW7-WG0dS3RAM9rijqDsICMu3vOOO1IExuLpVGkkwuzwlwHEqUv0Mh-k0oS-kLwa2fGvqPsYqVJfYcYentzkFm1PyFBTH24TluTA9CNl8=k-no"],"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tGdWJVWndlRmRwZVY5MVZEQm9OREZMTkcxa2VYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105349392582358830510/reviews?hl=en-GB","posted_at_unix_micros":1765920580209241,"updated_at_unix_micros":1765920580209241,"language":"en","translated_lang":"","text_original":"I’ve been a member since 2019 and I love it. The trainers are enthusiastic and the members are fun and the work outs have made me a fitter and stronger. The timetable of sessions fits around busy schedules and it really has become an important part of my week. I never ever thought I’d enjoy exercise and get up early on a Saturday morning to do it but I do and I walk away with a smile.","text_translated":"","reply_text_original":"And the gym would never be the same without you Del 😊","reply_language":"en","reply_posted_at_unix_micros":1765960910000000,"reply_updated_at_unix_micros":1765960910000000,"published_at":"2025-12-16T21:29:40.209241Z"}]</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>13</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Pinnacle+Fitness+and+Health+Club/data=!4m7!3m6!1s0x487619c5432aa283:0x90dbe0781370281d!8m2!3d51.6299561!4d-0.1757103!16s%2Fg%2F11f4qqqtzc!19sChIJg6IqQ8UZdkgRHShwE3jg25A</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Pinnacle Fitness and Health Club</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1-3 Totteridge Ln, London N20 0EX, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>{"Friday":["7 am–5 pm"],"Monday":["7 am–8 pm"],"Saturday":["8 am–2 pm"],"Sunday":["8 am–12:30 pm"],"Thursday":["7 am–8 pm"],"Tuesday":["7 am–8 pm"],"Wednesday":["7 am–8 pm"]}</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>http://www.pinnaclefh.com/</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>+44 20 8446 1122</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>JRHF+XP London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>158</v>
+      </c>
+      <c r="O105" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>{"1":3,"2":3,"3":0,"4":1,"5":151}</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>51.629956</v>
+      </c>
+      <c r="R105" t="n">
+        <v>-0.17571</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>10438183367688071197</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk8ksUDd5lo-WJVzWZ5nYwfarvbr6CdH_lvCUcSOVS6nXpe9rlGht_yav-2gIX7z35SjOFE-aTc0eb751K5Rz9zlPy8CltyOOkPTdhn_kpgzo1frIO1asCKrihSl5Y0wF4F2r6D=w408-h271-k-no</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>0x487619c5432aa283:0x90dbe0781370281d</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>ChIJg6IqQ8UZdkgRHShwE3jg25A</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>[{"link":"https://pinnacle-fitness-and-health-ltd.uk1.cliniko.com/bookings#location","source":"cliniko.com"},{"link":"https://club.pinnaclefh.com/reserve/#/login/site/1/st/ce46dea3-7da5-48af-99a4-8b31870644a9","source":"pinnaclefh.com"}]</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>{"id":"110825548143907371129","name":"Pinnacle Fitness and Health Club (Owner)","link":"https://www.google.com/maps/contrib/110825548143907371129"}</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"1-3 Totteridge Ln","city":"London","postal_code":"N20 0EX","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible seating","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>[{"Name":"James Osborn","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXfUhXtPxOYMg9bkrUV6G_Fvya9d2Pnr8-JmxQpODbldgcXm5Q=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Absolutely love the place.\nI joined 6 months ago, finally admitting enough was enough after a decade of neglecting my body and health.\nI can now honestly say I feel brand new in every metric.\nBig big thank you to Adam G for all the continued support and for putting up with my early starts mate. Allowing our sessions to fit into my crazy work life schedule has made this something i can stick at and I’m grateful.\nI look forward to every visit.\nFor anyone reading this contemplating joining Pinnacle Fitness… absolutely do not hesitate.\nIt may feel daunting, but every single PT/Physio/Staff member I’ve met or even in passing have been the most welcoming and encouraging.\nI can’t recommend Pinnacle highly enough.","Images":null,"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21admJqUm1WRWwzZVhCTWFsRkNaSFI0UzI1d1ZFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108864558278659797774/reviews?hl=en-GB","posted_at_unix_micros":1764930165328146,"updated_at_unix_micros":1764930165328146,"language":"en","translated_lang":"","text_original":"Absolutely love the place.\nI joined 6 months ago, finally admitting enough was enough after a decade of neglecting my body and health.\nI can now honestly say I feel brand new in every metric.\nBig big thank you to Adam G for all the continued support and for putting up with my early starts mate. Allowing our sessions to fit into my crazy work life schedule has made this something i can stick at and I’m grateful.\nI look forward to every visit.\nFor anyone reading this contemplating joining Pinnacle Fitness… absolutely do not hesitate.\nIt may feel daunting, but every single PT/Physio/Staff member I’ve met or even in passing have been the most welcoming and encouraging.\nI can’t recommend Pinnacle highly enough.","text_translated":"","reply_text_original":"James you have been amazing, so dedicated to your training and keeping on track and the result show! It’s been lovely helping support you with your journey and long forward to seeing you continue to smash your goals in 2026 ","reply_language":"en","reply_posted_at_unix_micros":1766085104000000,"reply_updated_at_unix_micros":1766085104000000,"published_at":"2025-12-05T10:22:45.328146Z"},{"Name":"Katie L","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKDP_6JyiGTOxpMS5UWMD7PjzYtbdevvP88Y1KImEAnj_pKGQ=s120-c-rp-mo-br100","Rating":5,"Description":"Highly recommmend Pinnacle Fitness and Health not only for injury recovery but also for fitness goals.  George worked on my damaged knee where I was struggling with severe pain and limited movement. His clear and targeted treatment plan restored strength and mobility and I am now able to enjoy PT sessions with him to get me fit again.  Gym atmosphere is great and the other personal trainers and staff are so friendly.  An exceptional place in my opinion.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tzNGRsWk1XRTlJWldaV1JXOVBVR2xzU1haeFdFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111870820933816938200/reviews?hl=en-GB","posted_at_unix_micros":1774530272144790,"updated_at_unix_micros":1774530378921208,"language":"en","translated_lang":"","text_original":"Highly recommmend Pinnacle Fitness and Health not only for injury recovery but also for fitness goals.  George worked on my damaged knee where I was struggling with severe pain and limited movement. His clear and targeted treatment plan restored strength and mobility and I am now able to enjoy PT sessions with him to get me fit again.  Gym atmosphere is great and the other personal trainers and staff are so friendly.  An exceptional place in my opinion.","text_translated":"","reply_text_original":"Thank you, Katie. We're so glad George's targeted treatment restored your knee strength and mobility. It's wonderful to hear you're enjoying your PT sessions and our gym atmosphere, and that our trainers and staff made you feel supported. We appreciate your high recommendation and look forward to helping you reach your next fitness goals.","reply_language":"en","reply_posted_at_unix_micros":1774537515000000,"reply_updated_at_unix_micros":1774537515000000,"published_at":"2026-03-26T13:04:32.14479Z"},{"Name":"James Wood","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLFNaQ-thU3E7-PfNEKoZh7GnuP4lszrUMu5n4q6hIG4UVwGw=s120-c-rp-mo-br100","Rating":5,"Description":"started seeing George purely to improve my golf performance — and the difference has been huge.\n\nAs a golfer, you know when something isn’t quite firing. I felt tight through my hips and thoracic spine, my rotation was restricted and I wasn’t moving efficiently through the ball. George immediately identified the root cause rather than just treating the symptoms.\n\nHis hands-on work and manipulation freed up areas I didn’t even realise were limiting me. Straight away I felt more mobile, more balanced and more connected. But what really sets him apart is what happens after the treatment.\n\nHe takes you onto the gym floor and shows you the change. We retested movements and you could literally see the improvement in range, control and stability. It wasn’t just “feels better” — it was measurable progress.\n\nHe then gave me specific exercises tailored to my swing, reinforcing the new movement patterns so the gains actually stick.\n\nSince working with him:\n• Improved hip and T-spine rotation\n• Better sequencing through impact\n• More speed without forcing it\n• Less post-round stiffness\n\nI’m moving better, swinging more efficiently and recovering faster between rounds.\n\nIf you’re serious about improving your golf performance — whether that’s speed, mobility or injury prevention — George is absolutely worth seeing.\n\nGame changer.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25sVllVVXdkaTFmTjNaalMzaHpNa0pZZFZsb1dtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113606073768622629795/reviews?hl=en-GB","posted_at_unix_micros":1772126328345906,"updated_at_unix_micros":1772126328345906,"language":"en","translated_lang":"","text_original":"started seeing George purely to improve my golf performance — and the difference has been huge.\n\nAs a golfer, you know when something isn’t quite firing. I felt tight through my hips and thoracic spine, my rotation was restricted and I wasn’t moving efficiently through the ball. George immediately identified the root cause rather than just treating the symptoms.\n\nHis hands-on work and manipulation freed up areas I didn’t even realise were limiting me. Straight away I felt more mobile, more balanced and more connected. But what really sets him apart is what happens after the treatment.\n\nHe takes you onto the gym floor and shows you the change. We retested movements and you could literally see the improvement in range, control and stability. It wasn’t just “feels better” — it was measurable progress.\n\nHe then gave me specific exercises tailored to my swing, reinforcing the new movement patterns so the gains actually stick.\n\nSince working with him:\n• Improved hip and T-spine rotation\n• Better sequencing through impact\n• More speed without forcing it\n• Less post-round stiffness\n\nI’m moving better, swinging more efficiently and recovering faster between rounds.\n\nIf you’re serious about improving your golf performance — whether that’s speed, mobility or injury prevention — George is absolutely worth seeing.\n\nGame changer.","text_translated":"","reply_text_original":"Thanks so much for the fantastic review, James. I’m thrilled the hands-on work, movement retesting and tailored exercises have delivered measurable gains in hip and T-spine rotation, sequencing, speed and recovery. We pride ourselves on treating the root cause rather than just the symptoms and helping golfers translate those changes into their swing. Looking forward to supporting your continued progress on and off the course.","reply_language":"en","reply_posted_at_unix_micros":1772134186000000,"reply_updated_at_unix_micros":1772134186000000,"published_at":"2026-02-26T17:18:48.345906Z"},{"Name":"S Bartlett","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUXYXrDOHKylKsebnXC9OFJv5gCkm7OlB0u1qIJKVkUM8P4-Kc=s120-c-rp-mo-br100","Rating":5,"Description":"This was my first time seeing Adam, and I came in with quite a lot of pain in my shoulders, and neck.  Adam’s knowledge really stood out, being both a fitness trainer and a sports massage therapist, he clearly understands how the muscles work together. He quickly identified the problem areas and worked through them.  I’d highly recommend Adam to anyone dealing with pain or tightness, he really knows what he’s doing.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25aSU56Rk1VamRSYUhGa1NqWnhiR0ptWVZCUlFtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104380290316723578611/reviews?hl=en-GB","posted_at_unix_micros":1774454516350007,"updated_at_unix_micros":1774454516350007,"language":"en","translated_lang":"","text_original":"This was my first time seeing Adam, and I came in with quite a lot of pain in my shoulders, and neck.  Adam’s knowledge really stood out, being both a fitness trainer and a sports massage therapist, he clearly understands how the muscles work together. He quickly identified the problem areas and worked through them.  I’d highly recommend Adam to anyone dealing with pain or tightness, he really knows what he’s doing.","text_translated":"","reply_text_original":"Thank you so much for your kind review, we are so pleased Adam was able to help you and get to the root cause of the problem causing your neck pain! \n\nIf you need any further support please let us know! We are always here to help\n\nThe Pinnacle Team\n \n","reply_language":"en","reply_posted_at_unix_micros":1774462740000000,"reply_updated_at_unix_micros":1774462740000000,"published_at":"2026-03-25T16:01:56.350007Z"},{"Name":"Mhairi Dora","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKyoo9xbxxOIxOsTaFWctkss7CUP27sgXjismhFPVQ1K-X_LQ=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been using the osteopathy clinic at Pinnacle Fitness and Health Club Whetstone, and I honestly wouldn’t go anywhere else. George has been amazing at fixing my back. He is professional, knowledgeable, and genuinely caring.\nThe space itself is clean, relaxing, and very comfortable, which adds to the overall experience. I would highly recommend Pinnacle and George to anyone suffering with pain or mobility issues.","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21SbWVIbFJObWxFU25kd2VGbFZVeTFOY0U1UFdHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108152063699600212203/reviews?hl=en-GB","posted_at_unix_micros":1766004854439188,"updated_at_unix_micros":1766004854439188,"language":"en","translated_lang":"","text_original":"I’ve been using the osteopathy clinic at Pinnacle Fitness and Health Club Whetstone, and I honestly wouldn’t go anywhere else. George has been amazing at fixing my back. He is professional, knowledgeable, and genuinely caring.\nThe space itself is clean, relaxing, and very comfortable, which adds to the overall experience. I would highly recommend Pinnacle and George to anyone suffering with pain or mobility issues.","text_translated":"","reply_text_original":"Thank you Mhairi, we appreciate the support and so happy we could help you through our osteopathic and sports injury services. Wishing you a very merry Christmas \n\n\n","reply_language":"en","reply_posted_at_unix_micros":1766068229000000,"reply_updated_at_unix_micros":1766068229000000,"published_at":"2025-12-17T20:54:14.439188Z"}]</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="inlineStr"/>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>13</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/F45+Training+Brixton/data=!4m7!3m6!1s0x487605bfc4da9a51:0xaabb102c135f5bdc!8m2!3d51.4717657!4d-0.112938!16s%2Fg%2F11g4gn97f5!19sChIJUZraxL8FdkgR3FtfEywQu6o</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>F45 Training Brixton</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>230-234 Brixton Rd, London SW9 6AH, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–7 pm"],"Monday":["6 am–7:50 pm"],"Saturday":["8 am–12 pm"],"Sunday":["Closed"],"Thursday":["6 am–7:50 pm"],"Tuesday":["6 am–7:50 pm"],"Wednesday":["6 am–7:50 pm"]}</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>https://f45training.com/uk/studio/brixton/</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>+44 7566 793654</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>FVCP+PR London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>148</v>
+      </c>
+      <c r="O106" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>{"1":6,"2":0,"3":0,"4":0,"5":142}</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>51.471766</v>
+      </c>
+      <c r="R106" t="n">
+        <v>-0.112938</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>12302444588582263772</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl6iLm3sqM1ZjPA71UjPmAaPuzDFwX0d-DI98Im254Jefp6rNY8lTkC16IBJ5-eayrGdBalrIuPWjsKjnHFuKSRObNdcSj4rS6taHuzehlnvletmoMsRSN2A8g9JpUCmWs_X0iu=w408-h408-k-no</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>0x487605bfc4da9a51:0xaabb102c135f5bdc</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>ChIJUZraxL8FdkgR3FtfEywQu6o</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>{"id":"116201860325035917084","name":"F45 Training Brixton (Owner)","link":"https://www.google.com/maps/contrib/116201860325035917084"}</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"230-234 Brixton Rd","city":"London","postal_code":"SW9 6AH","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>[{"Name":"Jasmine Schembri","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUCEfdawLSfErVK2cZjBuSo7XRbnq63_GSwkHBRX-3jdspsyZGV=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve joined my fair share of gyms and genuinely nothing compares to F45! An absolutely iconic team - kind, fun and welcoming, awesome workouts, absolute tunes and other great members to train with!\n\nCouldn’t recommend F45 Brixton more :) my only regret is not joining sooner!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pCM09YTnNOa2RoUVhkbk56TTVUeTFsYjFoMlRtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114159513738427034640/reviews?hl=en-GB","posted_at_unix_micros":1772281786965367,"updated_at_unix_micros":1772281861520468,"language":"en","translated_lang":"","text_original":"I’ve joined my fair share of gyms and genuinely nothing compares to F45! An absolutely iconic team - kind, fun and welcoming, awesome workouts, absolute tunes and other great members to train with!\n\nCouldn’t recommend F45 Brixton more :) my only regret is not joining sooner!","text_translated":"","reply_text_original":"Thank you so much, Jasmine! We’re really happy to hear you’re enjoying the workouts and the community.💙 It means a lot to have you with us—see you in class soon! 💪 -F45 Training Brixton\n","reply_language":"en","reply_posted_at_unix_micros":1780488551000000,"reply_updated_at_unix_micros":1780488551000000,"published_at":"2026-02-28T12:29:46.965367Z"},{"Name":"Jean-Pierre Wack","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWt5MetnxamxJhr6jJMmgJwWA17Z4A548pOIJj04FFRzLwfMYC8WQ=s120-c-rp-mo-br100","Rating":5,"Description":"F45 Brixton has an excellent team who are experienced and genuinely helpful throughout both the cardio and resistance phases. I've been attending since the beginning of the year, and it's been instrumental in keeping me consistent with my training. The flexibility of session times and the balanced mix of cardio and resistance work has been incredibly supportive of my fitness goals.\nThe community is welcoming and focused—you can chat if you want to, but most people are there to get their workout done efficiently. They also organise some great socials, which adds to the community feel. I've visited F45 studios in Cambridge, Paris, and Soho, and Brixton genuinely stands out. It's a fantastic space with an outstanding team.","Images":null,"When":"10 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pkcloxRTRkemR0Tm1KTFJHWjFhRVJOYmpOR2JXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105123684814698930477/reviews?hl=en-GB","posted_at_unix_micros":1760606462807681,"updated_at_unix_micros":1760606462807681,"language":"en","translated_lang":"","text_original":"F45 Brixton has an excellent team who are experienced and genuinely helpful throughout both the cardio and resistance phases. I've been attending since the beginning of the year, and it's been instrumental in keeping me consistent with my training. The flexibility of session times and the balanced mix of cardio and resistance work has been incredibly supportive of my fitness goals.\nThe community is welcoming and focused—you can chat if you want to, but most people are there to get their workout done efficiently. They also organise some great socials, which adds to the community feel. I've visited F45 studios in Cambridge, Paris, and Soho, and Brixton genuinely stands out. It's a fantastic space with an outstanding team.","text_translated":"","reply_text_original":"Thanks so much, Jean-Pierre! We really appreciate your kind words. 💙 It means a lot to hear we stand out, especially coming from someone who’s visited other studios. See you in class soon! 💪 -F45 Training Brixton\n","reply_language":"en","reply_posted_at_unix_micros":1780488643000000,"reply_updated_at_unix_micros":1780488643000000,"published_at":"2025-10-16T09:21:02.807681Z"},{"Name":"Eddie Letcher","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocL9QiOgSjylXCKdiqGFvUOsJj-9vX8XABXxRgfMoo1U3AD5Rg=s120-c-rp-mo-br100","Rating":5,"Description":"I joined having never done F45 before and the trainers are super friendly and make you feel so welcome. Been going 3/4 times a week since and seeing the benefits of the workouts!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSb04zSlJTQzFDUkhGUFdtUkNTMUZuZERSVVlsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114497336808800169506/reviews?hl=en-GB","posted_at_unix_micros":1776944767810616,"updated_at_unix_micros":1776944767810616,"language":"en","translated_lang":"","text_original":"I joined having never done F45 before and the trainers are super friendly and make you feel so welcome. Been going 3/4 times a week since and seeing the benefits of the workouts!","text_translated":"","reply_text_original":"Hey Eddie! Thank you so much for your kind review! We’re really glad to hear you felt welcomed from day one and are already seeing the benefits of your training. Keep up the great work—we love having you in class! 💪 -F45 Training Brixton\n","reply_language":"en","reply_posted_at_unix_micros":1780400904000000,"reply_updated_at_unix_micros":1780400904000000,"published_at":"2026-04-23T11:46:07.810616Z"},{"Name":"Leonor Moniz","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXtXnH6In9xZJp7HohSabgBPBy8x8MiiYHYuYgSQfEWzKJPibQ=s120-c-rp-mo-br100","Rating":5,"Description":"The most amazing coaches, great vibes and even better playlist! Would definitely recommend if you want to upgrade your workouts!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tKVlMyVlhOMk41VVVJd1NFZFBOMGhGVUZwbVdIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103897632245533791240/reviews?hl=en-GB","posted_at_unix_micros":1774650561672369,"updated_at_unix_micros":1774650561672369,"language":"en","translated_lang":"","text_original":"The most amazing coaches, great vibes and even better playlist! Would definitely recommend if you want to upgrade your workouts!","text_translated":"","reply_text_original":"Thank you so much for your lovely review, Leonor! We’re really glad you’re enjoying the coaches, vibes, and playlists 🎶💪 Appreciate the recommendation and look forward to seeing you in class again soon! -F45 Training Brixton\n","reply_language":"en","reply_posted_at_unix_micros":1780400972000000,"reply_updated_at_unix_micros":1780400972000000,"published_at":"2026-03-27T22:29:21.672369Z"},{"Name":"Adam Parker","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLHLLvi4eicu-koHRYwl0xzNLZv3Pv7KQky7D8D8KkaXN0zbg=s120-c-rp-mo-br100","Rating":5,"Description":"Recently joined F45 Brixton and it’s great. Very friendly and welcoming atmosphere and the trainers are amazing. Highly recommend giving them a try if you’re considering it!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s5QmVrbFBjalJYVkVNMk9USjNkRkJJYVVKVWNIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114792576750247262169/reviews?hl=en-GB","posted_at_unix_micros":1771163376641776,"updated_at_unix_micros":1771163376641776,"language":"en","translated_lang":"","text_original":"Recently joined F45 Brixton and it’s great. Very friendly and welcoming atmosphere and the trainers are amazing. Highly recommend giving them a try if you’re considering it!","text_translated":"","reply_text_original":"Thanks so much, Adam! Great to hear you’re enjoying F45 Brixton and feeling welcomed by the team 💙 We really appreciate the recommendation and look forward to seeing you in class! 💪 -F45 Training Brixton\n","reply_language":"en","reply_posted_at_unix_micros":1780488589000000,"reply_updated_at_unix_micros":1780488589000000,"published_at":"2026-02-15T13:49:36.641776Z"}]</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="inlineStr"/>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>13</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>c2406c1e-2fba-4c5c-8ab2-a599af517682</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Bootcamp+UK+Bexleyheath+-+Outdoors+Fitness+Classes+in+Bexleyheath/data=!4m7!3m6!1s0x47d8af0ef0c3b5ef:0x8f8f18463392a193!8m2!3d51.4524317!4d0.1554276!16s%2Fg%2F11m0ry8ffh!19sChIJ77XD8A6v2EcRk6GSM0YYj48</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Bootcamp UK Bexleyheath - Outdoors Fitness Classes in Bexleyheath</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Boot camp</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>St Columba’s Catholic Boys School, Halcot Ave, Bexleyheath DA6 7QB, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>{"Friday":["Closed"],"Monday":["Closed"],"Saturday":["Closed"],"Sunday":["8:30–9:30 am"],"Thursday":["7–8 pm"],"Tuesday":["7–8 pm"],"Wednesday":["Closed"]}</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bcuk.uk/all-locations/bexleyheath/</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>+44 7875 443216</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>F524+X5 Bexleyheath, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>146</v>
+      </c>
+      <c r="O107" t="n">
+        <v>5</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":6,"5":140}</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>51.452432</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.155428</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>10344513558885343635</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWldY8n69IySzDURj0oA548rntcCaQSs27dxwaJWz06rz9FCFT-c0envL3n3Hjwh7m6viclFJOD4Bo5PsZUFiK1KussamRYJOVv5MZNLsaDeZ45GCcZxlibMf9V7OMD7APyOyo4=w425-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>0x47d8af0ef0c3b5ef:0x8f8f18463392a193</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>ChIJ77XD8A6v2EcRk6GSM0YYj48</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>[{"link":"https://app.bcuk.uk/","source":"bcuk.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>{"id":"107773513910947304408","name":"Bootcamp UK Bexleyheath - Outdoors Fitness Classes in Bexleyheath (Owner)","link":"https://www.google.com/maps/contrib/107773513910947304408"}</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"St Columba’s Catholic Boys School, Halcot Ave","city":"Bexleyheath","postal_code":"DA6 7QB","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>[{"Name":"Sarah Cook","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJmuBBvnhxHFyB79ekT85QlG6mFsqF8tOV8dlg1-fQsL1tSvQ=s120-c-rp-mo-br100","Rating":5,"Description":"It was my first time tonight and I will definitely be returning. You can make it as easy or as hard as you want to. Both Andy and Gaz are there on hand to push you along and make sure you’re doing it all\nCorrectly. It was very good 😊","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s1TE4xTmpYMVkyUVRsRVdtTjNObVowYm1aMVJXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108406802346865495980/reviews?hl=en-GB","posted_at_unix_micros":1779220327655675,"updated_at_unix_micros":1779220327655675,"language":"en","translated_lang":"","text_original":"It was my first time tonight and I will definitely be returning. You can make it as easy or as hard as you want to. Both Andy and Gaz are there on hand to push you along and make sure you’re doing it all\nCorrectly. It was very good 😊","text_translated":"","reply_text_original":"We love to coach and encourage people to achieve their best. A wonderful first session for you guys \n\nSee you again soon ","reply_language":"en","reply_posted_at_unix_micros":1779224154000000,"reply_updated_at_unix_micros":1779224154000000,"published_at":"2026-05-19T19:52:07.655675Z"},{"Name":"Aneika Davis","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocI4OPoXWOtxAKDuJPyTk97KOPUi7ZJeaEQZO5xIm77JYbOhaQ=s120-c-rp-mo-br100","Rating":5,"Description":"Great first session even though my body is burning😅Andy and everyone was great and welcoming. Loved the vibes, will be seeing me every week😁","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2taNVpEQmFUVEJ6ZW5keWFtSm1iM2RJV1dWWmVWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102172488032299305888/reviews?hl=en-GB","posted_at_unix_micros":1776804287608730,"updated_at_unix_micros":1776804520022953,"language":"en","translated_lang":"","text_original":"Great first session even though my body is burning😅Andy and everyone was great and welcoming. Loved the vibes, will be seeing me every week😁","text_translated":"","reply_text_original":"Let’s do this - always put on a good show haha","reply_language":"en","reply_posted_at_unix_micros":1776841219000000,"reply_updated_at_unix_micros":1776841219000000,"published_at":"2026-04-21T20:44:47.60873Z"},{"Name":"Charlotte Laxton","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVXQptcQaAH37q_S_GZvME-lpJNtQ6G0KRmG72BbUtfVU_O_tFDqA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great first session at boot camp, Andy was great and explained everything. The group was encouraging and kept a fun atmosphere. I'll be back next week - if my muscles still function!","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25sV1IzUk5WVXBGUzNwdk5TMW5SM1ZrTW5CTFZsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114113674532594779108/reviews?hl=en-GB","posted_at_unix_micros":1767524053662730,"updated_at_unix_micros":1767524053662730,"language":"en","translated_lang":"","text_original":"Great first session at boot camp, Andy was great and explained everything. The group was encouraging and kept a fun atmosphere. I'll be back next week - if my muscles still function!","text_translated":"","reply_text_original":"Love this Charlotte! Rather chilly but fun start to 2026 that’s for sure. See you again soon \n","reply_language":"en","reply_posted_at_unix_micros":1767532167000000,"reply_updated_at_unix_micros":1768400242000000,"published_at":"2026-01-04T10:54:13.66273Z"},{"Name":"Emma Narine","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUNvN2kklwJPeZS2zG7QPeH6VLTwYMfGZ4N99ULGB2jxDqIu1hv=s120-c-rp-mo-br100","Rating":5,"Description":"I've not been going for long, but I am really enjoying it. It's great to be outdoors and everyone is friendly. The workouts are varied each session and I'm toning muscles I never realised I had. Everyone is on their own fitness journey from absolute beginners to advanced, but if you're just starting out, you can of course modify to suit your own abilities.","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT210c1ZrTkhXREE1ZUdNdE5UUnBkRXQ1Wms0emRVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110716174450987606507/reviews?hl=en-GB","posted_at_unix_micros":1753293340470006,"updated_at_unix_micros":1753293426338287,"language":"en","translated_lang":"","text_original":"I've not been going for long, but I am really enjoying it. It's great to be outdoors and everyone is friendly. The workouts are varied each session and I'm toning muscles I never realised I had. Everyone is on their own fitness journey from absolute beginners to advanced, but if you're just starting out, you can of course modify to suit your own abilities.","text_translated":"","reply_text_original":"Love this Emma! Thank you! We cater for everyone with our classes and just ask that people give things a try. Be bold and brave and you get your rewards ","reply_language":"en","reply_posted_at_unix_micros":1753303151000000,"reply_updated_at_unix_micros":1753303151000000,"published_at":"2025-07-23T17:55:40.470006Z"},{"Name":"Chloe Friebel","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJK-Q0-i2qavXLKqvQlB-tkBknxmK03xuNGxOtBoeofS1pi0w=s120-c-rp-mo-br100","Rating":5,"Description":"I had my first session tonight and absolutely loved it!! The instructors are so welcoming and supportive which made the whole experience such a positive one! Such a great way to keep fit, I can’t wait for next week. Not looking forward to the aches and pains in the morning 😂\nThank you Andy and Gazza","Images":null,"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnTUN3bzVMWDBnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114588413596746557976/reviews?hl=en-GB","posted_at_unix_micros":1742506105155997,"updated_at_unix_micros":1742506105155997,"language":"en","translated_lang":"","text_original":"I had my first session tonight and absolutely loved it!! The instructors are so welcoming and supportive which made the whole experience such a positive one! Such a great way to keep fit, I can’t wait for next week. Not looking forward to the aches and pains in the morning 😂\nThank you Andy and Gazza","text_translated":"","reply_text_original":"Love this! We are always there to supper, encourage and coach you to great things. The group dynamic is awesome and who can’t enjoy filling tyres and throwing barrels around? Haha see you again soon ","reply_language":"en","reply_posted_at_unix_micros":1742506848000000,"reply_updated_at_unix_micros":1742506848000000,"published_at":"2025-03-20T21:28:25.155997Z"}]</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="inlineStr"/>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>13</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/F45+Training+Fulham/data=!4m7!3m6!1s0x48760f852981bf4f:0xc66e320c940ff0e7!8m2!3d51.4823802!4d-0.1997773!16s%2Fg%2F11hbv2yyvv!19sChIJT7-BKYUPdkgR5_APlAwybsY</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>F45 Training Fulham</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>423 North End Rd, London SW6 1NY, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–2 pm","5:30–7:45 pm"],"Monday":["6 am–2 pm","5:30–7:45 pm"],"Saturday":["9–11 am"],"Sunday":["9–11 am"],"Thursday":["6 am–2 pm","5:30–7:45 pm"],"Tuesday":["6 am–2 pm","5:30–7:45 pm"],"Wednesday":["6 am–2 pm","5:30–7:45 pm"]}</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>https://f45training.com/uk/studio/fulham/</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>+44 7475 718319</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>FRJ2+X3 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>133</v>
+      </c>
+      <c r="O108" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>{"1":4,"2":1,"3":1,"4":1,"5":126}</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>51.48238</v>
+      </c>
+      <c r="R108" t="n">
+        <v>-0.199777</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>14298420896552972519</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gym with intensive cardio classes</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Fitness center featuring high-intensity cardio &amp; resistance training sessions.</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmWAddkbigOFvi_7b-_H5vKS6cTIEYRjhLUeYIWcPdGIbBHmfz0ujhK0CCPlbrE2N19rp4ZxKTzAcCntQXEUBRWJUgbVXuoSWo-ZJEO7vNljIRuUSIO8pP1vXa7fwX-w0ytCvBMBHxpol8=w408-h611-k-no</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>0x48760f852981bf4f:0xc66e320c940ff0e7</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>ChIJT7-BKYUPdkgR5_APlAwybsY</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>{"id":"110573467635475674415","name":"F45 Training Fulham (Owner)","link":"https://www.google.com/maps/contrib/110573467635475674415"}</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"423 North End Rd","city":"London","postal_code":"SW6 1NY","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>[{"Name":"Tom Riis-Bristow","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocISLYrO08JImWEMc55NZmM77eiKmp18mYCCffnMJKg8FwBINQ=s120-c-rp-mo-br100","Rating":5,"Description":"F45 Fulham is a great gym and very inclusive with a strong community vibe. I have been doing functional fitness for several years now, and I just couldn't go back to working out at a standard gym. Group PT/functional fitness has been so much better for my mental and physical health. Any gym like this is only ever as good as its team and all the coaches are super friendly/passionate about your progression, and push you to continue to improve. Highly recommend coming in for their trial sessions and seeing for yourself. Alongside classes, there are always events, activities and socials going on. Give this place a try, you will not regret it!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pOUVVGbzJUVTV3VlhScFJGcHNPREpqU3pSU05tYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112594809220287613406/reviews?hl=en-GB","posted_at_unix_micros":1778674247560778,"updated_at_unix_micros":1778674247560778,"language":"en","translated_lang":"","text_original":"F45 Fulham is a great gym and very inclusive with a strong community vibe. I have been doing functional fitness for several years now, and I just couldn't go back to working out at a standard gym. Group PT/functional fitness has been so much better for my mental and physical health. Any gym like this is only ever as good as its team and all the coaches are super friendly/passionate about your progression, and push you to continue to improve. Highly recommend coming in for their trial sessions and seeing for yourself. Alongside classes, there are always events, activities and socials going on. Give this place a try, you will not regret it!","text_translated":"","published_at":"2026-05-13T12:10:47.560778Z"},{"Name":"Rory Hardisty","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKsp7sBLDS8Tpmjey8c-EFyntW5ZO4lqrgJAsWqadV1q7DwAg=s120-c-rp-mo-br100","Rating":5,"Description":"Brilliant gym and class variety. Jen really helped improve my deadlift technique midway through a busy class. Great vibes and training 👌","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25vemFFSnpYMUZ0YmxkUVkwUnliVVYyUzNwWFptYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118437674847736656672/reviews?hl=en-GB","posted_at_unix_micros":1780672457079707,"updated_at_unix_micros":1780672457079707,"language":"en","translated_lang":"","text_original":"Brilliant gym and class variety. Jen really helped improve my deadlift technique midway through a busy class. Great vibes and training 👌","text_translated":"","published_at":"2026-06-05T15:14:17.079707Z"},{"Name":"yassi akbari","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUO6YMTp1YtntP7SX5HUHA4hdea6EI7KuJD9-JmAKYai4flmxVSZg=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been doing F45 for the last eight years — starting at F45 OC, then Soho, and for the past year at F45 Fulham. The team at F45 Fulham is exceptional. Every trainer is welcoming, knowledgeable, and genuinely invested in helping members improve, no matter their fitness level. Their attentiveness, encouragement, and energy create an environment where you feel supported, motivated, and pushed in exactly the right way.\n\nThe staff go above and beyond to make each session engaging and fun, correcting form, offering modifications, and celebrating progress. F45 has completely changed the way I look at exercise — what once felt like a chore is now an absolute joy, and I genuinely look forward to my alarm going off for the 6:10am classes. I can’t recommend F45 Fulham and its incredible team highly enough.","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tGSGVHUmFUSEpUZEcxdVREQnphekZETlhwZk1GRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100802892059490843284/reviews?hl=en-GB","posted_at_unix_micros":1765793491011134,"updated_at_unix_micros":1765793491011134,"language":"en","translated_lang":"","text_original":"I’ve been doing F45 for the last eight years — starting at F45 OC, then Soho, and for the past year at F45 Fulham. The team at F45 Fulham is exceptional. Every trainer is welcoming, knowledgeable, and genuinely invested in helping members improve, no matter their fitness level. Their attentiveness, encouragement, and energy create an environment where you feel supported, motivated, and pushed in exactly the right way.\n\nThe staff go above and beyond to make each session engaging and fun, correcting form, offering modifications, and celebrating progress. F45 has completely changed the way I look at exercise — what once felt like a chore is now an absolute joy, and I genuinely look forward to my alarm going off for the 6:10am classes. I can’t recommend F45 Fulham and its incredible team highly enough.","text_translated":"","reply_text_original":"Thank you so much for your review! We love having you with us! \u003c3 ","reply_language":"en","reply_posted_at_unix_micros":1778226782000000,"reply_updated_at_unix_micros":1778226782000000,"published_at":"2025-12-15T10:11:31.011134Z"},{"Name":"Ella Stephen","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUH62dAWXqFSjxdG5FFzwpiAvkMON-aK2YIjeU09GaNyeOfLg-y=s120-c-rp-mo-br100","Rating":5,"Description":"The vibes are high at Fulham f45!!!\nSuch a welcome team \u0026 members.\nI joined as a none regular gym goer \u0026 the coaches helped me feel so looked after \u0026 pushed me to my goals of strength alongside running! Couldn’t recommend enough","Images":null,"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xCT00xZzRSMVJyUjFoMlNEUkdUMDVzU0U5WVgyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107167591398227847205/reviews?hl=en-GB","posted_at_unix_micros":1765483007569849,"updated_at_unix_micros":1765483007569849,"language":"en","translated_lang":"","text_original":"The vibes are high at Fulham f45!!!\nSuch a welcome team \u0026 members.\nI joined as a none regular gym goer \u0026 the coaches helped me feel so looked after \u0026 pushed me to my goals of strength alongside running! Couldn’t recommend enough","text_translated":"","reply_text_original":"Thank you!! So glad you enjoy F45 Fulham!! ","reply_language":"en","reply_posted_at_unix_micros":1778226860000000,"reply_updated_at_unix_micros":1778226860000000,"published_at":"2025-12-11T19:56:47.569849Z"},{"Name":"Martha McCabe","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK5Y0GGx29olxStUsktxON5OYdEVjG1UKVMRo3HPLGgIxK6=s120-c-rp-mo-br100","Rating":5,"Description":"I absolutely love training at F45 Fulham! The atmosphere is so welcoming, and Jenny, Ben, and Alfie are always friendly, chatty, and full of positive energy. They’re incredibly supportive and really help you stay focused on your goals. Since joining, I’ve noticed such a big difference in how much stronger and fitter I feel. Highly recommend!","Images":null,"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25GeVVXaDNjM0ZJWkVGb00wcHJRMHcxVVRseE1XYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116199167073374847393/reviews?hl=en-GB","posted_at_unix_micros":1765460665411903,"updated_at_unix_micros":1765460665411903,"language":"en","translated_lang":"","text_original":"I absolutely love training at F45 Fulham! The atmosphere is so welcoming, and Jenny, Ben, and Alfie are always friendly, chatty, and full of positive energy. They’re incredibly supportive and really help you stay focused on your goals. Since joining, I’ve noticed such a big difference in how much stronger and fitter I feel. Highly recommend!","text_translated":"","reply_text_original":"Thank you so much, this has made our day! ","reply_language":"en","reply_posted_at_unix_micros":1778226924000000,"reply_updated_at_unix_micros":1778226924000000,"published_at":"2025-12-11T13:44:25.411903Z"}]</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>13</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>c2406c1e-2fba-4c5c-8ab2-a599af517682</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/The+Common+Purpose+Club/data=!4m7!3m6!1s0x48761be014995183:0xfbf2e294c989367d!8m2!3d51.5074867!4d-0.1442828!16s%2Fg%2F11h6yqxgyw!19sChIJg1GZFOAbdkgRfTaJyZTi8vs</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>The Common Purpose Club</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>10 Stratton St, London W1J 8LG, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:30 am–7 pm"],"Monday":["6:30 am–8 pm"],"Saturday":["8 am–2 pm"],"Sunday":["Closed"],"Thursday":["6:30 am–8 pm"],"Tuesday":["6:30 am–8 pm"],"Wednesday":["6:30 am–8 pm"]}</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>https://commonpurposeclub.co.uk/</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>+44 20 3336 3440</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>GV44+X7 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>132</v>
+      </c>
+      <c r="O109" t="n">
+        <v>5</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":0,"3":1,"4":0,"5":130}</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>51.507487</v>
+      </c>
+      <c r="R109" t="n">
+        <v>-0.144283</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>18154822176548140669</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWltUaY8rdwSXUl4xQPjVknM9Xa9Zy0Ie31qZ8cSt0KVplW_rqN1i7aqclxkny9CyoyHZRGpq57CiigSM-fznxrUgdknGEag4ZR4Uk4DC8po1Rj40zlH_q9iBsKxiAyhyedjMGps=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>0x48761be014995183:0xfbf2e294c989367d</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>ChIJg1GZFOAbdkgRfTaJyZTi8vs</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>{"id":"102851647686473848627","name":"The Common Purpose Club (Owner)","link":"https://www.google.com/maps/contrib/102851647686473848627"}</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"10 Stratton St","city":"London","postal_code":"W1J 8LG","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible toilet","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible seating","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>[{"Name":"David Khabie-Zeitoune","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVc3InjsfURD-2ZSltA874tv3auPGhIwauHBT201CUR-76btexu0Q=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Excellent private gym offering personal training in one-to-one or small group shared format. Facilities are superb (they even have a rare pendulum squat machine - excellent for rehab!). What really singles this place out though is the exceptional quality of the trainers.  I’ve known Tiago, one of the founders, for over a decade, and he has built a team who all combine a rigorous understanding of sports and nutrition science with a practical mastery of technique and an ability to adapt it to each client’s specific needs.\n\nWe have a corporate relationship with them too as our offices are on the same street. They organise small group personal training sessions for our staff several times a week, and annual summer games to bring out the competitive spirit, as well as a regular programme of talks and other events on health and wellbeing.\n\nCouldn’t recommend more!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pKU09HNXFZMjFLY1RGRFRWWXlVRkYxU0VFd2JsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106143997925064844545/reviews?hl=en-GB","posted_at_unix_micros":1784364800079817,"updated_at_unix_micros":1784364800079817,"language":"en","translated_lang":"","text_original":"Excellent private gym offering personal training in one-to-one or small group shared format. Facilities are superb (they even have a rare pendulum squat machine - excellent for rehab!). What really singles this place out though is the exceptional quality of the trainers.  I’ve known Tiago, one of the founders, for over a decade, and he has built a team who all combine a rigorous understanding of sports and nutrition science with a practical mastery of technique and an ability to adapt it to each client’s specific needs.\n\nWe have a corporate relationship with them too as our offices are on the same street. They organise small group personal training sessions for our staff several times a week, and annual summer games to bring out the competitive spirit, as well as a regular programme of talks and other events on health and wellbeing.\n\nCouldn’t recommend more!","text_translated":"","published_at":"2026-07-18T08:53:20.079817Z"},{"Name":"Allison Ford","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJNisU1jd8cuEYgcMK9fwdF7PN_lFZnD3Uhy6KjXGG2VcxKoA=s120-c-rp-mo-br100","Rating":5,"Description":"I can’t say enough nice things about Common Purpose and the team. I walked into CP with physical fitness goals but I left with a different relationship with my body and the way I think about strength. The whole team is exceptional and makes it a group mission to understand every clients unique journey and to be able to step in at anytime with anyone. Natalia and Oli are two of my favorite humans and are incredibly credentialed, knowledgable, and kind and worked with me to heal past injuries.This is the ultimate personal fitness gym and this is not just a “get fit” gym- this is a change the trajectory of your health gym.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25odGVtc3dUazlSTm10Sk1XaEhaa3RDYlhoUE9XYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114264028449544446877/reviews?hl=en-GB","posted_at_unix_micros":1780928877793248,"updated_at_unix_micros":1780928877793248,"language":"en","translated_lang":"","text_original":"I can’t say enough nice things about Common Purpose and the team. I walked into CP with physical fitness goals but I left with a different relationship with my body and the way I think about strength. The whole team is exceptional and makes it a group mission to understand every clients unique journey and to be able to step in at anytime with anyone. Natalia and Oli are two of my favorite humans and are incredibly credentialed, knowledgable, and kind and worked with me to heal past injuries.This is the ultimate personal fitness gym and this is not just a “get fit” gym- this is a change the trajectory of your health gym.","text_translated":"","published_at":"2026-06-08T14:27:57.793248Z"},{"Name":"Danna velasquez","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIc9TE4-nS1nv8Y30AOwHh60777Fsxg5XoNsxNuK586CyEcrg=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been training at The Common Purpose Club for over a year now, mainly with Natalia, and I honestly couldn’t be happier with my experience. She is an incredible trainer — dedicated, motivating, and genuinely attentive to every person she works with.\n\nWhat I appreciate most is how much she truly understands her clients. She constantly challenges me in a way that feels encouraging and sustainable, always taking into account my knee issues and adapting exercises so I can keep progressing safely. Thanks to her guidance and consistency, I feel much stronger and more confident than when I first started.\n\nYou can tell Natalia puts real care and effort into every session and every individual. The environment at the club is supportive, welcoming, and motivating, which has made it so much easier to stay committed over time. I’m genuinely grateful for everything she’s helped me achieve this past year.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2t4UWNEQnlXSFJHVmtKT2IwbHhkM2hSVWxjMmRVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117706180321457148703/reviews?hl=en-GB","posted_at_unix_micros":1779472770833505,"updated_at_unix_micros":1779472770833505,"language":"en","translated_lang":"","text_original":"I’ve been training at The Common Purpose Club for over a year now, mainly with Natalia, and I honestly couldn’t be happier with my experience. She is an incredible trainer — dedicated, motivating, and genuinely attentive to every person she works with.\n\nWhat I appreciate most is how much she truly understands her clients. She constantly challenges me in a way that feels encouraging and sustainable, always taking into account my knee issues and adapting exercises so I can keep progressing safely. Thanks to her guidance and consistency, I feel much stronger and more confident than when I first started.\n\nYou can tell Natalia puts real care and effort into every session and every individual. The environment at the club is supportive, welcoming, and motivating, which has made it so much easier to stay committed over time. I’m genuinely grateful for everything she’s helped me achieve this past year.","text_translated":"","published_at":"2026-05-22T17:59:30.833505Z"},{"Name":"Amalia Rebegea","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX5p6jYHmueUm0eW07U0pmUtpK-b4LsAg6gOiQnixsCqmIBR3c_=s120-c-rp-mo-br100","Rating":5,"Description":"After training here for over a year I can honestly say Common Purpose has been one of the best gyms I've ever been to. The entire team is super friendly and knowledgeable and create a great atmosphere while pushing you to get better.\nMy journey with Natalia has been fantastic, she has been amazing at creating a sense of community in our small group sessions and always coming up with a great variety of exercises to keep us engaged. While I was struggling with back and wrist injuries she was always able to work around them with different variations and the training helped so much with healing over time. Would warmly recommend Common Purpose!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25aMk9HSTRWQzE0VFVsUVQzaFRWazFJZGpKa1puYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102262466992491565533/reviews?hl=en-GB","posted_at_unix_micros":1773778301402450,"updated_at_unix_micros":1773778301402450,"language":"en","translated_lang":"","text_original":"After training here for over a year I can honestly say Common Purpose has been one of the best gyms I've ever been to. The entire team is super friendly and knowledgeable and create a great atmosphere while pushing you to get better.\nMy journey with Natalia has been fantastic, she has been amazing at creating a sense of community in our small group sessions and always coming up with a great variety of exercises to keep us engaged. While I was struggling with back and wrist injuries she was always able to work around them with different variations and the training helped so much with healing over time. Would warmly recommend Common Purpose!","text_translated":"","published_at":"2026-03-17T20:11:41.40245Z"},{"Name":"Anuj Talati","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ6dbu8J8pRjKz0SsbOWi4EkUkfqM1jtO0cU8Fyv143-s1FhA=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been training at this gym for nearly a year now, and I genuinely can’t recommend it highly enough. From day one, the environment has been incredibly supportive, welcoming, and consistent — something that has made a huge difference in my ability to stay motivated and committed.\n\nThe entire team has played a role in helping me achieve my goals. They know exactly when to push and challenge me, while also celebrating progress (big and small) and making me feel capable of continually improving. I’ve never felt judged — only encouraged.\n\nA special mention to Natalia who has been an invaluable resource, as well as Oli, Tiago, and many others who have each contributed in their own way to my journey. Their knowledge, energy, and genuine care for their clients really stand out, and it shows in the culture they’ve created.\n\nIf you’re looking for a personal training gym where you’ll feel supported, challenged, and truly invested in, this is the place. I’m incredibly grateful for the progress I’ve made here and for the team that made it possible.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2paNGNraFNYek5ZVjNoTk0wNXVSRkYyTFMxUVJsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110232887409046826394/reviews?hl=en-GB","posted_at_unix_micros":1768401664816984,"updated_at_unix_micros":1768401664816984,"language":"en","translated_lang":"","text_original":"I’ve been training at this gym for nearly a year now, and I genuinely can’t recommend it highly enough. From day one, the environment has been incredibly supportive, welcoming, and consistent — something that has made a huge difference in my ability to stay motivated and committed.\n\nThe entire team has played a role in helping me achieve my goals. They know exactly when to push and challenge me, while also celebrating progress (big and small) and making me feel capable of continually improving. I’ve never felt judged — only encouraged.\n\nA special mention to Natalia who has been an invaluable resource, as well as Oli, Tiago, and many others who have each contributed in their own way to my journey. Their knowledge, energy, and genuine care for their clients really stand out, and it shows in the culture they’ve created.\n\nIf you’re looking for a personal training gym where you’ll feel supported, challenged, and truly invested in, this is the place. I’m incredibly grateful for the progress I’ve made here and for the team that made it possible.","text_translated":"","published_at":"2026-01-14T14:41:04.816984Z"}]</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="inlineStr"/>
+      <c r="AN109" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>13</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Your+PT+Hub/data=!4m7!3m6!1s0x48761b8ad1a8c08d:0x993981ffbac92e73!8m2!3d51.532135!4d-0.0958722!16s%2Fg%2F11rn5j50bj!19sChIJjcCo0YobdkgRcy7Juv-BOZk</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Your PT Hub</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Unit 9, Your PT Hub, 44-48 Wharf Rd, London N1 7UX, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–10 pm"],"Monday":["6 am–10 pm"],"Saturday":["6 am–10 pm"],"Sunday":["6 am–10 pm"],"Thursday":["6 am–10 pm"],"Tuesday":["6 am–10 pm"],"Wednesday":["6 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>http://www.yourpthub.com/</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>+44 7702 991192</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>GWJ3+VM London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>128</v>
+      </c>
+      <c r="O110" t="n">
+        <v>5</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":0,"5":128}</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>51.532135</v>
+      </c>
+      <c r="R110" t="n">
+        <v>-0.095872</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>11040998896825871987</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm3-1glGHcb3fvfQF-CcHcN-fukIlEXrK6AdcmrE_sL8q2q6oam8dKJ_WisKRygtJxEVCqVpQaLGxh7O9MTvv4NlTiadHgXCJObe_pyVLv1wct1pvofJzef4m0LawX7b2gqPJZTUw=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>0x48761b8ad1a8c08d:0x993981ffbac92e73</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>ChIJjcCo0YobdkgRcy7Juv-BOZk</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>{"id":"116318261582800902315","name":"Your PT Hub (Owner)","link":"https://www.google.com/maps/contrib/116318261582800902315"}</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Unit 9, 44-48 Wharf Rd","city":"London","postal_code":"N1 7UX","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible seating","enabled":true},{"name":"Assistive hearing loop","enabled":false},{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false},{"name":"Wheelchair-accessible toilet","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>[{"Name":"Joli Nagy","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXpNDh2S8QuBOckqRBiEHhgyMiv73bE5-ZtzBGioYf0XCGhTno=s120-c-rp-mo-br100","Rating":5,"Description":"Your PT Hub is a great professional studio with very well equipped machines, free weights and cable machine plus cardio machines. Loved working alongside with all the other coaches too. Everyone is very friendly, knowledgeable and professional. It is a safe space for everyone. And I can only speak highly of Nick, the owner of Your PT Hub.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPnVg_PlNJEK77IM0QAw6npnn43ZHtDLfNFnUKRkS_IoNfkS-YEwd5rZrmSPu5CmkqCUtkTpZH8ba_etOIexcb5mB5YjmTTDpcav3Nb068zEX2X78TWisE8j42thj8fKL4pMHZB5SI82abF=k-no"],"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2trd1ZFRjFRM1l0WTJ0dWRrMTViVGRQUm1GblRWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104769019000000104251/reviews?hl=en-GB","posted_at_unix_micros":1768249257672212,"updated_at_unix_micros":1768249257672212,"language":"en","translated_lang":"","text_original":"Your PT Hub is a great professional studio with very well equipped machines, free weights and cable machine plus cardio machines. Loved working alongside with all the other coaches too. Everyone is very friendly, knowledgeable and professional. It is a safe space for everyone. And I can only speak highly of Nick, the owner of Your PT Hub.","text_translated":"","reply_text_original":"Thank you for the amazing review! We miss you and really hope you come back soon. You’re an incredible trainer and person, we wish you every success with the new career path. ","reply_language":"en","reply_posted_at_unix_micros":1768257331000000,"reply_updated_at_unix_micros":1768257331000000,"published_at":"2026-01-12T20:20:57.672212Z"},{"Name":"Souaf Mehdi","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUySrfjPq-DMsVb4oB0gsRTaUAlbp5NLYEXVwHWZIiE2qOx9NBD=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been bringing a group of 15 clients to YOURPTHUB regularly, and the experience has been consistently excellent. The facility is clean, well-equipped, and perfectly set up for both personal training and small group sessions.\n\nWhat really sets it apart is the professionalism and the atmosphere — it’s a space that allows coaches to deliver high-quality sessions while making clients feel comfortable, focused, and motivated. The layout is ideal for structured programming, whether you’re working on strength, conditioning, or functional training.\n\nA standout feature is the beautiful terrace overlooking the river — a unique touch that elevates the whole experience. It’s perfect for a breather between sessions or even integrating outdoor elements into training when the weather allows.\n\nFrom a coach’s perspective, it’s reliable, flexible, and supports business growth. From a client’s perspective, it’s an environment where they can train seriously and see real results.\n\nHighly recommend YOURPTHUB to any coach looking for a premium training space in London.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2paclpsQjVOa2xTTjFsblJFZEpOQzEyYzFnNFNYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117276124700837902208/reviews?hl=en-GB","posted_at_unix_micros":1775838124088157,"updated_at_unix_micros":1775838124088157,"language":"en","translated_lang":"","text_original":"I’ve been bringing a group of 15 clients to YOURPTHUB regularly, and the experience has been consistently excellent. The facility is clean, well-equipped, and perfectly set up for both personal training and small group sessions.\n\nWhat really sets it apart is the professionalism and the atmosphere — it’s a space that allows coaches to deliver high-quality sessions while making clients feel comfortable, focused, and motivated. The layout is ideal for structured programming, whether you’re working on strength, conditioning, or functional training.\n\nA standout feature is the beautiful terrace overlooking the river — a unique touch that elevates the whole experience. It’s perfect for a breather between sessions or even integrating outdoor elements into training when the weather allows.\n\nFrom a coach’s perspective, it’s reliable, flexible, and supports business growth. From a client’s perspective, it’s an environment where they can train seriously and see real results.\n\nHighly recommend YOURPTHUB to any coach looking for a premium training space in London.","text_translated":"","reply_text_original":"Thank you for the amazing review! We love having you and your clients at the Hub. You’re a fantastic trainer and it is clear why you’re very well liked! Thank you for everything you do at the Hub! ","reply_language":"en","reply_posted_at_unix_micros":1775849133000000,"reply_updated_at_unix_micros":1775849133000000,"published_at":"2026-04-10T16:22:04.088157Z"},{"Name":"Rohan Bhatia","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJp89M2KcLcImXU8EFAsHuKToGa1sLereGqx5TvQq3QTh7v-GA=s120-c-rp-mo-br100","Rating":5,"Description":"Excellent gym with attentive and knowledgeable PTs. The space is well equipped and consists of only PTs and their clients so it’s a really good gym for beginners and those who want to focus on strength training. I’ve been training with Nick (who is also the owner) and had amazing results in the past year!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xoeGFWQkVkRWd6WDBaaFdIZFFOVGt5ZEVSaVpFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115025978285582772402/reviews?hl=en-GB","posted_at_unix_micros":1779027731903660,"updated_at_unix_micros":1779027731903660,"language":"en","translated_lang":"","text_original":"Excellent gym with attentive and knowledgeable PTs. The space is well equipped and consists of only PTs and their clients so it’s a really good gym for beginners and those who want to focus on strength training. I’ve been training with Nick (who is also the owner) and had amazing results in the past year!","text_translated":"","reply_text_original":"Thank you for the amazing review. We’ve loved having you at the hub. Keep up the hard work 💪","reply_language":"en","reply_posted_at_unix_micros":1779028164000000,"reply_updated_at_unix_micros":1779028164000000,"published_at":"2026-05-17T14:22:11.90366Z"},{"Name":"Vinny Rock","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKTb0Q1nXYg32xeZY-OsPH_pmjsmbdKefGrN4HSkWHOrhHz0g=s120-c-rp-mo-br100","Rating":5,"Description":"​\"Absolute game-changer of a gym! The studio itself is top-tier, and the trainers are true experts who know exactly how to push you while keeping it fun. Beyond just the killer workouts, they’ve cultivated an genuinely welcoming community. It’s an incredible environment—not just for crushing your fitness goals, but also for networking and connecting with other driven professionals. Highly recommend!\"","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSNlJ6VllVamR6V0RkZlpDMXhUWEUwUWpWalluYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116199257267366278387/reviews?hl=en-GB","posted_at_unix_micros":1785351141430741,"updated_at_unix_micros":1785351141430741,"language":"en","translated_lang":"","text_original":"​\"Absolute game-changer of a gym! The studio itself is top-tier, and the trainers are true experts who know exactly how to push you while keeping it fun. Beyond just the killer workouts, they’ve cultivated an genuinely welcoming community. It’s an incredible environment—not just for crushing your fitness goals, but also for networking and connecting with other driven professionals. Highly recommend!\"","text_translated":"","reply_text_original":"Thank you for the amazing review! Keep up the hard work 😊","reply_language":"en","reply_posted_at_unix_micros":1785351622000000,"reply_updated_at_unix_micros":1785351622000000,"published_at":"2026-07-29T18:52:21.430741Z"},{"Name":"Iona Bernard","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUd1DowxNnm7Wc3DoVUcnrRLB3lL-kyxh3iPFxNBchIhgMK_8o=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Your PT Hub is a wonderful wellness space that offers excellent PT sessions, as well as osteo and physio treatments.The team strives to give you the best experience and is very friendly. I highly recommend joining this gym, it's a gem in Angel.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSbk5IWkZTM1JpYmpOWFJGSnhWSFJVYldsSGRXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110537149633376179251/reviews?hl=en-GB","posted_at_unix_micros":1778957124316297,"updated_at_unix_micros":1778957124316297,"language":"en","translated_lang":"","text_original":"Your PT Hub is a wonderful wellness space that offers excellent PT sessions, as well as osteo and physio treatments.The team strives to give you the best experience and is very friendly. I highly recommend joining this gym, it's a gem in Angel.","text_translated":"","reply_text_original":"Thank you for the amazing review. We love having you onboard at the Hub. Keep up the amazing work you do!","reply_language":"en","reply_posted_at_unix_micros":1778957329000000,"reply_updated_at_unix_micros":1778957329000000,"published_at":"2026-05-16T18:45:24.316297Z"}]</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr"/>
+      <c r="AM110" t="inlineStr"/>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>13</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Boom+Cycle+%26+Reformcore+-+Hammersmith/data=!4m7!3m6!1s0x48760fb7d7c687f3:0xd27bbc733e9c3e4a!8m2!3d51.493801!4d-0.2257094!16s%2Fg%2F11dyn9dwym!19sChIJ84fG17cPdkgRSj6cPnO8e9I</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Boom Cycle &amp; Reformcore - Hammersmith</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Indoor cycling</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>10 Hammersmith Grove, London W6 0ND, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:45 am–2:30 pm","4:30–8:30 pm"],"Monday":["6:45 am–8:30 pm"],"Saturday":["7:45 am–3:15 pm"],"Sunday":["7:45 am–2:45 pm"],"Thursday":["6:45 am–2:30 pm","4–8:30 pm"],"Tuesday":["6:45 am–2:30 pm","3:30–8:30 pm"],"Wednesday":["6:45 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>http://thecommonbond.co/boom-cycle</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>+44 20 3376 0879</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>FQVF+GP London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>127</v>
+      </c>
+      <c r="O111" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>{"1":10,"2":1,"3":2,"4":9,"5":105}</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>51.493801</v>
+      </c>
+      <c r="R111" t="n">
+        <v>-0.225709</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>15166923373257965130</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmXD0JIH7-7lNkrOeH3rZsPQoskynCjeW2omG_bcJggyVoTXgUze1pVrwuBpYSdO5dMT0uALjgoqPAZD4Najs5tj97pW-esX0T-UOgwB3Jlxrq1YSOyr1A7nde71mV5IqzL0XjP_Q=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>0x48760fb7d7c687f3:0xd27bbc733e9c3e4a</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>ChIJ84fG17cPdkgRSj6cPnO8e9I</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr"/>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.mindbodyonline.com/explore/locations/boom-cycle-hammersmith?rwg_token=AE37R_junTQvLSpqL5QRP4S9sStfdDB1YGUBeYN5tNwwIwenq1FblSIhOyMLnTr7h3qkwWz4_FLX--03EyiOsDGzlZxBG_22GAp4ufZTvGGJIkaS2CSqvLE%3D","source":"mindbodyonline.com"}]</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>{"id":"117754461861581388331","name":"Boom Cycle \u0026 Reformcore - Hammersmith (Owner)","link":"https://www.google.com/maps/contrib/117754461861581388331"}</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"10 Hammersmith Grove","city":"London","postal_code":"W6 0ND","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr"/>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>[{"Name":"Colleen Taylor","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXdNQ7bx6gmNHV59jK7JQug4OXngB2Oj9I77r9L3lnigT1xEYU=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"We were visiting from the States for 2 weeks and staying in Hammersmith and I wanted to keep up with my workouts. I work at a Pilates studio in Colorado and also belong to a spin studio. I happened upon Boom Cycle and Reformcore and it was a short walk from our flat. The classes are amazing and the instructors are wonderful and really push you. I took 2 of Isobel's classes and wow! she really pushes you. I felt it immediately.. in the best way possible.  The front desk and manager, Ben, were so welcoming and nice. It was refreshing to visit a studio and feel welcome from the start. I know it can be daunting to go into a studio as a new person, esp when you are a foreigner. But felt welcomed from the start. Ben answered all \"1000\" of my questions and was so kind and informative. Whether you are visiting or live near this location, I would highly recommend trying a few classes. If we stay in Hammersmith again, I will definitely be returning. *** and I definitely felt my abs shape up after only a few classes :)","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pObGFWRktUM2hUVDFRdFJYbDVlVlJoY2xNeGVWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110845700439200165224/reviews?hl=en-GB","posted_at_unix_micros":1781871162978539,"updated_at_unix_micros":1781871532348958,"language":"en","translated_lang":"","text_original":"We were visiting from the States for 2 weeks and staying in Hammersmith and I wanted to keep up with my workouts. I work at a Pilates studio in Colorado and also belong to a spin studio. I happened upon Boom Cycle and Reformcore and it was a short walk from our flat. The classes are amazing and the instructors are wonderful and really push you. I took 2 of Isobel's classes and wow! she really pushes you. I felt it immediately.. in the best way possible.  The front desk and manager, Ben, were so welcoming and nice. It was refreshing to visit a studio and feel welcome from the start. I know it can be daunting to go into a studio as a new person, esp when you are a foreigner. But felt welcomed from the start. Ben answered all \"1000\" of my questions and was so kind and informative. Whether you are visiting or live near this location, I would highly recommend trying a few classes. If we stay in Hammersmith again, I will definitely be returning. *** and I definitely felt my abs shape up after only a few classes :)","text_translated":"","reply_text_original":"Thank you so much for this wonderful review! It was such a pleasure having you train with us during your stay in London.\n\nWe're thrilled to hear you enjoyed both Boom Cycle and Reformcore, and that Isobel's classes left such an impression. We'll be sure to pass on your lovely words to Isobel and Ben—they'll be delighted to hear they helped make your experience so welcoming.\n\nWe know walking into a new studio, especially while travelling, can feel a little intimidating, so it means a lot to hear that you felt at home from the moment you arrived. Thank you for trusting us with your workouts while you were away from your home studio in Colorado.\n\nWe really appreciate your recommendation and can't wait to welcome you back the next time you're staying in Hammersmith. Safe travels, and we hope to see you again soon! ✨","reply_language":"en","reply_posted_at_unix_micros":1783595497000000,"reply_updated_at_unix_micros":1783595497000000,"published_at":"2026-06-19T12:12:42.978539Z"},{"Name":"Olivia Mellett","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKQxzWz8Wiey56DVJZWAxHM8hN8gZxGU8TI4c2l1sJ5gcwQ9g=s120-c-rp-mo-br100","Rating":5,"Description":"Can't recommend Reformcore Hammersmith enough. The atmosphere is motivating without being intimidating, what really sets this place apart is the teaching. Stacey, Zoe, Rebecca and Isobel are all fantastic — they're attentive to form, great at offering modifications for different levels, and genuinely encouraging without being over the top. You can tell they actually care about your progress. Every class I've taken has felt well-structured and challenging, no matter who's leading it.\nThe team at the front desk are equally welcoming — friendly from day one and always happy to help. If you're new to reformer Pilates or have been doing it for years, you'll be well looked after here.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pWVVdreGpaVWwwZVdoMWJVc3RkVUZWTjAwMlYzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101369275749906974579/reviews?hl=en-GB","posted_at_unix_micros":1776100018271432,"updated_at_unix_micros":1776100018271432,"language":"en","translated_lang":"","text_original":"Can't recommend Reformcore Hammersmith enough. The atmosphere is motivating without being intimidating, what really sets this place apart is the teaching. Stacey, Zoe, Rebecca and Isobel are all fantastic — they're attentive to form, great at offering modifications for different levels, and genuinely encouraging without being over the top. You can tell they actually care about your progress. Every class I've taken has felt well-structured and challenging, no matter who's leading it.\nThe team at the front desk are equally welcoming — friendly from day one and always happy to help. If you're new to reformer Pilates or have been doing it for years, you'll be well looked after here.","text_translated":"","reply_text_original":"Thank you so much for this incredibly thoughtful review Olivia! It means a lot to hear that you feel supported, challenged and welcomed at Reformcore Hammersmith — creating a motivating environment without intimidation is exactly what we strive for.\n\nWe’re so pleased to hear such lovely feedback about Stacey, Zoe, Rebecca and Isobel. Our instructors put a huge amount of care into making classes accessible, effective and encouraging for every level, so it’s wonderful to know that comes across in your experience. We’ll be sure to pass on your kind words to the whole team, including our front desk staff, who will be so happy to hear they’ve made you feel welcome from day one.\n\nThank you again for your support and for being part of the Reformcore community 💫 We can’t wait to see you in class again soon!","reply_language":"en","reply_posted_at_unix_micros":1778836394000000,"reply_updated_at_unix_micros":1778836394000000,"published_at":"2026-04-13T17:06:58.271432Z"},{"Name":"TaraIrish","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKRj31sciPt_cmxMgRxJ1locDBnIvLMoYHEl4wG3XeA0mQGbQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Burn with Dunya was amazing! It’s the first time I truly felt like we were a team of girls doing the class together. She made it so inclusive and I felt really comfortable with her style of teaching to go at the right pace and not feel judged. It was intense but achievable and I walked away feeling it too! Loved it.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT214aFNVRXpOWFZUUW1WZll6ZERTVTV3Vm5kMGRFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105357640062133063460/reviews?hl=en-GB","posted_at_unix_micros":1780603045416781,"updated_at_unix_micros":1780603045416781,"language":"en","translated_lang":"","text_original":"Burn with Dunya was amazing! It’s the first time I truly felt like we were a team of girls doing the class together. She made it so inclusive and I felt really comfortable with her style of teaching to go at the right pace and not feel judged. It was intense but achievable and I walked away feeling it too! Loved it.","text_translated":"","reply_text_original":"Thank you so much for this wonderful review! We're delighted to hear how much you enjoyed Burn with Dunya. Creating a supportive, inclusive environment where everyone feels comfortable, empowered, and part of the team is exactly what we strive for, so your feedback means a lot.\n\nWe'll be sure to pass your kind words on to Dunya—she'll be thrilled to hear that her coaching style helped you feel confident and challenged in all the right ways. We're so glad you left feeling stronger and accomplished. We can't wait to welcome you back for another class soon!","reply_language":"en","reply_posted_at_unix_micros":1781175672000000,"reply_updated_at_unix_micros":1781175672000000,"published_at":"2026-06-04T19:57:25.416781Z"},{"Name":"Shez S","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXo-fq9DjrD9zWKpqHMtC9WvQFFRiD-W3NBZAMqPGCbtKe1kvT3=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Dunya was absolutely incredible in my session, she knows exactly how to correct you and guide you through each movement. She has your body shaking but just enough to keep you returning back for more which I will be doing!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmP5pUwkhqdjoQNexHkQ48mBrGMYMI2aHOfK3p4Yrpzw57NPImvZZ8NJaJiUiIj9JtRjmQvemMcqYuypeE4PN-GmRRbQ7t96nONk2qjLPLcJEfpvgbm4wdl0UFVlhB0fx4bguHOvmwKS1gQt=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25OVWVFaFBUbEUyYmtwTU5sRm9aWEJUZDBaSE1sRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112326809340768587657/reviews?hl=en-GB","posted_at_unix_micros":1780603919477001,"updated_at_unix_micros":1780603919477001,"language":"en","translated_lang":"","text_original":"Dunya was absolutely incredible in my session, she knows exactly how to correct you and guide you through each movement. She has your body shaking but just enough to keep you returning back for more which I will be doing!","text_translated":"","reply_text_original":"Thank you so much for your lovely feedback! We're thrilled to hear that you had such a great session with Dunya. Her attention to detail and ability to guide and correct form while keeping classes challenging and enjoyable is something we truly value.\n\nWe love that you felt the burn in all the right ways—and even more that it's left you wanting to come back for more! We'll be sure to share your kind words with Dunya. We can't wait to see you back in the studio for your next session.","reply_language":"en","reply_posted_at_unix_micros":1781175733000000,"reply_updated_at_unix_micros":1781175733000000,"published_at":"2026-06-04T20:11:59.477001Z"},{"Name":"K M","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLuA7rJTYFee35v1QCpm4IUvdVUvR_tHzAi1v6lINLu67onCTw=s120-c-rp-mo-br100","Rating":3,"Description":"Arrived at 12:00 for a 12:00 class. Too late, doors closed, class cancelled. Wish I could come earlier but work for NHS - can't afford to take additional time. Thought I'd give a heads-up for others in a similar situation! :(\n\nOtherwise, really want to like the studio. It's clean and (largely) the classes are enjoyable. If you're able to take the time-off, I'm sure you'll have a better experience than I.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25VdE5tMUtYMGRVVWpKbGFtVmFRV2xDY2pJMlVsRRAB","source":"Google","rating_scale":5,"rating_float":3,"author_url":"https://www.google.com/maps/contrib/105606269332471162983/reviews?hl=en-GB","posted_at_unix_micros":1778067006462568,"updated_at_unix_micros":1778067551343135,"language":"en","translated_lang":"","text_original":"Arrived at 12:00 for a 12:00 class. Too late, doors closed, class cancelled. Wish I could come earlier but work for NHS - can't afford to take additional time. Thought I'd give a heads-up for others in a similar situation! :(\n\nOtherwise, really want to like the studio. It's clean and (largely) the classes are enjoyable. If you're able to take the time-off, I'm sure you'll have a better experience than I.","text_translated":"","reply_text_original":"Thank you for taking the time to leave such thoughtful feedback, and we’re really sorry to hear about your experience arriving for class.\n\nWe completely understand how frustrating this must have been, especially with the demands and time pressures that come with working for the NHS. Our late-entry policy is in place to minimise disruption and ensure everyone’s safety during class, but we appreciate that this can sometimes feel disappointing and inflexible.\n\nThat said, we truly value your comments and are glad to hear you’ve otherwise found the studio clean and the classes enjoyable. We’ll certainly take your feedback on board as we continue reviewing how we support clients with busy schedules.\n\nWe genuinely hope we’ll have the chance to welcome you back again soon.","reply_language":"en","reply_posted_at_unix_micros":1778835223000000,"reply_updated_at_unix_micros":1778835223000000,"published_at":"2026-05-06T11:30:06.462568Z"}]</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr"/>
+      <c r="AM111" t="inlineStr"/>
+      <c r="AN111" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>13</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/RUMBLE+-+Dalston/data=!4m7!3m6!1s0x48761d683e860233:0x981b23480ee621c7!8m2!3d51.5450297!4d-0.0741527!16s%2Fg%2F11hzy8n0b6!19sChIJMwKGPmgddkgRxyHmDkgjG5g</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>RUMBLE - Dalston</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Ground Floor, RUMBLE - Dalston, Labyrinth Tower, Dalston Square, London E8 3GP, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:20 am–8 pm"],"Monday":["6:20 am–9 pm"],"Saturday":["8 am–4 pm"],"Sunday":["8 am–4 pm"],"Thursday":["6:20 am–9 pm"],"Tuesday":["6:20 am–9 pm"],"Wednesday":["6:20 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rumble.fitness/Dalston</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>+44 20 8063 8404</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>GWWG+28 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>123</v>
+      </c>
+      <c r="O112" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":1,"3":1,"4":11,"5":110}</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>51.54503</v>
+      </c>
+      <c r="R112" t="n">
+        <v>-0.074153</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>10960392910530814407</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlaz17MBmSlZ0dAoCwP23wQJUXQzon1QkYdJj94cO-F6oOcwEDx4GK5TVQ6i3_k1xJUjBYDr0Y978i83rBlvOn_sxur4M351ZZQMVbzinnd7Ez1P8QEJlvVXifUlruYixGScmpP=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>0x48761d683e860233:0x981b23480ee621c7</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>ChIJMwKGPmgddkgRxyHmDkgjG5g</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.rumble-gym.com/booking/","source":"rumble-gym.com"}]</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>{"id":"112788667651420268842","name":"RUMBLE - Dalston (Owner)","link":"https://www.google.com/maps/contrib/112788667651420268842"}</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"Ground Floor, Labyrinth Tower, Dalston Square","city":"London","postal_code":"E8 3GP","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible seating","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>[{"Name":"Aleah Jaeger","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXZzshskLojtL7xgrpvGw2A69mtGR67hKxEuLzkmYSbavCpy5Xv=s120-c-rp-mo-br100","Rating":5,"Description":"I can't say enough about Rumble Dalston! It's been the best way to start my day for 2 years. I have the unlimited HIIT membership and I find the structure of a new circuit every ten minutes makes it so much easier and less daunting to get to the gym on days I don't feel like going. Great space, fun classes, not intimidating, and the BEST trainers, especially Lucas, Niles and Margie!! Their warmth and energy truly always makes my day, even on super early mornings.","Images":null,"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25OamNuTnZMVFU1ZEZSbFJVSlNZWE5wWjFkaWNFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115538804939727686031/reviews?hl=en-GB","posted_at_unix_micros":1765308922723863,"updated_at_unix_micros":1765308922723863,"language":"en","translated_lang":"","text_original":"I can't say enough about Rumble Dalston! It's been the best way to start my day for 2 years. I have the unlimited HIIT membership and I find the structure of a new circuit every ten minutes makes it so much easier and less daunting to get to the gym on days I don't feel like going. Great space, fun classes, not intimidating, and the BEST trainers, especially Lucas, Niles and Margie!! Their warmth and energy truly always makes my day, even on super early mornings.","text_translated":"","published_at":"2025-12-09T19:35:22.723863Z"},{"Name":"L O","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU8q2qU0hqLVT3Z11uOkLceVwvJKEqDNaK61q1xdgoyWrm13KUFOA=s120-c-rp-mo-ba12-br100","Rating":4,"Description":"Really lovely gym, even lovelier staff.\nOnly feedback I have is I wish the prices were more accessible \u0026 that they put more fans or AC on as it gets SUPER hot in there.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMxfxEHpvNkqo8H0bLGfOhz80AF3LptJkU1GlcxMonkcPb90GxmzyEWdy1A5qEhv-myqMLKVcXNmKyAnwQJ-jCrFBNRvQresb-qKKaas3lpwhYn8HUNaWnPSWVWyPW-51Sgl5XIk4o0yuCi=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNxQJo2tqfY-0OjEYiaF3ASNsT3CZ5SYLl9bjUFITaC90AxAlRnnkymoVKspf3QJhDJlIoUFXHsD0-imO__P9RgDHqZUlw3cpCHd0MlzM6UtkfVJukc2s8hz2_uNGTsVYgWHkD4lrGioAI=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMc33Vj1XMXG_1Ip4Kl9arg4RcIiZadk68J7MaFtoXhaGdidAuViuRl05x7uBGh5MVVnZA0VMreky1noxEuX_xDP4QXi6pjYlzM8SZfK_qT1yr7a8Gmk42Mrxg4ayPUANb3eM2WESwH7nM=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPRIgxlJaME53tpveuMx4dm-qYqsdisQu3tQAiQcfzPEFTcSwOqMQChngj4ibetBQpkDuhBHARi3UEC1G_F0Y2Zm_KzmEEUNdqBC27EMZ90LCm1bqkRHa2ETYwY3jH_ceoLqvU2P7cE1lE=k-no"],"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tKbFZqVTBla05OUlZjNFRVTXRUMkk1WDFCRVNHYxAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/106505596798688155151/reviews?hl=en-GB","posted_at_unix_micros":1749904213122214,"updated_at_unix_micros":1749904213122214,"language":"en","translated_lang":"","text_original":"Really lovely gym, even lovelier staff.\nOnly feedback I have is I wish the prices were more accessible \u0026 that they put more fans or AC on as it gets SUPER hot in there.","text_translated":"","published_at":"2025-06-14T12:30:13.122214Z"},{"Name":"Eddie Gould","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKcUpLOOjSNj3hc3wMYnfYCi0ExeoRjmyCVkxy14SNxEYbsfQ=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been training at Rumble Dalston for over a year and have smashed through 150+ HIIT classes, the trainer quality is consistently top-tier. But Lucas? He’s in a league of his own. Every session with him is electric. His energy, motivation and no-nonsense encouragement somehow pull another 20–30% out of me every single time. He’s the difference between a good workout and a great one. I’ll genuinely be gutted when I have to leave this place, Lucas has set the bar sky-high!","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2kxZlpsSmZOMEUxV0VKeWJXZFVRa05uUlhKQldHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102964800755305832184/reviews?hl=en-GB","posted_at_unix_micros":1749551574677931,"updated_at_unix_micros":1749551574677931,"language":"en","translated_lang":"","text_original":"I’ve been training at Rumble Dalston for over a year and have smashed through 150+ HIIT classes, the trainer quality is consistently top-tier. But Lucas? He’s in a league of his own. Every session with him is electric. His energy, motivation and no-nonsense encouragement somehow pull another 20–30% out of me every single time. He’s the difference between a good workout and a great one. I’ll genuinely be gutted when I have to leave this place, Lucas has set the bar sky-high!","text_translated":"","published_at":"2025-06-10T10:32:54.677931Z"},{"Name":"Daniel Hewitt","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjURXc98l90xGShF5otsNWZtlpUR_CK8mcDJlQp4v1nXe1ICaRP6uA=s120-c-rp-mo-br100","Rating":5,"Description":"Fantastic gym with fantastic trainers. I've been going to the HIIT classes for around a year, and seen great progress. A lot of this is down to the coaches who push you in a constructive and friendly way to do your best. Lucas and Paul in particular are amazing - you will always leave feeling like you've pushed yourself to the limit after training with them!","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xKb2MyMUNaR2xJUTJWQ1EwVnNkMlJMWDBKUWJsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115198507715566910641/reviews?hl=en-GB","posted_at_unix_micros":1750777762181965,"updated_at_unix_micros":1750777762181965,"language":"en","translated_lang":"","text_original":"Fantastic gym with fantastic trainers. I've been going to the HIIT classes for around a year, and seen great progress. A lot of this is down to the coaches who push you in a constructive and friendly way to do your best. Lucas and Paul in particular are amazing - you will always leave feeling like you've pushed yourself to the limit after training with them!","text_translated":"","published_at":"2025-06-24T15:09:22.181965Z"},{"Name":"Louisiana Wijaya","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWej4eecjYAexdH9_X-AcSe_mI-mfv_npbxdv6d15W2nTTzlnzM=s120-c-rp-mo-br100","Rating":5,"Description":"Love the gym and the space! The classes are always great, but Isa’s sessions stand out — his energy and music are always on point, and the flows and exercises are amazing! I always leave his classes feeling like I’ve done my body a world of good!","Images":null,"When":"11 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pReVExRkhZbnBXY0RSTE9WbFRUMnRwTjJ3eGEzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100268476648877634837/reviews?hl=en-GB","posted_at_unix_micros":1759253939110149,"updated_at_unix_micros":1759253939110149,"language":"en","translated_lang":"","text_original":"Love the gym and the space! The classes are always great, but Isa’s sessions stand out — his energy and music are always on point, and the flows and exercises are amazing! I always leave his classes feeling like I’ve done my body a world of good!","text_translated":"","published_at":"2025-09-30T17:38:59.110149Z"}]</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr"/>
+      <c r="AM112" t="inlineStr"/>
+      <c r="AN112" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>13</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>56e4e432-82e9-429f-a150-7979c76cbeea</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Psycle+Notting+Hill/data=!4m7!3m6!1s0x487611357c7f4471:0x21ac3cadb7851158!8m2!3d51.5154769!4d-0.1900455!16s%2Fg%2F11h1kn6kcn!19sChIJcUR_fDURdkgRWBGFt608rCE</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Psycle Notting Hill</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>37-41 Westbourne Grove, London W2 4UA, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>{"Friday":["7 am–2 pm","4:30–7 pm"],"Monday":["7 am–2 pm","5–9 pm"],"Saturday":["8:30 am–2:30 pm"],"Sunday":["8:30 am–3:30 pm"],"Thursday":["7 am–12 pm","5–8 pm"],"Tuesday":["6 am–12 pm","5–9 pm"],"Wednesday":["6 am–2 pm","5–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>https://psyclelondon.com/pages/notting-hill</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>+44 20 8106 5100</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>GR85+5X London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>121</v>
+      </c>
+      <c r="O113" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>{"1":12,"2":3,"3":3,"4":7,"5":96}</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>51.515477</v>
+      </c>
+      <c r="R113" t="n">
+        <v>-0.190045</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>2426381016051814744</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnzlUZlnKlKU2EOA3txRphVFLJ21Z3kq4FvOO9oCwzf0E0QUeZpANhospFk5ROAN0MQCaeknsAN4O6SlPAR8VUMWY-EX86ksa7z8QTdfy8pYWg7ZRTx4vJEjJs7EUKG0IwwK1A=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>0x487611357c7f4471:0x21ac3cadb7851158</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>ChIJcUR_fDURdkgRWBGFt608rCE</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>[{"link":"https://psyclelondon.com","source":"psyclelondon.com"}]</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>{"id":"105572432792511443416","name":"Psycle Notting Hill (Owner)","link":"https://www.google.com/maps/contrib/105572432792511443416"}</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"37-41 Westbourne Grove","city":"London","postal_code":"W2 4UA","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>[{"Name":"Chanita Susewi","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU8AvcSIvkWE682SqKXcr4t9N331tmGkozN5gAMss5MbFAWHrge=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"What a great team and space! I come here as often as I can. I’m 5 months pregnant and the instructors always help me modify where needed. The staff are always so kind and helpful 🥰🥰","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s0NWIyZzBhVzVzWHpORVMwaFZPWFJTYTNaMk5tYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107345288523480120423/reviews?hl=en-GB","posted_at_unix_micros":1784282037903798,"updated_at_unix_micros":1784282037903798,"language":"en","translated_lang":"","text_original":"What a great team and space! I come here as often as I can. I’m 5 months pregnant and the instructors always help me modify where needed. The staff are always so kind and helpful 🥰🥰","text_translated":"","reply_text_original":"We're so glad to hear this!! We absolutely love having you studio","reply_language":"en","reply_posted_at_unix_micros":1784357579000000,"reply_updated_at_unix_micros":1784357579000000,"published_at":"2026-07-17T09:53:57.903798Z"},{"Name":"Micah Smurthwaite","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUwQ48n2ww7yM--4ufZHhbIVNFQJ3eVHeSIkOfrMXO9-YU3iOQ=s120-c-rp-mo-br100","Rating":2,"Description":"There are no bikes at this gym, despite the name \"Psycle\". Instructor was low energy and during the class having a conversation about eating breakfast. Weird energy in the whole place. Nice showers, but a waste of £27.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xrMWVITnZabmt0UWtZMFIxZG9XVGgyVkMxak5IYxAB","source":"Google","rating_scale":5,"rating_float":2,"author_url":"https://www.google.com/maps/contrib/109241516184527278819/reviews?hl=en-GB","posted_at_unix_micros":1782730839796503,"updated_at_unix_micros":1782730839796503,"language":"en","translated_lang":"","text_original":"There are no bikes at this gym, despite the name \"Psycle\". Instructor was low energy and during the class having a conversation about eating breakfast. Weird energy in the whole place. Nice showers, but a waste of £27.","text_translated":"","reply_text_original":"Hi Micah\n\nI'm so sorry to hear that we have fallen short in your expectations this time.\nWe strive to create a fantastic experience every time. Please do reach out to us at nottinghill@psyclelondon.com to provide more feedback so that we can improve!\n\nKind regards,\nKatsie\nAssistant Manager","reply_language":"en","reply_posted_at_unix_micros":1782907216000000,"reply_updated_at_unix_micros":1782907216000000,"published_at":"2026-06-29T11:00:39.796503Z"},{"Name":"Maria Luisa Hernandez Raga","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWSiWgC-wabkKZCv5TI2GJbaNPmUoheERgst4WfpGbDLMGqVxI=s120-c-rp-mo-br100","Rating":5,"Description":"The best staff in the world. Specially Kinvara, the manager, the sunshine in the studio; every morning she is there with a huge smile and an amazing energy. Everyone is always so accommodating, and helpful. Psycle Notting Hill is the best, hands down!!!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMxkULuQs7I5DAyL_5bzStC_0zsVpz5brSD8W3FEZII5DR5T2m5-up2fUAoPWt33MAEGkHaLGVelgAMG_qcj6h6VEPk00tyUah2Z8ZqZxZiYCw5RohghffQQfRMrXjDzcow1BI=k-no"],"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnTURnaThtbjB3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118386395643412645436/reviews?hl=en-GB","posted_at_unix_micros":1740655795792387,"updated_at_unix_micros":1740655795792387,"language":"en","translated_lang":"","text_original":"The best staff in the world. Specially Kinvara, the manager, the sunshine in the studio; every morning she is there with a huge smile and an amazing energy. Everyone is always so accommodating, and helpful. Psycle Notting Hill is the best, hands down!!!","text_translated":"","reply_text_original":"Hey Maria, Thank you so much for these kind words!  We love having you in  the studio, see you very soon!","reply_language":"en","reply_posted_at_unix_micros":1743673955000000,"reply_updated_at_unix_micros":1743673955000000,"published_at":"2025-02-27T11:29:55.792387Z"},{"Name":"Arielle","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVshgzk_5Fhe7GxwRa2pbnpGTSG_cM6QXm8WauKo7GmY9AkPXoo=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This was the second Pyscle location I have tried (Oxford Circus is my go-to) and it did not disappoint! The class was led by Liam, who brought high energy, good tunes, and a great Monday morning workout. The studio was bright, the bikes felt new, and the change rooms clean and had all the usual amenities. We got the shake of the week afterwards (No Resistance) which was super tasty. We will be back at this location again!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPVPU5wttSqyaOubbwgjj2J6_zrvYUiC2rd8y2bUgy_FU0wa36d7AuycNlznlbD-I1C8UGmwSHDyTYu-qhF4vIEA2oD4DFR9JfZxU5JGgoA7-6ufgK6bgk76z3tQMxRbpto0b0f=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmN_y1K5NJSK2OHdYnYkrlzec0YEeTTKFZpW3MMij1GqgvcO0hugHYznX7RhwmHh7IqFsbapfQuOcFn3vRoc19F026XhlIp8xk3eBEuo_sEIvXf1N7-qLUFi2WrpndeJleUX0QWooQ=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNYoztLRWSi1VUCqyw3naZSN0yzIoD0oVOlI7yCp1pfcGTy3_bX1qyIvFM8dz8FlktO9VhSe3o7-c2KXBsXhyKO55ssOIDMBSRi9dwZSI0dJJPvGN35vwYUYkcww_NMLLQO4bMeXw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOzYUxTw2K6mYAFnsBH-zTjb7fE5sch9PR8SjC594z5s2mJzH_sphrpwHp5x-eg9AkLvwtymwWz6KM-3rrHJwm8wRXBwqclqRMCEjQiDPJy3JQILGZzaUs76U201vwV3IfrJcMo=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPXQbZDk6aEDWfqA_P1reIra4qly7CYJXxeIxuKAMB_MMVn531VoKkIX39ph5ikaAwAYERjFTyOEX2wC2OfBcxI2AV_GDTCekg6we2OdoYe64AnURPMgXLi5IzURQ3g502p7Ja-=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNMo9UMkENQq8AQK0JVjRylHig6zqPRzhLecCHS4pu6b6zwJA4snpfRs88j3R34_ag7A7AtlVs7nurslmiOBigM4nNQnFGmr-29j5mLHvexAo6Jy1PaNcMk5ukOEGNz5y86fJ_klg=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNEn1I8EHndmuFBc5up5ihIi87s7dPK5uglkYaoIrpge0EMClWo4E5j_R1Jh3ASKyxULFWPIx_ok3BWHQtl2b7yqiJND0RvyiHA9ehn9gm4O5bqk9wl173IIg2tzZ2yJHdDjpVk=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOeWkMZswZ0gcqc0fIMs778vodP1LWRjn9SuU8eEuzcLHdFDfLi60vJnd-hQvpT4gDYHYCGSOmbtD0LrxCspwLYOK8hYb0A3hAUOaZZjrfwJoGKCPUdn-aciHG7FZ03m3lBPeCfHQ=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOkZN4WyktUZn4-YLv819EveGn654tAthIBI4ASkj3dIEEh7IMk3EpVBGnc-OKwurUQ-cQoT1jGnTTZyHls9IsqFDDO6UBPztnh7b4UUZJ95ZlBFwYPCf0dv7YJ3_vv4DkguRbR9w=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOMvGhQsEE4V5Gif9SDc-B75LQVBkUN87SOgqTRfMsjeiXvClEXPTk3hiJLePBve-_8FoPp9chHmQuHovVZxI1_FJ9vS47p9n9akQFfSxIWw2UzUncjfcCBrnycck1BAtODa6kq=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNDZUxzWYh1Zgllrn_ZQt43A5CAVYY0LjRP82cKJNdsmNDDzqKxCU2DA_Y_P8yiAAb1x_xKudRyaoCHZeXHmlzRtIrtZEUwZFTWVenKKk0q5n6e5gDpOA_fpFUjw6zwLIRo48jnQA=k-no"],"When":"Edited 2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNaZ1l1Y3hBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102506547161608577480/reviews?hl=en-GB","posted_at_unix_micros":1694457160979050,"updated_at_unix_micros":1694545929308864,"language":"en","translated_lang":"","text_original":"This was the second Pyscle location I have tried (Oxford Circus is my go-to) and it did not disappoint! The class was led by Liam, who brought high energy, good tunes, and a great Monday morning workout. The studio was bright, the bikes felt new, and the change rooms clean and had all the usual amenities. We got the shake of the week afterwards (No Resistance) which was super tasty. We will be back at this location again!","text_translated":"","reply_text_original":"Hi Arielle, \nThank you so much for your feedabck, we are so happy you loved the studio and enjoyed your shake of the week and class, we love to hear it! We look forward to seeing you back in the studio soon!","reply_language":"en","reply_posted_at_unix_micros":1759397244000000,"reply_updated_at_unix_micros":1759397244000000,"published_at":"2023-09-11T18:32:40.97905Z"},{"Name":"Stephanie K.","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW5DcgflRVQDef-kTbpN810f_7UkeUg3st3AmQua5OlHH599p5u9w=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Love this studio and always have a great workout here! Super fun classes, delicious smoothies and everything is clean! :)","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2paa01IaE9RbGxTWlVsUVlVdG1PVkJKWVd0alNrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118003305736348217699/reviews?hl=en-GB","posted_at_unix_micros":1778589193087815,"updated_at_unix_micros":1778589193087815,"language":"en","translated_lang":"","text_original":"Love this studio and always have a great workout here! Super fun classes, delicious smoothies and everything is clean! :)","text_translated":"","published_at":"2026-05-12T12:33:13.087815Z"}]</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr"/>
+      <c r="AM113" t="inlineStr"/>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>13</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Barry%27s+St+Paul%27s/data=!4m7!3m6!1s0x48761ba68b4c222b:0x890593c07106bd35!8m2!3d51.5154017!4d-0.0955113!16s%2Fg%2F11j52tgwf2!19sChIJKyJMi6YbdkgRNb0GccCTBYk</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Barry's St Paul's</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>33 Gutter Ln, London EC2V 8AS, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:45 am–8 pm"],"Monday":["5:45 am–9 pm"],"Saturday":["8:30 am–2 pm"],"Sunday":["8:30 am–2 pm"],"Thursday":["5:45 am–9 pm"],"Tuesday":["5:45 am–9 pm"],"Wednesday":["5:45 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barrys.com/studio/london-st-pauls/</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>+44 20 8194 0110</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>GW83+5Q London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>118</v>
+      </c>
+      <c r="O114" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>{"1":9,"2":1,"3":9,"4":10,"5":89}</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>51.515402</v>
+      </c>
+      <c r="R114" t="n">
+        <v>-0.095511</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>9873460212818951477</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkDU1qgdEd-hRT-moqQIiPsXgax_P1x49CFZd6Gufk-tLq9yE2ulYivEJ5WTuZguSV7ywEYXx42Q9dTbDuJhrce3szKYUv8E1F8qP_-mms-XDh83Re78RrBqgoiVsLNqTmvgEg2=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>0x48761ba68b4c222b:0x890593c07106bd35</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>ChIJKyJMi6YbdkgRNb0GccCTBYk</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.ubereats.com/gb/store/barrys-london-st-pauls/WyFdDdiiWRC9eunlVS72aQ?diningMode=PICKUP\u0026utm_campaign=CM2508147-search-free-nonbrand-google-pas_e_all_acq_Global\u0026utm_medium=search-free-nonbrand\u0026utm_source=google-pas\u0026rwg_token=AE37R_jSdV5V6iay5i2-OhE7ggkFvJCDfNnpcdLXyb0nQpWV-Xqj2D_7srflMh9VLZf3Fg87wNy9e0xn5Vo6O8naq-MpSq2aurf3aS_PKrh1yOahkAhBpP4%3D","source":"ubereats.com"},{"link":"https://deliveroo.co.uk/menu/london/the-city/barrys-st-pauls?utm_medium=affiliate\u0026utm_source=google_maps_link\u0026fulfillment_type=DELIVERY\u0026rwg_token=AE37R_j9rwk8B5I_lvn6xqfCi89PzbysETXjWL_8DlpyfV9t2ABz24hzxWAjNK2MdBs7S37S-LsRQswL9yfLxOmY6QYMuz6GiLOxdZC-uSfuADro2jGSaTk%3D","source":"deliveroo.co.uk"}]</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>{"id":"108787211875534387908","name":"Barry's St Paul's (Owner)","link":"https://www.google.com/maps/contrib/108787211875534387908"}</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"33 Gutter Ln","city":"London","postal_code":"EC2V 8AS","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>[{"Name":"Nic Sol","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLV2f74SSXqu5txjVSy7Focv6quyNS4pOv5Kc37n0barpFn6Q=s120-c-rp-mo-br100","Rating":5,"Description":"Lovely studio and even better staff!\n\nI’m an instructor in the states and was in town for a short amount of time.\n\nMy husband and I wanted to make sure we got a workout in at Barry’s, of course, so we took an early class.\n\nReese and his counterpart (woman with a perfect sleek bun) were sooo welcoming and kind.\n\nMade it an easy process and answered all questions we had.\n\nThe merch is super cute here, too!\n\nThanks so much, Barry’s fam!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pSYVdWTmtOMnBtYm5OSVdHeE5iVFZFWnpKb2EyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105364562178925861415/reviews?hl=en-GB","posted_at_unix_micros":1781365182384002,"updated_at_unix_micros":1781365182384002,"language":"en","translated_lang":"","text_original":"Lovely studio and even better staff!\n\nI’m an instructor in the states and was in town for a short amount of time.\n\nMy husband and I wanted to make sure we got a workout in at Barry’s, of course, so we took an early class.\n\nReese and his counterpart (woman with a perfect sleek bun) were sooo welcoming and kind.\n\nMade it an easy process and answered all questions we had.\n\nThe merch is super cute here, too!\n\nThanks so much, Barry’s fam!","text_translated":"","reply_text_original":"Thanks for the feedback!","reply_language":"en","reply_posted_at_unix_micros":1782143256000000,"reply_updated_at_unix_micros":1782143256000000,"published_at":"2026-06-13T15:39:42.384002Z"},{"Name":"Negin Heidari","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXbrVyMvKRWZnOpXPQmEruH1dlfQjVaVpXkiRUHbSlFndZhE7Gz=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Loved my first experience at Barry’s! The atmosphere is really positive, the music is great, and the workout pushes you in the best way. Can’t wait to go back!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPJ7JIF7tGO6Q7rnPdf9IUlgHznOOanluNrz9dskG3oKFVQE5hInoe7_O9RMEgH5twoOkACt6ClzlHl1ZIVYFDU1bS69Po7FYGjOdHIekwYZHPdWjwXN_h0CQ1NaKr2Y0JB-Vpb1g=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOwpDUROM3WePxaiNVYJ26AYo9HgqoPsjGVfozsdtwa_HEfgZe_DRQMal7q1L9HaS4y1kgPoAJm_qOvmpHN7t2y12wyjGdSneY6-aI_tW3RGzBrb2AblpF5Ami5ZwfEZuzICfCW=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOqscZFwOA65FTMG7s65i9eWFErBmYYWZ_farMYQxZTZujfFt4G2M7z7qesz8EUjoBsoC3mHuzIQyiQIjk_a0tImV4v6KLxY1RUJH_7UOM_64IFFkZlp8qv-Qld8nZ9GAejSkiA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM_imvmySHjT5t1u_nS_vbcuE_HEhkorfkcNufD_iziYDiH4iK9AsNalWEwG5UFpGTiZtHi_t4jvl-yVBb3RhvGGHnr_vg5RSFZWjUAYPLTzD7gjt3YY8cvDDRqezptRbGdXtCpuQ=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNfcXBpZVN3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101389851088610085466/reviews?hl=en-GB","posted_at_unix_micros":1736905007345945,"updated_at_unix_micros":1736905007345945,"language":"en","translated_lang":"","text_original":"Loved my first experience at Barry’s! The atmosphere is really positive, the music is great, and the workout pushes you in the best way. Can’t wait to go back!","text_translated":"","reply_text_original":"Thanks for the feedback!","reply_language":"en","reply_posted_at_unix_micros":1737035825000000,"reply_updated_at_unix_micros":1737035825000000,"published_at":"2025-01-15T01:36:47.345945Z"},{"Name":"olivia G","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVKg3shnXJ8m2YiU08BrrE-SFbgEKrwL3zchzXosKJS6m6Wj6Q=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"We went to Barry’s London for the first time and had sooo much fun.\nThe studio and the shower was clean and the staff and Trainer where so helpful and friendly.\nWe had a great workout on Sunday early morning and our trainer gave everything even after a pride party night.\nWe got a free protein shake after our class which tasted amazing.\nWe are definitely coming back.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNU7EUr5SbmsD8jH6zFs6fUfNq4x1NdZ4Xi4Vv8dRo60LAxyMAAZ5sn2awj0S7ejvegLlC81s6_ARfoskQEY5vyk6Gqm09qjvQA8GIRDQpbkZpuZMMw0fnqcxjkBHjfoJUQQ0RUcA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNphxhIOzvQfaHHtynJgdkxqiR04XoZhXm5N2mXLpoUvYZJQ6BuuThn1vaB6XbovRY8syaWI9Z3OddciIgBoVyREEQE5TpeiI44jOA1QIH2KUTI9B9LSRQDtgJhm7bBUymsMq84=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNhKHUXi4wUqpJiCbareHdDGh4DJ69araFBTZFUBcxRcOG-_PNDNZgEJATrM4bK-_3ox64ZS0CX5o_7o0bHSgSzo4YiU8kclzF9tME4eCMwdAcE0wLa6BaZe9-f1dbY7nlorggrtw=k-no"],"When":"3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNKMV9ELUhREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115873981385140015089/reviews?hl=en-GB","posted_at_unix_micros":1688672247012334,"updated_at_unix_micros":1688672247012334,"language":"en","translated_lang":"","text_original":"We went to Barry’s London for the first time and had sooo much fun.\nThe studio and the shower was clean and the staff and Trainer where so helpful and friendly.\nWe had a great workout on Sunday early morning and our trainer gave everything even after a pride party night.\nWe got a free protein shake after our class which tasted amazing.\nWe are definitely coming back.","text_translated":"","reply_text_original":"Can't wait to see you again soon!","reply_language":"en","reply_posted_at_unix_micros":1695049799000000,"reply_updated_at_unix_micros":1695049799000000,"published_at":"2023-07-06T19:37:27.012334Z"},{"Name":"Vincent Rezzouk","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXrBSAIH26T9Zi-f55zQySKfC2FmNqd42xCF93IgUZI5jQIo1sUaA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Ouh la la! Barry’s, you’ve treated us! Massive changing rooms with big lockers. Massive red room with brand new stuff. Nice staff as usual, our favorite instructors (incl. Samuel, Chris, Jason and more!). Great location and 50 min is fine!! (I see some not very Barrys spirit comments above!)\n\nWould definitely recommend! 👍🏼","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMt2DC5FbX_Rdn-uzGNHDIbtLx2PC6b_sPHOL979qweSVFn6BcuISDFmFu8agZLa4abAkUo7Js2kE9UfqAHIWaZ09OZH5bVtgNaAg58Ru31FE3-OY4ocAZO2FpmzOW9KWw5RXZyuw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM41uzXVH0LxRbKFW-8rGgzNPN8MoHKmvwFiO9DxRbReoaLBSvCqkF5nGze4XJzTQhVwUuSKSVRQWKshNg6C8hcc7KjAwcJxHn8WOKwIdqoNGla3W--Qe_sEF9K1aOuh3BED_UkUw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNkdx8-OcWQ9a2OSWEa8RYEEJrG6Cfmc_jkZnjT93BeLZOIKOFYlMl0kQAicX0y0_lYW95Tw6gIzf2URxAxqg2u6jNezn4kefubq6HnF9eviFmN2VColbqz_1xLd6x07wmSbLQTsA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNY1zPfQpRp9Q2iTTIjr-sN_Y1qvI6Iii8ixUzE4_qQnI-fHZm91y8i1b4OOLCBJC4fOWryHjZxB35d3X_fJZibXdulC55SCoDag4cxl-2N3UtKXT0d1gP_MN5cCLyDcm2RQYg=k-no"],"When":"6 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNzZ1lPd1VREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114998778439749330012/reviews?hl=en-GB","posted_at_unix_micros":1580777410421144,"updated_at_unix_micros":1580777410421144,"language":"en","translated_lang":"","text_original":"Ouh la la! Barry’s, you’ve treated us! Massive changing rooms with big lockers. Massive red room with brand new stuff. Nice staff as usual, our favorite instructors (incl. Samuel, Chris, Jason and more!). Great location and 50 min is fine!! (I see some not very Barrys spirit comments above!)\n\nWould definitely recommend! 👍🏼","text_translated":"","published_at":"2020-02-04T00:50:10.421144Z"},{"Name":"X Y","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJVRDTD6zC8YI6e56SGO0Eo3TyYrldtcg-ks4CekZET2yTLDg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Very nice studio and the golden-themed men's changing room is great - best \"power shower\" in terms of water pressure I've had at a Barry's yet!\n\nWould go here more often but 50-minute classes on weekdays aren't my preference.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmMAeClJopS7IO53_RsbTOF2RospkTvfP8yi_g2H20J5ym2l0JBuZcV4KlLdSxriTvdkYgdOZhWxXYucODe04lne75ZkBHMy60o_hLferFNJpBLK2vR6u1BGB3SvUQLmIZ8Gzas=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNxggL7tE4IySfcuenohW-is0aCLyWqONeWPZTu3htmf9kIcFBVXAgBxNbjY-i-4czHd4JfLE6hGvaWMVQQk_jXcVAoCzG1aocHBjM-3Sfn3bDtPYYMYOq6hDBn44OY0lKg6CJUIw=k-no"],"When":"4 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUR1bWZMUE9REAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108105588886618587257/reviews?hl=en-GB","posted_at_unix_micros":1661336284744709,"updated_at_unix_micros":1661336383322565,"language":"en","translated_lang":"","text_original":"Very nice studio and the golden-themed men's changing room is great - best \"power shower\" in terms of water pressure I've had at a Barry's yet!\n\nWould go here more often but 50-minute classes on weekdays aren't my preference.","text_translated":"","published_at":"2022-08-24T10:18:04.744709Z"}]</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr"/>
+      <c r="AM114" t="inlineStr"/>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>13</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/ROWBOTS+Oxford+Circus/data=!4m7!3m6!1s0x48761b064eeb4973:0x8d627b7a14cb16aa!8m2!3d51.5166615!4d-0.1396016!16s%2Fg%2F11h4np7wt_!19sChIJc0nrTgYbdkgRqhbLFHp7Yo0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ROWBOTS Oxford Circus</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>6 Great Titchfield St., London W1W 8BB, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–8:30 pm"],"Monday":["6 am–8:30 pm"],"Saturday":["8 am–2 pm"],"Sunday":["8 am–2 pm"],"Thursday":["6 am–8:30 pm"],"Tuesday":["6 am–8:30 pm"],"Wednesday":["6 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>http://rowbots.co.uk/</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>+44 20 7436 8901</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>GV86+M5 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>113</v>
+      </c>
+      <c r="O115" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>{"1":3,"2":1,"3":0,"4":4,"5":105}</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>51.516661</v>
+      </c>
+      <c r="R115" t="n">
+        <v>-0.139602</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>10187841071330563754</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlH8BwYVSLnqli56aXDIna3bReYPQ65IzOaEFvaEBWUAWMrjnyFQ66TtsNHJ82VIcUNV8lIBWQwNOj0reMYPYPv4amEgUwa3izUy3r-bL_NlpYxRUtCXA7fgedAoHNYp-LqOQUuh2G-uWdN=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>0x48761b064eeb4973:0x8d627b7a14cb16aa</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>ChIJc0nrTgYbdkgRqhbLFHp7Yo0</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>{"id":"103757387630215504049","name":"ROWBOTS Oxford Circus (Owner)","link":"https://www.google.com/maps/contrib/103757387630215504049"}</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"6 Great Titchfield St.","city":"London","postal_code":"W1W 8BB","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>[{"Name":"Sophie Fry","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIJEWSlrLiUSgkIRVtYlEuu3T8ZvbP61k5T71XKMTbqw5qqoA=s120-c-rp-mo-br100","Rating":5,"Description":"There is no fitness community quite like Rowbots. Saturday Switch On is a favourite - coaches Nick and Myles give amazing energy and never disappoint with a tough workout, accompanied by a great playlist to go with it. Front of house staff are always helpful and give a gorgeous welcome. Go and try it !!! ⭐️ ⭐️ ⭐️ ⭐️ ⭐️","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2taQ2NXWTNRa0Z3VjJ0UmNEUnpZamR3UlZFelkyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100799232739103456845/reviews?hl=en-GB","posted_at_unix_micros":1776668527027648,"updated_at_unix_micros":1776668959699081,"language":"en","translated_lang":"","text_original":"There is no fitness community quite like Rowbots. Saturday Switch On is a favourite - coaches Nick and Myles give amazing energy and never disappoint with a tough workout, accompanied by a great playlist to go with it. Front of house staff are always helpful and give a gorgeous welcome. Go and try it !!! ⭐️ ⭐️ ⭐️ ⭐️ ⭐️","text_translated":"","published_at":"2026-04-20T07:02:07.027648Z"},{"Name":"Louize Williams","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIYY8vj3fxe5vuS2na5wqfCbyDPa-3DHEx5_SLPrRDynecz2A=s120-c-rp-mo-br100","Rating":5,"Description":"Great workout spot right in the centre of London. Amazing workout, cute studio, incredible instructor. Left feeling better than I walked in! Everything you need including sweat towels and stocked bathrooms. Be prepared to work and have fun!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tRMVdURnZVa1ZxYlhsdmJWcENhSEZZVldWSWRYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113053366132483870400/reviews?hl=en-GB","posted_at_unix_micros":1774710393630360,"updated_at_unix_micros":1774710393630360,"language":"en","translated_lang":"","text_original":"Great workout spot right in the centre of London. Amazing workout, cute studio, incredible instructor. Left feeling better than I walked in! Everything you need including sweat towels and stocked bathrooms. Be prepared to work and have fun!","text_translated":"","published_at":"2026-03-28T15:06:33.63036Z"},{"Name":"Gabriella Robinson","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUtEKWUR9U5b5VlsHunTYj_5cDMs9DwD-QaPwMGiv5Jp8H8MHpG=s120-c-rp-mo-br100","Rating":5,"Description":"Love training at ROWBOTS!! The front of house team bring the best vibes and are super friendly and happy to help with whatever you need. The classes are really well thought out and welcoming for all ages and abilities. Honestly makes working out feel way more fun 🫶","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tOVWRuSkRVQzA0Y0ZkallVZEdSR2RuVTBSM1ZXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111911844729035808564/reviews?hl=en-GB","posted_at_unix_micros":1773129827002318,"updated_at_unix_micros":1773129827002318,"language":"en","translated_lang":"","text_original":"Love training at ROWBOTS!! The front of house team bring the best vibes and are super friendly and happy to help with whatever you need. The classes are really well thought out and welcoming for all ages and abilities. Honestly makes working out feel way more fun 🫶","text_translated":"","published_at":"2026-03-10T08:03:47.002318Z"},{"Name":"Eva Spasova","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIx9I7xXrSDbbTwEo0wesr_E7e6lQv-QL3jPiW72MwUaonhLg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"The vibes here are amazing! The coaches are top-tier, the workouts are unique and challenging, and the studio has everything you need. It’s the perfect mix of rowing and full-body training. Highly recommend!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmM4AQsMSOpRsQc0bBsPxWlPF45lUvWqWOivUykiJ2hGVPF5oUOo0XqfuBu4Q-bcEfo2GAiyDktXXmcZZ5FGy37KDBsNlpu-0fk6CXYRtmqVRNKOkIu62OVhrxgqtV4SMD_iSqwGxs3sd8Y=k-no"],"When":"11 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT201VldWaDZZM2xPTTFSc1dtTk9Ra0ozUldoNFVGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110912650333048181375/reviews?hl=en-GB","posted_at_unix_micros":1758301233988343,"updated_at_unix_micros":1758301233988343,"language":"en","translated_lang":"","text_original":"The vibes here are amazing! The coaches are top-tier, the workouts are unique and challenging, and the studio has everything you need. It’s the perfect mix of rowing and full-body training. Highly recommend!","text_translated":"","published_at":"2025-09-19T17:00:33.988343Z"},{"Name":"Wesley Elizabeth","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW8WYqmopnyUlMS3ZKv_YYRMMSZDdQYe5RL0iDr-qeyfEh0JQhO=s120-c-rp-mo-ba12-br100","Rating":4,"Description":"Enjoyed it! Things to know for first-timers:\n\nYou have to create an account, but they do offer a single class purchase option.\n\nWhen you pick your spot, know that you will start either on the rower or floor, depending on which you reserved.\n\nThere was no warm up/stretch at the beginning, so you may want to do your own beforehand.\n\nThe Reset class was focused on making time/distance - everyone at their own rhythm, which felt a little chaotic but the instructor keeps you focused on your goal.\n\nI appreciated the form tips. The music was high energy electronic type. Not my preference but works for the class.\n\nThe instructor, Pele, was friendly, encouraging and paid attention to everyone.\n\nTowels provided and a water filling station. They also sell coffee and smoothies, which you can preorder when you book your class.\n\nThe changing room is small but decent. If you plan to shower and dress after, allow time as the room was crowded and you may have to wait for a shower or dryer. The products provided seemed like they were nice, but I didn’t use.\n\nI enjoyed it and it was a good workout. A little intimidating at first with some very fit people there, but the low light, loud music and friendly instructor keep you focused on yourself. When visiting London, I’ll return. Would be a regular if I lived here.\n\nThanks, Rowbots!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPbUtXC3AnQv1XfwhAHvpV7N9ILyOZthTi0oqgUiWLVI5uW3wi_zobcjAeq-9yVVDV6PJlyNQM_QH-RQZGdUKziQC8q2-fqjkXFdHoj20WMTwxvrfUpECZdnmKP8Tt1BRq5EMNr=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPRbICqTuV04R-ya6pCVnlvBSjG_IzCHR6UvVUOxaFaokU4yiy4A1ab-SG-hfLKi98JFvlr1EbDi07F6alTutauPj1f2a04YsLNroObPI3zfGSRAHYy2EHyH5oAymPvR-3gNJuU=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM6rFq6J2rdyF1fnlJjxCA9H9MkM00SjlLmqZU1MIzUxLnFc1GMrs2PfjQVQcHJwSvLRSPUJbXWJn4yAKye0flQMtn37AQHOMDg74YrLZkg1jxwKig3-oWnfGn9Kc5LeXxR2v0y=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO1p-onlsbsyOlo0p5AFQxkmAuJBImF5qUyX9roqhsufpnoBErfPRP7weIjRdAROsOML4Hc_vo3VflODR42tGZjz9kf_E2e9R0m65RSMpd3hd68xJH1KFq6bcztXVnaP2TOE4mS=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNnUdXObYh8HVCKAddhWx4WhRjB5GrdYeX1O6mo4pj_oPUpWBPXQ7lGIf-RPgNLAEmFM_YyyUTUIsucMKXpXVw4vprXoIS9Ja23bhdKtZvE2c8dE_fz9LVt_WEwmPMgbXq_T97hHw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNY_b-JsyE5eXutic5lRk19XGVcPYimIbexD7ZGUcR7WLThMHVMsmWe7kY44bpn-3hmRkW5-ezhvd6ak7bV0-kiiYzefEdAd1ZYuE86PynP6zGC5tP9OwwTyHwzoxN-BiioCg=k-no"],"When":"3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURoa0s3QUh3EAE","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/115975371409115243511/reviews?hl=en-GB","posted_at_unix_micros":1677487948241038,"updated_at_unix_micros":1677487948241038,"language":"en","translated_lang":"","text_original":"Enjoyed it! Things to know for first-timers:\n\nYou have to create an account, but they do offer a single class purchase option.\n\nWhen you pick your spot, know that you will start either on the rower or floor, depending on which you reserved.\n\nThere was no warm up/stretch at the beginning, so you may want to do your own beforehand.\n\nThe Reset class was focused on making time/distance - everyone at their own rhythm, which felt a little chaotic but the instructor keeps you focused on your goal.\n\nI appreciated the form tips. The music was high energy electronic type. Not my preference but works for the class.\n\nThe instructor, Pele, was friendly, encouraging and paid attention to everyone.\n\nTowels provided and a water filling station. They also sell coffee and smoothies, which you can preorder when you book your class.\n\nThe changing room is small but decent. If you plan to shower and dress after, allow time as the room was crowded and you may have to wait for a shower or dryer. The products provided seemed like they were nice, but I didn’t use.\n\nI enjoyed it and it was a good workout. A little intimidating at first with some very fit people there, but the low light, loud music and friendly instructor keep you focused on yourself. When visiting London, I’ll return. Would be a regular if I lived here.\n\nThanks, Rowbots!","text_translated":"","published_at":"2023-02-27T08:52:28.241038Z"}]</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr"/>
+      <c r="AM115" t="inlineStr"/>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>13</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>c2406c1e-2fba-4c5c-8ab2-a599af517682</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/BMF+Urban+Battersea+Power+Station+and+Park/data=!4m7!3m6!1s0x4876054c7238f38f:0x6f12d73910184730!8m2!3d51.4835382!4d-0.1477097!16s%2Fg%2F11r5d2khrm!19sChIJj_M4ckwFdkgRMEcYEDnXEm8</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>BMF Urban Battersea Power Station and Park</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Grosvenor Arch, Battersea Power Station, Nine Elms, London SW11 8AB, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>{"Friday":["6:30 am–1 pm"],"Monday":["6:30 am–9 pm"],"Saturday":["9–11 am"],"Sunday":["9:30–10:30 am"],"Thursday":["6:30 am–8 pm"],"Tuesday":["6:30 am–8 pm"],"Wednesday":["6:30 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>https://app.glofox.com/portal/</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>+44 7460 372419</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>FVM2+CW London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>110</v>
+      </c>
+      <c r="O116" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>{"1":2,"2":1,"3":0,"4":1,"5":106}</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>51.483538</v>
+      </c>
+      <c r="R116" t="n">
+        <v>-0.14771</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>8003696127873926960</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkDpV8wnD_n4Du1kqt_TQKNyXKuWuiLHgzNwWW-jdkLqNcJsGeu9J3F5ue5hjVgVN4mSMaQZESR-z3dhIsMSai0DxOT-oZR65ZXHB4WfZumzi-tG36qN98-cp72TQIPycK8Vbap-3Rx7PI=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>0x4876054c7238f38f:0x6f12d73910184730</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>ChIJj_M4ckwFdkgRMEcYEDnXEm8</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>{"id":"101981792755523356566","name":"BMF Urban Battersea Power Station and Park (Owner)","link":"https://www.google.com/maps/contrib/101981792755523356566"}</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>{"borough":"Nine Elms","street":"Grosvenor Arch, Battersea Power Station","city":"London","postal_code":"SW11 8AB","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>[{"Name":"Rhys Harris","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKwtxbW68i3o2nAhKtyIsxH0tbIvx6xZQ5ZbUfYRZvcQBueWg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Best outdoor fitness/training in Battersea! Have been training here since January 2026. There’s lots of variety in the sessions and session types including strength, conditioning, and outdoor military movements. Exceptional coaching, friendly banter in every session and a welcoming group of people. Recommend for anyone wanting to try something new!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPvZ-_nK2Z7kjf5t-4e5mr94se1cqcMaA3HJcSG7ghR9sHBvT8EaJgNEmWC6ybtLDuiGeAX00hnnvRIG4fU4Ycr6B3oU7jhsrI6MUbbx-6OXKXDo9WEidfwXsUUeqyri0DMZGl8VCRrbLeK=k-no"],"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25wUVluWjNWMEZwVjJsaE0ydERObXBpYW10TVgzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113560241975107433631/reviews?hl=en-GB","posted_at_unix_micros":1776269692125053,"updated_at_unix_micros":1776269692125053,"language":"en","translated_lang":"","text_original":"Best outdoor fitness/training in Battersea! Have been training here since January 2026. There’s lots of variety in the sessions and session types including strength, conditioning, and outdoor military movements. Exceptional coaching, friendly banter in every session and a welcoming group of people. Recommend for anyone wanting to try something new!","text_translated":"","published_at":"2026-04-15T16:14:52.125053Z"},{"Name":"Louisa Tee","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVCYTLDht9u0rjf3f7_PnfO-Yy-R6tmvIZN4kXlXb_Ylr-xlBlf9Q=s120-c-rp-mo-br100","Rating":5,"Description":"Excellent coaching and equipment, I felt really welcomed and comfortable in the classes. Francis is great! He really takes time to help with your form and technique. I came out of the class feeling amazing. Small groups, so it often fest like a session with a PT. I highly recommend to anyone who has never tried BMF.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21oMlJuSndNbEpRWWtwMU4yRm9iSGRaWmxSU1RFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107761288964975269777/reviews?hl=en-GB","posted_at_unix_micros":1777615049447852,"updated_at_unix_micros":1777615049447852,"language":"en","translated_lang":"","text_original":"Excellent coaching and equipment, I felt really welcomed and comfortable in the classes. Francis is great! He really takes time to help with your form and technique. I came out of the class feeling amazing. Small groups, so it often fest like a session with a PT. I highly recommend to anyone who has never tried BMF.","text_translated":"","published_at":"2026-05-01T05:57:29.447852Z"},{"Name":"Vincenzo","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUKFwjyT7NNQQItN_CSkEZitnOIKlInN8uAWcJnEzz95F6fCqCr=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been training with BMF in Battersea and, honestly, I’m absolutely chuffed with it. Thanks to them, I’m properly getting back into shape and feeling the best I have in ages. You can see real progress after just a few weeks, which keeps you going.\n\nEvery session is a proper graft — I finish completely shattered, but in a good way. It sets you up nicely for the rest of the day. It’s exactly what I needed to feel good again, both physically and mentally.\n\nThe group is brilliant and everyone’s really friendly and welcoming — no egos, just good vibes. Big shout-out to Francis, who’s inclusive, looks out for everyone, and really pushes you to give it your all.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21RelRteE5WbGRTYm5RdGNGOHpNM1UxYVRZMk1uYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109017204002757058993/reviews?hl=en-GB","posted_at_unix_micros":1776521389338421,"updated_at_unix_micros":1776521389338421,"language":"en","translated_lang":"","text_original":"I’ve been training with BMF in Battersea and, honestly, I’m absolutely chuffed with it. Thanks to them, I’m properly getting back into shape and feeling the best I have in ages. You can see real progress after just a few weeks, which keeps you going.\n\nEvery session is a proper graft — I finish completely shattered, but in a good way. It sets you up nicely for the rest of the day. It’s exactly what I needed to feel good again, both physically and mentally.\n\nThe group is brilliant and everyone’s really friendly and welcoming — no egos, just good vibes. Big shout-out to Francis, who’s inclusive, looks out for everyone, and really pushes you to give it your all.","text_translated":"","published_at":"2026-04-18T14:09:49.338421Z"},{"Name":"Alex Fairholm","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUT16EbYGAodVPpcPD3s1N0lDPgQGNwY4qBR06mLwl6m6gNbqgD1g=s120-c-rp-mo-br100","Rating":5,"Description":"If you’re looking to get fit, meet a fantastic community, and actually enjoy the grind of a tough workout, BMF Urban Battersea is the place to be.\n\nWhy It Stands Out\nThe sessions strike the perfect balance between a high-energy, team-oriented atmosphere and a serious physical challenge. The workouts consist of high-octane intervals designed to keep your heart rate spiked while building functional, total-body strength.\n\nFitness for Every Level\nOne of the best things about this location is how inclusive it feels. Whether you are a seasoned athlete or just starting your fitness journey, the structure ensures you are pushed to your own personal limit, rather than trying to keep up with someone else's pace.\n\nExpert Coaching\nFrancis is a massive highlight he is incredibly friendly, approachable, and an expert at motivation. They have a knack for knowing exactly when to push you a little harder to ensure you’re getting the most out of every minute.\n\nOverall I would highly recommend BMF Urban Battersea to anyone ready to level up their fitness in a supportive, outdoor environment!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21Oc2JEVmZUVEJNUmtsVFJXUnZiWFoyYWtGTWVuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117642340004406607600/reviews?hl=en-GB","posted_at_unix_micros":1776681703840602,"updated_at_unix_micros":1776681703840602,"language":"en","translated_lang":"","text_original":"If you’re looking to get fit, meet a fantastic community, and actually enjoy the grind of a tough workout, BMF Urban Battersea is the place to be.\n\nWhy It Stands Out\nThe sessions strike the perfect balance between a high-energy, team-oriented atmosphere and a serious physical challenge. The workouts consist of high-octane intervals designed to keep your heart rate spiked while building functional, total-body strength.\n\nFitness for Every Level\nOne of the best things about this location is how inclusive it feels. Whether you are a seasoned athlete or just starting your fitness journey, the structure ensures you are pushed to your own personal limit, rather than trying to keep up with someone else's pace.\n\nExpert Coaching\nFrancis is a massive highlight he is incredibly friendly, approachable, and an expert at motivation. They have a knack for knowing exactly when to push you a little harder to ensure you’re getting the most out of every minute.\n\nOverall I would highly recommend BMF Urban Battersea to anyone ready to level up their fitness in a supportive, outdoor environment!","text_translated":"","published_at":"2026-04-20T10:41:43.840602Z"},{"Name":"Lucy Ellwood","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKid9mohVUzRmjrOdQHbi-L7gQeEJJO9R-hoyRjRKMud6dYXg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I joined BMF as I wanted to to try outdoor fitness classes for the summer. Although I run quite often I am a beginner +++ in terms of strength / weight training. I am absolutely loving the classes, it’s a really friendly group of people and everyone is so focussed on their own workout that no one notices how uncoordinated I am. There’s a real variety of classes to choose from too. The setting is lovely and it’s great to get outdoors, especially in the morning. Francis is really friendly and patient too. I recommend this massively for anyone who intimidated by the gym and wants to get fitter / stronger with a friendly group of people. If you are doubting whether to give it a go, I would recommend doing a month trial. You won’t look back!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNsqVBbBs3syriC60FptZ_bU9j2yC27dCZ5Bw6cYIMEuS8aeizrOZmJPgQ8s1RaMoVeKrljRbPIJPF_QnPukd-M8MpfeLrYmrWHgR978cTrXvutx9mbK-ZbSSQXbAO0gIvVXES7=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmM0DQTeCB6d2lI45DFaO5L7THQEmzYTHO123124S8hGGuC2jFu8dAs3FVrcR69KOrM9U0IAyPcjND-nYxbJ0Yl_uhpIbFal5uACSSewQoF_kj13mZFFHPoKwS52snBV7PKU9BWh=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMTC6bD5cdymMIIxKZD0ziX8Jcz0fPDc23DG9rMLS0-rqIYCnOE_ymFaDWJ4Cyu8jqBLxH9ExYNBhtoLEd6apD5kHIhpEUJi2VUg0iFSg25eMPvBAV7S4jH-xtxRKhIMUCFjpse=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOTrTauaXw_zjrIdtRZvLxEmAPrJx7v9qUfLi28GRsEoUB5jtAsurYLJ2cgxIvK0ZugH0kcNmnE4v36534xSMDD_mSfdo0d6rYuJeYz4s7Mu81VA0-zJ15yy9_76nnAiS9I5fl4Mg=k-no"],"When":"3 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUR4MU9EOTNnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108622833767181050153/reviews?hl=en-GB","posted_at_unix_micros":1685713990029346,"updated_at_unix_micros":1685713990029346,"language":"en","translated_lang":"","text_original":"I joined BMF as I wanted to to try outdoor fitness classes for the summer. Although I run quite often I am a beginner +++ in terms of strength / weight training. I am absolutely loving the classes, it’s a really friendly group of people and everyone is so focussed on their own workout that no one notices how uncoordinated I am. There’s a real variety of classes to choose from too. The setting is lovely and it’s great to get outdoors, especially in the morning. Francis is really friendly and patient too. I recommend this massively for anyone who intimidated by the gym and wants to get fitter / stronger with a friendly group of people. If you are doubting whether to give it a go, I would recommend doing a month trial. You won’t look back!","text_translated":"","published_at":"2023-06-02T13:53:10.029346Z"}]</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr"/>
+      <c r="AM116" t="inlineStr"/>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>13</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>6758c484-00e9-4c1c-a81f-56f19a65c71b</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/House+of+Fitness:+Old+Street/data=!4m7!3m6!1s0x48761dffaf70b4c1:0x9a80fa0da465341d!8m2!3d51.5247665!4d-0.0881428!16s%2Fg%2F11nmmjstnq!19sChIJwbRwr_8ddkgRHTRlpA36gJo</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>House of Fitness: Old Street</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>32 Featherstone St, London EC1Y 8AE, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–8:30 pm"],"Monday":["6 am–8:30 pm"],"Saturday":["8 am–1 pm"],"Sunday":["9 am–12 pm"],"Thursday":["6 am–8:30 pm"],"Tuesday":["6 am–8:30 pm"],"Wednesday":["6 am–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>http://houseoffitness.co/</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>+44 7700 145771</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>GWF6+WP London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>108</v>
+      </c>
+      <c r="O117" t="n">
+        <v>5</v>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":0,"3":0,"4":1,"5":106}</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>51.524766</v>
+      </c>
+      <c r="R117" t="n">
+        <v>-0.088143</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>11133173215359480861</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnbNNXNrwlABrird-VH3it0QyXvGO3yA2cXWhbyvYRuhuo8FhQ3-QhTafj5KlMyIo80w7uzsFOLnwheyKTwdGLt11-dng18C75Q6dzkz2_pXyEsOIRA1bMKOG77B7OLO4MTKpvcIQ67HfKO=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>0x48761dffaf70b4c1:0x9a80fa0da465341d</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>ChIJwbRwr_8ddkgRHTRlpA36gJo</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr"/>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>[{"link":"https://www.mindbodyonline.com/explore/locations/house-of-fitness?rwg_token=AE37R_g8bZ4rFtsaIdTPcNxPRHGtgM0YD-QQjI3qbtWOy_MvzGVvKtvEVCT3VcH8XMbG-_k-yDMpun9PEieFchSY2_oLtm3eYnRpVUTeidmuZ4kmSYdLi0s%3D","source":"mindbodyonline.com"},{"link":"https://www.tagvenue.com/venues/london/35152/house-of-fitness?rwg_token=AE37R_iUND6aBCfwTnQs25YhyKrv0Vvp9y13FutZkNgTOO5htKPKyJQE3n8209mXHXyqg-gy0NK24wThzCwYph8uO2VmXnM3V8VrUgmMO4exhw2tPhDn8hI%3D","source":"tagvenue.com"}]</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>{"id":"112215763211417719592","name":"House of Fitness: Old Street (Owner)","link":"https://www.google.com/maps/contrib/112215763211417719592"}</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"32 Featherstone St","city":"London","postal_code":"EC1Y 8AE","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr"/>
+      <c r="AJ117" t="inlineStr"/>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>[{"Name":"Nausicaa Voukalis","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLYM8QEvO2NWwzU6HGskhUz80ulngLz9LcPHQnCZDtLoDndL7U=s120-c-rp-mo-br100","Rating":5,"Description":"Highly recommended!\nFantastic gym and phenomenal coaches.\n\nI have been going to House of Fitness in Old Street for around 18 months. When I started, I was completely unfit, recovering from four surgeries, and feeling quite low. I was convinced that my plan to get fit wouldn’t last.\n\nDevon and Josh listened carefully to my concerns and structured my training in a very thoughtful way, allowing me to build strength and confidence without losing motivation. They are true magicians.\n\nI can honestly say that I now feel physically strong for the first time in year . I am much happier with how I look, I absolutely love training, and I make every effort to attend the gym every day.\nAnother huge bonus is the HoF setup, which allows people to do their own personal training in small groups. This creates a real sense of camaraderie and makes training a lot more fun.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xoc1NWOXpSR1EyWW1KcllrTlJRekZ6TjFaaFFYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101398863916218227367/reviews?hl=en-GB","posted_at_unix_micros":1778227633094365,"updated_at_unix_micros":1778227633094365,"language":"en","translated_lang":"","text_original":"Highly recommended!\nFantastic gym and phenomenal coaches.\n\nI have been going to House of Fitness in Old Street for around 18 months. When I started, I was completely unfit, recovering from four surgeries, and feeling quite low. I was convinced that my plan to get fit wouldn’t last.\n\nDevon and Josh listened carefully to my concerns and structured my training in a very thoughtful way, allowing me to build strength and confidence without losing motivation. They are true magicians.\n\nI can honestly say that I now feel physically strong for the first time in year . I am much happier with how I look, I absolutely love training, and I make every effort to attend the gym every day.\nAnother huge bonus is the HoF setup, which allows people to do their own personal training in small groups. This creates a real sense of camaraderie and makes training a lot more fun.","text_translated":"","reply_text_original":"Thank you so much for your fantastic review, Nausicaa. We’re thrilled that Devon and Josh could support your recovery and help you build strength and confidence — hearing that you now feel physically strong and love training means so much to the whole team. It’s great to know the small-group setup has created the camaraderie that makes workouts enjoyable. We look forward to continuing to support your progress at House of Fitness Old Street.\n\n- House of Fitness Team","reply_language":"en","reply_posted_at_unix_micros":1778228267000000,"reply_updated_at_unix_micros":1778228267000000,"published_at":"2026-05-08T08:07:13.094365Z"},{"Name":"ian southcott","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKpsfEV3pAFTYXF9Oh5WJrbWAaXgOKu0uiBY3yZzJvPhsGPvA=s120-c-rp-mo-br100","Rating":5,"Description":"Joining House of Fitness in my 60s, with no previous strength training experience, felt quite daunting at first, especially after a major heart operation and ongoing aches in my shoulders and knees. But from day one, the team made me feel completely at ease. They listened carefully, understood my situation, and explained how everything would be adapted to suit me.\n\nThe small group setup is brilliant. It’s a real mix of abilities, with some people lifting heavy while I’m still building my confidence, but the environment is incredibly supportive and the coaching is excellent/ super knowledgeable. I always feel safe, well guided, and encouraged by both the coaches and the other members.\n\nSince starting, I’ve become stronger, more mobile, and much more confident. For me, it’s about staying healthy and active for the long term, and House of Fitness has given me exactly that. I’m really glad I started and would highly recommend it to anyone!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25WYU9EUXdkRkpwUm5FNVNXcHlVMDUxWVhGb1gzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115917630873626773900/reviews?hl=en-GB","posted_at_unix_micros":1776778582642853,"updated_at_unix_micros":1776778582642853,"language":"en","translated_lang":"","text_original":"Joining House of Fitness in my 60s, with no previous strength training experience, felt quite daunting at first, especially after a major heart operation and ongoing aches in my shoulders and knees. But from day one, the team made me feel completely at ease. They listened carefully, understood my situation, and explained how everything would be adapted to suit me.\n\nThe small group setup is brilliant. It’s a real mix of abilities, with some people lifting heavy while I’m still building my confidence, but the environment is incredibly supportive and the coaching is excellent/ super knowledgeable. I always feel safe, well guided, and encouraged by both the coaches and the other members.\n\nSince starting, I’ve become stronger, more mobile, and much more confident. For me, it’s about staying healthy and active for the long term, and House of Fitness has given me exactly that. I’m really glad I started and would highly recommend it to anyone!","text_translated":"","reply_text_original":"Ian, thank you for your wonderful review and for trusting us with your recovery and fitness journey. We're so glad our coaches could tailor sessions to your needs and that the small-group format made you feel safe and supported. It's fantastic to hear you've gained strength, mobility, and confidence — that's exactly what we aim for. We appreciate your recommendation and look forward to keeping you active and healthy for the long term.\n\n- House of Fitness Team","reply_language":"en","reply_posted_at_unix_micros":1776783561000000,"reply_updated_at_unix_micros":1776783561000000,"published_at":"2026-04-21T13:36:22.642853Z"},{"Name":"Tamira Nunez","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUwGD48kLKoJvdhWqrBuN-c4vqBdtVj-h-MpYeHwIrt5RwouPXG2g=s120-c-rp-mo-br100","Rating":5,"Description":"My experience at House of Fitness was truly amazing. From the very first day I walked in, I felt incredibly welcomed and comfortable in the environment. Dev and Josh are outstanding trainers, they take the time to listen carefully to your goals and tailor their support to help you achieve them.\nTheir encouragement, professionalism, and genuine care made every session enjoyable and motivating. I only wish I could have continued my fitness journey there, but I will always remember the warm and supportive atmosphere they created.\nI highly recommend House of Fitness to anyone looking for a positive and results-driven gym experience.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tob01VZFlXbE5YTURBeGJuTm5lREkyTkdSeloxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109082350833934972565/reviews?hl=en-GB","posted_at_unix_micros":1777366865824270,"updated_at_unix_micros":1777366865824270,"language":"en","translated_lang":"","text_original":"My experience at House of Fitness was truly amazing. From the very first day I walked in, I felt incredibly welcomed and comfortable in the environment. Dev and Josh are outstanding trainers, they take the time to listen carefully to your goals and tailor their support to help you achieve them.\nTheir encouragement, professionalism, and genuine care made every session enjoyable and motivating. I only wish I could have continued my fitness journey there, but I will always remember the warm and supportive atmosphere they created.\nI highly recommend House of Fitness to anyone looking for a positive and results-driven gym experience.","text_translated":"","reply_text_original":"Thank you so much for your kind words, Tamira. We’re thrilled you felt welcomed and supported by Dev and Josh and that their professionalism and encouragement made your sessions enjoyable. We’re sorry you weren’t able to continue your fitness journey with us and would love to welcome you back anytime. Your recommendation means a lot to our team.\n\n- House of Fitness Team","reply_language":"en","reply_posted_at_unix_micros":1777367498000000,"reply_updated_at_unix_micros":1777367498000000,"published_at":"2026-04-28T09:01:05.82427Z"},{"Name":"Alexandrina Pereira","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXgYGhpw4D38CNx_BkAPbrf0OTt7zVdsfcMsp5g0crYC3E40Ljj=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"One of the best semi-private training experiences in London! The facilities are brand new and spotless, creating a welcoming and comfortable environment. The team is super professional, friendly, and genuinely passionate about helping clients achieve their goals. Every session is tailored to each individual fitness level, needs, and objectives, making the training both effective and enjoyable. Highly recommended!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25STlRHTnRXbkpUV21aNlUxOW1NREZ0WDI0MWJtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104765674373624931523/reviews?hl=en-GB","posted_at_unix_micros":1781129364473316,"updated_at_unix_micros":1781129364473316,"language":"en","translated_lang":"","text_original":"One of the best semi-private training experiences in London! The facilities are brand new and spotless, creating a welcoming and comfortable environment. The team is super professional, friendly, and genuinely passionate about helping clients achieve their goals. Every session is tailored to each individual fitness level, needs, and objectives, making the training both effective and enjoyable. Highly recommended!","text_translated":"","reply_text_original":"Thank you so much, Alexandrina — we really appreciate your kind words and are thrilled you enjoyed our semi-private training and spotless facilities. It means a lot that you found the team professional, friendly, and genuinely supportive. We're glad the tailored sessions helped make your training effective and enjoyable. We look forward to continuing to support your fitness journey.\n\n- House of Fitness Team","reply_language":"en","reply_posted_at_unix_micros":1781129995000000,"reply_updated_at_unix_micros":1781129995000000,"published_at":"2026-06-10T22:09:24.473316Z"},{"Name":"Kathryn Larin","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVPv7R6XwqWqapmZKT7Pp1s256u663qPbIx6gUs35CFyTs4GCMoEg=s120-c-rp-mo-br100","Rating":5,"Description":"Incredible gym, incredible trainers, incredible community. House of Fitness feels like a well-kept secret in Old Street. The coaching is top-tier, my strength training has completely transformed since joining and I've hit fitness goals I didn't think were possible, largely because the trainers genuinely care about your progress and keep you motivated even on the days you don't feel like showing up. The atmosphere is welcoming and you actually look forward to going. Whether you're a beginner or experienced, the trainers meet you where you are. Best fitness decision I've made in London","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21aM2NtaEJiMVpYUlZoU1QyOVdRWFl0WW1sNlltYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104364556810167589684/reviews?hl=en-GB","posted_at_unix_micros":1780060558461576,"updated_at_unix_micros":1780060558461576,"language":"en","translated_lang":"","text_original":"Incredible gym, incredible trainers, incredible community. House of Fitness feels like a well-kept secret in Old Street. The coaching is top-tier, my strength training has completely transformed since joining and I've hit fitness goals I didn't think were possible, largely because the trainers genuinely care about your progress and keep you motivated even on the days you don't feel like showing up. The atmosphere is welcoming and you actually look forward to going. Whether you're a beginner or experienced, the trainers meet you where you are. Best fitness decision I've made in London","text_translated":"","reply_text_original":"Thank you so much, Kathryn — we’re thrilled to hear House of Fitness has been such a positive part of your journey. It’s fantastic that our coaching and community have helped you surpass goals and enjoy training again. Our trainers care deeply about every member, and your progress and motivation mean a lot to the team. We can’t wait to see what you achieve next.\n\n- House of Fitness Team","reply_language":"en","reply_posted_at_unix_micros":1780061198000000,"reply_updated_at_unix_micros":1780061198000000,"published_at":"2026-05-29T13:15:58.461576Z"}]</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr"/>
+      <c r="AM117" t="inlineStr"/>
+      <c r="AN117" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>13</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/West+4+Gym/data=!4m7!3m6!1s0x48760e6df6ded4b9:0xb95b2f430a3217ef!8m2!3d51.4892247!4d-0.2699956!16s%2Fg%2F1tfptrh2!19sChIJudTe9m0OdkgR7xcyCkMvW7k</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>West 4 Gym</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sutton Lane Gymnasium, West 4 Gym, Sutton Ln N, Chiswick, London W4 4LD, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>{"Friday":["7 am–8 pm"],"Monday":["7 am–9 pm"],"Saturday":["9 am–5 pm"],"Sunday":["9 am–5 pm"],"Thursday":["7 am–9 pm"],"Tuesday":["7 am–9 pm"],"Wednesday":["7 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.west4gym.co.uk/</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>+44 20 8747 1713</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>FPQJ+M2 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>107</v>
+      </c>
+      <c r="O118" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>{"1":3,"2":0,"3":1,"4":7,"5":96}</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>51.489225</v>
+      </c>
+      <c r="R118" t="n">
+        <v>-0.269996</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>13356321084877707247</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm_oBKQhjsmq_CvmfvqbrSt5Qw_WM-lGipmpYJY3m48O4EIkwbZVAr_uMObdZZ9aaoFWaVVVHU0cI2JdXPXOr3yBWFruYeV42ngyuIGLV90aCGragxsyX-JlBbWJ3eX8ef82F8utRSE9Oo=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>0x48760e6df6ded4b9:0xb95b2f430a3217ef</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>ChIJudTe9m0OdkgR7xcyCkMvW7k</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>{"id":"104392203655557877635","name":"West 4 Gym (Owner)","link":"https://www.google.com/maps/contrib/104392203655557877635"}</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>{"borough":"Chiswick","street":"Sutton Lane Gymnasium, Sutton Ln N","city":"London","postal_code":"W4 4LD","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>[{"Name":"TheLaughingHalibut","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVEMml7cQtWkmFvyKkzG3i6GdurJ_j5VUwkGDXHvQPVtBSqN8U=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"An excellent, friendly space with a very kind team. The temperature is always perfect, machines well maintained and the inside is completely unlike any other space. Airy, warm, you get a gentle breeze and much more natural light. A big recommendation.","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmPv6fPyNr5Xj7h2p4HJKYgE7ZdwGZqlXXuT6oK_uLjWGqxORDxBZfVeOzGcp-opNERjrgqBg-mrRCKRCoFse6pigmwXZO_pCUauWgYJjulkW_8tiweSd9-pEhem-rieDA_SffwLP20NWjY=k-no"],"When":"10 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tVMU1VOXpaak0wUVU5Zk4wSTVNR3hUT0hGa1RWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113601313494857098797/reviews?hl=en-GB","posted_at_unix_micros":1762869176892707,"updated_at_unix_micros":1762869176892707,"language":"en","translated_lang":"","text_original":"An excellent, friendly space with a very kind team. The temperature is always perfect, machines well maintained and the inside is completely unlike any other space. Airy, warm, you get a gentle breeze and much more natural light. A big recommendation.","text_translated":"","reply_text_original":"Thank you very much for your kind words.\n","reply_language":"en","reply_posted_at_unix_micros":1762877482000000,"reply_updated_at_unix_micros":1762877482000000,"published_at":"2025-11-11T13:52:56.892707Z"},{"Name":"themtvofficial Tar","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKwtu2WwZW1a0jU9aV3PCb65NC-SJTVdcFcUPQpEv08BaXwdg=s120-c-rp-mo-br100","Rating":5,"Description":"This gym is the best in the area and exudes a warm family atmosphere.  The staff are incredibly polite and the quality of the members is top-notch.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21nd2ExWk5hRGN3WTJsaVgzcFViRVUyTlZwRU4zYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106553764446568635391/reviews?hl=en-GB","posted_at_unix_micros":1782322103028349,"updated_at_unix_micros":1782322103028349,"language":"en","translated_lang":"","text_original":"This gym is the best in the area and exudes a warm family atmosphere.  The staff are incredibly polite and the quality of the members is top-notch.","text_translated":"","reply_text_original":"Thank you for taking the time to give us such a great review.\n\n","reply_language":"en","reply_posted_at_unix_micros":1782368283000000,"reply_updated_at_unix_micros":1782368283000000,"published_at":"2026-06-24T17:28:23.028349Z"},{"Name":"Mark Murphy","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ3AyWF2Ai6E9OeL4ROak7-DIcid3C4iLXKLJ5ULr5MH1fS4w=s120-c-rp-mo-br100","Rating":5,"Description":"Hands down the best gym I've ever been a member of. The equipment is excellent, the staff are really friendly and knowledgeable, and the atmosphere is motivating. Clean facilities, plenty of parking, and great classes. I've seen real progress since joining 10 years ago and the support from trainers Sam \u0026 Paul has been invaluable. Highly recommend to anyone looking to take their fitness journey to the next level. 👍🏋️‍♀️\"","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21ZeGExWjJOM0YzZHpnMVNuVnBNVFZoYlRrd2FFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116339383491910618417/reviews?hl=en-GB","posted_at_unix_micros":1757011349366164,"updated_at_unix_micros":1757011349366164,"language":"en","translated_lang":"","text_original":"Hands down the best gym I've ever been a member of. The equipment is excellent, the staff are really friendly and knowledgeable, and the atmosphere is motivating. Clean facilities, plenty of parking, and great classes. I've seen real progress since joining 10 years ago and the support from trainers Sam \u0026 Paul has been invaluable. Highly recommend to anyone looking to take their fitness journey to the next level. 👍🏋️‍♀️\"","text_translated":"","reply_text_original":"Thank you Mark. \nMuch appreciated. ","reply_language":"en","reply_posted_at_unix_micros":1757012102000000,"reply_updated_at_unix_micros":1757012102000000,"published_at":"2025-09-04T18:42:29.366164Z"},{"Name":"Adrian Ross","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLGcy1Taq7jGngl-aAUKB-wCfObEYoaqJemGmtHQ67hmVy8NA=s120-c-rp-mo-br100","Rating":5,"Description":"What a great environment to train in. A beautiful building with excellent equipment and very personal feel. Wonderful staff who are always willing to discuss your fitness goals and develop and guide you to achieve your potential. I have trained with Sam for over 30 years and his breadth of knowledge, patience and ability to motivate is amazing. Try a personal training session with him, you won’t look back. Can’t recommend highly enough 5⭐️.","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pnMGRGWkdSM2xZVURsRlNYQXpSemhJWVROWmJVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104926766204231415070/reviews?hl=en-GB","posted_at_unix_micros":1757014251618841,"updated_at_unix_micros":1757014251618841,"language":"en","translated_lang":"","text_original":"What a great environment to train in. A beautiful building with excellent equipment and very personal feel. Wonderful staff who are always willing to discuss your fitness goals and develop and guide you to achieve your potential. I have trained with Sam for over 30 years and his breadth of knowledge, patience and ability to motivate is amazing. Try a personal training session with him, you won’t look back. Can’t recommend highly enough 5⭐️.","text_translated":"","reply_text_original":"Thank you Adrian. We love the building too.","reply_language":"en","reply_posted_at_unix_micros":1759498771000000,"reply_updated_at_unix_micros":1759498771000000,"published_at":"2025-09-04T19:30:51.618841Z"},{"Name":"Martha Harrison","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ4iSXaSShnlaYKEmWJSXNmdpIVdQMdPX-QqGphAC61GtM0DQ=s120-c-rp-mo-br100","Rating":5,"Description":"The perfect local gym - friendly and helpful team, great classes, and a light and airy space to train in (especially upstairs). Plus it never feels crowded. Couldn't recommend it more!","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pWTU1tOVZhbk5YWlVKR1ZFZzBNRFJ2TFZOdmVYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108393202364928376381/reviews?hl=en-GB","posted_at_unix_micros":1755509284170557,"updated_at_unix_micros":1755509284170557,"language":"en","translated_lang":"","text_original":"The perfect local gym - friendly and helpful team, great classes, and a light and airy space to train in (especially upstairs). Plus it never feels crowded. Couldn't recommend it more!","text_translated":"","reply_text_original":"Thank you for your kind review.","reply_language":"en","reply_posted_at_unix_micros":1756928103000000,"reply_updated_at_unix_micros":1756928103000000,"published_at":"2025-08-18T09:28:04.170557Z"}]</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr"/>
+      <c r="AM118" t="inlineStr"/>
+      <c r="AN118" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>13</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/hiitbeat/data=!4m7!3m6!1s0x48761fff17bfffff:0x433b3387ee888526!8m2!3d51.6817267!4d-0.0032735!16s%2Fg%2F11fzfc0439!19sChIJ__-_F_8fdkgRJoWI7oczO0M</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>hiitbeat</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Personal trainer</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>112 Brooker Rd, Waltham Abbey EN9 1JH, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:45 am–6:45 pm"],"Monday":["5:45 am–7:45 pm"],"Saturday":["8–11:30 am"],"Sunday":["9 am–12:15 pm"],"Thursday":["5:45 am–7:45 pm"],"Tuesday":["5:45 am–6:45 pm"],"Wednesday":["5:45 am–7:45 pm"]}</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>http://www.hiitbeat.co.uk/</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>+44 7457 403875</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>MXJW+MM Waltham Abbey, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>106</v>
+      </c>
+      <c r="O119" t="n">
+        <v>5</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":0,"5":106}</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>51.681727</v>
+      </c>
+      <c r="R119" t="n">
+        <v>-0.003273</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>4844522483082626342</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnRL1WEpRK_TUGbVeBebKFNtNGJHnBet9jDeIAlnX2iPsjzFx07COwZCVtykzdpgQpKOS8WukBBbCPosFEU7AiNsUMh1fB_EKSYZryoRdPNLmgVzfOAD_BQAkWimU2n6F0F_7-H=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>0x48761fff17bfffff:0x433b3387ee888526</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>ChIJ__-_F_8fdkgRJoWI7oczO0M</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>{"id":"104971679662994886597","name":"hiitbeat (Owner)","link":"https://www.google.com/maps/contrib/104971679662994886597"}</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"112 Brooker Rd","city":"Waltham Abbey","postal_code":"EN9 1JH","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>[{"Name":"Puichi H","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVBuQ8U3_MBhcSk_7tSufITEeb4BvFwpf8jnv-g4YXbE11Qv-VpSw=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I first heard of Hiitbeat back in January 2024. I was already a member at another gym and had attended a solo Spin class with Michaela, one of the PTs at Hiitbeat. As soon as my gym membership expired, I attended a couple of classes at Hiitbeat during the summer of 2025 to get a feel for what it was like before committing.\n\nBetween May and September 2025, I went to various classes at Hiitbeat, and finally made the decision in January 2026 to get locked-in and take part in the six-week transformation programme, which was a complete game changer for me. It was easily one of the best decisions I’ve ever made! The six weeks helped me stay consistent, accountable and motivated. Attending four 6am classes every week was brutal, but it’s amazing how quickly you adapt when your mind and body are aligned and committed to improving your health and fitness goal.\n\nI’ve left it quite a while to write this review because I wanted to do this place, the structure, the variety of class types, and the quality and calibre of the coaches justice. I can honestly say there’s no other gym, no coaches, and no community that has ever pushed me as much as the people here.\n\nI go to the Hiitbeat in Waltham Abbey, and they also have a studio in Chingford. Both gyms have amazing equipments and facilities to support you with your goals.\n\nI’ve now been a solid member since January 2026, and in the last four months I’ve discovered my love for CrossFit-style training. I’ve even purchased my first Myzone belt, which shows how seriously I’m taking it.\nI’m also partnering with Mark, one of the coaches, to take part in my first ATHX competition in August alongside a lot of the Hiitbeat family. It still hasn’t quite sunk in. Mark is one of the most supportive and encouraging coaches there is. He’s a bit crazy and really puts us through our paces, but he’s a massive inspiration and just fab!\n\nI genuinely love all the coaches and all the classes. I try to attend as many as I can, but with work it’s mostly early mornings, late evenings and weekends.\n\nIf I miss a Saturday, I get real FOMO...\n\nIf you’re in two minds about training or not sure where to start, speak to Leon at Hiitbeat and go from there. I can’t imagine my life now without it. I went from training with no structure, no plan and no direction, to having all of that and actually enjoying the process and the benefits.\n\nI come out of every session feeling on top of the world, and that’s down to the community and the coaches. They are super knowledgeable, experienced, and genuinely care about what they do.\n\nDon’t delay investing in your health, because health really is wealth ✨🙏💯","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21Gd1JtVnNVbE4xTmxkNlZqUkhUaTFSTW5kYUxVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105464471131460255737/reviews?hl=en-GB","posted_at_unix_micros":1775722908746594,"updated_at_unix_micros":1775722908746594,"language":"en","translated_lang":"","text_original":"I first heard of Hiitbeat back in January 2024. I was already a member at another gym and had attended a solo Spin class with Michaela, one of the PTs at Hiitbeat. As soon as my gym membership expired, I attended a couple of classes at Hiitbeat during the summer of 2025 to get a feel for what it was like before committing.\n\nBetween May and September 2025, I went to various classes at Hiitbeat, and finally made the decision in January 2026 to get locked-in and take part in the six-week transformation programme, which was a complete game changer for me. It was easily one of the best decisions I’ve ever made! The six weeks helped me stay consistent, accountable and motivated. Attending four 6am classes every week was brutal, but it’s amazing how quickly you adapt when your mind and body are aligned and committed to improving your health and fitness goal.\n\nI’ve left it quite a while to write this review because I wanted to do this place, the structure, the variety of class types, and the quality and calibre of the coaches justice. I can honestly say there’s no other gym, no coaches, and no community that has ever pushed me as much as the people here.\n\nI go to the Hiitbeat in Waltham Abbey, and they also have a studio in Chingford. Both gyms have amazing equipments and facilities to support you with your goals.\n\nI’ve now been a solid member since January 2026, and in the last four months I’ve discovered my love for CrossFit-style training. I’ve even purchased my first Myzone belt, which shows how seriously I’m taking it.\nI’m also partnering with Mark, one of the coaches, to take part in my first ATHX competition in August alongside a lot of the Hiitbeat family. It still hasn’t quite sunk in. Mark is one of the most supportive and encouraging coaches there is. He’s a bit crazy and really puts us through our paces, but he’s a massive inspiration and just fab!\n\nI genuinely love all the coaches and all the classes. I try to attend as many as I can, but with work it’s mostly early mornings, late evenings and weekends.\n\nIf I miss a Saturday, I get real FOMO...\n\nIf you’re in two minds about training or not sure where to start, speak to Leon at Hiitbeat and go from there. I can’t imagine my life now without it. I went from training with no structure, no plan and no direction, to having all of that and actually enjoying the process and the benefits.\n\nI come out of every session feeling on top of the world, and that’s down to the community and the coaches. They are super knowledgeable, experienced, and genuinely care about what they do.\n\nDon’t delay investing in your health, because health really is wealth ✨🙏💯","text_translated":"","reply_text_original":"That is a super detailed review. We really appreciate you taking the time to write that in such detail you’ve been amazing. You bring a great energy to the studio and you and others are the reason why the atmosphere is so good because you all push each other encourage each other and I appreciate every single one of you thank you so much","reply_language":"en","reply_posted_at_unix_micros":1775753822000000,"reply_updated_at_unix_micros":1775753822000000,"published_at":"2026-04-09T08:21:48.746594Z"},{"Name":"Kerry Sweeney","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIP35MykE3xo28Ez17m9vB075FeZUm8LimefuAZ7r5ybthqSA=s120-c-rp-mo-br100","Rating":5,"Description":"I can honestly say this is one of the best gym’s i’ve been too and i’ve been to a lot and always lose interest! Not one session has been the same , the trainers are amazing. very friendly gang. I would highly recommend and 2 year in and still enjoying every session so thank you Hiitbeat x","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSRk1tdGZjMlpvVTJ4Zk4ySlFMV3Q1UVZOUFJYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100254929223452311236/reviews?hl=en-GB","posted_at_unix_micros":1765922464392164,"updated_at_unix_micros":1765922464392164,"language":"en","translated_lang":"","text_original":"I can honestly say this is one of the best gym’s i’ve been too and i’ve been to a lot and always lose interest! Not one session has been the same , the trainers are amazing. very friendly gang. I would highly recommend and 2 year in and still enjoying every session so thank you Hiitbeat x","text_translated":"","reply_text_original":"You smash it every session 100%\n\nKeep up the great work and we look forward to seeing you smash your first ATHX games","reply_language":"en","reply_posted_at_unix_micros":1765987459000000,"reply_updated_at_unix_micros":1765987459000000,"published_at":"2025-12-16T22:01:04.392164Z"},{"Name":"Mustafaa Nazir","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXsmLwFbZk4bu2SQZIAJLUAOgLfPeTKrEoGHx3ZUk5PvN15geQ8=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I recently joined trialed Hiitbeat in Woodford during the Christmas period and my experience has been fantastic! The facility is clean and well-maintained, with a great variety of equipment that caters to all fitness levels. Whether you’re into weightlifting, cardio, or group classes, there’s something for everyone.\n\nLeon is incredibly friendly and always ready to help with tips or answer questions, whether you’re looking for personal training or just casual advice.\n\nIf you’re looking for a gym that offers great value, supportive staff, and a clean, modern environment, I highly recommend Hiitbeat!","Images":null,"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURmNl96QzRRRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114094038466112961595/reviews?hl=en-GB","posted_at_unix_micros":1736506012733288,"updated_at_unix_micros":1736506012733288,"language":"en","translated_lang":"","text_original":"I recently joined trialed Hiitbeat in Woodford during the Christmas period and my experience has been fantastic! The facility is clean and well-maintained, with a great variety of equipment that caters to all fitness levels. Whether you’re into weightlifting, cardio, or group classes, there’s something for everyone.\n\nLeon is incredibly friendly and always ready to help with tips or answer questions, whether you’re looking for personal training or just casual advice.\n\nIf you’re looking for a gym that offers great value, supportive staff, and a clean, modern environment, I highly recommend Hiitbeat!","text_translated":"","reply_text_original":"Many thanks Mustafaa!  we love having you train with us and it’s nice to see someone with clear goals dedicated to achieving them!  keep up the great work.\n\nLeon ","reply_language":"en","reply_posted_at_unix_micros":1736506632000000,"reply_updated_at_unix_micros":1736506728000000,"published_at":"2025-01-10T10:46:52.733288Z"},{"Name":"Paula Keane","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWNO2qTnCUw3cq1pxRbiLgCf7_zz1nINGa6bcETARPB3qA8E3Y=s120-c-rp-mo-br100","Rating":5,"Description":"I started at Hiitbeat in March 2024 having put on a few pounds and not attending my usual gym (standard of classes deteriorated). I started with a six week exercise and diet plan. I found Leon and the whole team incredible, I was hooked from the start because every PT offers you a brilliant gym experience. Tuition, demonstration, encouragement, care and fun, not to mention the great tunes - all in one session. You are shown alternatives if the routine doesn’t fit with your strengths and abilities but never made to feel it’s a problem. Equipment is plentiful and there’s an extensive range. It’s also very clean in the gym, with cleaning the equipment part of the session.\nI find everyone welcoming and truly enjoy attending the classes and would thoroughly recommend Hiitbeat.","Images":null,"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURib1pTOUVBEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106163229204941962921/reviews?hl=en-GB","posted_at_unix_micros":1722930020978780,"updated_at_unix_micros":1722947560060337,"language":"en","translated_lang":"","text_original":"I started at Hiitbeat in March 2024 having put on a few pounds and not attending my usual gym (standard of classes deteriorated). I started with a six week exercise and diet plan. I found Leon and the whole team incredible, I was hooked from the start because every PT offers you a brilliant gym experience. Tuition, demonstration, encouragement, care and fun, not to mention the great tunes - all in one session. You are shown alternatives if the routine doesn’t fit with your strengths and abilities but never made to feel it’s a problem. Equipment is plentiful and there’s an extensive range. It’s also very clean in the gym, with cleaning the equipment part of the session.\nI find everyone welcoming and truly enjoy attending the classes and would thoroughly recommend Hiitbeat.","text_translated":"","reply_text_original":"Great to have you back after your holiday and we look forward to helping achieve your long term goals ","reply_language":"en","reply_posted_at_unix_micros":1722931690000000,"reply_updated_at_unix_micros":1722931690000000,"published_at":"2024-08-06T07:40:20.97878Z"},{"Name":"Emma Pidgeon","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLAFUG9nBABIYZ5O4bh9Q0zCvSVyswJ8C6gq3jAdwkbrRGhNQ=s120-c-rp-mo-br100","Rating":5,"Description":"I have been a member of Hiitbeat Studio for just under a year now and I can not recommend the gym enough, Leon and all the trainers are friendly, professional, knowledgeable and no matter how many people are in their classes they always make sure you are doing the training right. Having also just finished the 6 week challenge, managing to loose just under a stone and 13.4 inches, Chloe was always at the end of the phone to advise with dietary requirements and healthy options.\nLeon has built a really wonderful environment to train in, with not only great attentive coaches but also friendly and welcoming clients.","Images":null,"When":"4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNPNHBYVTRBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102927756082395505611/reviews?hl=en-GB","posted_at_unix_micros":1654452014053429,"updated_at_unix_micros":1654452014053429,"language":"en","translated_lang":"","text_original":"I have been a member of Hiitbeat Studio for just under a year now and I can not recommend the gym enough, Leon and all the trainers are friendly, professional, knowledgeable and no matter how many people are in their classes they always make sure you are doing the training right. Having also just finished the 6 week challenge, managing to loose just under a stone and 13.4 inches, Chloe was always at the end of the phone to advise with dietary requirements and healthy options.\nLeon has built a really wonderful environment to train in, with not only great attentive coaches but also friendly and welcoming clients.","text_translated":"","reply_text_original":"Amazing effort!  Keep up the great work Emma!  Hope to see how much more progress you can make in the next 6 weeks","reply_language":"en","reply_posted_at_unix_micros":1654453818000000,"reply_updated_at_unix_micros":1654453818000000,"published_at":"2022-06-05T18:00:14.053429Z"}]</t>
+        </is>
+      </c>
+      <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr"/>
+      <c r="AN119" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>13</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Milo+and+the+Bull/data=!4m7!3m6!1s0x487605ee866628cb:0xaf6f123aa23238a7!8m2!3d51.4620332!4d-0.1730564!16s%2Fg%2F11gk0wcngt!19sChIJyyhmhu4FdkgRpzgyojoSb68</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Milo and the Bull</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>62 St John's Hl, London SW11 1AD, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9 pm"],"Monday":["6 am–9 pm"],"Saturday":["8 am–12 pm"],"Sunday":["8 am–12 pm"],"Thursday":["6 am–9 pm"],"Tuesday":["6 am–9 pm"],"Wednesday":["6 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miloandthebull.com/</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>+44 20 7228 3885</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>FR6G+RQ London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>105</v>
+      </c>
+      <c r="O120" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>{"1":2,"2":2,"3":2,"4":2,"5":97}</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>51.462033</v>
+      </c>
+      <c r="R120" t="n">
+        <v>-0.173056</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>12641342722090875047</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlSdsVEYVYro1L_-20swZU13fjDR-bpY4jRgJlqI9IoDgsSYmYSlYT6NYS8t8wrnX1gmV-fkBhBSYpkNrCJUJKkgCezJD-3-V_R6oIUnFnjS8OJzJwmGxUvNHIU2AHb-JcHVU5l=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>0x487605ee866628cb:0xaf6f123aa23238a7</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>ChIJyyhmhu4FdkgRpzgyojoSb68</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>{"id":"113703236340980460954","name":"Milo and the Bull (Owner)","link":"https://www.google.com/maps/contrib/113703236340980460954"}</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"62 St John's Hl","city":"London","postal_code":"SW11 1AD","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible car park","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>[{"Name":"Imelda Simone","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKkQkMeuEVN3KeQa6ShDKxpeg0DbOZ1tJy7F6NR8CftzFmIVIM=s120-c-rp-mo-br100","Rating":4,"Description":"I’ve really enjoyed the Reformer Pilates classes at Milo and the Bull so far. The instructors I’ve tried have all been friendly, welcoming, and helpful, creating a great atmosphere regardless of your experience level.\n\nOne thing that would make the experience even better would be having a brief description of each class in advance not just a general one for all. It would be helpful to know whether the session is more athletic and strength-focused or more centred around stretching and mobility, as that would make it easier to choose the right class depending on how you’re feeling that day.\n\nAs someone who’s relatively new to Reformer Pilates, I also found that there are a few blind spots in the studio because it’s not fully surrounded by mirrors. Occasionally it can be difficult to see the instructor or follow along with certain movements, not a major issue, but it’s something beginners might notice.\n\nOverall, it’s been a really positive experience, and I’d definitely recommend it.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pWWVZHSTFSa290V0VsUGNtUTNRMjE1WW1WeldWRRAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/116861505882684084429/reviews?hl=en-GB","posted_at_unix_micros":1784405436920643,"updated_at_unix_micros":1784405436920643,"language":"en","translated_lang":"","text_original":"I’ve really enjoyed the Reformer Pilates classes at Milo and the Bull so far. The instructors I’ve tried have all been friendly, welcoming, and helpful, creating a great atmosphere regardless of your experience level.\n\nOne thing that would make the experience even better would be having a brief description of each class in advance not just a general one for all. It would be helpful to know whether the session is more athletic and strength-focused or more centred around stretching and mobility, as that would make it easier to choose the right class depending on how you’re feeling that day.\n\nAs someone who’s relatively new to Reformer Pilates, I also found that there are a few blind spots in the studio because it’s not fully surrounded by mirrors. Occasionally it can be difficult to see the instructor or follow along with certain movements, not a major issue, but it’s something beginners might notice.\n\nOverall, it’s been a really positive experience, and I’d definitely recommend it.","text_translated":"","published_at":"2026-07-18T20:10:36.920643Z"},{"Name":"Rachel Jane Fisher","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUvk103Mb7GnNwZWfXAMMd1clRGXimvqQgNGXVnk7PN1jiGjpfd=s120-c-rp-mo-br100","Rating":5,"Description":"Trying a new gym for the first time is always a bit daunting. Sam made me feel so welcome in my first Hyrox class and really listened to my history of injuries and encouraged me throughout the session and offered to tailor to suit\nmy needs. Such a friendly warm atmosphere and lovely clean facilities. Everyone in the class was so friendly and welcoming, cheering me on and pushed me to keep going. The best gym I’ve found in London by a country mile! If you are thinking of trying it but feeling apprehensive do it!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21kaWJETnNlV1I0Ykd0YWFrZGFUMDR3Y1ZkUVEzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110209728508811945073/reviews?hl=en-GB","posted_at_unix_micros":1781813320325398,"updated_at_unix_micros":1781813320325398,"language":"en","translated_lang":"","text_original":"Trying a new gym for the first time is always a bit daunting. Sam made me feel so welcome in my first Hyrox class and really listened to my history of injuries and encouraged me throughout the session and offered to tailor to suit\nmy needs. Such a friendly warm atmosphere and lovely clean facilities. Everyone in the class was so friendly and welcoming, cheering me on and pushed me to keep going. The best gym I’ve found in London by a country mile! If you are thinking of trying it but feeling apprehensive do it!","text_translated":"","published_at":"2026-06-18T20:08:40.325398Z"},{"Name":"Nathan Cullen","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJIH_55cwLUwurRcD5BAQDWo6SKWPZznGe9VXoT6Rq6b0A2Aw=s120-c-rp-mo-br100","Rating":5,"Description":"I signed up to the unlimited 2-week trial at Milo and the Bull and I’m loving each class so far. The trainers have been really friendly and clear when explaining the workouts, which makes a big difference. Can’t wait to go back!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2sxZmRUaHRNek5VYkRjeU9YbEJZbnBrY25CMFdGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113717442725944603421/reviews?hl=en-GB","posted_at_unix_micros":1775498203408933,"updated_at_unix_micros":1775498203408933,"language":"en","translated_lang":"","text_original":"I signed up to the unlimited 2-week trial at Milo and the Bull and I’m loving each class so far. The trainers have been really friendly and clear when explaining the workouts, which makes a big difference. Can’t wait to go back!","text_translated":"","published_at":"2026-04-06T17:56:43.408933Z"},{"Name":"Isabella Copland","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIRX7iLS3gr_hxi7nd1cUb1h_UVfWhIFI1DNUaegXzaON171A=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"After moving to the neighbourhood we’ve been trying loads of different classes/gyms/studios and we can categorically say this has been our favourite! Never thought I’d look forward to a 9am class on a bank holiday Monday, but between the quality of the trainers, the studio and the class - it’s the best studio we’ve found by a mile!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xWa1VGUlVaMWxYVlRjMFNHaFdhSFJ0WkVoaVkwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115776970588901040390/reviews?hl=en-GB","posted_at_unix_micros":1775498732831185,"updated_at_unix_micros":1775498732831185,"language":"en","translated_lang":"","text_original":"After moving to the neighbourhood we’ve been trying loads of different classes/gyms/studios and we can categorically say this has been our favourite! Never thought I’d look forward to a 9am class on a bank holiday Monday, but between the quality of the trainers, the studio and the class - it’s the best studio we’ve found by a mile!","text_translated":"","published_at":"2026-04-06T18:05:32.831185Z"},{"Name":"olivia ashton","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLaRknkigXBtPPDZMLOhJUE8KJyXCK1voD_cDkEbvAKzCbPOg=s120-c-rp-mo-br100","Rating":5,"Description":"I was new to reformer before trying out these classes, since i have purchased a monthly membership really good for all levels. No class is the same good variety","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25wZlMyOU1WMmhmTTNkNFNrcHlNRmRYVkhWalNVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113372096658034882889/reviews?hl=en-GB","posted_at_unix_micros":1786014386625802,"updated_at_unix_micros":1786014386625802,"language":"en","translated_lang":"","text_original":"I was new to reformer before trying out these classes, since i have purchased a monthly membership really good for all levels. No class is the same good variety","text_translated":"","published_at":"2026-08-06T11:06:26.625802Z"}]</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr"/>
+      <c r="AN120" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>13</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Boutique Fitness Studio</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>London, England, UK</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>86f401d5-2c71-4805-89a0-8c9c2ac37675</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/UN1T+Southwark/data=!4m7!3m6!1s0x4876035867ca1897:0x6705bf4c7720046d!8m2!3d51.4970556!4d-0.0995981!16s%2Fg%2F11dxs_x6wg!19sChIJlxjKZ1gDdkgRbQQgd0y_BWc</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>UN1T Southwark</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>251 Southwark Bridge Rd, London SE1 6FJ, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–7 pm"],"Monday":["6 am–8 pm"],"Saturday":["9–11 am"],"Sunday":["9 am–12 pm"],"Thursday":["6 am–8 pm"],"Tuesday":["6 am–8 pm"],"Wednesday":["6 am–8 pm"]}</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>https://un1t.com/london-southwark/</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>+44 7782 130093</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>FWW2+R5 London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>103</v>
+      </c>
+      <c r="O121" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":0,"3":1,"4":5,"5":96}</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>51.497056</v>
+      </c>
+      <c r="R121" t="n">
+        <v>-0.09959800000000001</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>7423549895927137389</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkhtkSjsqrPXraqXswMNB1XmPTO83okqDEUaBxCXPrNrLxLbFC1nGo27XBUDGAaQnxKpMZvH00SBQ6G24WI8_hxDSUPopd5OngSwN5lfCUJLZbCfuUWTXmFNr6dz3pPmriVD3swbO-UWheZ=w408-h509-k-no</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Europe/London</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>0x4876035867ca1897:0x6705bf4c7720046d</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>ChIJlxjKZ1gDdkgRbQQgd0y_BWc</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="inlineStr"/>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>{"id":"110076802388226101114","name":"UN1T Southwark (Owner)","link":"https://www.google.com/maps/contrib/110076802388226101114"}</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>{"borough":"","street":"251 Southwark Bridge Rd","city":"London","postal_code":"SE1 6FJ","state":"","country":"GB"}</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr"/>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>[{"Name":"Ev","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXw59VqvRWkRmODT8d4qgweMDVHDI4wgLDAVGfMv4FSp552VUo=s120-c-rp-mo-br100","Rating":5,"Description":"The team at UN1T have honestly provided the best experience I’ve had at any gym I’ve been to. I used to cycle past it every morning and then decided to give it a try, it’s now the highlight of my mornings. The atmosphere is top tier and the variations in exercises whilst still maintaining high intensity so you’re building a sweat is wicked. Highly recommend.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25SeFdUUkdkWHA0UTBWbFdVRjRMWHBVWDFsVFlYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111986077197679816826/reviews?hl=en-GB","posted_at_unix_micros":1779267350257571,"updated_at_unix_micros":1779267350257571,"language":"en","translated_lang":"","text_original":"The team at UN1T have honestly provided the best experience I’ve had at any gym I’ve been to. I used to cycle past it every morning and then decided to give it a try, it’s now the highlight of my mornings. The atmosphere is top tier and the variations in exercises whilst still maintaining high intensity so you’re building a sweat is wicked. Highly recommend.","text_translated":"","reply_text_original":"And having you as part of our fitness family is one of OUR highlights.  It is an honour to guide the positive progression of your fitness journey ","reply_language":"en","reply_posted_at_unix_micros":1779267752000000,"reply_updated_at_unix_micros":1779267752000000,"published_at":"2026-05-20T08:55:50.257571Z"},{"Name":"Gillian Goh","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX9yFMQlkheJCqnYU9RNiVsMeD40sg15LlDLGZtUK_CM8kmdYdF=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Did the 12:30pm strength class. Very clean \u0026 friendly training environment, well organized set up with clear instructions \u0026 demonstrations by coaches George \u0026 Scott. Great effective 45 mins workout, you can push as hard you want with solid guidance by the coaches.\n\nThanks Sophie for the warm welcome too!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOLQ7icx113oT7vQRoWLkEqQTMw5ZbBTJ61izA6nVSYLfcuVFCLKLsXL-TINcJOfKeNKueeEKZcqRpcZnoeh8XpmavroNvlnQe4CSTl0ltpi-2ZhDCMHxcQa4ElqD7smQOq1Cmr4g=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMJ2IDpkQqHwwj8yZE1yAUqzJirgrKNMWJJ3QphAwewMsG-FxH8ry43-f2FnFx7RdEWCkGi9M8oBJuaoVPg544KWFD3KFco6vAHMRx7S6CaON8fc5ZUnQk2C4pa-n6a8WZllOk=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmPATlKb1lVTeDsiFh1XCHAR6BS6WLs5-f2I4mkvvRbD26vHsw1bVmilPV1I0OkNO_ewhrOVZAkPbJXOyRVUIN_2Pki_whGC6JIfgZpOOUu7SsdnwSXZAVQALd09iIDulr1VmqRTUw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMvBghR8FYW6nWBApnAKHdfp_b8-gjdtsIorV8Mfer1ngDtryC8ZMV_klwuuY2H0pVdBGuXPpq_4olB9XeE9His_i8s4RXF-f0t03_P0MCLmIIby7PY578BXD1NHs5Os9oKthxf=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNWkw-E0pOxa99VPObgPc-KcWXwIdIknkioYWUqJ5pengrIkseRdOrFf8viqQR6KsuRFkOCHsrVsHapbJcbapjjtSzxum8ATYRH_ptCAJHhE-j649iXd-TgAW5hkaweXwgP5SMP6A=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmMiZjG0LEvqrl4bp4whO0jPBUVcSvIPo0RzH_dqFSOxSfeNiWqaL87XkjreuiR47qWb5fy-4-bECI1MDdFy0U21RSMmI7bxNbUFEHHzygk0tuN3LcaXzSIGjyv1wL5z9l4NNGI=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnTUNRdTVhQllBEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113779323974772989843/reviews?hl=en-GB","posted_at_unix_micros":1741344316867627,"updated_at_unix_micros":1741344316867627,"language":"en","translated_lang":"","text_original":"Did the 12:30pm strength class. Very clean \u0026 friendly training environment, well organized set up with clear instructions \u0026 demonstrations by coaches George \u0026 Scott. Great effective 45 mins workout, you can push as hard you want with solid guidance by the coaches.\n\nThanks Sophie for the warm welcome too!","text_translated":"","published_at":"2025-03-07T10:45:16.867627Z"},{"Name":"Arielle","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVshgzk_5Fhe7GxwRa2pbnpGTSG_cM6QXm8WauKo7GmY9AkPXoo=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great gym with great workouts! We came for the FURY workout on the weekend and loved the partner on/off flow. The energy was 10/10, supportive coaches, friendly reception staff, good music, and everyone working hard in class. The workout was easy to follow and clearly instructed. Good facilities for freshening up afterwards. Looking forward to coming back soon!","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmOqIAGE78BiKxybZbljP-AsxQx1IEEPXhpiLjKkRlqPh9iCYLRF_I6KqbFa7FOBTagFVDlw5dT1aS7JFUnp3au_JqTbR2DWe8wLmcYZe2d2r_EEqHZvprT3Jkb07_9T8QVhhLp2Dw=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmO8hIPuo28Sar0mSk7epFkTQVLgAyr4p78pjVwXRKojjh_aYGzQtpjlQhzNOVc2uBq6OQh-2uDEaFtlpyB3T9i9jd-nQ_A7xWA7xHCxOR-0GZM2Tgt_zi0Jsioz7YBP8dI7jgnK=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmOvXHAZ1FCjKGx4vi3nerBRJ35OkBqhU7HNFm2csJA_N66GZagat6n2LgPELvYeBC05bkIIsBqrpQdOCT4GBQgJogpSWKTgMk3KzSqKr3atx8M4CeqVWFHSEd93BtIVw_TbMei8kQ=k-no"],"When":"3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNaOXFlTEx3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102506547161608577480/reviews?hl=en-GB","posted_at_unix_micros":1694347283810960,"updated_at_unix_micros":1694347283810960,"language":"en","translated_lang":"","text_original":"Great gym with great workouts! We came for the FURY workout on the weekend and loved the partner on/off flow. The energy was 10/10, supportive coaches, friendly reception staff, good music, and everyone working hard in class. The workout was easy to follow and clearly instructed. Good facilities for freshening up afterwards. Looking forward to coming back soon!","text_translated":"","published_at":"2023-09-10T12:01:23.81096Z"},{"Name":"Maria Alejandra Zapata","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW8XuZC0aa-qv8uDsTqWG04jQjjFu15DeRhrlK5F50-G2DULF0RmQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Incredible experience at UN1T Southwark! From the moment you walk in, the staff makes you feel welcome, creating an atmosphere that feels like family. The gym itself is fantastic, and having two instructors guiding you throughout the entire session makes a huge difference. The workouts exceeded my expectations—challenging, focused, and incredibly well-structured. Booking classes is super easy, which makes the whole process seamless. I’m excited to continue training here! This type of personalized and structured training is truly a game-changer","Images":["https://lh3.googleusercontent.com/grass-cs/ACvplmNtrdg03ceCwrt8ha5iZrUPf93M0Uf_a8hW6hRnljnidjAVFlolaC2bA9fn2osdxyegJidYDSIAZ4Xw8qwOX9pK8ksRh5bxWW9mdQrnpST1CwvYony8ccDC3-6pTSHJkdH5fpMpsA=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNM00sB7qJat5KItGszMR4gpTg42kl1H4dqVaYo_MorS4ed0VGMTlmVYdMQgvCtKd8QlxvvkjgfLGvF7HSh0-JQVSXwg9Y7pi0SkF_LZhczdhAhf2oBFjCP8vSHvx3JAOVaQ7JZ=k-no","https://lh3.googleusercontent.com/grass-cs/ACvplmNWdBfZTT1IXXVbfR_NSjkhXQW-enTHvF8ziaKvkvlgbTK7gyaEqCjWCuMmaTw2q-ui4MPvUqLPc6eD0OdgNT66b0A2xc7KpoX3bcqfgkS8aK6Y5Pl4Cj3_ZynUj1j8_f918JBI1w=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnTUNRbXFxWkpREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112632650380791797717/reviews?hl=en-GB","posted_at_unix_micros":1741024271706679,"updated_at_unix_micros":1741024271706679,"language":"en","translated_lang":"","text_original":"Incredible experience at UN1T Southwark! From the moment you walk in, the staff makes you feel welcome, creating an atmosphere that feels like family. The gym itself is fantastic, and having two instructors guiding you throughout the entire session makes a huge difference. The workouts exceeded my expectations—challenging, focused, and incredibly well-structured. Booking classes is super easy, which makes the whole process seamless. I’m excited to continue training here! This type of personalized and structured training is truly a game-changer","text_translated":"","reply_text_original":"Thanks for the 5 star review Maria! Glad you are loving the sessions and feeling the benefit! We'll see you soon in the studio!","reply_language":"en","reply_posted_at_unix_micros":1743327444000000,"reply_updated_at_unix_micros":1743327444000000,"published_at":"2025-03-03T17:51:11.706679Z"},{"Name":"Vikas Sharma","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLJYkx6iZnxNCNRtcCk8xqWSEI8hj9lg51-HgLddpC1znNp7Q=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My favourite studio in london. I have been going few times a week since more than a year. They got the best strength and conditioning classes. The trainers are knowledgeable and supportive. Un1t Southwark has helped me improve my fitness level.\nThe classes here are top notch esp the cardio ones. Strength sessions are equally good. I like if they had classes after 11 am on Saturday","Images":null,"When":"Edited a month ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURWclpLTDhRRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115034343648633736997/reviews?hl=en-GB","posted_at_unix_micros":1702595569949034,"updated_at_unix_micros":1784897389292282,"language":"en","translated_lang":"","text_original":"My favourite studio in london. I have been going few times a week since more than a year. They got the best strength and conditioning classes. The trainers are knowledgeable and supportive. Un1t Southwark has helped me improve my fitness level.\nThe classes here are top notch esp the cardio ones. Strength sessions are equally good. I like if they had classes after 11 am on Saturday","text_translated":"","reply_text_original":"Thanks for the 5 star review Vikas! Glad you are loving the classes! We'll see you soon in the studio! \nSophie - General Manager - UN1T Southwark","reply_language":"en","reply_posted_at_unix_micros":1716218977000000,"reply_updated_at_unix_micros":1716218977000000,"published_at":"2023-12-14T23:12:49.949034Z"}]</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr"/>
+      <c r="AM121" t="inlineStr"/>
+      <c r="AN121" t="inlineStr">
+        <is>
+          <t>2026-09-12T08:36:59.746739+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN61"/>
+  <autoFilter ref="A1:AN121"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
@@ -10250,6 +19522,126 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId239"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
